--- a/excel/item.xlsx
+++ b/excel/item.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$608</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$607</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -133,7 +133,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="23">
   <si>
     <t>编号</t>
   </si>
@@ -181,6 +181,12 @@
   </si>
   <si>
     <t>int</t>
+  </si>
+  <si>
+    <t>银币</t>
+  </si>
+  <si>
+    <t>金币</t>
   </si>
   <si>
     <t>变卖物1</t>
@@ -367,17 +373,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1190,7 +1196,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R608"/>
+  <dimension ref="A1:R607"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="7" width="25.125" style="2" customWidth="1"/>
@@ -1280,15 +1286,9 @@
       <c r="D4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="3">
-        <v>0</v>
-      </c>
-      <c r="F4" s="3">
-        <v>200</v>
-      </c>
-      <c r="G4" s="3">
-        <v>1</v>
-      </c>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
@@ -1314,15 +1314,9 @@
       <c r="D5" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="3">
-        <v>1</v>
-      </c>
-      <c r="F5" s="3">
-        <v>300</v>
-      </c>
-      <c r="G5" s="3">
-        <v>1</v>
-      </c>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
@@ -1349,7 +1343,7 @@
         <v>18</v>
       </c>
       <c r="E6" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F6" s="3">
         <v>400</v>
@@ -1383,7 +1377,7 @@
         <v>19</v>
       </c>
       <c r="E7" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F7" s="3">
         <v>500</v>
@@ -1417,7 +1411,7 @@
         <v>20</v>
       </c>
       <c r="E8" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F8" s="3">
         <v>501</v>
@@ -1438,13 +1432,27 @@
       <c r="R8" s="3"/>
     </row>
     <row r="9" s="1" customFormat="1" spans="1:18">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
+      <c r="A9" s="3">
+        <v>5</v>
+      </c>
+      <c r="B9" s="3">
+        <v>200006</v>
+      </c>
+      <c r="C9" s="3">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9" s="3">
+        <v>3</v>
+      </c>
+      <c r="F9" s="3">
+        <v>502</v>
+      </c>
+      <c r="G9" s="3">
+        <v>7</v>
+      </c>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
@@ -1458,13 +1466,27 @@
       <c r="R9" s="3"/>
     </row>
     <row r="10" s="1" customFormat="1" spans="1:18">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
+      <c r="A10" s="3">
+        <v>6</v>
+      </c>
+      <c r="B10" s="3">
+        <v>200007</v>
+      </c>
+      <c r="C10" s="3">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" s="3">
+        <v>4</v>
+      </c>
+      <c r="F10" s="3">
+        <v>503</v>
+      </c>
+      <c r="G10" s="3">
+        <v>8</v>
+      </c>
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
@@ -1557,25 +1579,14 @@
       <c r="Q14" s="3"/>
       <c r="R14" s="3"/>
     </row>
-    <row r="15" s="1" customFormat="1" spans="1:18">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3"/>
-      <c r="K15" s="3"/>
-      <c r="L15" s="3"/>
-      <c r="M15" s="3"/>
-      <c r="N15" s="3"/>
-      <c r="O15" s="3"/>
-      <c r="P15" s="3"/>
-      <c r="Q15" s="3"/>
-      <c r="R15" s="3"/>
+    <row r="15" spans="1:18">
+      <c r="A15" s="5"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
     </row>
     <row r="16" spans="1:18">
       <c r="A16" s="5"/>
@@ -5458,12 +5469,6 @@
     </row>
     <row r="447" spans="1:7">
       <c r="A447" s="5"/>
-      <c r="B447" s="5"/>
-      <c r="C447" s="5"/>
-      <c r="D447" s="5"/>
-      <c r="E447" s="5"/>
-      <c r="F447" s="5"/>
-      <c r="G447" s="5"/>
     </row>
     <row r="448" spans="1:7">
       <c r="A448" s="5"/>
@@ -5945,11 +5950,8 @@
     <row r="607" spans="1:1">
       <c r="A607" s="5"/>
     </row>
-    <row r="608" spans="1:1">
-      <c r="A608" s="5"/>
-    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:H608" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:H607" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/excel/item.xlsx
+++ b/excel/item.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$607</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$615</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -133,7 +133,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="33">
   <si>
     <t>编号</t>
   </si>
@@ -189,19 +189,49 @@
     <t>金币</t>
   </si>
   <si>
-    <t>变卖物1</t>
+    <t>绿色变卖物1</t>
   </si>
   <si>
-    <t>变卖物2</t>
+    <t>绿色变卖物2</t>
   </si>
   <si>
-    <t>变卖物3</t>
+    <t>绿色变卖物3</t>
   </si>
   <si>
-    <t>变卖物4</t>
+    <t>蓝色变卖物1</t>
   </si>
   <si>
-    <t>变卖物5</t>
+    <t>蓝色变卖物2</t>
+  </si>
+  <si>
+    <t>蓝色变卖物3</t>
+  </si>
+  <si>
+    <t>紫色变卖物1</t>
+  </si>
+  <si>
+    <t>紫色变卖物2</t>
+  </si>
+  <si>
+    <t>紫色变卖物3</t>
+  </si>
+  <si>
+    <t>金色变卖物1</t>
+  </si>
+  <si>
+    <t>金色变卖物2</t>
+  </si>
+  <si>
+    <t>金色变卖物3</t>
+  </si>
+  <si>
+    <t>红色变卖物1</t>
+  </si>
+  <si>
+    <t>红色变卖物2</t>
+  </si>
+  <si>
+    <t>红色变卖物3</t>
   </si>
 </sst>
 </file>
@@ -1196,7 +1226,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R607"/>
+  <dimension ref="A1:R615"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="7" width="25.125" style="2" customWidth="1"/>
@@ -1377,13 +1407,13 @@
         <v>19</v>
       </c>
       <c r="E7" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" s="3">
-        <v>500</v>
+        <v>401</v>
       </c>
       <c r="G7" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
@@ -1411,13 +1441,13 @@
         <v>20</v>
       </c>
       <c r="E8" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F8" s="3">
-        <v>501</v>
+        <v>402</v>
       </c>
       <c r="G8" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
@@ -1445,13 +1475,13 @@
         <v>21</v>
       </c>
       <c r="E9" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F9" s="3">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="G9" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
@@ -1479,13 +1509,13 @@
         <v>22</v>
       </c>
       <c r="E10" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F10" s="3">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="G10" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
@@ -1500,13 +1530,27 @@
       <c r="R10" s="3"/>
     </row>
     <row r="11" s="1" customFormat="1" spans="1:18">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
+      <c r="A11" s="3">
+        <v>7</v>
+      </c>
+      <c r="B11" s="3">
+        <v>200008</v>
+      </c>
+      <c r="C11" s="3">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E11" s="3">
+        <v>1</v>
+      </c>
+      <c r="F11" s="3">
+        <v>502</v>
+      </c>
+      <c r="G11" s="3">
+        <v>7</v>
+      </c>
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
@@ -1520,13 +1564,27 @@
       <c r="R11" s="3"/>
     </row>
     <row r="12" s="1" customFormat="1" spans="1:18">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
+      <c r="A12" s="3">
+        <v>8</v>
+      </c>
+      <c r="B12" s="3">
+        <v>200009</v>
+      </c>
+      <c r="C12" s="3">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E12" s="3">
+        <v>2</v>
+      </c>
+      <c r="F12" s="3">
+        <v>501</v>
+      </c>
+      <c r="G12" s="3">
+        <v>6</v>
+      </c>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
@@ -1540,13 +1598,27 @@
       <c r="R12" s="3"/>
     </row>
     <row r="13" s="1" customFormat="1" spans="1:18">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
+      <c r="A13" s="3">
+        <v>9</v>
+      </c>
+      <c r="B13" s="3">
+        <v>200010</v>
+      </c>
+      <c r="C13" s="3">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E13" s="3">
+        <v>2</v>
+      </c>
+      <c r="F13" s="3">
+        <v>502</v>
+      </c>
+      <c r="G13" s="3">
+        <v>7</v>
+      </c>
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
       <c r="J13" s="3"/>
@@ -1560,13 +1632,27 @@
       <c r="R13" s="3"/>
     </row>
     <row r="14" s="1" customFormat="1" spans="1:18">
-      <c r="A14" s="3"/>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
+      <c r="A14" s="3">
+        <v>10</v>
+      </c>
+      <c r="B14" s="3">
+        <v>200011</v>
+      </c>
+      <c r="C14" s="3">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E14" s="3">
+        <v>2</v>
+      </c>
+      <c r="F14" s="3">
+        <v>503</v>
+      </c>
+      <c r="G14" s="3">
+        <v>8</v>
+      </c>
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
       <c r="J14" s="3"/>
@@ -1579,79 +1665,251 @@
       <c r="Q14" s="3"/>
       <c r="R14" s="3"/>
     </row>
-    <row r="15" spans="1:18">
-      <c r="A15" s="5"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-    </row>
-    <row r="16" spans="1:18">
-      <c r="A16" s="5"/>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" s="5"/>
-      <c r="B17" s="5"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18" s="5"/>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="5"/>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19" s="5"/>
-      <c r="B19" s="5"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="5"/>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20" s="5"/>
-      <c r="B20" s="5"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
-      <c r="G20" s="5"/>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21" s="5"/>
-      <c r="B21" s="5"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="5"/>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22" s="5"/>
-      <c r="B22" s="5"/>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="5"/>
-    </row>
-    <row r="23" spans="1:7">
+    <row r="15" s="1" customFormat="1" spans="1:18">
+      <c r="A15" s="3">
+        <v>11</v>
+      </c>
+      <c r="B15" s="3">
+        <v>200012</v>
+      </c>
+      <c r="C15" s="3">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E15" s="3">
+        <v>3</v>
+      </c>
+      <c r="F15" s="3">
+        <v>502</v>
+      </c>
+      <c r="G15" s="3">
+        <v>7</v>
+      </c>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
+      <c r="J15" s="3"/>
+      <c r="K15" s="3"/>
+      <c r="L15" s="3"/>
+      <c r="M15" s="3"/>
+      <c r="N15" s="3"/>
+      <c r="O15" s="3"/>
+      <c r="P15" s="3"/>
+      <c r="Q15" s="3"/>
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" s="1" customFormat="1" spans="1:18">
+      <c r="A16" s="3">
+        <v>12</v>
+      </c>
+      <c r="B16" s="3">
+        <v>200013</v>
+      </c>
+      <c r="C16" s="3">
+        <v>0</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E16" s="3">
+        <v>3</v>
+      </c>
+      <c r="F16" s="3">
+        <v>503</v>
+      </c>
+      <c r="G16" s="3">
+        <v>8</v>
+      </c>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3"/>
+      <c r="J16" s="3"/>
+      <c r="K16" s="3"/>
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
+      <c r="N16" s="3"/>
+      <c r="O16" s="3"/>
+      <c r="P16" s="3"/>
+      <c r="Q16" s="3"/>
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" s="1" customFormat="1" spans="1:18">
+      <c r="A17" s="3">
+        <v>13</v>
+      </c>
+      <c r="B17" s="3">
+        <v>200014</v>
+      </c>
+      <c r="C17" s="3">
+        <v>0</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E17" s="3">
+        <v>3</v>
+      </c>
+      <c r="F17" s="3">
+        <v>504</v>
+      </c>
+      <c r="G17" s="3">
+        <v>9</v>
+      </c>
+      <c r="H17" s="3"/>
+      <c r="I17" s="3"/>
+      <c r="J17" s="3"/>
+      <c r="K17" s="3"/>
+      <c r="L17" s="3"/>
+      <c r="M17" s="3"/>
+      <c r="N17" s="3"/>
+      <c r="O17" s="3"/>
+      <c r="P17" s="3"/>
+      <c r="Q17" s="3"/>
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" s="1" customFormat="1" spans="1:18">
+      <c r="A18" s="3">
+        <v>14</v>
+      </c>
+      <c r="B18" s="3">
+        <v>200015</v>
+      </c>
+      <c r="C18" s="3">
+        <v>0</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E18" s="3">
+        <v>4</v>
+      </c>
+      <c r="F18" s="3">
+        <v>503</v>
+      </c>
+      <c r="G18" s="3">
+        <v>8</v>
+      </c>
+      <c r="H18" s="3"/>
+      <c r="I18" s="3"/>
+      <c r="J18" s="3"/>
+      <c r="K18" s="3"/>
+      <c r="L18" s="3"/>
+      <c r="M18" s="3"/>
+      <c r="N18" s="3"/>
+      <c r="O18" s="3"/>
+      <c r="P18" s="3"/>
+      <c r="Q18" s="3"/>
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" s="1" customFormat="1" spans="1:18">
+      <c r="A19" s="3">
+        <v>15</v>
+      </c>
+      <c r="B19" s="3">
+        <v>200016</v>
+      </c>
+      <c r="C19" s="3">
+        <v>0</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E19" s="3">
+        <v>4</v>
+      </c>
+      <c r="F19" s="3">
+        <v>504</v>
+      </c>
+      <c r="G19" s="3">
+        <v>9</v>
+      </c>
+      <c r="H19" s="3"/>
+      <c r="I19" s="3"/>
+      <c r="J19" s="3"/>
+      <c r="K19" s="3"/>
+      <c r="L19" s="3"/>
+      <c r="M19" s="3"/>
+      <c r="N19" s="3"/>
+      <c r="O19" s="3"/>
+      <c r="P19" s="3"/>
+      <c r="Q19" s="3"/>
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" s="1" customFormat="1" spans="1:18">
+      <c r="A20" s="3">
+        <v>16</v>
+      </c>
+      <c r="B20" s="3">
+        <v>200017</v>
+      </c>
+      <c r="C20" s="3">
+        <v>0</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E20" s="3">
+        <v>4</v>
+      </c>
+      <c r="F20" s="3">
+        <v>505</v>
+      </c>
+      <c r="G20" s="3">
+        <v>10</v>
+      </c>
+      <c r="H20" s="3"/>
+      <c r="I20" s="3"/>
+      <c r="J20" s="3"/>
+      <c r="K20" s="3"/>
+      <c r="L20" s="3"/>
+      <c r="M20" s="3"/>
+      <c r="N20" s="3"/>
+      <c r="O20" s="3"/>
+      <c r="P20" s="3"/>
+      <c r="Q20" s="3"/>
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" s="1" customFormat="1" spans="1:18">
+      <c r="A21" s="3"/>
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3"/>
+      <c r="I21" s="3"/>
+      <c r="J21" s="3"/>
+      <c r="K21" s="3"/>
+      <c r="L21" s="3"/>
+      <c r="M21" s="3"/>
+      <c r="N21" s="3"/>
+      <c r="O21" s="3"/>
+      <c r="P21" s="3"/>
+      <c r="Q21" s="3"/>
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" s="1" customFormat="1" spans="1:18">
+      <c r="A22" s="3"/>
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3"/>
+      <c r="J22" s="3"/>
+      <c r="K22" s="3"/>
+      <c r="L22" s="3"/>
+      <c r="M22" s="3"/>
+      <c r="N22" s="3"/>
+      <c r="O22" s="3"/>
+      <c r="P22" s="3"/>
+      <c r="Q22" s="3"/>
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="1:18">
       <c r="A23" s="5"/>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
@@ -1660,7 +1918,7 @@
       <c r="F23" s="5"/>
       <c r="G23" s="5"/>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:18">
       <c r="A24" s="5"/>
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
@@ -1669,7 +1927,7 @@
       <c r="F24" s="5"/>
       <c r="G24" s="5"/>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:18">
       <c r="A25" s="5"/>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
@@ -1678,7 +1936,7 @@
       <c r="F25" s="5"/>
       <c r="G25" s="5"/>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:18">
       <c r="A26" s="5"/>
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
@@ -1687,7 +1945,7 @@
       <c r="F26" s="5"/>
       <c r="G26" s="5"/>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:18">
       <c r="A27" s="5"/>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
@@ -1696,7 +1954,7 @@
       <c r="F27" s="5"/>
       <c r="G27" s="5"/>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:18">
       <c r="A28" s="5"/>
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
@@ -1705,7 +1963,7 @@
       <c r="F28" s="5"/>
       <c r="G28" s="5"/>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:18">
       <c r="A29" s="5"/>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
@@ -1714,7 +1972,7 @@
       <c r="F29" s="5"/>
       <c r="G29" s="5"/>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:18">
       <c r="A30" s="5"/>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
@@ -1723,7 +1981,7 @@
       <c r="F30" s="5"/>
       <c r="G30" s="5"/>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:18">
       <c r="A31" s="5"/>
       <c r="B31" s="5"/>
       <c r="C31" s="5"/>
@@ -1732,7 +1990,7 @@
       <c r="F31" s="5"/>
       <c r="G31" s="5"/>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:18">
       <c r="A32" s="5"/>
       <c r="B32" s="5"/>
       <c r="C32" s="5"/>
@@ -5469,56 +5727,104 @@
     </row>
     <row r="447" spans="1:7">
       <c r="A447" s="5"/>
+      <c r="B447" s="5"/>
+      <c r="C447" s="5"/>
+      <c r="D447" s="5"/>
+      <c r="E447" s="5"/>
+      <c r="F447" s="5"/>
+      <c r="G447" s="5"/>
     </row>
     <row r="448" spans="1:7">
       <c r="A448" s="5"/>
-    </row>
-    <row r="449" spans="1:1">
+      <c r="B448" s="5"/>
+      <c r="C448" s="5"/>
+      <c r="D448" s="5"/>
+      <c r="E448" s="5"/>
+      <c r="F448" s="5"/>
+      <c r="G448" s="5"/>
+    </row>
+    <row r="449" spans="1:7">
       <c r="A449" s="5"/>
-    </row>
-    <row r="450" spans="1:1">
+      <c r="B449" s="5"/>
+      <c r="C449" s="5"/>
+      <c r="D449" s="5"/>
+      <c r="E449" s="5"/>
+      <c r="F449" s="5"/>
+      <c r="G449" s="5"/>
+    </row>
+    <row r="450" spans="1:7">
       <c r="A450" s="5"/>
-    </row>
-    <row r="451" spans="1:1">
+      <c r="B450" s="5"/>
+      <c r="C450" s="5"/>
+      <c r="D450" s="5"/>
+      <c r="E450" s="5"/>
+      <c r="F450" s="5"/>
+      <c r="G450" s="5"/>
+    </row>
+    <row r="451" spans="1:7">
       <c r="A451" s="5"/>
-    </row>
-    <row r="452" spans="1:1">
+      <c r="B451" s="5"/>
+      <c r="C451" s="5"/>
+      <c r="D451" s="5"/>
+      <c r="E451" s="5"/>
+      <c r="F451" s="5"/>
+      <c r="G451" s="5"/>
+    </row>
+    <row r="452" spans="1:7">
       <c r="A452" s="5"/>
-    </row>
-    <row r="453" spans="1:1">
+      <c r="B452" s="5"/>
+      <c r="C452" s="5"/>
+      <c r="D452" s="5"/>
+      <c r="E452" s="5"/>
+      <c r="F452" s="5"/>
+      <c r="G452" s="5"/>
+    </row>
+    <row r="453" spans="1:7">
       <c r="A453" s="5"/>
-    </row>
-    <row r="454" spans="1:1">
+      <c r="B453" s="5"/>
+      <c r="C453" s="5"/>
+      <c r="D453" s="5"/>
+      <c r="E453" s="5"/>
+      <c r="F453" s="5"/>
+      <c r="G453" s="5"/>
+    </row>
+    <row r="454" spans="1:7">
       <c r="A454" s="5"/>
-    </row>
-    <row r="455" spans="1:1">
+      <c r="B454" s="5"/>
+      <c r="C454" s="5"/>
+      <c r="D454" s="5"/>
+      <c r="E454" s="5"/>
+      <c r="F454" s="5"/>
+      <c r="G454" s="5"/>
+    </row>
+    <row r="455" spans="1:7">
       <c r="A455" s="5"/>
     </row>
-    <row r="456" spans="1:1">
+    <row r="456" spans="1:7">
       <c r="A456" s="5"/>
     </row>
-    <row r="457" spans="1:1">
+    <row r="457" spans="1:7">
       <c r="A457" s="5"/>
     </row>
-    <row r="458" spans="1:1">
+    <row r="458" spans="1:7">
       <c r="A458" s="5"/>
     </row>
-    <row r="459" spans="1:1">
+    <row r="459" spans="1:7">
       <c r="A459" s="5"/>
     </row>
-    <row r="460" spans="1:1">
+    <row r="460" spans="1:7">
       <c r="A460" s="5"/>
     </row>
-    <row r="461" spans="1:1">
+    <row r="461" spans="1:7">
       <c r="A461" s="5"/>
     </row>
-    <row r="462" spans="1:1">
+    <row r="462" spans="1:7">
       <c r="A462" s="5"/>
     </row>
-    <row r="463" spans="1:1">
+    <row r="463" spans="1:7">
       <c r="A463" s="5"/>
     </row>
-    <row r="464" spans="1:1">
+    <row r="464" spans="1:7">
       <c r="A464" s="5"/>
     </row>
     <row r="465" spans="1:1">
@@ -5950,8 +6256,32 @@
     <row r="607" spans="1:1">
       <c r="A607" s="5"/>
     </row>
+    <row r="608" spans="1:1">
+      <c r="A608" s="5"/>
+    </row>
+    <row r="609" spans="1:1">
+      <c r="A609" s="5"/>
+    </row>
+    <row r="610" spans="1:1">
+      <c r="A610" s="5"/>
+    </row>
+    <row r="611" spans="1:1">
+      <c r="A611" s="5"/>
+    </row>
+    <row r="612" spans="1:1">
+      <c r="A612" s="5"/>
+    </row>
+    <row r="613" spans="1:1">
+      <c r="A613" s="5"/>
+    </row>
+    <row r="614" spans="1:1">
+      <c r="A614" s="5"/>
+    </row>
+    <row r="615" spans="1:1">
+      <c r="A615" s="5"/>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:H607" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:H615" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/excel/item.xlsx
+++ b/excel/item.xlsx
@@ -133,7 +133,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="35">
   <si>
     <t>编号</t>
   </si>
@@ -153,7 +153,10 @@
     <t>价值</t>
   </si>
   <si>
-    <t>重量</t>
+    <t>容量</t>
+  </si>
+  <si>
+    <t>权重</t>
   </si>
   <si>
     <t>id</t>
@@ -172,6 +175,9 @@
   </si>
   <si>
     <t>value</t>
+  </si>
+  <si>
+    <t>capacity</t>
   </si>
   <si>
     <t>weight</t>
@@ -1229,8 +1235,8 @@
   <dimension ref="A1:R615"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="7" width="25.125" style="2" customWidth="1"/>
-    <col min="8" max="18" width="25.125" style="3" customWidth="1"/>
+    <col min="1" max="8" width="25.125" style="2" customWidth="1"/>
+    <col min="9" max="18" width="25.125" style="3" customWidth="1"/>
     <col min="19" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
@@ -1256,51 +1262,60 @@
       <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="2" ht="16.5" spans="1:18">
       <c r="A2" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="3" ht="16.5" spans="1:18">
       <c r="A3" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" spans="1:18">
@@ -1314,7 +1329,7 @@
         <v>0</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
@@ -1342,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
@@ -1370,7 +1385,7 @@
         <v>0</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E6" s="3">
         <v>0</v>
@@ -1381,7 +1396,9 @@
       <c r="G6" s="3">
         <v>5</v>
       </c>
-      <c r="H6" s="3"/>
+      <c r="H6" s="3">
+        <v>2</v>
+      </c>
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
@@ -1404,7 +1421,7 @@
         <v>0</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E7" s="3">
         <v>0</v>
@@ -1415,7 +1432,9 @@
       <c r="G7" s="3">
         <v>6</v>
       </c>
-      <c r="H7" s="3"/>
+      <c r="H7" s="3">
+        <v>3</v>
+      </c>
       <c r="I7" s="3"/>
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
@@ -1438,7 +1457,7 @@
         <v>0</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E8" s="3">
         <v>0</v>
@@ -1449,7 +1468,9 @@
       <c r="G8" s="3">
         <v>7</v>
       </c>
-      <c r="H8" s="3"/>
+      <c r="H8" s="3">
+        <v>1</v>
+      </c>
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
@@ -1472,7 +1493,7 @@
         <v>0</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E9" s="3">
         <v>1</v>
@@ -1483,7 +1504,9 @@
       <c r="G9" s="3">
         <v>5</v>
       </c>
-      <c r="H9" s="3"/>
+      <c r="H9" s="3">
+        <v>4</v>
+      </c>
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
@@ -1506,7 +1529,7 @@
         <v>0</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E10" s="3">
         <v>1</v>
@@ -1517,7 +1540,9 @@
       <c r="G10" s="3">
         <v>6</v>
       </c>
-      <c r="H10" s="3"/>
+      <c r="H10" s="3">
+        <v>2</v>
+      </c>
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
@@ -1540,7 +1565,7 @@
         <v>0</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E11" s="3">
         <v>1</v>
@@ -1551,7 +1576,9 @@
       <c r="G11" s="3">
         <v>7</v>
       </c>
-      <c r="H11" s="3"/>
+      <c r="H11" s="3">
+        <v>1</v>
+      </c>
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
@@ -1574,7 +1601,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E12" s="3">
         <v>2</v>
@@ -1585,7 +1612,9 @@
       <c r="G12" s="3">
         <v>6</v>
       </c>
-      <c r="H12" s="3"/>
+      <c r="H12" s="3">
+        <v>4</v>
+      </c>
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
       <c r="K12" s="3"/>
@@ -1608,7 +1637,7 @@
         <v>0</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E13" s="3">
         <v>2</v>
@@ -1619,7 +1648,9 @@
       <c r="G13" s="3">
         <v>7</v>
       </c>
-      <c r="H13" s="3"/>
+      <c r="H13" s="3">
+        <v>2</v>
+      </c>
       <c r="I13" s="3"/>
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
@@ -1642,7 +1673,7 @@
         <v>0</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E14" s="3">
         <v>2</v>
@@ -1653,7 +1684,9 @@
       <c r="G14" s="3">
         <v>8</v>
       </c>
-      <c r="H14" s="3"/>
+      <c r="H14" s="3">
+        <v>1</v>
+      </c>
       <c r="I14" s="3"/>
       <c r="J14" s="3"/>
       <c r="K14" s="3"/>
@@ -1676,7 +1709,7 @@
         <v>0</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E15" s="3">
         <v>3</v>
@@ -1687,7 +1720,9 @@
       <c r="G15" s="3">
         <v>7</v>
       </c>
-      <c r="H15" s="3"/>
+      <c r="H15" s="3">
+        <v>4</v>
+      </c>
       <c r="I15" s="3"/>
       <c r="J15" s="3"/>
       <c r="K15" s="3"/>
@@ -1710,7 +1745,7 @@
         <v>0</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E16" s="3">
         <v>3</v>
@@ -1721,7 +1756,9 @@
       <c r="G16" s="3">
         <v>8</v>
       </c>
-      <c r="H16" s="3"/>
+      <c r="H16" s="3">
+        <v>2</v>
+      </c>
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
@@ -1744,7 +1781,7 @@
         <v>0</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E17" s="3">
         <v>3</v>
@@ -1755,7 +1792,9 @@
       <c r="G17" s="3">
         <v>9</v>
       </c>
-      <c r="H17" s="3"/>
+      <c r="H17" s="3">
+        <v>1</v>
+      </c>
       <c r="I17" s="3"/>
       <c r="J17" s="3"/>
       <c r="K17" s="3"/>
@@ -1778,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E18" s="3">
         <v>4</v>
@@ -1789,7 +1828,9 @@
       <c r="G18" s="3">
         <v>8</v>
       </c>
-      <c r="H18" s="3"/>
+      <c r="H18" s="3">
+        <v>4</v>
+      </c>
       <c r="I18" s="3"/>
       <c r="J18" s="3"/>
       <c r="K18" s="3"/>
@@ -1812,7 +1853,7 @@
         <v>0</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E19" s="3">
         <v>4</v>
@@ -1823,7 +1864,9 @@
       <c r="G19" s="3">
         <v>9</v>
       </c>
-      <c r="H19" s="3"/>
+      <c r="H19" s="3">
+        <v>2</v>
+      </c>
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
@@ -1846,7 +1889,7 @@
         <v>0</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E20" s="3">
         <v>4</v>
@@ -1857,7 +1900,9 @@
       <c r="G20" s="3">
         <v>10</v>
       </c>
-      <c r="H20" s="3"/>
+      <c r="H20" s="3">
+        <v>1</v>
+      </c>
       <c r="I20" s="3"/>
       <c r="J20" s="3"/>
       <c r="K20" s="3"/>
@@ -1917,6 +1962,7 @@
       <c r="E23" s="5"/>
       <c r="F23" s="5"/>
       <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
     </row>
     <row r="24" spans="1:18">
       <c r="A24" s="5"/>
@@ -1926,6 +1972,7 @@
       <c r="E24" s="5"/>
       <c r="F24" s="5"/>
       <c r="G24" s="5"/>
+      <c r="H24" s="5"/>
     </row>
     <row r="25" spans="1:18">
       <c r="A25" s="5"/>
@@ -1935,6 +1982,7 @@
       <c r="E25" s="5"/>
       <c r="F25" s="5"/>
       <c r="G25" s="5"/>
+      <c r="H25" s="5"/>
     </row>
     <row r="26" spans="1:18">
       <c r="A26" s="5"/>
@@ -1944,6 +1992,7 @@
       <c r="E26" s="5"/>
       <c r="F26" s="5"/>
       <c r="G26" s="5"/>
+      <c r="H26" s="5"/>
     </row>
     <row r="27" spans="1:18">
       <c r="A27" s="5"/>
@@ -1953,6 +2002,7 @@
       <c r="E27" s="5"/>
       <c r="F27" s="5"/>
       <c r="G27" s="5"/>
+      <c r="H27" s="5"/>
     </row>
     <row r="28" spans="1:18">
       <c r="A28" s="5"/>
@@ -1962,6 +2012,7 @@
       <c r="E28" s="5"/>
       <c r="F28" s="5"/>
       <c r="G28" s="5"/>
+      <c r="H28" s="5"/>
     </row>
     <row r="29" spans="1:18">
       <c r="A29" s="5"/>
@@ -1971,6 +2022,7 @@
       <c r="E29" s="5"/>
       <c r="F29" s="5"/>
       <c r="G29" s="5"/>
+      <c r="H29" s="5"/>
     </row>
     <row r="30" spans="1:18">
       <c r="A30" s="5"/>
@@ -1980,6 +2032,7 @@
       <c r="E30" s="5"/>
       <c r="F30" s="5"/>
       <c r="G30" s="5"/>
+      <c r="H30" s="5"/>
     </row>
     <row r="31" spans="1:18">
       <c r="A31" s="5"/>
@@ -1989,6 +2042,7 @@
       <c r="E31" s="5"/>
       <c r="F31" s="5"/>
       <c r="G31" s="5"/>
+      <c r="H31" s="5"/>
     </row>
     <row r="32" spans="1:18">
       <c r="A32" s="5"/>
@@ -1998,8 +2052,9 @@
       <c r="E32" s="5"/>
       <c r="F32" s="5"/>
       <c r="G32" s="5"/>
-    </row>
-    <row r="33" spans="1:7">
+      <c r="H32" s="5"/>
+    </row>
+    <row r="33" spans="1:8">
       <c r="A33" s="5"/>
       <c r="B33" s="5"/>
       <c r="C33" s="5"/>
@@ -2007,8 +2062,9 @@
       <c r="E33" s="5"/>
       <c r="F33" s="5"/>
       <c r="G33" s="5"/>
-    </row>
-    <row r="34" spans="1:7">
+      <c r="H33" s="5"/>
+    </row>
+    <row r="34" spans="1:8">
       <c r="A34" s="5"/>
       <c r="B34" s="5"/>
       <c r="C34" s="5"/>
@@ -2016,8 +2072,9 @@
       <c r="E34" s="5"/>
       <c r="F34" s="5"/>
       <c r="G34" s="5"/>
-    </row>
-    <row r="35" spans="1:7">
+      <c r="H34" s="5"/>
+    </row>
+    <row r="35" spans="1:8">
       <c r="A35" s="5"/>
       <c r="B35" s="5"/>
       <c r="C35" s="5"/>
@@ -2025,8 +2082,9 @@
       <c r="E35" s="5"/>
       <c r="F35" s="5"/>
       <c r="G35" s="5"/>
-    </row>
-    <row r="36" spans="1:7">
+      <c r="H35" s="5"/>
+    </row>
+    <row r="36" spans="1:8">
       <c r="A36" s="5"/>
       <c r="B36" s="5"/>
       <c r="C36" s="5"/>
@@ -2034,8 +2092,9 @@
       <c r="E36" s="5"/>
       <c r="F36" s="5"/>
       <c r="G36" s="5"/>
-    </row>
-    <row r="37" spans="1:7">
+      <c r="H36" s="5"/>
+    </row>
+    <row r="37" spans="1:8">
       <c r="A37" s="5"/>
       <c r="B37" s="5"/>
       <c r="C37" s="5"/>
@@ -2043,8 +2102,9 @@
       <c r="E37" s="5"/>
       <c r="F37" s="5"/>
       <c r="G37" s="5"/>
-    </row>
-    <row r="38" spans="1:7">
+      <c r="H37" s="5"/>
+    </row>
+    <row r="38" spans="1:8">
       <c r="A38" s="5"/>
       <c r="B38" s="5"/>
       <c r="C38" s="5"/>
@@ -2052,8 +2112,9 @@
       <c r="E38" s="5"/>
       <c r="F38" s="5"/>
       <c r="G38" s="5"/>
-    </row>
-    <row r="39" spans="1:7">
+      <c r="H38" s="5"/>
+    </row>
+    <row r="39" spans="1:8">
       <c r="A39" s="5"/>
       <c r="B39" s="5"/>
       <c r="C39" s="5"/>
@@ -2061,8 +2122,9 @@
       <c r="E39" s="5"/>
       <c r="F39" s="5"/>
       <c r="G39" s="5"/>
-    </row>
-    <row r="40" spans="1:7">
+      <c r="H39" s="5"/>
+    </row>
+    <row r="40" spans="1:8">
       <c r="A40" s="5"/>
       <c r="B40" s="5"/>
       <c r="C40" s="5"/>
@@ -2070,8 +2132,9 @@
       <c r="E40" s="5"/>
       <c r="F40" s="5"/>
       <c r="G40" s="5"/>
-    </row>
-    <row r="41" spans="1:7">
+      <c r="H40" s="5"/>
+    </row>
+    <row r="41" spans="1:8">
       <c r="A41" s="5"/>
       <c r="B41" s="5"/>
       <c r="C41" s="5"/>
@@ -2079,8 +2142,9 @@
       <c r="E41" s="5"/>
       <c r="F41" s="5"/>
       <c r="G41" s="5"/>
-    </row>
-    <row r="42" spans="1:7">
+      <c r="H41" s="5"/>
+    </row>
+    <row r="42" spans="1:8">
       <c r="A42" s="5"/>
       <c r="B42" s="5"/>
       <c r="C42" s="5"/>
@@ -2088,8 +2152,9 @@
       <c r="E42" s="5"/>
       <c r="F42" s="5"/>
       <c r="G42" s="5"/>
-    </row>
-    <row r="43" spans="1:7">
+      <c r="H42" s="5"/>
+    </row>
+    <row r="43" spans="1:8">
       <c r="A43" s="5"/>
       <c r="B43" s="5"/>
       <c r="C43" s="5"/>
@@ -2097,8 +2162,9 @@
       <c r="E43" s="5"/>
       <c r="F43" s="5"/>
       <c r="G43" s="5"/>
-    </row>
-    <row r="44" spans="1:7">
+      <c r="H43" s="5"/>
+    </row>
+    <row r="44" spans="1:8">
       <c r="A44" s="5"/>
       <c r="B44" s="5"/>
       <c r="C44" s="5"/>
@@ -2106,8 +2172,9 @@
       <c r="E44" s="5"/>
       <c r="F44" s="5"/>
       <c r="G44" s="5"/>
-    </row>
-    <row r="45" spans="1:7">
+      <c r="H44" s="5"/>
+    </row>
+    <row r="45" spans="1:8">
       <c r="A45" s="5"/>
       <c r="B45" s="5"/>
       <c r="C45" s="5"/>
@@ -2115,8 +2182,9 @@
       <c r="E45" s="5"/>
       <c r="F45" s="5"/>
       <c r="G45" s="5"/>
-    </row>
-    <row r="46" spans="1:7">
+      <c r="H45" s="5"/>
+    </row>
+    <row r="46" spans="1:8">
       <c r="A46" s="5"/>
       <c r="B46" s="5"/>
       <c r="C46" s="5"/>
@@ -2124,8 +2192,9 @@
       <c r="E46" s="5"/>
       <c r="F46" s="5"/>
       <c r="G46" s="5"/>
-    </row>
-    <row r="47" spans="1:7">
+      <c r="H46" s="5"/>
+    </row>
+    <row r="47" spans="1:8">
       <c r="A47" s="5"/>
       <c r="B47" s="5"/>
       <c r="C47" s="5"/>
@@ -2133,8 +2202,9 @@
       <c r="E47" s="5"/>
       <c r="F47" s="5"/>
       <c r="G47" s="5"/>
-    </row>
-    <row r="48" spans="1:7">
+      <c r="H47" s="5"/>
+    </row>
+    <row r="48" spans="1:8">
       <c r="A48" s="5"/>
       <c r="B48" s="5"/>
       <c r="C48" s="5"/>
@@ -2142,8 +2212,9 @@
       <c r="E48" s="5"/>
       <c r="F48" s="5"/>
       <c r="G48" s="5"/>
-    </row>
-    <row r="49" spans="1:7">
+      <c r="H48" s="5"/>
+    </row>
+    <row r="49" spans="1:8">
       <c r="A49" s="5"/>
       <c r="B49" s="5"/>
       <c r="C49" s="5"/>
@@ -2151,8 +2222,9 @@
       <c r="E49" s="5"/>
       <c r="F49" s="5"/>
       <c r="G49" s="5"/>
-    </row>
-    <row r="50" spans="1:7">
+      <c r="H49" s="5"/>
+    </row>
+    <row r="50" spans="1:8">
       <c r="A50" s="5"/>
       <c r="B50" s="5"/>
       <c r="C50" s="5"/>
@@ -2160,8 +2232,9 @@
       <c r="E50" s="5"/>
       <c r="F50" s="5"/>
       <c r="G50" s="5"/>
-    </row>
-    <row r="51" spans="1:7">
+      <c r="H50" s="5"/>
+    </row>
+    <row r="51" spans="1:8">
       <c r="A51" s="5"/>
       <c r="B51" s="5"/>
       <c r="C51" s="5"/>
@@ -2169,8 +2242,9 @@
       <c r="E51" s="5"/>
       <c r="F51" s="5"/>
       <c r="G51" s="5"/>
-    </row>
-    <row r="52" spans="1:7">
+      <c r="H51" s="5"/>
+    </row>
+    <row r="52" spans="1:8">
       <c r="A52" s="5"/>
       <c r="B52" s="5"/>
       <c r="C52" s="5"/>
@@ -2178,8 +2252,9 @@
       <c r="E52" s="5"/>
       <c r="F52" s="5"/>
       <c r="G52" s="5"/>
-    </row>
-    <row r="53" spans="1:7">
+      <c r="H52" s="5"/>
+    </row>
+    <row r="53" spans="1:8">
       <c r="A53" s="5"/>
       <c r="B53" s="5"/>
       <c r="C53" s="5"/>
@@ -2187,8 +2262,9 @@
       <c r="E53" s="5"/>
       <c r="F53" s="5"/>
       <c r="G53" s="5"/>
-    </row>
-    <row r="54" spans="1:7">
+      <c r="H53" s="5"/>
+    </row>
+    <row r="54" spans="1:8">
       <c r="A54" s="5"/>
       <c r="B54" s="5"/>
       <c r="C54" s="5"/>
@@ -2196,8 +2272,9 @@
       <c r="E54" s="5"/>
       <c r="F54" s="5"/>
       <c r="G54" s="5"/>
-    </row>
-    <row r="55" spans="1:7">
+      <c r="H54" s="5"/>
+    </row>
+    <row r="55" spans="1:8">
       <c r="A55" s="5"/>
       <c r="B55" s="5"/>
       <c r="C55" s="5"/>
@@ -2205,8 +2282,9 @@
       <c r="E55" s="5"/>
       <c r="F55" s="5"/>
       <c r="G55" s="5"/>
-    </row>
-    <row r="56" spans="1:7">
+      <c r="H55" s="5"/>
+    </row>
+    <row r="56" spans="1:8">
       <c r="A56" s="5"/>
       <c r="B56" s="5"/>
       <c r="C56" s="5"/>
@@ -2214,8 +2292,9 @@
       <c r="E56" s="5"/>
       <c r="F56" s="5"/>
       <c r="G56" s="5"/>
-    </row>
-    <row r="57" spans="1:7">
+      <c r="H56" s="5"/>
+    </row>
+    <row r="57" spans="1:8">
       <c r="A57" s="5"/>
       <c r="B57" s="5"/>
       <c r="C57" s="5"/>
@@ -2223,8 +2302,9 @@
       <c r="E57" s="5"/>
       <c r="F57" s="5"/>
       <c r="G57" s="5"/>
-    </row>
-    <row r="58" spans="1:7">
+      <c r="H57" s="5"/>
+    </row>
+    <row r="58" spans="1:8">
       <c r="A58" s="5"/>
       <c r="B58" s="5"/>
       <c r="C58" s="5"/>
@@ -2232,8 +2312,9 @@
       <c r="E58" s="5"/>
       <c r="F58" s="5"/>
       <c r="G58" s="5"/>
-    </row>
-    <row r="59" spans="1:7">
+      <c r="H58" s="5"/>
+    </row>
+    <row r="59" spans="1:8">
       <c r="A59" s="5"/>
       <c r="B59" s="5"/>
       <c r="C59" s="5"/>
@@ -2241,8 +2322,9 @@
       <c r="E59" s="5"/>
       <c r="F59" s="5"/>
       <c r="G59" s="5"/>
-    </row>
-    <row r="60" spans="1:7">
+      <c r="H59" s="5"/>
+    </row>
+    <row r="60" spans="1:8">
       <c r="A60" s="5"/>
       <c r="B60" s="5"/>
       <c r="C60" s="5"/>
@@ -2250,8 +2332,9 @@
       <c r="E60" s="5"/>
       <c r="F60" s="5"/>
       <c r="G60" s="5"/>
-    </row>
-    <row r="61" spans="1:7">
+      <c r="H60" s="5"/>
+    </row>
+    <row r="61" spans="1:8">
       <c r="A61" s="5"/>
       <c r="B61" s="5"/>
       <c r="C61" s="5"/>
@@ -2259,8 +2342,9 @@
       <c r="E61" s="5"/>
       <c r="F61" s="5"/>
       <c r="G61" s="5"/>
-    </row>
-    <row r="62" spans="1:7">
+      <c r="H61" s="5"/>
+    </row>
+    <row r="62" spans="1:8">
       <c r="A62" s="5"/>
       <c r="B62" s="5"/>
       <c r="C62" s="5"/>
@@ -2268,8 +2352,9 @@
       <c r="E62" s="5"/>
       <c r="F62" s="5"/>
       <c r="G62" s="5"/>
-    </row>
-    <row r="63" spans="1:7">
+      <c r="H62" s="5"/>
+    </row>
+    <row r="63" spans="1:8">
       <c r="A63" s="5"/>
       <c r="B63" s="5"/>
       <c r="C63" s="5"/>
@@ -2277,8 +2362,9 @@
       <c r="E63" s="5"/>
       <c r="F63" s="5"/>
       <c r="G63" s="5"/>
-    </row>
-    <row r="64" spans="1:7">
+      <c r="H63" s="5"/>
+    </row>
+    <row r="64" spans="1:8">
       <c r="A64" s="5"/>
       <c r="B64" s="5"/>
       <c r="C64" s="5"/>
@@ -2286,8 +2372,9 @@
       <c r="E64" s="5"/>
       <c r="F64" s="5"/>
       <c r="G64" s="5"/>
-    </row>
-    <row r="65" spans="1:7">
+      <c r="H64" s="5"/>
+    </row>
+    <row r="65" spans="1:8">
       <c r="A65" s="5"/>
       <c r="B65" s="5"/>
       <c r="C65" s="5"/>
@@ -2295,8 +2382,9 @@
       <c r="E65" s="5"/>
       <c r="F65" s="5"/>
       <c r="G65" s="5"/>
-    </row>
-    <row r="66" spans="1:7">
+      <c r="H65" s="5"/>
+    </row>
+    <row r="66" spans="1:8">
       <c r="A66" s="5"/>
       <c r="B66" s="5"/>
       <c r="C66" s="5"/>
@@ -2304,8 +2392,9 @@
       <c r="E66" s="5"/>
       <c r="F66" s="5"/>
       <c r="G66" s="5"/>
-    </row>
-    <row r="67" spans="1:7">
+      <c r="H66" s="5"/>
+    </row>
+    <row r="67" spans="1:8">
       <c r="A67" s="5"/>
       <c r="B67" s="5"/>
       <c r="C67" s="5"/>
@@ -2313,8 +2402,9 @@
       <c r="E67" s="5"/>
       <c r="F67" s="5"/>
       <c r="G67" s="5"/>
-    </row>
-    <row r="68" spans="1:7">
+      <c r="H67" s="5"/>
+    </row>
+    <row r="68" spans="1:8">
       <c r="A68" s="5"/>
       <c r="B68" s="5"/>
       <c r="C68" s="5"/>
@@ -2322,8 +2412,9 @@
       <c r="E68" s="5"/>
       <c r="F68" s="5"/>
       <c r="G68" s="5"/>
-    </row>
-    <row r="69" spans="1:7">
+      <c r="H68" s="5"/>
+    </row>
+    <row r="69" spans="1:8">
       <c r="A69" s="5"/>
       <c r="B69" s="5"/>
       <c r="C69" s="5"/>
@@ -2331,8 +2422,9 @@
       <c r="E69" s="5"/>
       <c r="F69" s="5"/>
       <c r="G69" s="5"/>
-    </row>
-    <row r="70" spans="1:7">
+      <c r="H69" s="5"/>
+    </row>
+    <row r="70" spans="1:8">
       <c r="A70" s="5"/>
       <c r="B70" s="5"/>
       <c r="C70" s="5"/>
@@ -2340,8 +2432,9 @@
       <c r="E70" s="5"/>
       <c r="F70" s="5"/>
       <c r="G70" s="5"/>
-    </row>
-    <row r="71" spans="1:7">
+      <c r="H70" s="5"/>
+    </row>
+    <row r="71" spans="1:8">
       <c r="A71" s="5"/>
       <c r="B71" s="5"/>
       <c r="C71" s="5"/>
@@ -2349,8 +2442,9 @@
       <c r="E71" s="5"/>
       <c r="F71" s="5"/>
       <c r="G71" s="5"/>
-    </row>
-    <row r="72" spans="1:7">
+      <c r="H71" s="5"/>
+    </row>
+    <row r="72" spans="1:8">
       <c r="A72" s="5"/>
       <c r="B72" s="5"/>
       <c r="C72" s="5"/>
@@ -2358,8 +2452,9 @@
       <c r="E72" s="5"/>
       <c r="F72" s="5"/>
       <c r="G72" s="5"/>
-    </row>
-    <row r="73" spans="1:7">
+      <c r="H72" s="5"/>
+    </row>
+    <row r="73" spans="1:8">
       <c r="A73" s="5"/>
       <c r="B73" s="5"/>
       <c r="C73" s="5"/>
@@ -2367,8 +2462,9 @@
       <c r="E73" s="5"/>
       <c r="F73" s="5"/>
       <c r="G73" s="5"/>
-    </row>
-    <row r="74" spans="1:7">
+      <c r="H73" s="5"/>
+    </row>
+    <row r="74" spans="1:8">
       <c r="A74" s="5"/>
       <c r="B74" s="5"/>
       <c r="C74" s="5"/>
@@ -2376,8 +2472,9 @@
       <c r="E74" s="5"/>
       <c r="F74" s="5"/>
       <c r="G74" s="5"/>
-    </row>
-    <row r="75" spans="1:7">
+      <c r="H74" s="5"/>
+    </row>
+    <row r="75" spans="1:8">
       <c r="A75" s="5"/>
       <c r="B75" s="5"/>
       <c r="C75" s="5"/>
@@ -2385,8 +2482,9 @@
       <c r="E75" s="5"/>
       <c r="F75" s="5"/>
       <c r="G75" s="5"/>
-    </row>
-    <row r="76" spans="1:7">
+      <c r="H75" s="5"/>
+    </row>
+    <row r="76" spans="1:8">
       <c r="A76" s="5"/>
       <c r="B76" s="5"/>
       <c r="C76" s="5"/>
@@ -2394,8 +2492,9 @@
       <c r="E76" s="5"/>
       <c r="F76" s="5"/>
       <c r="G76" s="5"/>
-    </row>
-    <row r="77" spans="1:7">
+      <c r="H76" s="5"/>
+    </row>
+    <row r="77" spans="1:8">
       <c r="A77" s="5"/>
       <c r="B77" s="5"/>
       <c r="C77" s="5"/>
@@ -2403,8 +2502,9 @@
       <c r="E77" s="5"/>
       <c r="F77" s="5"/>
       <c r="G77" s="5"/>
-    </row>
-    <row r="78" spans="1:7">
+      <c r="H77" s="5"/>
+    </row>
+    <row r="78" spans="1:8">
       <c r="A78" s="5"/>
       <c r="B78" s="5"/>
       <c r="C78" s="5"/>
@@ -2412,8 +2512,9 @@
       <c r="E78" s="5"/>
       <c r="F78" s="5"/>
       <c r="G78" s="5"/>
-    </row>
-    <row r="79" spans="1:7">
+      <c r="H78" s="5"/>
+    </row>
+    <row r="79" spans="1:8">
       <c r="A79" s="5"/>
       <c r="B79" s="5"/>
       <c r="C79" s="5"/>
@@ -2421,8 +2522,9 @@
       <c r="E79" s="5"/>
       <c r="F79" s="5"/>
       <c r="G79" s="5"/>
-    </row>
-    <row r="80" spans="1:7">
+      <c r="H79" s="5"/>
+    </row>
+    <row r="80" spans="1:8">
       <c r="A80" s="5"/>
       <c r="B80" s="5"/>
       <c r="C80" s="5"/>
@@ -2430,8 +2532,9 @@
       <c r="E80" s="5"/>
       <c r="F80" s="5"/>
       <c r="G80" s="5"/>
-    </row>
-    <row r="81" spans="1:7">
+      <c r="H80" s="5"/>
+    </row>
+    <row r="81" spans="1:8">
       <c r="A81" s="5"/>
       <c r="B81" s="5"/>
       <c r="C81" s="5"/>
@@ -2439,8 +2542,9 @@
       <c r="E81" s="5"/>
       <c r="F81" s="5"/>
       <c r="G81" s="5"/>
-    </row>
-    <row r="82" spans="1:7">
+      <c r="H81" s="5"/>
+    </row>
+    <row r="82" spans="1:8">
       <c r="A82" s="5"/>
       <c r="B82" s="5"/>
       <c r="C82" s="5"/>
@@ -2448,8 +2552,9 @@
       <c r="E82" s="5"/>
       <c r="F82" s="5"/>
       <c r="G82" s="5"/>
-    </row>
-    <row r="83" spans="1:7">
+      <c r="H82" s="5"/>
+    </row>
+    <row r="83" spans="1:8">
       <c r="A83" s="5"/>
       <c r="B83" s="5"/>
       <c r="C83" s="5"/>
@@ -2457,8 +2562,9 @@
       <c r="E83" s="5"/>
       <c r="F83" s="5"/>
       <c r="G83" s="5"/>
-    </row>
-    <row r="84" spans="1:7">
+      <c r="H83" s="5"/>
+    </row>
+    <row r="84" spans="1:8">
       <c r="A84" s="5"/>
       <c r="B84" s="5"/>
       <c r="C84" s="5"/>
@@ -2466,8 +2572,9 @@
       <c r="E84" s="5"/>
       <c r="F84" s="5"/>
       <c r="G84" s="5"/>
-    </row>
-    <row r="85" spans="1:7">
+      <c r="H84" s="5"/>
+    </row>
+    <row r="85" spans="1:8">
       <c r="A85" s="5"/>
       <c r="B85" s="5"/>
       <c r="C85" s="5"/>
@@ -2475,8 +2582,9 @@
       <c r="E85" s="5"/>
       <c r="F85" s="5"/>
       <c r="G85" s="5"/>
-    </row>
-    <row r="86" spans="1:7">
+      <c r="H85" s="5"/>
+    </row>
+    <row r="86" spans="1:8">
       <c r="A86" s="5"/>
       <c r="B86" s="5"/>
       <c r="C86" s="5"/>
@@ -2484,8 +2592,9 @@
       <c r="E86" s="5"/>
       <c r="F86" s="5"/>
       <c r="G86" s="5"/>
-    </row>
-    <row r="87" spans="1:7">
+      <c r="H86" s="5"/>
+    </row>
+    <row r="87" spans="1:8">
       <c r="A87" s="5"/>
       <c r="B87" s="5"/>
       <c r="C87" s="5"/>
@@ -2493,8 +2602,9 @@
       <c r="E87" s="5"/>
       <c r="F87" s="5"/>
       <c r="G87" s="5"/>
-    </row>
-    <row r="88" spans="1:7">
+      <c r="H87" s="5"/>
+    </row>
+    <row r="88" spans="1:8">
       <c r="A88" s="5"/>
       <c r="B88" s="5"/>
       <c r="C88" s="5"/>
@@ -2502,8 +2612,9 @@
       <c r="E88" s="5"/>
       <c r="F88" s="5"/>
       <c r="G88" s="5"/>
-    </row>
-    <row r="89" spans="1:7">
+      <c r="H88" s="5"/>
+    </row>
+    <row r="89" spans="1:8">
       <c r="A89" s="5"/>
       <c r="B89" s="5"/>
       <c r="C89" s="5"/>
@@ -2511,8 +2622,9 @@
       <c r="E89" s="5"/>
       <c r="F89" s="5"/>
       <c r="G89" s="5"/>
-    </row>
-    <row r="90" spans="1:7">
+      <c r="H89" s="5"/>
+    </row>
+    <row r="90" spans="1:8">
       <c r="A90" s="5"/>
       <c r="B90" s="5"/>
       <c r="C90" s="5"/>
@@ -2520,8 +2632,9 @@
       <c r="E90" s="5"/>
       <c r="F90" s="5"/>
       <c r="G90" s="5"/>
-    </row>
-    <row r="91" spans="1:7">
+      <c r="H90" s="5"/>
+    </row>
+    <row r="91" spans="1:8">
       <c r="A91" s="5"/>
       <c r="B91" s="5"/>
       <c r="C91" s="5"/>
@@ -2529,8 +2642,9 @@
       <c r="E91" s="5"/>
       <c r="F91" s="5"/>
       <c r="G91" s="5"/>
-    </row>
-    <row r="92" spans="1:7">
+      <c r="H91" s="5"/>
+    </row>
+    <row r="92" spans="1:8">
       <c r="A92" s="5"/>
       <c r="B92" s="5"/>
       <c r="C92" s="5"/>
@@ -2538,8 +2652,9 @@
       <c r="E92" s="5"/>
       <c r="F92" s="5"/>
       <c r="G92" s="5"/>
-    </row>
-    <row r="93" spans="1:7">
+      <c r="H92" s="5"/>
+    </row>
+    <row r="93" spans="1:8">
       <c r="A93" s="5"/>
       <c r="B93" s="5"/>
       <c r="C93" s="5"/>
@@ -2547,8 +2662,9 @@
       <c r="E93" s="5"/>
       <c r="F93" s="5"/>
       <c r="G93" s="5"/>
-    </row>
-    <row r="94" spans="1:7">
+      <c r="H93" s="5"/>
+    </row>
+    <row r="94" spans="1:8">
       <c r="A94" s="5"/>
       <c r="B94" s="5"/>
       <c r="C94" s="5"/>
@@ -2556,8 +2672,9 @@
       <c r="E94" s="5"/>
       <c r="F94" s="5"/>
       <c r="G94" s="5"/>
-    </row>
-    <row r="95" spans="1:7">
+      <c r="H94" s="5"/>
+    </row>
+    <row r="95" spans="1:8">
       <c r="A95" s="5"/>
       <c r="B95" s="5"/>
       <c r="C95" s="5"/>
@@ -2565,8 +2682,9 @@
       <c r="E95" s="5"/>
       <c r="F95" s="5"/>
       <c r="G95" s="5"/>
-    </row>
-    <row r="96" spans="1:7">
+      <c r="H95" s="5"/>
+    </row>
+    <row r="96" spans="1:8">
       <c r="A96" s="5"/>
       <c r="B96" s="5"/>
       <c r="C96" s="5"/>
@@ -2574,8 +2692,9 @@
       <c r="E96" s="5"/>
       <c r="F96" s="5"/>
       <c r="G96" s="5"/>
-    </row>
-    <row r="97" spans="1:7">
+      <c r="H96" s="5"/>
+    </row>
+    <row r="97" spans="1:8">
       <c r="A97" s="5"/>
       <c r="B97" s="5"/>
       <c r="C97" s="5"/>
@@ -2583,8 +2702,9 @@
       <c r="E97" s="5"/>
       <c r="F97" s="5"/>
       <c r="G97" s="5"/>
-    </row>
-    <row r="98" spans="1:7">
+      <c r="H97" s="5"/>
+    </row>
+    <row r="98" spans="1:8">
       <c r="A98" s="5"/>
       <c r="B98" s="5"/>
       <c r="C98" s="5"/>
@@ -2592,8 +2712,9 @@
       <c r="E98" s="5"/>
       <c r="F98" s="5"/>
       <c r="G98" s="5"/>
-    </row>
-    <row r="99" spans="1:7">
+      <c r="H98" s="5"/>
+    </row>
+    <row r="99" spans="1:8">
       <c r="A99" s="5"/>
       <c r="B99" s="5"/>
       <c r="C99" s="5"/>
@@ -2601,8 +2722,9 @@
       <c r="E99" s="5"/>
       <c r="F99" s="5"/>
       <c r="G99" s="5"/>
-    </row>
-    <row r="100" spans="1:7">
+      <c r="H99" s="5"/>
+    </row>
+    <row r="100" spans="1:8">
       <c r="A100" s="5"/>
       <c r="B100" s="5"/>
       <c r="C100" s="5"/>
@@ -2610,8 +2732,9 @@
       <c r="E100" s="5"/>
       <c r="F100" s="5"/>
       <c r="G100" s="5"/>
-    </row>
-    <row r="101" spans="1:7">
+      <c r="H100" s="5"/>
+    </row>
+    <row r="101" spans="1:8">
       <c r="A101" s="5"/>
       <c r="B101" s="5"/>
       <c r="C101" s="5"/>
@@ -2619,8 +2742,9 @@
       <c r="E101" s="5"/>
       <c r="F101" s="5"/>
       <c r="G101" s="5"/>
-    </row>
-    <row r="102" spans="1:7">
+      <c r="H101" s="5"/>
+    </row>
+    <row r="102" spans="1:8">
       <c r="A102" s="5"/>
       <c r="B102" s="5"/>
       <c r="C102" s="5"/>
@@ -2628,8 +2752,9 @@
       <c r="E102" s="5"/>
       <c r="F102" s="5"/>
       <c r="G102" s="5"/>
-    </row>
-    <row r="103" spans="1:7">
+      <c r="H102" s="5"/>
+    </row>
+    <row r="103" spans="1:8">
       <c r="A103" s="5"/>
       <c r="B103" s="5"/>
       <c r="C103" s="5"/>
@@ -2637,8 +2762,9 @@
       <c r="E103" s="5"/>
       <c r="F103" s="5"/>
       <c r="G103" s="5"/>
-    </row>
-    <row r="104" spans="1:7">
+      <c r="H103" s="5"/>
+    </row>
+    <row r="104" spans="1:8">
       <c r="A104" s="5"/>
       <c r="B104" s="5"/>
       <c r="C104" s="5"/>
@@ -2646,8 +2772,9 @@
       <c r="E104" s="5"/>
       <c r="F104" s="5"/>
       <c r="G104" s="5"/>
-    </row>
-    <row r="105" spans="1:7">
+      <c r="H104" s="5"/>
+    </row>
+    <row r="105" spans="1:8">
       <c r="A105" s="5"/>
       <c r="B105" s="5"/>
       <c r="C105" s="5"/>
@@ -2655,8 +2782,9 @@
       <c r="E105" s="5"/>
       <c r="F105" s="5"/>
       <c r="G105" s="5"/>
-    </row>
-    <row r="106" spans="1:7">
+      <c r="H105" s="5"/>
+    </row>
+    <row r="106" spans="1:8">
       <c r="A106" s="5"/>
       <c r="B106" s="5"/>
       <c r="C106" s="5"/>
@@ -2664,8 +2792,9 @@
       <c r="E106" s="5"/>
       <c r="F106" s="5"/>
       <c r="G106" s="5"/>
-    </row>
-    <row r="107" spans="1:7">
+      <c r="H106" s="5"/>
+    </row>
+    <row r="107" spans="1:8">
       <c r="A107" s="5"/>
       <c r="B107" s="5"/>
       <c r="C107" s="5"/>
@@ -2673,8 +2802,9 @@
       <c r="E107" s="5"/>
       <c r="F107" s="5"/>
       <c r="G107" s="5"/>
-    </row>
-    <row r="108" spans="1:7">
+      <c r="H107" s="5"/>
+    </row>
+    <row r="108" spans="1:8">
       <c r="A108" s="5"/>
       <c r="B108" s="5"/>
       <c r="C108" s="5"/>
@@ -2682,8 +2812,9 @@
       <c r="E108" s="5"/>
       <c r="F108" s="5"/>
       <c r="G108" s="5"/>
-    </row>
-    <row r="109" spans="1:7">
+      <c r="H108" s="5"/>
+    </row>
+    <row r="109" spans="1:8">
       <c r="A109" s="5"/>
       <c r="B109" s="5"/>
       <c r="C109" s="5"/>
@@ -2691,8 +2822,9 @@
       <c r="E109" s="5"/>
       <c r="F109" s="5"/>
       <c r="G109" s="5"/>
-    </row>
-    <row r="110" spans="1:7">
+      <c r="H109" s="5"/>
+    </row>
+    <row r="110" spans="1:8">
       <c r="A110" s="5"/>
       <c r="B110" s="5"/>
       <c r="C110" s="5"/>
@@ -2700,8 +2832,9 @@
       <c r="E110" s="5"/>
       <c r="F110" s="5"/>
       <c r="G110" s="5"/>
-    </row>
-    <row r="111" spans="1:7">
+      <c r="H110" s="5"/>
+    </row>
+    <row r="111" spans="1:8">
       <c r="A111" s="5"/>
       <c r="B111" s="5"/>
       <c r="C111" s="5"/>
@@ -2709,8 +2842,9 @@
       <c r="E111" s="5"/>
       <c r="F111" s="5"/>
       <c r="G111" s="5"/>
-    </row>
-    <row r="112" spans="1:7">
+      <c r="H111" s="5"/>
+    </row>
+    <row r="112" spans="1:8">
       <c r="A112" s="5"/>
       <c r="B112" s="5"/>
       <c r="C112" s="5"/>
@@ -2718,8 +2852,9 @@
       <c r="E112" s="5"/>
       <c r="F112" s="5"/>
       <c r="G112" s="5"/>
-    </row>
-    <row r="113" spans="1:7">
+      <c r="H112" s="5"/>
+    </row>
+    <row r="113" spans="1:8">
       <c r="A113" s="5"/>
       <c r="B113" s="5"/>
       <c r="C113" s="5"/>
@@ -2727,8 +2862,9 @@
       <c r="E113" s="5"/>
       <c r="F113" s="5"/>
       <c r="G113" s="5"/>
-    </row>
-    <row r="114" spans="1:7">
+      <c r="H113" s="5"/>
+    </row>
+    <row r="114" spans="1:8">
       <c r="A114" s="5"/>
       <c r="B114" s="5"/>
       <c r="C114" s="5"/>
@@ -2736,8 +2872,9 @@
       <c r="E114" s="5"/>
       <c r="F114" s="5"/>
       <c r="G114" s="5"/>
-    </row>
-    <row r="115" spans="1:7">
+      <c r="H114" s="5"/>
+    </row>
+    <row r="115" spans="1:8">
       <c r="A115" s="5"/>
       <c r="B115" s="5"/>
       <c r="C115" s="5"/>
@@ -2745,8 +2882,9 @@
       <c r="E115" s="5"/>
       <c r="F115" s="5"/>
       <c r="G115" s="5"/>
-    </row>
-    <row r="116" spans="1:7">
+      <c r="H115" s="5"/>
+    </row>
+    <row r="116" spans="1:8">
       <c r="A116" s="5"/>
       <c r="B116" s="5"/>
       <c r="C116" s="5"/>
@@ -2754,8 +2892,9 @@
       <c r="E116" s="5"/>
       <c r="F116" s="5"/>
       <c r="G116" s="5"/>
-    </row>
-    <row r="117" spans="1:7">
+      <c r="H116" s="5"/>
+    </row>
+    <row r="117" spans="1:8">
       <c r="A117" s="5"/>
       <c r="B117" s="5"/>
       <c r="C117" s="5"/>
@@ -2763,8 +2902,9 @@
       <c r="E117" s="5"/>
       <c r="F117" s="5"/>
       <c r="G117" s="5"/>
-    </row>
-    <row r="118" spans="1:7">
+      <c r="H117" s="5"/>
+    </row>
+    <row r="118" spans="1:8">
       <c r="A118" s="5"/>
       <c r="B118" s="5"/>
       <c r="C118" s="5"/>
@@ -2772,8 +2912,9 @@
       <c r="E118" s="5"/>
       <c r="F118" s="5"/>
       <c r="G118" s="5"/>
-    </row>
-    <row r="119" spans="1:7">
+      <c r="H118" s="5"/>
+    </row>
+    <row r="119" spans="1:8">
       <c r="A119" s="5"/>
       <c r="B119" s="5"/>
       <c r="C119" s="5"/>
@@ -2781,8 +2922,9 @@
       <c r="E119" s="5"/>
       <c r="F119" s="5"/>
       <c r="G119" s="5"/>
-    </row>
-    <row r="120" spans="1:7">
+      <c r="H119" s="5"/>
+    </row>
+    <row r="120" spans="1:8">
       <c r="A120" s="5"/>
       <c r="B120" s="5"/>
       <c r="C120" s="5"/>
@@ -2790,8 +2932,9 @@
       <c r="E120" s="5"/>
       <c r="F120" s="5"/>
       <c r="G120" s="5"/>
-    </row>
-    <row r="121" spans="1:7">
+      <c r="H120" s="5"/>
+    </row>
+    <row r="121" spans="1:8">
       <c r="A121" s="5"/>
       <c r="B121" s="5"/>
       <c r="C121" s="5"/>
@@ -2799,8 +2942,9 @@
       <c r="E121" s="5"/>
       <c r="F121" s="5"/>
       <c r="G121" s="5"/>
-    </row>
-    <row r="122" spans="1:7">
+      <c r="H121" s="5"/>
+    </row>
+    <row r="122" spans="1:8">
       <c r="A122" s="5"/>
       <c r="B122" s="5"/>
       <c r="C122" s="5"/>
@@ -2808,8 +2952,9 @@
       <c r="E122" s="5"/>
       <c r="F122" s="5"/>
       <c r="G122" s="5"/>
-    </row>
-    <row r="123" spans="1:7">
+      <c r="H122" s="5"/>
+    </row>
+    <row r="123" spans="1:8">
       <c r="A123" s="5"/>
       <c r="B123" s="5"/>
       <c r="C123" s="5"/>
@@ -2817,8 +2962,9 @@
       <c r="E123" s="5"/>
       <c r="F123" s="5"/>
       <c r="G123" s="5"/>
-    </row>
-    <row r="124" spans="1:7">
+      <c r="H123" s="5"/>
+    </row>
+    <row r="124" spans="1:8">
       <c r="A124" s="5"/>
       <c r="B124" s="5"/>
       <c r="C124" s="5"/>
@@ -2826,8 +2972,9 @@
       <c r="E124" s="5"/>
       <c r="F124" s="5"/>
       <c r="G124" s="5"/>
-    </row>
-    <row r="125" spans="1:7">
+      <c r="H124" s="5"/>
+    </row>
+    <row r="125" spans="1:8">
       <c r="A125" s="5"/>
       <c r="B125" s="5"/>
       <c r="C125" s="5"/>
@@ -2835,8 +2982,9 @@
       <c r="E125" s="5"/>
       <c r="F125" s="5"/>
       <c r="G125" s="5"/>
-    </row>
-    <row r="126" spans="1:7">
+      <c r="H125" s="5"/>
+    </row>
+    <row r="126" spans="1:8">
       <c r="A126" s="5"/>
       <c r="B126" s="5"/>
       <c r="C126" s="5"/>
@@ -2844,8 +2992,9 @@
       <c r="E126" s="5"/>
       <c r="F126" s="5"/>
       <c r="G126" s="5"/>
-    </row>
-    <row r="127" spans="1:7">
+      <c r="H126" s="5"/>
+    </row>
+    <row r="127" spans="1:8">
       <c r="A127" s="5"/>
       <c r="B127" s="5"/>
       <c r="C127" s="5"/>
@@ -2853,8 +3002,9 @@
       <c r="E127" s="5"/>
       <c r="F127" s="5"/>
       <c r="G127" s="5"/>
-    </row>
-    <row r="128" spans="1:7">
+      <c r="H127" s="5"/>
+    </row>
+    <row r="128" spans="1:8">
       <c r="A128" s="5"/>
       <c r="B128" s="5"/>
       <c r="C128" s="5"/>
@@ -2862,8 +3012,9 @@
       <c r="E128" s="5"/>
       <c r="F128" s="5"/>
       <c r="G128" s="5"/>
-    </row>
-    <row r="129" spans="1:7">
+      <c r="H128" s="5"/>
+    </row>
+    <row r="129" spans="1:8">
       <c r="A129" s="5"/>
       <c r="B129" s="5"/>
       <c r="C129" s="5"/>
@@ -2871,8 +3022,9 @@
       <c r="E129" s="5"/>
       <c r="F129" s="5"/>
       <c r="G129" s="5"/>
-    </row>
-    <row r="130" spans="1:7">
+      <c r="H129" s="5"/>
+    </row>
+    <row r="130" spans="1:8">
       <c r="A130" s="5"/>
       <c r="B130" s="5"/>
       <c r="C130" s="5"/>
@@ -2880,8 +3032,9 @@
       <c r="E130" s="5"/>
       <c r="F130" s="5"/>
       <c r="G130" s="5"/>
-    </row>
-    <row r="131" spans="1:7">
+      <c r="H130" s="5"/>
+    </row>
+    <row r="131" spans="1:8">
       <c r="A131" s="5"/>
       <c r="B131" s="5"/>
       <c r="C131" s="5"/>
@@ -2889,8 +3042,9 @@
       <c r="E131" s="5"/>
       <c r="F131" s="5"/>
       <c r="G131" s="5"/>
-    </row>
-    <row r="132" spans="1:7">
+      <c r="H131" s="5"/>
+    </row>
+    <row r="132" spans="1:8">
       <c r="A132" s="5"/>
       <c r="B132" s="5"/>
       <c r="C132" s="5"/>
@@ -2898,8 +3052,9 @@
       <c r="E132" s="5"/>
       <c r="F132" s="5"/>
       <c r="G132" s="5"/>
-    </row>
-    <row r="133" spans="1:7">
+      <c r="H132" s="5"/>
+    </row>
+    <row r="133" spans="1:8">
       <c r="A133" s="5"/>
       <c r="B133" s="5"/>
       <c r="C133" s="5"/>
@@ -2907,8 +3062,9 @@
       <c r="E133" s="5"/>
       <c r="F133" s="5"/>
       <c r="G133" s="5"/>
-    </row>
-    <row r="134" spans="1:7">
+      <c r="H133" s="5"/>
+    </row>
+    <row r="134" spans="1:8">
       <c r="A134" s="5"/>
       <c r="B134" s="5"/>
       <c r="C134" s="5"/>
@@ -2916,8 +3072,9 @@
       <c r="E134" s="5"/>
       <c r="F134" s="5"/>
       <c r="G134" s="5"/>
-    </row>
-    <row r="135" spans="1:7">
+      <c r="H134" s="5"/>
+    </row>
+    <row r="135" spans="1:8">
       <c r="A135" s="5"/>
       <c r="B135" s="5"/>
       <c r="C135" s="5"/>
@@ -2925,8 +3082,9 @@
       <c r="E135" s="5"/>
       <c r="F135" s="5"/>
       <c r="G135" s="5"/>
-    </row>
-    <row r="136" spans="1:7">
+      <c r="H135" s="5"/>
+    </row>
+    <row r="136" spans="1:8">
       <c r="A136" s="5"/>
       <c r="B136" s="5"/>
       <c r="C136" s="5"/>
@@ -2934,8 +3092,9 @@
       <c r="E136" s="5"/>
       <c r="F136" s="5"/>
       <c r="G136" s="5"/>
-    </row>
-    <row r="137" spans="1:7">
+      <c r="H136" s="5"/>
+    </row>
+    <row r="137" spans="1:8">
       <c r="A137" s="5"/>
       <c r="B137" s="5"/>
       <c r="C137" s="5"/>
@@ -2943,8 +3102,9 @@
       <c r="E137" s="5"/>
       <c r="F137" s="5"/>
       <c r="G137" s="5"/>
-    </row>
-    <row r="138" spans="1:7">
+      <c r="H137" s="5"/>
+    </row>
+    <row r="138" spans="1:8">
       <c r="A138" s="5"/>
       <c r="B138" s="5"/>
       <c r="C138" s="5"/>
@@ -2952,8 +3112,9 @@
       <c r="E138" s="5"/>
       <c r="F138" s="5"/>
       <c r="G138" s="5"/>
-    </row>
-    <row r="139" spans="1:7">
+      <c r="H138" s="5"/>
+    </row>
+    <row r="139" spans="1:8">
       <c r="A139" s="5"/>
       <c r="B139" s="5"/>
       <c r="C139" s="5"/>
@@ -2961,8 +3122,9 @@
       <c r="E139" s="5"/>
       <c r="F139" s="5"/>
       <c r="G139" s="5"/>
-    </row>
-    <row r="140" spans="1:7">
+      <c r="H139" s="5"/>
+    </row>
+    <row r="140" spans="1:8">
       <c r="A140" s="5"/>
       <c r="B140" s="5"/>
       <c r="C140" s="5"/>
@@ -2970,8 +3132,9 @@
       <c r="E140" s="5"/>
       <c r="F140" s="5"/>
       <c r="G140" s="5"/>
-    </row>
-    <row r="141" spans="1:7">
+      <c r="H140" s="5"/>
+    </row>
+    <row r="141" spans="1:8">
       <c r="A141" s="5"/>
       <c r="B141" s="5"/>
       <c r="C141" s="5"/>
@@ -2979,8 +3142,9 @@
       <c r="E141" s="5"/>
       <c r="F141" s="5"/>
       <c r="G141" s="5"/>
-    </row>
-    <row r="142" spans="1:7">
+      <c r="H141" s="5"/>
+    </row>
+    <row r="142" spans="1:8">
       <c r="A142" s="5"/>
       <c r="B142" s="5"/>
       <c r="C142" s="5"/>
@@ -2988,8 +3152,9 @@
       <c r="E142" s="5"/>
       <c r="F142" s="5"/>
       <c r="G142" s="5"/>
-    </row>
-    <row r="143" spans="1:7">
+      <c r="H142" s="5"/>
+    </row>
+    <row r="143" spans="1:8">
       <c r="A143" s="5"/>
       <c r="B143" s="5"/>
       <c r="C143" s="5"/>
@@ -2997,8 +3162,9 @@
       <c r="E143" s="5"/>
       <c r="F143" s="5"/>
       <c r="G143" s="5"/>
-    </row>
-    <row r="144" spans="1:7">
+      <c r="H143" s="5"/>
+    </row>
+    <row r="144" spans="1:8">
       <c r="A144" s="5"/>
       <c r="B144" s="5"/>
       <c r="C144" s="5"/>
@@ -3006,8 +3172,9 @@
       <c r="E144" s="5"/>
       <c r="F144" s="5"/>
       <c r="G144" s="5"/>
-    </row>
-    <row r="145" spans="1:7">
+      <c r="H144" s="5"/>
+    </row>
+    <row r="145" spans="1:8">
       <c r="A145" s="5"/>
       <c r="B145" s="5"/>
       <c r="C145" s="5"/>
@@ -3015,8 +3182,9 @@
       <c r="E145" s="5"/>
       <c r="F145" s="5"/>
       <c r="G145" s="5"/>
-    </row>
-    <row r="146" spans="1:7">
+      <c r="H145" s="5"/>
+    </row>
+    <row r="146" spans="1:8">
       <c r="A146" s="5"/>
       <c r="B146" s="5"/>
       <c r="C146" s="5"/>
@@ -3024,8 +3192,9 @@
       <c r="E146" s="5"/>
       <c r="F146" s="5"/>
       <c r="G146" s="5"/>
-    </row>
-    <row r="147" spans="1:7">
+      <c r="H146" s="5"/>
+    </row>
+    <row r="147" spans="1:8">
       <c r="A147" s="5"/>
       <c r="B147" s="5"/>
       <c r="C147" s="5"/>
@@ -3033,8 +3202,9 @@
       <c r="E147" s="5"/>
       <c r="F147" s="5"/>
       <c r="G147" s="5"/>
-    </row>
-    <row r="148" spans="1:7">
+      <c r="H147" s="5"/>
+    </row>
+    <row r="148" spans="1:8">
       <c r="A148" s="5"/>
       <c r="B148" s="5"/>
       <c r="C148" s="5"/>
@@ -3042,8 +3212,9 @@
       <c r="E148" s="5"/>
       <c r="F148" s="5"/>
       <c r="G148" s="5"/>
-    </row>
-    <row r="149" spans="1:7">
+      <c r="H148" s="5"/>
+    </row>
+    <row r="149" spans="1:8">
       <c r="A149" s="5"/>
       <c r="B149" s="5"/>
       <c r="C149" s="5"/>
@@ -3051,8 +3222,9 @@
       <c r="E149" s="5"/>
       <c r="F149" s="5"/>
       <c r="G149" s="5"/>
-    </row>
-    <row r="150" spans="1:7">
+      <c r="H149" s="5"/>
+    </row>
+    <row r="150" spans="1:8">
       <c r="A150" s="5"/>
       <c r="B150" s="5"/>
       <c r="C150" s="5"/>
@@ -3060,8 +3232,9 @@
       <c r="E150" s="5"/>
       <c r="F150" s="5"/>
       <c r="G150" s="5"/>
-    </row>
-    <row r="151" spans="1:7">
+      <c r="H150" s="5"/>
+    </row>
+    <row r="151" spans="1:8">
       <c r="A151" s="5"/>
       <c r="B151" s="5"/>
       <c r="C151" s="5"/>
@@ -3069,8 +3242,9 @@
       <c r="E151" s="5"/>
       <c r="F151" s="5"/>
       <c r="G151" s="5"/>
-    </row>
-    <row r="152" spans="1:7">
+      <c r="H151" s="5"/>
+    </row>
+    <row r="152" spans="1:8">
       <c r="A152" s="5"/>
       <c r="B152" s="5"/>
       <c r="C152" s="5"/>
@@ -3078,8 +3252,9 @@
       <c r="E152" s="5"/>
       <c r="F152" s="5"/>
       <c r="G152" s="5"/>
-    </row>
-    <row r="153" spans="1:7">
+      <c r="H152" s="5"/>
+    </row>
+    <row r="153" spans="1:8">
       <c r="A153" s="5"/>
       <c r="B153" s="5"/>
       <c r="C153" s="5"/>
@@ -3087,8 +3262,9 @@
       <c r="E153" s="5"/>
       <c r="F153" s="5"/>
       <c r="G153" s="5"/>
-    </row>
-    <row r="154" spans="1:7">
+      <c r="H153" s="5"/>
+    </row>
+    <row r="154" spans="1:8">
       <c r="A154" s="5"/>
       <c r="B154" s="5"/>
       <c r="C154" s="5"/>
@@ -3096,8 +3272,9 @@
       <c r="E154" s="5"/>
       <c r="F154" s="5"/>
       <c r="G154" s="5"/>
-    </row>
-    <row r="155" spans="1:7">
+      <c r="H154" s="5"/>
+    </row>
+    <row r="155" spans="1:8">
       <c r="A155" s="5"/>
       <c r="B155" s="5"/>
       <c r="C155" s="5"/>
@@ -3105,8 +3282,9 @@
       <c r="E155" s="5"/>
       <c r="F155" s="5"/>
       <c r="G155" s="5"/>
-    </row>
-    <row r="156" spans="1:7">
+      <c r="H155" s="5"/>
+    </row>
+    <row r="156" spans="1:8">
       <c r="A156" s="5"/>
       <c r="B156" s="5"/>
       <c r="C156" s="5"/>
@@ -3114,8 +3292,9 @@
       <c r="E156" s="5"/>
       <c r="F156" s="5"/>
       <c r="G156" s="5"/>
-    </row>
-    <row r="157" spans="1:7">
+      <c r="H156" s="5"/>
+    </row>
+    <row r="157" spans="1:8">
       <c r="A157" s="5"/>
       <c r="B157" s="5"/>
       <c r="C157" s="5"/>
@@ -3123,8 +3302,9 @@
       <c r="E157" s="5"/>
       <c r="F157" s="5"/>
       <c r="G157" s="5"/>
-    </row>
-    <row r="158" spans="1:7">
+      <c r="H157" s="5"/>
+    </row>
+    <row r="158" spans="1:8">
       <c r="A158" s="5"/>
       <c r="B158" s="5"/>
       <c r="C158" s="5"/>
@@ -3132,8 +3312,9 @@
       <c r="E158" s="5"/>
       <c r="F158" s="5"/>
       <c r="G158" s="5"/>
-    </row>
-    <row r="159" spans="1:7">
+      <c r="H158" s="5"/>
+    </row>
+    <row r="159" spans="1:8">
       <c r="A159" s="5"/>
       <c r="B159" s="5"/>
       <c r="C159" s="5"/>
@@ -3141,8 +3322,9 @@
       <c r="E159" s="5"/>
       <c r="F159" s="5"/>
       <c r="G159" s="5"/>
-    </row>
-    <row r="160" spans="1:7">
+      <c r="H159" s="5"/>
+    </row>
+    <row r="160" spans="1:8">
       <c r="A160" s="5"/>
       <c r="B160" s="5"/>
       <c r="C160" s="5"/>
@@ -3150,8 +3332,9 @@
       <c r="E160" s="5"/>
       <c r="F160" s="5"/>
       <c r="G160" s="5"/>
-    </row>
-    <row r="161" spans="1:7">
+      <c r="H160" s="5"/>
+    </row>
+    <row r="161" spans="1:8">
       <c r="A161" s="5"/>
       <c r="B161" s="5"/>
       <c r="C161" s="5"/>
@@ -3159,8 +3342,9 @@
       <c r="E161" s="5"/>
       <c r="F161" s="5"/>
       <c r="G161" s="5"/>
-    </row>
-    <row r="162" spans="1:7">
+      <c r="H161" s="5"/>
+    </row>
+    <row r="162" spans="1:8">
       <c r="A162" s="5"/>
       <c r="B162" s="5"/>
       <c r="C162" s="5"/>
@@ -3168,8 +3352,9 @@
       <c r="E162" s="5"/>
       <c r="F162" s="5"/>
       <c r="G162" s="5"/>
-    </row>
-    <row r="163" spans="1:7">
+      <c r="H162" s="5"/>
+    </row>
+    <row r="163" spans="1:8">
       <c r="A163" s="5"/>
       <c r="B163" s="5"/>
       <c r="C163" s="5"/>
@@ -3177,8 +3362,9 @@
       <c r="E163" s="5"/>
       <c r="F163" s="5"/>
       <c r="G163" s="5"/>
-    </row>
-    <row r="164" spans="1:7">
+      <c r="H163" s="5"/>
+    </row>
+    <row r="164" spans="1:8">
       <c r="A164" s="5"/>
       <c r="B164" s="5"/>
       <c r="C164" s="5"/>
@@ -3186,8 +3372,9 @@
       <c r="E164" s="5"/>
       <c r="F164" s="5"/>
       <c r="G164" s="5"/>
-    </row>
-    <row r="165" spans="1:7">
+      <c r="H164" s="5"/>
+    </row>
+    <row r="165" spans="1:8">
       <c r="A165" s="5"/>
       <c r="B165" s="5"/>
       <c r="C165" s="5"/>
@@ -3195,8 +3382,9 @@
       <c r="E165" s="5"/>
       <c r="F165" s="5"/>
       <c r="G165" s="5"/>
-    </row>
-    <row r="166" spans="1:7">
+      <c r="H165" s="5"/>
+    </row>
+    <row r="166" spans="1:8">
       <c r="A166" s="5"/>
       <c r="B166" s="5"/>
       <c r="C166" s="5"/>
@@ -3204,8 +3392,9 @@
       <c r="E166" s="5"/>
       <c r="F166" s="5"/>
       <c r="G166" s="5"/>
-    </row>
-    <row r="167" spans="1:7">
+      <c r="H166" s="5"/>
+    </row>
+    <row r="167" spans="1:8">
       <c r="A167" s="5"/>
       <c r="B167" s="5"/>
       <c r="C167" s="5"/>
@@ -3213,8 +3402,9 @@
       <c r="E167" s="5"/>
       <c r="F167" s="5"/>
       <c r="G167" s="5"/>
-    </row>
-    <row r="168" spans="1:7">
+      <c r="H167" s="5"/>
+    </row>
+    <row r="168" spans="1:8">
       <c r="A168" s="5"/>
       <c r="B168" s="5"/>
       <c r="C168" s="5"/>
@@ -3222,8 +3412,9 @@
       <c r="E168" s="5"/>
       <c r="F168" s="5"/>
       <c r="G168" s="5"/>
-    </row>
-    <row r="169" spans="1:7">
+      <c r="H168" s="5"/>
+    </row>
+    <row r="169" spans="1:8">
       <c r="A169" s="5"/>
       <c r="B169" s="5"/>
       <c r="C169" s="5"/>
@@ -3231,8 +3422,9 @@
       <c r="E169" s="5"/>
       <c r="F169" s="5"/>
       <c r="G169" s="5"/>
-    </row>
-    <row r="170" spans="1:7">
+      <c r="H169" s="5"/>
+    </row>
+    <row r="170" spans="1:8">
       <c r="A170" s="5"/>
       <c r="B170" s="5"/>
       <c r="C170" s="5"/>
@@ -3240,8 +3432,9 @@
       <c r="E170" s="5"/>
       <c r="F170" s="5"/>
       <c r="G170" s="5"/>
-    </row>
-    <row r="171" spans="1:7">
+      <c r="H170" s="5"/>
+    </row>
+    <row r="171" spans="1:8">
       <c r="A171" s="5"/>
       <c r="B171" s="5"/>
       <c r="C171" s="5"/>
@@ -3249,8 +3442,9 @@
       <c r="E171" s="5"/>
       <c r="F171" s="5"/>
       <c r="G171" s="5"/>
-    </row>
-    <row r="172" spans="1:7">
+      <c r="H171" s="5"/>
+    </row>
+    <row r="172" spans="1:8">
       <c r="A172" s="5"/>
       <c r="B172" s="5"/>
       <c r="C172" s="5"/>
@@ -3258,8 +3452,9 @@
       <c r="E172" s="5"/>
       <c r="F172" s="5"/>
       <c r="G172" s="5"/>
-    </row>
-    <row r="173" spans="1:7">
+      <c r="H172" s="5"/>
+    </row>
+    <row r="173" spans="1:8">
       <c r="A173" s="5"/>
       <c r="B173" s="5"/>
       <c r="C173" s="5"/>
@@ -3267,8 +3462,9 @@
       <c r="E173" s="5"/>
       <c r="F173" s="5"/>
       <c r="G173" s="5"/>
-    </row>
-    <row r="174" spans="1:7">
+      <c r="H173" s="5"/>
+    </row>
+    <row r="174" spans="1:8">
       <c r="A174" s="5"/>
       <c r="B174" s="5"/>
       <c r="C174" s="5"/>
@@ -3276,8 +3472,9 @@
       <c r="E174" s="5"/>
       <c r="F174" s="5"/>
       <c r="G174" s="5"/>
-    </row>
-    <row r="175" spans="1:7">
+      <c r="H174" s="5"/>
+    </row>
+    <row r="175" spans="1:8">
       <c r="A175" s="5"/>
       <c r="B175" s="5"/>
       <c r="C175" s="5"/>
@@ -3285,8 +3482,9 @@
       <c r="E175" s="5"/>
       <c r="F175" s="5"/>
       <c r="G175" s="5"/>
-    </row>
-    <row r="176" spans="1:7">
+      <c r="H175" s="5"/>
+    </row>
+    <row r="176" spans="1:8">
       <c r="A176" s="5"/>
       <c r="B176" s="5"/>
       <c r="C176" s="5"/>
@@ -3294,8 +3492,9 @@
       <c r="E176" s="5"/>
       <c r="F176" s="5"/>
       <c r="G176" s="5"/>
-    </row>
-    <row r="177" spans="1:7">
+      <c r="H176" s="5"/>
+    </row>
+    <row r="177" spans="1:8">
       <c r="A177" s="5"/>
       <c r="B177" s="5"/>
       <c r="C177" s="5"/>
@@ -3303,8 +3502,9 @@
       <c r="E177" s="5"/>
       <c r="F177" s="5"/>
       <c r="G177" s="5"/>
-    </row>
-    <row r="178" spans="1:7">
+      <c r="H177" s="5"/>
+    </row>
+    <row r="178" spans="1:8">
       <c r="A178" s="5"/>
       <c r="B178" s="5"/>
       <c r="C178" s="5"/>
@@ -3312,8 +3512,9 @@
       <c r="E178" s="5"/>
       <c r="F178" s="5"/>
       <c r="G178" s="5"/>
-    </row>
-    <row r="179" spans="1:7">
+      <c r="H178" s="5"/>
+    </row>
+    <row r="179" spans="1:8">
       <c r="A179" s="5"/>
       <c r="B179" s="5"/>
       <c r="C179" s="5"/>
@@ -3321,8 +3522,9 @@
       <c r="E179" s="5"/>
       <c r="F179" s="5"/>
       <c r="G179" s="5"/>
-    </row>
-    <row r="180" spans="1:7">
+      <c r="H179" s="5"/>
+    </row>
+    <row r="180" spans="1:8">
       <c r="A180" s="5"/>
       <c r="B180" s="5"/>
       <c r="C180" s="5"/>
@@ -3330,8 +3532,9 @@
       <c r="E180" s="5"/>
       <c r="F180" s="5"/>
       <c r="G180" s="5"/>
-    </row>
-    <row r="181" spans="1:7">
+      <c r="H180" s="5"/>
+    </row>
+    <row r="181" spans="1:8">
       <c r="A181" s="5"/>
       <c r="B181" s="5"/>
       <c r="C181" s="5"/>
@@ -3339,8 +3542,9 @@
       <c r="E181" s="5"/>
       <c r="F181" s="5"/>
       <c r="G181" s="5"/>
-    </row>
-    <row r="182" spans="1:7">
+      <c r="H181" s="5"/>
+    </row>
+    <row r="182" spans="1:8">
       <c r="A182" s="5"/>
       <c r="B182" s="5"/>
       <c r="C182" s="5"/>
@@ -3348,8 +3552,9 @@
       <c r="E182" s="5"/>
       <c r="F182" s="5"/>
       <c r="G182" s="5"/>
-    </row>
-    <row r="183" spans="1:7">
+      <c r="H182" s="5"/>
+    </row>
+    <row r="183" spans="1:8">
       <c r="A183" s="5"/>
       <c r="B183" s="5"/>
       <c r="C183" s="5"/>
@@ -3357,8 +3562,9 @@
       <c r="E183" s="5"/>
       <c r="F183" s="5"/>
       <c r="G183" s="5"/>
-    </row>
-    <row r="184" spans="1:7">
+      <c r="H183" s="5"/>
+    </row>
+    <row r="184" spans="1:8">
       <c r="A184" s="5"/>
       <c r="B184" s="5"/>
       <c r="C184" s="5"/>
@@ -3366,8 +3572,9 @@
       <c r="E184" s="5"/>
       <c r="F184" s="5"/>
       <c r="G184" s="5"/>
-    </row>
-    <row r="185" spans="1:7">
+      <c r="H184" s="5"/>
+    </row>
+    <row r="185" spans="1:8">
       <c r="A185" s="5"/>
       <c r="B185" s="5"/>
       <c r="C185" s="5"/>
@@ -3375,8 +3582,9 @@
       <c r="E185" s="5"/>
       <c r="F185" s="5"/>
       <c r="G185" s="5"/>
-    </row>
-    <row r="186" spans="1:7">
+      <c r="H185" s="5"/>
+    </row>
+    <row r="186" spans="1:8">
       <c r="A186" s="5"/>
       <c r="B186" s="5"/>
       <c r="C186" s="5"/>
@@ -3384,8 +3592,9 @@
       <c r="E186" s="5"/>
       <c r="F186" s="5"/>
       <c r="G186" s="5"/>
-    </row>
-    <row r="187" spans="1:7">
+      <c r="H186" s="5"/>
+    </row>
+    <row r="187" spans="1:8">
       <c r="A187" s="5"/>
       <c r="B187" s="5"/>
       <c r="C187" s="5"/>
@@ -3393,8 +3602,9 @@
       <c r="E187" s="5"/>
       <c r="F187" s="5"/>
       <c r="G187" s="5"/>
-    </row>
-    <row r="188" spans="1:7">
+      <c r="H187" s="5"/>
+    </row>
+    <row r="188" spans="1:8">
       <c r="A188" s="5"/>
       <c r="B188" s="5"/>
       <c r="C188" s="5"/>
@@ -3402,8 +3612,9 @@
       <c r="E188" s="5"/>
       <c r="F188" s="5"/>
       <c r="G188" s="5"/>
-    </row>
-    <row r="189" spans="1:7">
+      <c r="H188" s="5"/>
+    </row>
+    <row r="189" spans="1:8">
       <c r="A189" s="5"/>
       <c r="B189" s="5"/>
       <c r="C189" s="5"/>
@@ -3411,8 +3622,9 @@
       <c r="E189" s="5"/>
       <c r="F189" s="5"/>
       <c r="G189" s="5"/>
-    </row>
-    <row r="190" spans="1:7">
+      <c r="H189" s="5"/>
+    </row>
+    <row r="190" spans="1:8">
       <c r="A190" s="5"/>
       <c r="B190" s="5"/>
       <c r="C190" s="5"/>
@@ -3420,8 +3632,9 @@
       <c r="E190" s="5"/>
       <c r="F190" s="5"/>
       <c r="G190" s="5"/>
-    </row>
-    <row r="191" spans="1:7">
+      <c r="H190" s="5"/>
+    </row>
+    <row r="191" spans="1:8">
       <c r="A191" s="5"/>
       <c r="B191" s="5"/>
       <c r="C191" s="5"/>
@@ -3429,8 +3642,9 @@
       <c r="E191" s="5"/>
       <c r="F191" s="5"/>
       <c r="G191" s="5"/>
-    </row>
-    <row r="192" spans="1:7">
+      <c r="H191" s="5"/>
+    </row>
+    <row r="192" spans="1:8">
       <c r="A192" s="5"/>
       <c r="B192" s="5"/>
       <c r="C192" s="5"/>
@@ -3438,8 +3652,9 @@
       <c r="E192" s="5"/>
       <c r="F192" s="5"/>
       <c r="G192" s="5"/>
-    </row>
-    <row r="193" spans="1:7">
+      <c r="H192" s="5"/>
+    </row>
+    <row r="193" spans="1:8">
       <c r="A193" s="5"/>
       <c r="B193" s="5"/>
       <c r="C193" s="5"/>
@@ -3447,8 +3662,9 @@
       <c r="E193" s="5"/>
       <c r="F193" s="5"/>
       <c r="G193" s="5"/>
-    </row>
-    <row r="194" spans="1:7">
+      <c r="H193" s="5"/>
+    </row>
+    <row r="194" spans="1:8">
       <c r="A194" s="5"/>
       <c r="B194" s="5"/>
       <c r="C194" s="5"/>
@@ -3456,8 +3672,9 @@
       <c r="E194" s="5"/>
       <c r="F194" s="5"/>
       <c r="G194" s="5"/>
-    </row>
-    <row r="195" spans="1:7">
+      <c r="H194" s="5"/>
+    </row>
+    <row r="195" spans="1:8">
       <c r="A195" s="5"/>
       <c r="B195" s="5"/>
       <c r="C195" s="5"/>
@@ -3465,8 +3682,9 @@
       <c r="E195" s="5"/>
       <c r="F195" s="5"/>
       <c r="G195" s="5"/>
-    </row>
-    <row r="196" spans="1:7">
+      <c r="H195" s="5"/>
+    </row>
+    <row r="196" spans="1:8">
       <c r="A196" s="5"/>
       <c r="B196" s="5"/>
       <c r="C196" s="5"/>
@@ -3474,8 +3692,9 @@
       <c r="E196" s="5"/>
       <c r="F196" s="5"/>
       <c r="G196" s="5"/>
-    </row>
-    <row r="197" spans="1:7">
+      <c r="H196" s="5"/>
+    </row>
+    <row r="197" spans="1:8">
       <c r="A197" s="5"/>
       <c r="B197" s="5"/>
       <c r="C197" s="5"/>
@@ -3483,8 +3702,9 @@
       <c r="E197" s="5"/>
       <c r="F197" s="5"/>
       <c r="G197" s="5"/>
-    </row>
-    <row r="198" spans="1:7">
+      <c r="H197" s="5"/>
+    </row>
+    <row r="198" spans="1:8">
       <c r="A198" s="5"/>
       <c r="B198" s="5"/>
       <c r="C198" s="5"/>
@@ -3492,8 +3712,9 @@
       <c r="E198" s="5"/>
       <c r="F198" s="5"/>
       <c r="G198" s="5"/>
-    </row>
-    <row r="199" spans="1:7">
+      <c r="H198" s="5"/>
+    </row>
+    <row r="199" spans="1:8">
       <c r="A199" s="5"/>
       <c r="B199" s="5"/>
       <c r="C199" s="5"/>
@@ -3501,8 +3722,9 @@
       <c r="E199" s="5"/>
       <c r="F199" s="5"/>
       <c r="G199" s="5"/>
-    </row>
-    <row r="200" spans="1:7">
+      <c r="H199" s="5"/>
+    </row>
+    <row r="200" spans="1:8">
       <c r="A200" s="5"/>
       <c r="B200" s="5"/>
       <c r="C200" s="5"/>
@@ -3510,8 +3732,9 @@
       <c r="E200" s="5"/>
       <c r="F200" s="5"/>
       <c r="G200" s="5"/>
-    </row>
-    <row r="201" spans="1:7">
+      <c r="H200" s="5"/>
+    </row>
+    <row r="201" spans="1:8">
       <c r="A201" s="5"/>
       <c r="B201" s="5"/>
       <c r="C201" s="5"/>
@@ -3519,8 +3742,9 @@
       <c r="E201" s="5"/>
       <c r="F201" s="5"/>
       <c r="G201" s="5"/>
-    </row>
-    <row r="202" spans="1:7">
+      <c r="H201" s="5"/>
+    </row>
+    <row r="202" spans="1:8">
       <c r="A202" s="5"/>
       <c r="B202" s="5"/>
       <c r="C202" s="5"/>
@@ -3528,8 +3752,9 @@
       <c r="E202" s="5"/>
       <c r="F202" s="5"/>
       <c r="G202" s="5"/>
-    </row>
-    <row r="203" spans="1:7">
+      <c r="H202" s="5"/>
+    </row>
+    <row r="203" spans="1:8">
       <c r="A203" s="5"/>
       <c r="B203" s="5"/>
       <c r="C203" s="5"/>
@@ -3537,8 +3762,9 @@
       <c r="E203" s="5"/>
       <c r="F203" s="5"/>
       <c r="G203" s="5"/>
-    </row>
-    <row r="204" spans="1:7">
+      <c r="H203" s="5"/>
+    </row>
+    <row r="204" spans="1:8">
       <c r="A204" s="5"/>
       <c r="B204" s="5"/>
       <c r="C204" s="5"/>
@@ -3546,8 +3772,9 @@
       <c r="E204" s="5"/>
       <c r="F204" s="5"/>
       <c r="G204" s="5"/>
-    </row>
-    <row r="205" spans="1:7">
+      <c r="H204" s="5"/>
+    </row>
+    <row r="205" spans="1:8">
       <c r="A205" s="5"/>
       <c r="B205" s="5"/>
       <c r="C205" s="5"/>
@@ -3555,8 +3782,9 @@
       <c r="E205" s="5"/>
       <c r="F205" s="5"/>
       <c r="G205" s="5"/>
-    </row>
-    <row r="206" spans="1:7">
+      <c r="H205" s="5"/>
+    </row>
+    <row r="206" spans="1:8">
       <c r="A206" s="5"/>
       <c r="B206" s="5"/>
       <c r="C206" s="5"/>
@@ -3564,8 +3792,9 @@
       <c r="E206" s="5"/>
       <c r="F206" s="5"/>
       <c r="G206" s="5"/>
-    </row>
-    <row r="207" spans="1:7">
+      <c r="H206" s="5"/>
+    </row>
+    <row r="207" spans="1:8">
       <c r="A207" s="5"/>
       <c r="B207" s="5"/>
       <c r="C207" s="5"/>
@@ -3573,8 +3802,9 @@
       <c r="E207" s="5"/>
       <c r="F207" s="5"/>
       <c r="G207" s="5"/>
-    </row>
-    <row r="208" spans="1:7">
+      <c r="H207" s="5"/>
+    </row>
+    <row r="208" spans="1:8">
       <c r="A208" s="5"/>
       <c r="B208" s="5"/>
       <c r="C208" s="5"/>
@@ -3582,8 +3812,9 @@
       <c r="E208" s="5"/>
       <c r="F208" s="5"/>
       <c r="G208" s="5"/>
-    </row>
-    <row r="209" spans="1:7">
+      <c r="H208" s="5"/>
+    </row>
+    <row r="209" spans="1:8">
       <c r="A209" s="5"/>
       <c r="B209" s="5"/>
       <c r="C209" s="5"/>
@@ -3591,8 +3822,9 @@
       <c r="E209" s="5"/>
       <c r="F209" s="5"/>
       <c r="G209" s="5"/>
-    </row>
-    <row r="210" spans="1:7">
+      <c r="H209" s="5"/>
+    </row>
+    <row r="210" spans="1:8">
       <c r="A210" s="5"/>
       <c r="B210" s="5"/>
       <c r="C210" s="5"/>
@@ -3600,8 +3832,9 @@
       <c r="E210" s="5"/>
       <c r="F210" s="5"/>
       <c r="G210" s="5"/>
-    </row>
-    <row r="211" spans="1:7">
+      <c r="H210" s="5"/>
+    </row>
+    <row r="211" spans="1:8">
       <c r="A211" s="5"/>
       <c r="B211" s="5"/>
       <c r="C211" s="5"/>
@@ -3609,8 +3842,9 @@
       <c r="E211" s="5"/>
       <c r="F211" s="5"/>
       <c r="G211" s="5"/>
-    </row>
-    <row r="212" spans="1:7">
+      <c r="H211" s="5"/>
+    </row>
+    <row r="212" spans="1:8">
       <c r="A212" s="5"/>
       <c r="B212" s="5"/>
       <c r="C212" s="5"/>
@@ -3618,8 +3852,9 @@
       <c r="E212" s="5"/>
       <c r="F212" s="5"/>
       <c r="G212" s="5"/>
-    </row>
-    <row r="213" spans="1:7">
+      <c r="H212" s="5"/>
+    </row>
+    <row r="213" spans="1:8">
       <c r="A213" s="5"/>
       <c r="B213" s="5"/>
       <c r="C213" s="5"/>
@@ -3627,8 +3862,9 @@
       <c r="E213" s="5"/>
       <c r="F213" s="5"/>
       <c r="G213" s="5"/>
-    </row>
-    <row r="214" spans="1:7">
+      <c r="H213" s="5"/>
+    </row>
+    <row r="214" spans="1:8">
       <c r="A214" s="5"/>
       <c r="B214" s="5"/>
       <c r="C214" s="5"/>
@@ -3636,8 +3872,9 @@
       <c r="E214" s="5"/>
       <c r="F214" s="5"/>
       <c r="G214" s="5"/>
-    </row>
-    <row r="215" spans="1:7">
+      <c r="H214" s="5"/>
+    </row>
+    <row r="215" spans="1:8">
       <c r="A215" s="5"/>
       <c r="B215" s="5"/>
       <c r="C215" s="5"/>
@@ -3645,8 +3882,9 @@
       <c r="E215" s="5"/>
       <c r="F215" s="5"/>
       <c r="G215" s="5"/>
-    </row>
-    <row r="216" spans="1:7">
+      <c r="H215" s="5"/>
+    </row>
+    <row r="216" spans="1:8">
       <c r="A216" s="5"/>
       <c r="B216" s="5"/>
       <c r="C216" s="5"/>
@@ -3654,8 +3892,9 @@
       <c r="E216" s="5"/>
       <c r="F216" s="5"/>
       <c r="G216" s="5"/>
-    </row>
-    <row r="217" spans="1:7">
+      <c r="H216" s="5"/>
+    </row>
+    <row r="217" spans="1:8">
       <c r="A217" s="5"/>
       <c r="B217" s="5"/>
       <c r="C217" s="5"/>
@@ -3663,8 +3902,9 @@
       <c r="E217" s="5"/>
       <c r="F217" s="5"/>
       <c r="G217" s="5"/>
-    </row>
-    <row r="218" spans="1:7">
+      <c r="H217" s="5"/>
+    </row>
+    <row r="218" spans="1:8">
       <c r="A218" s="5"/>
       <c r="B218" s="5"/>
       <c r="C218" s="5"/>
@@ -3672,8 +3912,9 @@
       <c r="E218" s="5"/>
       <c r="F218" s="5"/>
       <c r="G218" s="5"/>
-    </row>
-    <row r="219" spans="1:7">
+      <c r="H218" s="5"/>
+    </row>
+    <row r="219" spans="1:8">
       <c r="A219" s="5"/>
       <c r="B219" s="5"/>
       <c r="C219" s="5"/>
@@ -3681,8 +3922,9 @@
       <c r="E219" s="5"/>
       <c r="F219" s="5"/>
       <c r="G219" s="5"/>
-    </row>
-    <row r="220" spans="1:7">
+      <c r="H219" s="5"/>
+    </row>
+    <row r="220" spans="1:8">
       <c r="A220" s="5"/>
       <c r="B220" s="5"/>
       <c r="C220" s="5"/>
@@ -3690,8 +3932,9 @@
       <c r="E220" s="5"/>
       <c r="F220" s="5"/>
       <c r="G220" s="5"/>
-    </row>
-    <row r="221" spans="1:7">
+      <c r="H220" s="5"/>
+    </row>
+    <row r="221" spans="1:8">
       <c r="A221" s="5"/>
       <c r="B221" s="5"/>
       <c r="C221" s="5"/>
@@ -3699,8 +3942,9 @@
       <c r="E221" s="5"/>
       <c r="F221" s="5"/>
       <c r="G221" s="5"/>
-    </row>
-    <row r="222" spans="1:7">
+      <c r="H221" s="5"/>
+    </row>
+    <row r="222" spans="1:8">
       <c r="A222" s="5"/>
       <c r="B222" s="5"/>
       <c r="C222" s="5"/>
@@ -3708,8 +3952,9 @@
       <c r="E222" s="5"/>
       <c r="F222" s="5"/>
       <c r="G222" s="5"/>
-    </row>
-    <row r="223" spans="1:7">
+      <c r="H222" s="5"/>
+    </row>
+    <row r="223" spans="1:8">
       <c r="A223" s="5"/>
       <c r="B223" s="5"/>
       <c r="C223" s="5"/>
@@ -3717,8 +3962,9 @@
       <c r="E223" s="5"/>
       <c r="F223" s="5"/>
       <c r="G223" s="5"/>
-    </row>
-    <row r="224" spans="1:7">
+      <c r="H223" s="5"/>
+    </row>
+    <row r="224" spans="1:8">
       <c r="A224" s="5"/>
       <c r="B224" s="5"/>
       <c r="C224" s="5"/>
@@ -3726,8 +3972,9 @@
       <c r="E224" s="5"/>
       <c r="F224" s="5"/>
       <c r="G224" s="5"/>
-    </row>
-    <row r="225" spans="1:7">
+      <c r="H224" s="5"/>
+    </row>
+    <row r="225" spans="1:8">
       <c r="A225" s="5"/>
       <c r="B225" s="5"/>
       <c r="C225" s="5"/>
@@ -3735,8 +3982,9 @@
       <c r="E225" s="5"/>
       <c r="F225" s="5"/>
       <c r="G225" s="5"/>
-    </row>
-    <row r="226" spans="1:7">
+      <c r="H225" s="5"/>
+    </row>
+    <row r="226" spans="1:8">
       <c r="A226" s="5"/>
       <c r="B226" s="5"/>
       <c r="C226" s="5"/>
@@ -3744,8 +3992,9 @@
       <c r="E226" s="5"/>
       <c r="F226" s="5"/>
       <c r="G226" s="5"/>
-    </row>
-    <row r="227" spans="1:7">
+      <c r="H226" s="5"/>
+    </row>
+    <row r="227" spans="1:8">
       <c r="A227" s="5"/>
       <c r="B227" s="5"/>
       <c r="C227" s="5"/>
@@ -3753,8 +4002,9 @@
       <c r="E227" s="5"/>
       <c r="F227" s="5"/>
       <c r="G227" s="5"/>
-    </row>
-    <row r="228" spans="1:7">
+      <c r="H227" s="5"/>
+    </row>
+    <row r="228" spans="1:8">
       <c r="A228" s="5"/>
       <c r="B228" s="5"/>
       <c r="C228" s="5"/>
@@ -3762,8 +4012,9 @@
       <c r="E228" s="5"/>
       <c r="F228" s="5"/>
       <c r="G228" s="5"/>
-    </row>
-    <row r="229" spans="1:7">
+      <c r="H228" s="5"/>
+    </row>
+    <row r="229" spans="1:8">
       <c r="A229" s="5"/>
       <c r="B229" s="5"/>
       <c r="C229" s="5"/>
@@ -3771,8 +4022,9 @@
       <c r="E229" s="5"/>
       <c r="F229" s="5"/>
       <c r="G229" s="5"/>
-    </row>
-    <row r="230" spans="1:7">
+      <c r="H229" s="5"/>
+    </row>
+    <row r="230" spans="1:8">
       <c r="A230" s="5"/>
       <c r="B230" s="5"/>
       <c r="C230" s="5"/>
@@ -3780,8 +4032,9 @@
       <c r="E230" s="5"/>
       <c r="F230" s="5"/>
       <c r="G230" s="5"/>
-    </row>
-    <row r="231" spans="1:7">
+      <c r="H230" s="5"/>
+    </row>
+    <row r="231" spans="1:8">
       <c r="A231" s="5"/>
       <c r="B231" s="5"/>
       <c r="C231" s="5"/>
@@ -3789,8 +4042,9 @@
       <c r="E231" s="5"/>
       <c r="F231" s="5"/>
       <c r="G231" s="5"/>
-    </row>
-    <row r="232" spans="1:7">
+      <c r="H231" s="5"/>
+    </row>
+    <row r="232" spans="1:8">
       <c r="A232" s="5"/>
       <c r="B232" s="5"/>
       <c r="C232" s="5"/>
@@ -3798,8 +4052,9 @@
       <c r="E232" s="5"/>
       <c r="F232" s="5"/>
       <c r="G232" s="5"/>
-    </row>
-    <row r="233" spans="1:7">
+      <c r="H232" s="5"/>
+    </row>
+    <row r="233" spans="1:8">
       <c r="A233" s="5"/>
       <c r="B233" s="5"/>
       <c r="C233" s="5"/>
@@ -3807,8 +4062,9 @@
       <c r="E233" s="5"/>
       <c r="F233" s="5"/>
       <c r="G233" s="5"/>
-    </row>
-    <row r="234" spans="1:7">
+      <c r="H233" s="5"/>
+    </row>
+    <row r="234" spans="1:8">
       <c r="A234" s="5"/>
       <c r="B234" s="5"/>
       <c r="C234" s="5"/>
@@ -3816,8 +4072,9 @@
       <c r="E234" s="5"/>
       <c r="F234" s="5"/>
       <c r="G234" s="5"/>
-    </row>
-    <row r="235" spans="1:7">
+      <c r="H234" s="5"/>
+    </row>
+    <row r="235" spans="1:8">
       <c r="A235" s="5"/>
       <c r="B235" s="5"/>
       <c r="C235" s="5"/>
@@ -3825,8 +4082,9 @@
       <c r="E235" s="5"/>
       <c r="F235" s="5"/>
       <c r="G235" s="5"/>
-    </row>
-    <row r="236" spans="1:7">
+      <c r="H235" s="5"/>
+    </row>
+    <row r="236" spans="1:8">
       <c r="A236" s="5"/>
       <c r="B236" s="5"/>
       <c r="C236" s="5"/>
@@ -3834,8 +4092,9 @@
       <c r="E236" s="5"/>
       <c r="F236" s="5"/>
       <c r="G236" s="5"/>
-    </row>
-    <row r="237" spans="1:7">
+      <c r="H236" s="5"/>
+    </row>
+    <row r="237" spans="1:8">
       <c r="A237" s="5"/>
       <c r="B237" s="5"/>
       <c r="C237" s="5"/>
@@ -3843,8 +4102,9 @@
       <c r="E237" s="5"/>
       <c r="F237" s="5"/>
       <c r="G237" s="5"/>
-    </row>
-    <row r="238" spans="1:7">
+      <c r="H237" s="5"/>
+    </row>
+    <row r="238" spans="1:8">
       <c r="A238" s="5"/>
       <c r="B238" s="5"/>
       <c r="C238" s="5"/>
@@ -3852,8 +4112,9 @@
       <c r="E238" s="5"/>
       <c r="F238" s="5"/>
       <c r="G238" s="5"/>
-    </row>
-    <row r="239" spans="1:7">
+      <c r="H238" s="5"/>
+    </row>
+    <row r="239" spans="1:8">
       <c r="A239" s="5"/>
       <c r="B239" s="5"/>
       <c r="C239" s="5"/>
@@ -3861,8 +4122,9 @@
       <c r="E239" s="5"/>
       <c r="F239" s="5"/>
       <c r="G239" s="5"/>
-    </row>
-    <row r="240" spans="1:7">
+      <c r="H239" s="5"/>
+    </row>
+    <row r="240" spans="1:8">
       <c r="A240" s="5"/>
       <c r="B240" s="5"/>
       <c r="C240" s="5"/>
@@ -3870,8 +4132,9 @@
       <c r="E240" s="5"/>
       <c r="F240" s="5"/>
       <c r="G240" s="5"/>
-    </row>
-    <row r="241" spans="1:7">
+      <c r="H240" s="5"/>
+    </row>
+    <row r="241" spans="1:8">
       <c r="A241" s="5"/>
       <c r="B241" s="5"/>
       <c r="C241" s="5"/>
@@ -3879,8 +4142,9 @@
       <c r="E241" s="5"/>
       <c r="F241" s="5"/>
       <c r="G241" s="5"/>
-    </row>
-    <row r="242" spans="1:7">
+      <c r="H241" s="5"/>
+    </row>
+    <row r="242" spans="1:8">
       <c r="A242" s="5"/>
       <c r="B242" s="5"/>
       <c r="C242" s="5"/>
@@ -3888,8 +4152,9 @@
       <c r="E242" s="5"/>
       <c r="F242" s="5"/>
       <c r="G242" s="5"/>
-    </row>
-    <row r="243" spans="1:7">
+      <c r="H242" s="5"/>
+    </row>
+    <row r="243" spans="1:8">
       <c r="A243" s="5"/>
       <c r="B243" s="5"/>
       <c r="C243" s="5"/>
@@ -3897,8 +4162,9 @@
       <c r="E243" s="5"/>
       <c r="F243" s="5"/>
       <c r="G243" s="5"/>
-    </row>
-    <row r="244" spans="1:7">
+      <c r="H243" s="5"/>
+    </row>
+    <row r="244" spans="1:8">
       <c r="A244" s="5"/>
       <c r="B244" s="5"/>
       <c r="C244" s="5"/>
@@ -3906,8 +4172,9 @@
       <c r="E244" s="5"/>
       <c r="F244" s="5"/>
       <c r="G244" s="5"/>
-    </row>
-    <row r="245" spans="1:7">
+      <c r="H244" s="5"/>
+    </row>
+    <row r="245" spans="1:8">
       <c r="A245" s="5"/>
       <c r="B245" s="5"/>
       <c r="C245" s="5"/>
@@ -3915,8 +4182,9 @@
       <c r="E245" s="5"/>
       <c r="F245" s="5"/>
       <c r="G245" s="5"/>
-    </row>
-    <row r="246" spans="1:7">
+      <c r="H245" s="5"/>
+    </row>
+    <row r="246" spans="1:8">
       <c r="A246" s="5"/>
       <c r="B246" s="5"/>
       <c r="C246" s="5"/>
@@ -3924,8 +4192,9 @@
       <c r="E246" s="5"/>
       <c r="F246" s="5"/>
       <c r="G246" s="5"/>
-    </row>
-    <row r="247" spans="1:7">
+      <c r="H246" s="5"/>
+    </row>
+    <row r="247" spans="1:8">
       <c r="A247" s="5"/>
       <c r="B247" s="5"/>
       <c r="C247" s="5"/>
@@ -3933,8 +4202,9 @@
       <c r="E247" s="5"/>
       <c r="F247" s="5"/>
       <c r="G247" s="5"/>
-    </row>
-    <row r="248" spans="1:7">
+      <c r="H247" s="5"/>
+    </row>
+    <row r="248" spans="1:8">
       <c r="A248" s="5"/>
       <c r="B248" s="5"/>
       <c r="C248" s="5"/>
@@ -3942,8 +4212,9 @@
       <c r="E248" s="5"/>
       <c r="F248" s="5"/>
       <c r="G248" s="5"/>
-    </row>
-    <row r="249" spans="1:7">
+      <c r="H248" s="5"/>
+    </row>
+    <row r="249" spans="1:8">
       <c r="A249" s="5"/>
       <c r="B249" s="5"/>
       <c r="C249" s="5"/>
@@ -3951,8 +4222,9 @@
       <c r="E249" s="5"/>
       <c r="F249" s="5"/>
       <c r="G249" s="5"/>
-    </row>
-    <row r="250" spans="1:7">
+      <c r="H249" s="5"/>
+    </row>
+    <row r="250" spans="1:8">
       <c r="A250" s="5"/>
       <c r="B250" s="5"/>
       <c r="C250" s="5"/>
@@ -3960,8 +4232,9 @@
       <c r="E250" s="5"/>
       <c r="F250" s="5"/>
       <c r="G250" s="5"/>
-    </row>
-    <row r="251" spans="1:7">
+      <c r="H250" s="5"/>
+    </row>
+    <row r="251" spans="1:8">
       <c r="A251" s="5"/>
       <c r="B251" s="5"/>
       <c r="C251" s="5"/>
@@ -3969,8 +4242,9 @@
       <c r="E251" s="5"/>
       <c r="F251" s="5"/>
       <c r="G251" s="5"/>
-    </row>
-    <row r="252" spans="1:7">
+      <c r="H251" s="5"/>
+    </row>
+    <row r="252" spans="1:8">
       <c r="A252" s="5"/>
       <c r="B252" s="5"/>
       <c r="C252" s="5"/>
@@ -3978,8 +4252,9 @@
       <c r="E252" s="5"/>
       <c r="F252" s="5"/>
       <c r="G252" s="5"/>
-    </row>
-    <row r="253" spans="1:7">
+      <c r="H252" s="5"/>
+    </row>
+    <row r="253" spans="1:8">
       <c r="A253" s="5"/>
       <c r="B253" s="5"/>
       <c r="C253" s="5"/>
@@ -3987,8 +4262,9 @@
       <c r="E253" s="5"/>
       <c r="F253" s="5"/>
       <c r="G253" s="5"/>
-    </row>
-    <row r="254" spans="1:7">
+      <c r="H253" s="5"/>
+    </row>
+    <row r="254" spans="1:8">
       <c r="A254" s="5"/>
       <c r="B254" s="5"/>
       <c r="C254" s="5"/>
@@ -3996,8 +4272,9 @@
       <c r="E254" s="5"/>
       <c r="F254" s="5"/>
       <c r="G254" s="5"/>
-    </row>
-    <row r="255" spans="1:7">
+      <c r="H254" s="5"/>
+    </row>
+    <row r="255" spans="1:8">
       <c r="A255" s="5"/>
       <c r="B255" s="5"/>
       <c r="C255" s="5"/>
@@ -4005,8 +4282,9 @@
       <c r="E255" s="5"/>
       <c r="F255" s="5"/>
       <c r="G255" s="5"/>
-    </row>
-    <row r="256" spans="1:7">
+      <c r="H255" s="5"/>
+    </row>
+    <row r="256" spans="1:8">
       <c r="A256" s="5"/>
       <c r="B256" s="5"/>
       <c r="C256" s="5"/>
@@ -4014,8 +4292,9 @@
       <c r="E256" s="5"/>
       <c r="F256" s="5"/>
       <c r="G256" s="5"/>
-    </row>
-    <row r="257" spans="1:7">
+      <c r="H256" s="5"/>
+    </row>
+    <row r="257" spans="1:8">
       <c r="A257" s="5"/>
       <c r="B257" s="5"/>
       <c r="C257" s="5"/>
@@ -4023,8 +4302,9 @@
       <c r="E257" s="5"/>
       <c r="F257" s="5"/>
       <c r="G257" s="5"/>
-    </row>
-    <row r="258" spans="1:7">
+      <c r="H257" s="5"/>
+    </row>
+    <row r="258" spans="1:8">
       <c r="A258" s="5"/>
       <c r="B258" s="5"/>
       <c r="C258" s="5"/>
@@ -4032,8 +4312,9 @@
       <c r="E258" s="5"/>
       <c r="F258" s="5"/>
       <c r="G258" s="5"/>
-    </row>
-    <row r="259" spans="1:7">
+      <c r="H258" s="5"/>
+    </row>
+    <row r="259" spans="1:8">
       <c r="A259" s="5"/>
       <c r="B259" s="5"/>
       <c r="C259" s="5"/>
@@ -4041,8 +4322,9 @@
       <c r="E259" s="5"/>
       <c r="F259" s="5"/>
       <c r="G259" s="5"/>
-    </row>
-    <row r="260" spans="1:7">
+      <c r="H259" s="5"/>
+    </row>
+    <row r="260" spans="1:8">
       <c r="A260" s="5"/>
       <c r="B260" s="5"/>
       <c r="C260" s="5"/>
@@ -4050,8 +4332,9 @@
       <c r="E260" s="5"/>
       <c r="F260" s="5"/>
       <c r="G260" s="5"/>
-    </row>
-    <row r="261" spans="1:7">
+      <c r="H260" s="5"/>
+    </row>
+    <row r="261" spans="1:8">
       <c r="A261" s="5"/>
       <c r="B261" s="5"/>
       <c r="C261" s="5"/>
@@ -4059,8 +4342,9 @@
       <c r="E261" s="5"/>
       <c r="F261" s="5"/>
       <c r="G261" s="5"/>
-    </row>
-    <row r="262" spans="1:7">
+      <c r="H261" s="5"/>
+    </row>
+    <row r="262" spans="1:8">
       <c r="A262" s="5"/>
       <c r="B262" s="5"/>
       <c r="C262" s="5"/>
@@ -4068,8 +4352,9 @@
       <c r="E262" s="5"/>
       <c r="F262" s="5"/>
       <c r="G262" s="5"/>
-    </row>
-    <row r="263" spans="1:7">
+      <c r="H262" s="5"/>
+    </row>
+    <row r="263" spans="1:8">
       <c r="A263" s="5"/>
       <c r="B263" s="5"/>
       <c r="C263" s="5"/>
@@ -4077,8 +4362,9 @@
       <c r="E263" s="5"/>
       <c r="F263" s="5"/>
       <c r="G263" s="5"/>
-    </row>
-    <row r="264" spans="1:7">
+      <c r="H263" s="5"/>
+    </row>
+    <row r="264" spans="1:8">
       <c r="A264" s="5"/>
       <c r="B264" s="5"/>
       <c r="C264" s="5"/>
@@ -4086,8 +4372,9 @@
       <c r="E264" s="5"/>
       <c r="F264" s="5"/>
       <c r="G264" s="5"/>
-    </row>
-    <row r="265" spans="1:7">
+      <c r="H264" s="5"/>
+    </row>
+    <row r="265" spans="1:8">
       <c r="A265" s="5"/>
       <c r="B265" s="5"/>
       <c r="C265" s="5"/>
@@ -4095,8 +4382,9 @@
       <c r="E265" s="5"/>
       <c r="F265" s="5"/>
       <c r="G265" s="5"/>
-    </row>
-    <row r="266" spans="1:7">
+      <c r="H265" s="5"/>
+    </row>
+    <row r="266" spans="1:8">
       <c r="A266" s="5"/>
       <c r="B266" s="5"/>
       <c r="C266" s="5"/>
@@ -4104,8 +4392,9 @@
       <c r="E266" s="5"/>
       <c r="F266" s="5"/>
       <c r="G266" s="5"/>
-    </row>
-    <row r="267" spans="1:7">
+      <c r="H266" s="5"/>
+    </row>
+    <row r="267" spans="1:8">
       <c r="A267" s="5"/>
       <c r="B267" s="5"/>
       <c r="C267" s="5"/>
@@ -4113,8 +4402,9 @@
       <c r="E267" s="5"/>
       <c r="F267" s="5"/>
       <c r="G267" s="5"/>
-    </row>
-    <row r="268" spans="1:7">
+      <c r="H267" s="5"/>
+    </row>
+    <row r="268" spans="1:8">
       <c r="A268" s="5"/>
       <c r="B268" s="5"/>
       <c r="C268" s="5"/>
@@ -4122,8 +4412,9 @@
       <c r="E268" s="5"/>
       <c r="F268" s="5"/>
       <c r="G268" s="5"/>
-    </row>
-    <row r="269" spans="1:7">
+      <c r="H268" s="5"/>
+    </row>
+    <row r="269" spans="1:8">
       <c r="A269" s="5"/>
       <c r="B269" s="5"/>
       <c r="C269" s="5"/>
@@ -4131,8 +4422,9 @@
       <c r="E269" s="5"/>
       <c r="F269" s="5"/>
       <c r="G269" s="5"/>
-    </row>
-    <row r="270" spans="1:7">
+      <c r="H269" s="5"/>
+    </row>
+    <row r="270" spans="1:8">
       <c r="A270" s="5"/>
       <c r="B270" s="5"/>
       <c r="C270" s="5"/>
@@ -4140,8 +4432,9 @@
       <c r="E270" s="5"/>
       <c r="F270" s="5"/>
       <c r="G270" s="5"/>
-    </row>
-    <row r="271" spans="1:7">
+      <c r="H270" s="5"/>
+    </row>
+    <row r="271" spans="1:8">
       <c r="A271" s="5"/>
       <c r="B271" s="5"/>
       <c r="C271" s="5"/>
@@ -4149,8 +4442,9 @@
       <c r="E271" s="5"/>
       <c r="F271" s="5"/>
       <c r="G271" s="5"/>
-    </row>
-    <row r="272" spans="1:7">
+      <c r="H271" s="5"/>
+    </row>
+    <row r="272" spans="1:8">
       <c r="A272" s="5"/>
       <c r="B272" s="5"/>
       <c r="C272" s="5"/>
@@ -4158,8 +4452,9 @@
       <c r="E272" s="5"/>
       <c r="F272" s="5"/>
       <c r="G272" s="5"/>
-    </row>
-    <row r="273" spans="1:7">
+      <c r="H272" s="5"/>
+    </row>
+    <row r="273" spans="1:8">
       <c r="A273" s="5"/>
       <c r="B273" s="5"/>
       <c r="C273" s="5"/>
@@ -4167,8 +4462,9 @@
       <c r="E273" s="5"/>
       <c r="F273" s="5"/>
       <c r="G273" s="5"/>
-    </row>
-    <row r="274" spans="1:7">
+      <c r="H273" s="5"/>
+    </row>
+    <row r="274" spans="1:8">
       <c r="A274" s="5"/>
       <c r="B274" s="5"/>
       <c r="C274" s="5"/>
@@ -4176,8 +4472,9 @@
       <c r="E274" s="5"/>
       <c r="F274" s="5"/>
       <c r="G274" s="5"/>
-    </row>
-    <row r="275" spans="1:7">
+      <c r="H274" s="5"/>
+    </row>
+    <row r="275" spans="1:8">
       <c r="A275" s="5"/>
       <c r="B275" s="5"/>
       <c r="C275" s="5"/>
@@ -4185,8 +4482,9 @@
       <c r="E275" s="5"/>
       <c r="F275" s="5"/>
       <c r="G275" s="5"/>
-    </row>
-    <row r="276" spans="1:7">
+      <c r="H275" s="5"/>
+    </row>
+    <row r="276" spans="1:8">
       <c r="A276" s="5"/>
       <c r="B276" s="5"/>
       <c r="C276" s="5"/>
@@ -4194,8 +4492,9 @@
       <c r="E276" s="5"/>
       <c r="F276" s="5"/>
       <c r="G276" s="5"/>
-    </row>
-    <row r="277" spans="1:7">
+      <c r="H276" s="5"/>
+    </row>
+    <row r="277" spans="1:8">
       <c r="A277" s="5"/>
       <c r="B277" s="5"/>
       <c r="C277" s="5"/>
@@ -4203,8 +4502,9 @@
       <c r="E277" s="5"/>
       <c r="F277" s="5"/>
       <c r="G277" s="5"/>
-    </row>
-    <row r="278" spans="1:7">
+      <c r="H277" s="5"/>
+    </row>
+    <row r="278" spans="1:8">
       <c r="A278" s="5"/>
       <c r="B278" s="5"/>
       <c r="C278" s="5"/>
@@ -4212,8 +4512,9 @@
       <c r="E278" s="5"/>
       <c r="F278" s="5"/>
       <c r="G278" s="5"/>
-    </row>
-    <row r="279" spans="1:7">
+      <c r="H278" s="5"/>
+    </row>
+    <row r="279" spans="1:8">
       <c r="A279" s="5"/>
       <c r="B279" s="5"/>
       <c r="C279" s="5"/>
@@ -4221,8 +4522,9 @@
       <c r="E279" s="5"/>
       <c r="F279" s="5"/>
       <c r="G279" s="5"/>
-    </row>
-    <row r="280" spans="1:7">
+      <c r="H279" s="5"/>
+    </row>
+    <row r="280" spans="1:8">
       <c r="A280" s="5"/>
       <c r="B280" s="5"/>
       <c r="C280" s="5"/>
@@ -4230,8 +4532,9 @@
       <c r="E280" s="5"/>
       <c r="F280" s="5"/>
       <c r="G280" s="5"/>
-    </row>
-    <row r="281" spans="1:7">
+      <c r="H280" s="5"/>
+    </row>
+    <row r="281" spans="1:8">
       <c r="A281" s="5"/>
       <c r="B281" s="5"/>
       <c r="C281" s="5"/>
@@ -4239,8 +4542,9 @@
       <c r="E281" s="5"/>
       <c r="F281" s="5"/>
       <c r="G281" s="5"/>
-    </row>
-    <row r="282" spans="1:7">
+      <c r="H281" s="5"/>
+    </row>
+    <row r="282" spans="1:8">
       <c r="A282" s="5"/>
       <c r="B282" s="5"/>
       <c r="C282" s="5"/>
@@ -4248,8 +4552,9 @@
       <c r="E282" s="5"/>
       <c r="F282" s="5"/>
       <c r="G282" s="5"/>
-    </row>
-    <row r="283" spans="1:7">
+      <c r="H282" s="5"/>
+    </row>
+    <row r="283" spans="1:8">
       <c r="A283" s="5"/>
       <c r="B283" s="5"/>
       <c r="C283" s="5"/>
@@ -4257,8 +4562,9 @@
       <c r="E283" s="5"/>
       <c r="F283" s="5"/>
       <c r="G283" s="5"/>
-    </row>
-    <row r="284" spans="1:7">
+      <c r="H283" s="5"/>
+    </row>
+    <row r="284" spans="1:8">
       <c r="A284" s="5"/>
       <c r="B284" s="5"/>
       <c r="C284" s="5"/>
@@ -4266,8 +4572,9 @@
       <c r="E284" s="5"/>
       <c r="F284" s="5"/>
       <c r="G284" s="5"/>
-    </row>
-    <row r="285" spans="1:7">
+      <c r="H284" s="5"/>
+    </row>
+    <row r="285" spans="1:8">
       <c r="A285" s="5"/>
       <c r="B285" s="5"/>
       <c r="C285" s="5"/>
@@ -4275,8 +4582,9 @@
       <c r="E285" s="5"/>
       <c r="F285" s="5"/>
       <c r="G285" s="5"/>
-    </row>
-    <row r="286" spans="1:7">
+      <c r="H285" s="5"/>
+    </row>
+    <row r="286" spans="1:8">
       <c r="A286" s="5"/>
       <c r="B286" s="5"/>
       <c r="C286" s="5"/>
@@ -4284,8 +4592,9 @@
       <c r="E286" s="5"/>
       <c r="F286" s="5"/>
       <c r="G286" s="5"/>
-    </row>
-    <row r="287" spans="1:7">
+      <c r="H286" s="5"/>
+    </row>
+    <row r="287" spans="1:8">
       <c r="A287" s="5"/>
       <c r="B287" s="5"/>
       <c r="C287" s="5"/>
@@ -4293,8 +4602,9 @@
       <c r="E287" s="5"/>
       <c r="F287" s="5"/>
       <c r="G287" s="5"/>
-    </row>
-    <row r="288" spans="1:7">
+      <c r="H287" s="5"/>
+    </row>
+    <row r="288" spans="1:8">
       <c r="A288" s="5"/>
       <c r="B288" s="5"/>
       <c r="C288" s="5"/>
@@ -4302,8 +4612,9 @@
       <c r="E288" s="5"/>
       <c r="F288" s="5"/>
       <c r="G288" s="5"/>
-    </row>
-    <row r="289" spans="1:7">
+      <c r="H288" s="5"/>
+    </row>
+    <row r="289" spans="1:8">
       <c r="A289" s="5"/>
       <c r="B289" s="5"/>
       <c r="C289" s="5"/>
@@ -4311,8 +4622,9 @@
       <c r="E289" s="5"/>
       <c r="F289" s="5"/>
       <c r="G289" s="5"/>
-    </row>
-    <row r="290" spans="1:7">
+      <c r="H289" s="5"/>
+    </row>
+    <row r="290" spans="1:8">
       <c r="A290" s="5"/>
       <c r="B290" s="5"/>
       <c r="C290" s="5"/>
@@ -4320,8 +4632,9 @@
       <c r="E290" s="5"/>
       <c r="F290" s="5"/>
       <c r="G290" s="5"/>
-    </row>
-    <row r="291" spans="1:7">
+      <c r="H290" s="5"/>
+    </row>
+    <row r="291" spans="1:8">
       <c r="A291" s="5"/>
       <c r="B291" s="5"/>
       <c r="C291" s="5"/>
@@ -4329,8 +4642,9 @@
       <c r="E291" s="5"/>
       <c r="F291" s="5"/>
       <c r="G291" s="5"/>
-    </row>
-    <row r="292" spans="1:7">
+      <c r="H291" s="5"/>
+    </row>
+    <row r="292" spans="1:8">
       <c r="A292" s="5"/>
       <c r="B292" s="5"/>
       <c r="C292" s="5"/>
@@ -4338,8 +4652,9 @@
       <c r="E292" s="5"/>
       <c r="F292" s="5"/>
       <c r="G292" s="5"/>
-    </row>
-    <row r="293" spans="1:7">
+      <c r="H292" s="5"/>
+    </row>
+    <row r="293" spans="1:8">
       <c r="A293" s="5"/>
       <c r="B293" s="5"/>
       <c r="C293" s="5"/>
@@ -4347,8 +4662,9 @@
       <c r="E293" s="5"/>
       <c r="F293" s="5"/>
       <c r="G293" s="5"/>
-    </row>
-    <row r="294" spans="1:7">
+      <c r="H293" s="5"/>
+    </row>
+    <row r="294" spans="1:8">
       <c r="A294" s="5"/>
       <c r="B294" s="5"/>
       <c r="C294" s="5"/>
@@ -4356,8 +4672,9 @@
       <c r="E294" s="5"/>
       <c r="F294" s="5"/>
       <c r="G294" s="5"/>
-    </row>
-    <row r="295" spans="1:7">
+      <c r="H294" s="5"/>
+    </row>
+    <row r="295" spans="1:8">
       <c r="A295" s="5"/>
       <c r="B295" s="5"/>
       <c r="C295" s="5"/>
@@ -4365,8 +4682,9 @@
       <c r="E295" s="5"/>
       <c r="F295" s="5"/>
       <c r="G295" s="5"/>
-    </row>
-    <row r="296" spans="1:7">
+      <c r="H295" s="5"/>
+    </row>
+    <row r="296" spans="1:8">
       <c r="A296" s="5"/>
       <c r="B296" s="5"/>
       <c r="C296" s="5"/>
@@ -4374,8 +4692,9 @@
       <c r="E296" s="5"/>
       <c r="F296" s="5"/>
       <c r="G296" s="5"/>
-    </row>
-    <row r="297" spans="1:7">
+      <c r="H296" s="5"/>
+    </row>
+    <row r="297" spans="1:8">
       <c r="A297" s="5"/>
       <c r="B297" s="5"/>
       <c r="C297" s="5"/>
@@ -4383,8 +4702,9 @@
       <c r="E297" s="5"/>
       <c r="F297" s="5"/>
       <c r="G297" s="5"/>
-    </row>
-    <row r="298" spans="1:7">
+      <c r="H297" s="5"/>
+    </row>
+    <row r="298" spans="1:8">
       <c r="A298" s="5"/>
       <c r="B298" s="5"/>
       <c r="C298" s="5"/>
@@ -4392,8 +4712,9 @@
       <c r="E298" s="5"/>
       <c r="F298" s="5"/>
       <c r="G298" s="5"/>
-    </row>
-    <row r="299" spans="1:7">
+      <c r="H298" s="5"/>
+    </row>
+    <row r="299" spans="1:8">
       <c r="A299" s="5"/>
       <c r="B299" s="5"/>
       <c r="C299" s="5"/>
@@ -4401,8 +4722,9 @@
       <c r="E299" s="5"/>
       <c r="F299" s="5"/>
       <c r="G299" s="5"/>
-    </row>
-    <row r="300" spans="1:7">
+      <c r="H299" s="5"/>
+    </row>
+    <row r="300" spans="1:8">
       <c r="A300" s="5"/>
       <c r="B300" s="5"/>
       <c r="C300" s="5"/>
@@ -4410,8 +4732,9 @@
       <c r="E300" s="5"/>
       <c r="F300" s="5"/>
       <c r="G300" s="5"/>
-    </row>
-    <row r="301" spans="1:7">
+      <c r="H300" s="5"/>
+    </row>
+    <row r="301" spans="1:8">
       <c r="A301" s="5"/>
       <c r="B301" s="5"/>
       <c r="C301" s="5"/>
@@ -4419,8 +4742,9 @@
       <c r="E301" s="5"/>
       <c r="F301" s="5"/>
       <c r="G301" s="5"/>
-    </row>
-    <row r="302" spans="1:7">
+      <c r="H301" s="5"/>
+    </row>
+    <row r="302" spans="1:8">
       <c r="A302" s="5"/>
       <c r="B302" s="5"/>
       <c r="C302" s="5"/>
@@ -4428,8 +4752,9 @@
       <c r="E302" s="5"/>
       <c r="F302" s="5"/>
       <c r="G302" s="5"/>
-    </row>
-    <row r="303" spans="1:7">
+      <c r="H302" s="5"/>
+    </row>
+    <row r="303" spans="1:8">
       <c r="A303" s="5"/>
       <c r="B303" s="5"/>
       <c r="C303" s="5"/>
@@ -4437,8 +4762,9 @@
       <c r="E303" s="5"/>
       <c r="F303" s="5"/>
       <c r="G303" s="5"/>
-    </row>
-    <row r="304" spans="1:7">
+      <c r="H303" s="5"/>
+    </row>
+    <row r="304" spans="1:8">
       <c r="A304" s="5"/>
       <c r="B304" s="5"/>
       <c r="C304" s="5"/>
@@ -4446,8 +4772,9 @@
       <c r="E304" s="5"/>
       <c r="F304" s="5"/>
       <c r="G304" s="5"/>
-    </row>
-    <row r="305" spans="1:7">
+      <c r="H304" s="5"/>
+    </row>
+    <row r="305" spans="1:8">
       <c r="A305" s="5"/>
       <c r="B305" s="5"/>
       <c r="C305" s="5"/>
@@ -4455,8 +4782,9 @@
       <c r="E305" s="5"/>
       <c r="F305" s="5"/>
       <c r="G305" s="5"/>
-    </row>
-    <row r="306" spans="1:7">
+      <c r="H305" s="5"/>
+    </row>
+    <row r="306" spans="1:8">
       <c r="A306" s="5"/>
       <c r="B306" s="5"/>
       <c r="C306" s="5"/>
@@ -4464,8 +4792,9 @@
       <c r="E306" s="5"/>
       <c r="F306" s="5"/>
       <c r="G306" s="5"/>
-    </row>
-    <row r="307" spans="1:7">
+      <c r="H306" s="5"/>
+    </row>
+    <row r="307" spans="1:8">
       <c r="A307" s="5"/>
       <c r="B307" s="5"/>
       <c r="C307" s="5"/>
@@ -4473,8 +4802,9 @@
       <c r="E307" s="5"/>
       <c r="F307" s="5"/>
       <c r="G307" s="5"/>
-    </row>
-    <row r="308" spans="1:7">
+      <c r="H307" s="5"/>
+    </row>
+    <row r="308" spans="1:8">
       <c r="A308" s="5"/>
       <c r="B308" s="5"/>
       <c r="C308" s="5"/>
@@ -4482,8 +4812,9 @@
       <c r="E308" s="5"/>
       <c r="F308" s="5"/>
       <c r="G308" s="5"/>
-    </row>
-    <row r="309" spans="1:7">
+      <c r="H308" s="5"/>
+    </row>
+    <row r="309" spans="1:8">
       <c r="A309" s="5"/>
       <c r="B309" s="5"/>
       <c r="C309" s="5"/>
@@ -4491,8 +4822,9 @@
       <c r="E309" s="5"/>
       <c r="F309" s="5"/>
       <c r="G309" s="5"/>
-    </row>
-    <row r="310" spans="1:7">
+      <c r="H309" s="5"/>
+    </row>
+    <row r="310" spans="1:8">
       <c r="A310" s="5"/>
       <c r="B310" s="5"/>
       <c r="C310" s="5"/>
@@ -4500,8 +4832,9 @@
       <c r="E310" s="5"/>
       <c r="F310" s="5"/>
       <c r="G310" s="5"/>
-    </row>
-    <row r="311" spans="1:7">
+      <c r="H310" s="5"/>
+    </row>
+    <row r="311" spans="1:8">
       <c r="A311" s="5"/>
       <c r="B311" s="5"/>
       <c r="C311" s="5"/>
@@ -4509,8 +4842,9 @@
       <c r="E311" s="5"/>
       <c r="F311" s="5"/>
       <c r="G311" s="5"/>
-    </row>
-    <row r="312" spans="1:7">
+      <c r="H311" s="5"/>
+    </row>
+    <row r="312" spans="1:8">
       <c r="A312" s="5"/>
       <c r="B312" s="5"/>
       <c r="C312" s="5"/>
@@ -4518,8 +4852,9 @@
       <c r="E312" s="5"/>
       <c r="F312" s="5"/>
       <c r="G312" s="5"/>
-    </row>
-    <row r="313" spans="1:7">
+      <c r="H312" s="5"/>
+    </row>
+    <row r="313" spans="1:8">
       <c r="A313" s="5"/>
       <c r="B313" s="5"/>
       <c r="C313" s="5"/>
@@ -4527,8 +4862,9 @@
       <c r="E313" s="5"/>
       <c r="F313" s="5"/>
       <c r="G313" s="5"/>
-    </row>
-    <row r="314" spans="1:7">
+      <c r="H313" s="5"/>
+    </row>
+    <row r="314" spans="1:8">
       <c r="A314" s="5"/>
       <c r="B314" s="5"/>
       <c r="C314" s="5"/>
@@ -4536,8 +4872,9 @@
       <c r="E314" s="5"/>
       <c r="F314" s="5"/>
       <c r="G314" s="5"/>
-    </row>
-    <row r="315" spans="1:7">
+      <c r="H314" s="5"/>
+    </row>
+    <row r="315" spans="1:8">
       <c r="A315" s="5"/>
       <c r="B315" s="5"/>
       <c r="C315" s="5"/>
@@ -4545,8 +4882,9 @@
       <c r="E315" s="5"/>
       <c r="F315" s="5"/>
       <c r="G315" s="5"/>
-    </row>
-    <row r="316" spans="1:7">
+      <c r="H315" s="5"/>
+    </row>
+    <row r="316" spans="1:8">
       <c r="A316" s="5"/>
       <c r="B316" s="5"/>
       <c r="C316" s="5"/>
@@ -4554,8 +4892,9 @@
       <c r="E316" s="5"/>
       <c r="F316" s="5"/>
       <c r="G316" s="5"/>
-    </row>
-    <row r="317" spans="1:7">
+      <c r="H316" s="5"/>
+    </row>
+    <row r="317" spans="1:8">
       <c r="A317" s="5"/>
       <c r="B317" s="5"/>
       <c r="C317" s="5"/>
@@ -4563,8 +4902,9 @@
       <c r="E317" s="5"/>
       <c r="F317" s="5"/>
       <c r="G317" s="5"/>
-    </row>
-    <row r="318" spans="1:7">
+      <c r="H317" s="5"/>
+    </row>
+    <row r="318" spans="1:8">
       <c r="A318" s="5"/>
       <c r="B318" s="5"/>
       <c r="C318" s="5"/>
@@ -4572,8 +4912,9 @@
       <c r="E318" s="5"/>
       <c r="F318" s="5"/>
       <c r="G318" s="5"/>
-    </row>
-    <row r="319" spans="1:7">
+      <c r="H318" s="5"/>
+    </row>
+    <row r="319" spans="1:8">
       <c r="A319" s="5"/>
       <c r="B319" s="5"/>
       <c r="C319" s="5"/>
@@ -4581,8 +4922,9 @@
       <c r="E319" s="5"/>
       <c r="F319" s="5"/>
       <c r="G319" s="5"/>
-    </row>
-    <row r="320" spans="1:7">
+      <c r="H319" s="5"/>
+    </row>
+    <row r="320" spans="1:8">
       <c r="A320" s="5"/>
       <c r="B320" s="5"/>
       <c r="C320" s="5"/>
@@ -4590,8 +4932,9 @@
       <c r="E320" s="5"/>
       <c r="F320" s="5"/>
       <c r="G320" s="5"/>
-    </row>
-    <row r="321" spans="1:7">
+      <c r="H320" s="5"/>
+    </row>
+    <row r="321" spans="1:8">
       <c r="A321" s="5"/>
       <c r="B321" s="5"/>
       <c r="C321" s="5"/>
@@ -4599,8 +4942,9 @@
       <c r="E321" s="5"/>
       <c r="F321" s="5"/>
       <c r="G321" s="5"/>
-    </row>
-    <row r="322" spans="1:7">
+      <c r="H321" s="5"/>
+    </row>
+    <row r="322" spans="1:8">
       <c r="A322" s="5"/>
       <c r="B322" s="5"/>
       <c r="C322" s="5"/>
@@ -4608,8 +4952,9 @@
       <c r="E322" s="5"/>
       <c r="F322" s="5"/>
       <c r="G322" s="5"/>
-    </row>
-    <row r="323" spans="1:7">
+      <c r="H322" s="5"/>
+    </row>
+    <row r="323" spans="1:8">
       <c r="A323" s="5"/>
       <c r="B323" s="5"/>
       <c r="C323" s="5"/>
@@ -4617,8 +4962,9 @@
       <c r="E323" s="5"/>
       <c r="F323" s="5"/>
       <c r="G323" s="5"/>
-    </row>
-    <row r="324" spans="1:7">
+      <c r="H323" s="5"/>
+    </row>
+    <row r="324" spans="1:8">
       <c r="A324" s="5"/>
       <c r="B324" s="5"/>
       <c r="C324" s="5"/>
@@ -4626,8 +4972,9 @@
       <c r="E324" s="5"/>
       <c r="F324" s="5"/>
       <c r="G324" s="5"/>
-    </row>
-    <row r="325" spans="1:7">
+      <c r="H324" s="5"/>
+    </row>
+    <row r="325" spans="1:8">
       <c r="A325" s="5"/>
       <c r="B325" s="5"/>
       <c r="C325" s="5"/>
@@ -4635,8 +4982,9 @@
       <c r="E325" s="5"/>
       <c r="F325" s="5"/>
       <c r="G325" s="5"/>
-    </row>
-    <row r="326" spans="1:7">
+      <c r="H325" s="5"/>
+    </row>
+    <row r="326" spans="1:8">
       <c r="A326" s="5"/>
       <c r="B326" s="5"/>
       <c r="C326" s="5"/>
@@ -4644,8 +4992,9 @@
       <c r="E326" s="5"/>
       <c r="F326" s="5"/>
       <c r="G326" s="5"/>
-    </row>
-    <row r="327" spans="1:7">
+      <c r="H326" s="5"/>
+    </row>
+    <row r="327" spans="1:8">
       <c r="A327" s="5"/>
       <c r="B327" s="5"/>
       <c r="C327" s="5"/>
@@ -4653,8 +5002,9 @@
       <c r="E327" s="5"/>
       <c r="F327" s="5"/>
       <c r="G327" s="5"/>
-    </row>
-    <row r="328" spans="1:7">
+      <c r="H327" s="5"/>
+    </row>
+    <row r="328" spans="1:8">
       <c r="A328" s="5"/>
       <c r="B328" s="5"/>
       <c r="C328" s="5"/>
@@ -4662,8 +5012,9 @@
       <c r="E328" s="5"/>
       <c r="F328" s="5"/>
       <c r="G328" s="5"/>
-    </row>
-    <row r="329" spans="1:7">
+      <c r="H328" s="5"/>
+    </row>
+    <row r="329" spans="1:8">
       <c r="A329" s="5"/>
       <c r="B329" s="5"/>
       <c r="C329" s="5"/>
@@ -4671,8 +5022,9 @@
       <c r="E329" s="5"/>
       <c r="F329" s="5"/>
       <c r="G329" s="5"/>
-    </row>
-    <row r="330" spans="1:7">
+      <c r="H329" s="5"/>
+    </row>
+    <row r="330" spans="1:8">
       <c r="A330" s="5"/>
       <c r="B330" s="5"/>
       <c r="C330" s="5"/>
@@ -4680,8 +5032,9 @@
       <c r="E330" s="5"/>
       <c r="F330" s="5"/>
       <c r="G330" s="5"/>
-    </row>
-    <row r="331" spans="1:7">
+      <c r="H330" s="5"/>
+    </row>
+    <row r="331" spans="1:8">
       <c r="A331" s="5"/>
       <c r="B331" s="5"/>
       <c r="C331" s="5"/>
@@ -4689,8 +5042,9 @@
       <c r="E331" s="5"/>
       <c r="F331" s="5"/>
       <c r="G331" s="5"/>
-    </row>
-    <row r="332" spans="1:7">
+      <c r="H331" s="5"/>
+    </row>
+    <row r="332" spans="1:8">
       <c r="A332" s="5"/>
       <c r="B332" s="5"/>
       <c r="C332" s="5"/>
@@ -4698,8 +5052,9 @@
       <c r="E332" s="5"/>
       <c r="F332" s="5"/>
       <c r="G332" s="5"/>
-    </row>
-    <row r="333" spans="1:7">
+      <c r="H332" s="5"/>
+    </row>
+    <row r="333" spans="1:8">
       <c r="A333" s="5"/>
       <c r="B333" s="5"/>
       <c r="C333" s="5"/>
@@ -4707,8 +5062,9 @@
       <c r="E333" s="5"/>
       <c r="F333" s="5"/>
       <c r="G333" s="5"/>
-    </row>
-    <row r="334" spans="1:7">
+      <c r="H333" s="5"/>
+    </row>
+    <row r="334" spans="1:8">
       <c r="A334" s="5"/>
       <c r="B334" s="5"/>
       <c r="C334" s="5"/>
@@ -4716,8 +5072,9 @@
       <c r="E334" s="5"/>
       <c r="F334" s="5"/>
       <c r="G334" s="5"/>
-    </row>
-    <row r="335" spans="1:7">
+      <c r="H334" s="5"/>
+    </row>
+    <row r="335" spans="1:8">
       <c r="A335" s="5"/>
       <c r="B335" s="5"/>
       <c r="C335" s="5"/>
@@ -4725,8 +5082,9 @@
       <c r="E335" s="5"/>
       <c r="F335" s="5"/>
       <c r="G335" s="5"/>
-    </row>
-    <row r="336" spans="1:7">
+      <c r="H335" s="5"/>
+    </row>
+    <row r="336" spans="1:8">
       <c r="A336" s="5"/>
       <c r="B336" s="5"/>
       <c r="C336" s="5"/>
@@ -4734,8 +5092,9 @@
       <c r="E336" s="5"/>
       <c r="F336" s="5"/>
       <c r="G336" s="5"/>
-    </row>
-    <row r="337" spans="1:7">
+      <c r="H336" s="5"/>
+    </row>
+    <row r="337" spans="1:8">
       <c r="A337" s="5"/>
       <c r="B337" s="5"/>
       <c r="C337" s="5"/>
@@ -4743,8 +5102,9 @@
       <c r="E337" s="5"/>
       <c r="F337" s="5"/>
       <c r="G337" s="5"/>
-    </row>
-    <row r="338" spans="1:7">
+      <c r="H337" s="5"/>
+    </row>
+    <row r="338" spans="1:8">
       <c r="A338" s="5"/>
       <c r="B338" s="5"/>
       <c r="C338" s="5"/>
@@ -4752,8 +5112,9 @@
       <c r="E338" s="5"/>
       <c r="F338" s="5"/>
       <c r="G338" s="5"/>
-    </row>
-    <row r="339" spans="1:7">
+      <c r="H338" s="5"/>
+    </row>
+    <row r="339" spans="1:8">
       <c r="A339" s="5"/>
       <c r="B339" s="5"/>
       <c r="C339" s="5"/>
@@ -4761,8 +5122,9 @@
       <c r="E339" s="5"/>
       <c r="F339" s="5"/>
       <c r="G339" s="5"/>
-    </row>
-    <row r="340" spans="1:7">
+      <c r="H339" s="5"/>
+    </row>
+    <row r="340" spans="1:8">
       <c r="A340" s="5"/>
       <c r="B340" s="5"/>
       <c r="C340" s="5"/>
@@ -4770,8 +5132,9 @@
       <c r="E340" s="5"/>
       <c r="F340" s="5"/>
       <c r="G340" s="5"/>
-    </row>
-    <row r="341" spans="1:7">
+      <c r="H340" s="5"/>
+    </row>
+    <row r="341" spans="1:8">
       <c r="A341" s="5"/>
       <c r="B341" s="5"/>
       <c r="C341" s="5"/>
@@ -4779,8 +5142,9 @@
       <c r="E341" s="5"/>
       <c r="F341" s="5"/>
       <c r="G341" s="5"/>
-    </row>
-    <row r="342" spans="1:7">
+      <c r="H341" s="5"/>
+    </row>
+    <row r="342" spans="1:8">
       <c r="A342" s="5"/>
       <c r="B342" s="5"/>
       <c r="C342" s="5"/>
@@ -4788,8 +5152,9 @@
       <c r="E342" s="5"/>
       <c r="F342" s="5"/>
       <c r="G342" s="5"/>
-    </row>
-    <row r="343" spans="1:7">
+      <c r="H342" s="5"/>
+    </row>
+    <row r="343" spans="1:8">
       <c r="A343" s="5"/>
       <c r="B343" s="5"/>
       <c r="C343" s="5"/>
@@ -4797,8 +5162,9 @@
       <c r="E343" s="5"/>
       <c r="F343" s="5"/>
       <c r="G343" s="5"/>
-    </row>
-    <row r="344" spans="1:7">
+      <c r="H343" s="5"/>
+    </row>
+    <row r="344" spans="1:8">
       <c r="A344" s="5"/>
       <c r="B344" s="5"/>
       <c r="C344" s="5"/>
@@ -4806,8 +5172,9 @@
       <c r="E344" s="5"/>
       <c r="F344" s="5"/>
       <c r="G344" s="5"/>
-    </row>
-    <row r="345" spans="1:7">
+      <c r="H344" s="5"/>
+    </row>
+    <row r="345" spans="1:8">
       <c r="A345" s="5"/>
       <c r="B345" s="5"/>
       <c r="C345" s="5"/>
@@ -4815,8 +5182,9 @@
       <c r="E345" s="5"/>
       <c r="F345" s="5"/>
       <c r="G345" s="5"/>
-    </row>
-    <row r="346" spans="1:7">
+      <c r="H345" s="5"/>
+    </row>
+    <row r="346" spans="1:8">
       <c r="A346" s="5"/>
       <c r="B346" s="5"/>
       <c r="C346" s="5"/>
@@ -4824,8 +5192,9 @@
       <c r="E346" s="5"/>
       <c r="F346" s="5"/>
       <c r="G346" s="5"/>
-    </row>
-    <row r="347" spans="1:7">
+      <c r="H346" s="5"/>
+    </row>
+    <row r="347" spans="1:8">
       <c r="A347" s="5"/>
       <c r="B347" s="5"/>
       <c r="C347" s="5"/>
@@ -4833,8 +5202,9 @@
       <c r="E347" s="5"/>
       <c r="F347" s="5"/>
       <c r="G347" s="5"/>
-    </row>
-    <row r="348" spans="1:7">
+      <c r="H347" s="5"/>
+    </row>
+    <row r="348" spans="1:8">
       <c r="A348" s="5"/>
       <c r="B348" s="5"/>
       <c r="C348" s="5"/>
@@ -4842,8 +5212,9 @@
       <c r="E348" s="5"/>
       <c r="F348" s="5"/>
       <c r="G348" s="5"/>
-    </row>
-    <row r="349" spans="1:7">
+      <c r="H348" s="5"/>
+    </row>
+    <row r="349" spans="1:8">
       <c r="A349" s="5"/>
       <c r="B349" s="5"/>
       <c r="C349" s="5"/>
@@ -4851,8 +5222,9 @@
       <c r="E349" s="5"/>
       <c r="F349" s="5"/>
       <c r="G349" s="5"/>
-    </row>
-    <row r="350" spans="1:7">
+      <c r="H349" s="5"/>
+    </row>
+    <row r="350" spans="1:8">
       <c r="A350" s="5"/>
       <c r="B350" s="5"/>
       <c r="C350" s="5"/>
@@ -4860,8 +5232,9 @@
       <c r="E350" s="5"/>
       <c r="F350" s="5"/>
       <c r="G350" s="5"/>
-    </row>
-    <row r="351" spans="1:7">
+      <c r="H350" s="5"/>
+    </row>
+    <row r="351" spans="1:8">
       <c r="A351" s="5"/>
       <c r="B351" s="5"/>
       <c r="C351" s="5"/>
@@ -4869,8 +5242,9 @@
       <c r="E351" s="5"/>
       <c r="F351" s="5"/>
       <c r="G351" s="5"/>
-    </row>
-    <row r="352" spans="1:7">
+      <c r="H351" s="5"/>
+    </row>
+    <row r="352" spans="1:8">
       <c r="A352" s="5"/>
       <c r="B352" s="5"/>
       <c r="C352" s="5"/>
@@ -4878,8 +5252,9 @@
       <c r="E352" s="5"/>
       <c r="F352" s="5"/>
       <c r="G352" s="5"/>
-    </row>
-    <row r="353" spans="1:7">
+      <c r="H352" s="5"/>
+    </row>
+    <row r="353" spans="1:8">
       <c r="A353" s="5"/>
       <c r="B353" s="5"/>
       <c r="C353" s="5"/>
@@ -4887,8 +5262,9 @@
       <c r="E353" s="5"/>
       <c r="F353" s="5"/>
       <c r="G353" s="5"/>
-    </row>
-    <row r="354" spans="1:7">
+      <c r="H353" s="5"/>
+    </row>
+    <row r="354" spans="1:8">
       <c r="A354" s="5"/>
       <c r="B354" s="5"/>
       <c r="C354" s="5"/>
@@ -4896,8 +5272,9 @@
       <c r="E354" s="5"/>
       <c r="F354" s="5"/>
       <c r="G354" s="5"/>
-    </row>
-    <row r="355" spans="1:7">
+      <c r="H354" s="5"/>
+    </row>
+    <row r="355" spans="1:8">
       <c r="A355" s="5"/>
       <c r="B355" s="5"/>
       <c r="C355" s="5"/>
@@ -4905,8 +5282,9 @@
       <c r="E355" s="5"/>
       <c r="F355" s="5"/>
       <c r="G355" s="5"/>
-    </row>
-    <row r="356" spans="1:7">
+      <c r="H355" s="5"/>
+    </row>
+    <row r="356" spans="1:8">
       <c r="A356" s="5"/>
       <c r="B356" s="5"/>
       <c r="C356" s="5"/>
@@ -4914,8 +5292,9 @@
       <c r="E356" s="5"/>
       <c r="F356" s="5"/>
       <c r="G356" s="5"/>
-    </row>
-    <row r="357" spans="1:7">
+      <c r="H356" s="5"/>
+    </row>
+    <row r="357" spans="1:8">
       <c r="A357" s="5"/>
       <c r="B357" s="5"/>
       <c r="C357" s="5"/>
@@ -4923,8 +5302,9 @@
       <c r="E357" s="5"/>
       <c r="F357" s="5"/>
       <c r="G357" s="5"/>
-    </row>
-    <row r="358" spans="1:7">
+      <c r="H357" s="5"/>
+    </row>
+    <row r="358" spans="1:8">
       <c r="A358" s="5"/>
       <c r="B358" s="5"/>
       <c r="C358" s="5"/>
@@ -4932,8 +5312,9 @@
       <c r="E358" s="5"/>
       <c r="F358" s="5"/>
       <c r="G358" s="5"/>
-    </row>
-    <row r="359" spans="1:7">
+      <c r="H358" s="5"/>
+    </row>
+    <row r="359" spans="1:8">
       <c r="A359" s="5"/>
       <c r="B359" s="5"/>
       <c r="C359" s="5"/>
@@ -4941,8 +5322,9 @@
       <c r="E359" s="5"/>
       <c r="F359" s="5"/>
       <c r="G359" s="5"/>
-    </row>
-    <row r="360" spans="1:7">
+      <c r="H359" s="5"/>
+    </row>
+    <row r="360" spans="1:8">
       <c r="A360" s="5"/>
       <c r="B360" s="5"/>
       <c r="C360" s="5"/>
@@ -4950,8 +5332,9 @@
       <c r="E360" s="5"/>
       <c r="F360" s="5"/>
       <c r="G360" s="5"/>
-    </row>
-    <row r="361" spans="1:7">
+      <c r="H360" s="5"/>
+    </row>
+    <row r="361" spans="1:8">
       <c r="A361" s="5"/>
       <c r="B361" s="5"/>
       <c r="C361" s="5"/>
@@ -4959,8 +5342,9 @@
       <c r="E361" s="5"/>
       <c r="F361" s="5"/>
       <c r="G361" s="5"/>
-    </row>
-    <row r="362" spans="1:7">
+      <c r="H361" s="5"/>
+    </row>
+    <row r="362" spans="1:8">
       <c r="A362" s="5"/>
       <c r="B362" s="5"/>
       <c r="C362" s="5"/>
@@ -4968,8 +5352,9 @@
       <c r="E362" s="5"/>
       <c r="F362" s="5"/>
       <c r="G362" s="5"/>
-    </row>
-    <row r="363" spans="1:7">
+      <c r="H362" s="5"/>
+    </row>
+    <row r="363" spans="1:8">
       <c r="A363" s="5"/>
       <c r="B363" s="5"/>
       <c r="C363" s="5"/>
@@ -4977,8 +5362,9 @@
       <c r="E363" s="5"/>
       <c r="F363" s="5"/>
       <c r="G363" s="5"/>
-    </row>
-    <row r="364" spans="1:7">
+      <c r="H363" s="5"/>
+    </row>
+    <row r="364" spans="1:8">
       <c r="A364" s="5"/>
       <c r="B364" s="5"/>
       <c r="C364" s="5"/>
@@ -4986,8 +5372,9 @@
       <c r="E364" s="5"/>
       <c r="F364" s="5"/>
       <c r="G364" s="5"/>
-    </row>
-    <row r="365" spans="1:7">
+      <c r="H364" s="5"/>
+    </row>
+    <row r="365" spans="1:8">
       <c r="A365" s="5"/>
       <c r="B365" s="5"/>
       <c r="C365" s="5"/>
@@ -4995,8 +5382,9 @@
       <c r="E365" s="5"/>
       <c r="F365" s="5"/>
       <c r="G365" s="5"/>
-    </row>
-    <row r="366" spans="1:7">
+      <c r="H365" s="5"/>
+    </row>
+    <row r="366" spans="1:8">
       <c r="A366" s="5"/>
       <c r="B366" s="5"/>
       <c r="C366" s="5"/>
@@ -5004,8 +5392,9 @@
       <c r="E366" s="5"/>
       <c r="F366" s="5"/>
       <c r="G366" s="5"/>
-    </row>
-    <row r="367" spans="1:7">
+      <c r="H366" s="5"/>
+    </row>
+    <row r="367" spans="1:8">
       <c r="A367" s="5"/>
       <c r="B367" s="5"/>
       <c r="C367" s="5"/>
@@ -5013,8 +5402,9 @@
       <c r="E367" s="5"/>
       <c r="F367" s="5"/>
       <c r="G367" s="5"/>
-    </row>
-    <row r="368" spans="1:7">
+      <c r="H367" s="5"/>
+    </row>
+    <row r="368" spans="1:8">
       <c r="A368" s="5"/>
       <c r="B368" s="5"/>
       <c r="C368" s="5"/>
@@ -5022,8 +5412,9 @@
       <c r="E368" s="5"/>
       <c r="F368" s="5"/>
       <c r="G368" s="5"/>
-    </row>
-    <row r="369" spans="1:7">
+      <c r="H368" s="5"/>
+    </row>
+    <row r="369" spans="1:8">
       <c r="A369" s="5"/>
       <c r="B369" s="5"/>
       <c r="C369" s="5"/>
@@ -5031,8 +5422,9 @@
       <c r="E369" s="5"/>
       <c r="F369" s="5"/>
       <c r="G369" s="5"/>
-    </row>
-    <row r="370" spans="1:7">
+      <c r="H369" s="5"/>
+    </row>
+    <row r="370" spans="1:8">
       <c r="A370" s="5"/>
       <c r="B370" s="5"/>
       <c r="C370" s="5"/>
@@ -5040,8 +5432,9 @@
       <c r="E370" s="5"/>
       <c r="F370" s="5"/>
       <c r="G370" s="5"/>
-    </row>
-    <row r="371" spans="1:7">
+      <c r="H370" s="5"/>
+    </row>
+    <row r="371" spans="1:8">
       <c r="A371" s="5"/>
       <c r="B371" s="5"/>
       <c r="C371" s="5"/>
@@ -5049,8 +5442,9 @@
       <c r="E371" s="5"/>
       <c r="F371" s="5"/>
       <c r="G371" s="5"/>
-    </row>
-    <row r="372" spans="1:7">
+      <c r="H371" s="5"/>
+    </row>
+    <row r="372" spans="1:8">
       <c r="A372" s="5"/>
       <c r="B372" s="5"/>
       <c r="C372" s="5"/>
@@ -5058,8 +5452,9 @@
       <c r="E372" s="5"/>
       <c r="F372" s="5"/>
       <c r="G372" s="5"/>
-    </row>
-    <row r="373" spans="1:7">
+      <c r="H372" s="5"/>
+    </row>
+    <row r="373" spans="1:8">
       <c r="A373" s="5"/>
       <c r="B373" s="5"/>
       <c r="C373" s="5"/>
@@ -5067,8 +5462,9 @@
       <c r="E373" s="5"/>
       <c r="F373" s="5"/>
       <c r="G373" s="5"/>
-    </row>
-    <row r="374" spans="1:7">
+      <c r="H373" s="5"/>
+    </row>
+    <row r="374" spans="1:8">
       <c r="A374" s="5"/>
       <c r="B374" s="5"/>
       <c r="C374" s="5"/>
@@ -5076,8 +5472,9 @@
       <c r="E374" s="5"/>
       <c r="F374" s="5"/>
       <c r="G374" s="5"/>
-    </row>
-    <row r="375" spans="1:7">
+      <c r="H374" s="5"/>
+    </row>
+    <row r="375" spans="1:8">
       <c r="A375" s="5"/>
       <c r="B375" s="5"/>
       <c r="C375" s="5"/>
@@ -5085,8 +5482,9 @@
       <c r="E375" s="5"/>
       <c r="F375" s="5"/>
       <c r="G375" s="5"/>
-    </row>
-    <row r="376" spans="1:7">
+      <c r="H375" s="5"/>
+    </row>
+    <row r="376" spans="1:8">
       <c r="A376" s="5"/>
       <c r="B376" s="5"/>
       <c r="C376" s="5"/>
@@ -5094,8 +5492,9 @@
       <c r="E376" s="5"/>
       <c r="F376" s="5"/>
       <c r="G376" s="5"/>
-    </row>
-    <row r="377" spans="1:7">
+      <c r="H376" s="5"/>
+    </row>
+    <row r="377" spans="1:8">
       <c r="A377" s="5"/>
       <c r="B377" s="5"/>
       <c r="C377" s="5"/>
@@ -5103,8 +5502,9 @@
       <c r="E377" s="5"/>
       <c r="F377" s="5"/>
       <c r="G377" s="5"/>
-    </row>
-    <row r="378" spans="1:7">
+      <c r="H377" s="5"/>
+    </row>
+    <row r="378" spans="1:8">
       <c r="A378" s="5"/>
       <c r="B378" s="5"/>
       <c r="C378" s="5"/>
@@ -5112,8 +5512,9 @@
       <c r="E378" s="5"/>
       <c r="F378" s="5"/>
       <c r="G378" s="5"/>
-    </row>
-    <row r="379" spans="1:7">
+      <c r="H378" s="5"/>
+    </row>
+    <row r="379" spans="1:8">
       <c r="A379" s="5"/>
       <c r="B379" s="5"/>
       <c r="C379" s="5"/>
@@ -5121,8 +5522,9 @@
       <c r="E379" s="5"/>
       <c r="F379" s="5"/>
       <c r="G379" s="5"/>
-    </row>
-    <row r="380" spans="1:7">
+      <c r="H379" s="5"/>
+    </row>
+    <row r="380" spans="1:8">
       <c r="A380" s="5"/>
       <c r="B380" s="5"/>
       <c r="C380" s="5"/>
@@ -5130,8 +5532,9 @@
       <c r="E380" s="5"/>
       <c r="F380" s="5"/>
       <c r="G380" s="5"/>
-    </row>
-    <row r="381" spans="1:7">
+      <c r="H380" s="5"/>
+    </row>
+    <row r="381" spans="1:8">
       <c r="A381" s="5"/>
       <c r="B381" s="5"/>
       <c r="C381" s="5"/>
@@ -5139,8 +5542,9 @@
       <c r="E381" s="5"/>
       <c r="F381" s="5"/>
       <c r="G381" s="5"/>
-    </row>
-    <row r="382" spans="1:7">
+      <c r="H381" s="5"/>
+    </row>
+    <row r="382" spans="1:8">
       <c r="A382" s="5"/>
       <c r="B382" s="5"/>
       <c r="C382" s="5"/>
@@ -5148,8 +5552,9 @@
       <c r="E382" s="5"/>
       <c r="F382" s="5"/>
       <c r="G382" s="5"/>
-    </row>
-    <row r="383" spans="1:7">
+      <c r="H382" s="5"/>
+    </row>
+    <row r="383" spans="1:8">
       <c r="A383" s="5"/>
       <c r="B383" s="5"/>
       <c r="C383" s="5"/>
@@ -5157,8 +5562,9 @@
       <c r="E383" s="5"/>
       <c r="F383" s="5"/>
       <c r="G383" s="5"/>
-    </row>
-    <row r="384" spans="1:7">
+      <c r="H383" s="5"/>
+    </row>
+    <row r="384" spans="1:8">
       <c r="A384" s="5"/>
       <c r="B384" s="5"/>
       <c r="C384" s="5"/>
@@ -5166,8 +5572,9 @@
       <c r="E384" s="5"/>
       <c r="F384" s="5"/>
       <c r="G384" s="5"/>
-    </row>
-    <row r="385" spans="1:7">
+      <c r="H384" s="5"/>
+    </row>
+    <row r="385" spans="1:8">
       <c r="A385" s="5"/>
       <c r="B385" s="5"/>
       <c r="C385" s="5"/>
@@ -5175,8 +5582,9 @@
       <c r="E385" s="5"/>
       <c r="F385" s="5"/>
       <c r="G385" s="5"/>
-    </row>
-    <row r="386" spans="1:7">
+      <c r="H385" s="5"/>
+    </row>
+    <row r="386" spans="1:8">
       <c r="A386" s="5"/>
       <c r="B386" s="5"/>
       <c r="C386" s="5"/>
@@ -5184,8 +5592,9 @@
       <c r="E386" s="5"/>
       <c r="F386" s="5"/>
       <c r="G386" s="5"/>
-    </row>
-    <row r="387" spans="1:7">
+      <c r="H386" s="5"/>
+    </row>
+    <row r="387" spans="1:8">
       <c r="A387" s="5"/>
       <c r="B387" s="5"/>
       <c r="C387" s="5"/>
@@ -5193,8 +5602,9 @@
       <c r="E387" s="5"/>
       <c r="F387" s="5"/>
       <c r="G387" s="5"/>
-    </row>
-    <row r="388" spans="1:7">
+      <c r="H387" s="5"/>
+    </row>
+    <row r="388" spans="1:8">
       <c r="A388" s="5"/>
       <c r="B388" s="5"/>
       <c r="C388" s="5"/>
@@ -5202,8 +5612,9 @@
       <c r="E388" s="5"/>
       <c r="F388" s="5"/>
       <c r="G388" s="5"/>
-    </row>
-    <row r="389" spans="1:7">
+      <c r="H388" s="5"/>
+    </row>
+    <row r="389" spans="1:8">
       <c r="A389" s="5"/>
       <c r="B389" s="5"/>
       <c r="C389" s="5"/>
@@ -5211,8 +5622,9 @@
       <c r="E389" s="5"/>
       <c r="F389" s="5"/>
       <c r="G389" s="5"/>
-    </row>
-    <row r="390" spans="1:7">
+      <c r="H389" s="5"/>
+    </row>
+    <row r="390" spans="1:8">
       <c r="A390" s="5"/>
       <c r="B390" s="5"/>
       <c r="C390" s="5"/>
@@ -5220,8 +5632,9 @@
       <c r="E390" s="5"/>
       <c r="F390" s="5"/>
       <c r="G390" s="5"/>
-    </row>
-    <row r="391" spans="1:7">
+      <c r="H390" s="5"/>
+    </row>
+    <row r="391" spans="1:8">
       <c r="A391" s="5"/>
       <c r="B391" s="5"/>
       <c r="C391" s="5"/>
@@ -5229,8 +5642,9 @@
       <c r="E391" s="5"/>
       <c r="F391" s="5"/>
       <c r="G391" s="5"/>
-    </row>
-    <row r="392" spans="1:7">
+      <c r="H391" s="5"/>
+    </row>
+    <row r="392" spans="1:8">
       <c r="A392" s="5"/>
       <c r="B392" s="5"/>
       <c r="C392" s="5"/>
@@ -5238,8 +5652,9 @@
       <c r="E392" s="5"/>
       <c r="F392" s="5"/>
       <c r="G392" s="5"/>
-    </row>
-    <row r="393" spans="1:7">
+      <c r="H392" s="5"/>
+    </row>
+    <row r="393" spans="1:8">
       <c r="A393" s="5"/>
       <c r="B393" s="5"/>
       <c r="C393" s="5"/>
@@ -5247,8 +5662,9 @@
       <c r="E393" s="5"/>
       <c r="F393" s="5"/>
       <c r="G393" s="5"/>
-    </row>
-    <row r="394" spans="1:7">
+      <c r="H393" s="5"/>
+    </row>
+    <row r="394" spans="1:8">
       <c r="A394" s="5"/>
       <c r="B394" s="5"/>
       <c r="C394" s="5"/>
@@ -5256,8 +5672,9 @@
       <c r="E394" s="5"/>
       <c r="F394" s="5"/>
       <c r="G394" s="5"/>
-    </row>
-    <row r="395" spans="1:7">
+      <c r="H394" s="5"/>
+    </row>
+    <row r="395" spans="1:8">
       <c r="A395" s="5"/>
       <c r="B395" s="5"/>
       <c r="C395" s="5"/>
@@ -5265,8 +5682,9 @@
       <c r="E395" s="5"/>
       <c r="F395" s="5"/>
       <c r="G395" s="5"/>
-    </row>
-    <row r="396" spans="1:7">
+      <c r="H395" s="5"/>
+    </row>
+    <row r="396" spans="1:8">
       <c r="A396" s="5"/>
       <c r="B396" s="5"/>
       <c r="C396" s="5"/>
@@ -5274,8 +5692,9 @@
       <c r="E396" s="5"/>
       <c r="F396" s="5"/>
       <c r="G396" s="5"/>
-    </row>
-    <row r="397" spans="1:7">
+      <c r="H396" s="5"/>
+    </row>
+    <row r="397" spans="1:8">
       <c r="A397" s="5"/>
       <c r="B397" s="5"/>
       <c r="C397" s="5"/>
@@ -5283,8 +5702,9 @@
       <c r="E397" s="5"/>
       <c r="F397" s="5"/>
       <c r="G397" s="5"/>
-    </row>
-    <row r="398" spans="1:7">
+      <c r="H397" s="5"/>
+    </row>
+    <row r="398" spans="1:8">
       <c r="A398" s="5"/>
       <c r="B398" s="5"/>
       <c r="C398" s="5"/>
@@ -5292,8 +5712,9 @@
       <c r="E398" s="5"/>
       <c r="F398" s="5"/>
       <c r="G398" s="5"/>
-    </row>
-    <row r="399" spans="1:7">
+      <c r="H398" s="5"/>
+    </row>
+    <row r="399" spans="1:8">
       <c r="A399" s="5"/>
       <c r="B399" s="5"/>
       <c r="C399" s="5"/>
@@ -5301,8 +5722,9 @@
       <c r="E399" s="5"/>
       <c r="F399" s="5"/>
       <c r="G399" s="5"/>
-    </row>
-    <row r="400" spans="1:7">
+      <c r="H399" s="5"/>
+    </row>
+    <row r="400" spans="1:8">
       <c r="A400" s="5"/>
       <c r="B400" s="5"/>
       <c r="C400" s="5"/>
@@ -5310,8 +5732,9 @@
       <c r="E400" s="5"/>
       <c r="F400" s="5"/>
       <c r="G400" s="5"/>
-    </row>
-    <row r="401" spans="1:7">
+      <c r="H400" s="5"/>
+    </row>
+    <row r="401" spans="1:8">
       <c r="A401" s="5"/>
       <c r="B401" s="5"/>
       <c r="C401" s="5"/>
@@ -5319,8 +5742,9 @@
       <c r="E401" s="5"/>
       <c r="F401" s="5"/>
       <c r="G401" s="5"/>
-    </row>
-    <row r="402" spans="1:7">
+      <c r="H401" s="5"/>
+    </row>
+    <row r="402" spans="1:8">
       <c r="A402" s="5"/>
       <c r="B402" s="5"/>
       <c r="C402" s="5"/>
@@ -5328,8 +5752,9 @@
       <c r="E402" s="5"/>
       <c r="F402" s="5"/>
       <c r="G402" s="5"/>
-    </row>
-    <row r="403" spans="1:7">
+      <c r="H402" s="5"/>
+    </row>
+    <row r="403" spans="1:8">
       <c r="A403" s="5"/>
       <c r="B403" s="5"/>
       <c r="C403" s="5"/>
@@ -5337,8 +5762,9 @@
       <c r="E403" s="5"/>
       <c r="F403" s="5"/>
       <c r="G403" s="5"/>
-    </row>
-    <row r="404" spans="1:7">
+      <c r="H403" s="5"/>
+    </row>
+    <row r="404" spans="1:8">
       <c r="A404" s="5"/>
       <c r="B404" s="5"/>
       <c r="C404" s="5"/>
@@ -5346,8 +5772,9 @@
       <c r="E404" s="5"/>
       <c r="F404" s="5"/>
       <c r="G404" s="5"/>
-    </row>
-    <row r="405" spans="1:7">
+      <c r="H404" s="5"/>
+    </row>
+    <row r="405" spans="1:8">
       <c r="A405" s="5"/>
       <c r="B405" s="5"/>
       <c r="C405" s="5"/>
@@ -5355,8 +5782,9 @@
       <c r="E405" s="5"/>
       <c r="F405" s="5"/>
       <c r="G405" s="5"/>
-    </row>
-    <row r="406" spans="1:7">
+      <c r="H405" s="5"/>
+    </row>
+    <row r="406" spans="1:8">
       <c r="A406" s="5"/>
       <c r="B406" s="5"/>
       <c r="C406" s="5"/>
@@ -5364,8 +5792,9 @@
       <c r="E406" s="5"/>
       <c r="F406" s="5"/>
       <c r="G406" s="5"/>
-    </row>
-    <row r="407" spans="1:7">
+      <c r="H406" s="5"/>
+    </row>
+    <row r="407" spans="1:8">
       <c r="A407" s="5"/>
       <c r="B407" s="5"/>
       <c r="C407" s="5"/>
@@ -5373,8 +5802,9 @@
       <c r="E407" s="5"/>
       <c r="F407" s="5"/>
       <c r="G407" s="5"/>
-    </row>
-    <row r="408" spans="1:7">
+      <c r="H407" s="5"/>
+    </row>
+    <row r="408" spans="1:8">
       <c r="A408" s="5"/>
       <c r="B408" s="5"/>
       <c r="C408" s="5"/>
@@ -5382,8 +5812,9 @@
       <c r="E408" s="5"/>
       <c r="F408" s="5"/>
       <c r="G408" s="5"/>
-    </row>
-    <row r="409" spans="1:7">
+      <c r="H408" s="5"/>
+    </row>
+    <row r="409" spans="1:8">
       <c r="A409" s="5"/>
       <c r="B409" s="5"/>
       <c r="C409" s="5"/>
@@ -5391,8 +5822,9 @@
       <c r="E409" s="5"/>
       <c r="F409" s="5"/>
       <c r="G409" s="5"/>
-    </row>
-    <row r="410" spans="1:7">
+      <c r="H409" s="5"/>
+    </row>
+    <row r="410" spans="1:8">
       <c r="A410" s="5"/>
       <c r="B410" s="5"/>
       <c r="C410" s="5"/>
@@ -5400,8 +5832,9 @@
       <c r="E410" s="5"/>
       <c r="F410" s="5"/>
       <c r="G410" s="5"/>
-    </row>
-    <row r="411" spans="1:7">
+      <c r="H410" s="5"/>
+    </row>
+    <row r="411" spans="1:8">
       <c r="A411" s="5"/>
       <c r="B411" s="5"/>
       <c r="C411" s="5"/>
@@ -5409,8 +5842,9 @@
       <c r="E411" s="5"/>
       <c r="F411" s="5"/>
       <c r="G411" s="5"/>
-    </row>
-    <row r="412" spans="1:7">
+      <c r="H411" s="5"/>
+    </row>
+    <row r="412" spans="1:8">
       <c r="A412" s="5"/>
       <c r="B412" s="5"/>
       <c r="C412" s="5"/>
@@ -5418,8 +5852,9 @@
       <c r="E412" s="5"/>
       <c r="F412" s="5"/>
       <c r="G412" s="5"/>
-    </row>
-    <row r="413" spans="1:7">
+      <c r="H412" s="5"/>
+    </row>
+    <row r="413" spans="1:8">
       <c r="A413" s="5"/>
       <c r="B413" s="5"/>
       <c r="C413" s="5"/>
@@ -5427,8 +5862,9 @@
       <c r="E413" s="5"/>
       <c r="F413" s="5"/>
       <c r="G413" s="5"/>
-    </row>
-    <row r="414" spans="1:7">
+      <c r="H413" s="5"/>
+    </row>
+    <row r="414" spans="1:8">
       <c r="A414" s="5"/>
       <c r="B414" s="5"/>
       <c r="C414" s="5"/>
@@ -5436,8 +5872,9 @@
       <c r="E414" s="5"/>
       <c r="F414" s="5"/>
       <c r="G414" s="5"/>
-    </row>
-    <row r="415" spans="1:7">
+      <c r="H414" s="5"/>
+    </row>
+    <row r="415" spans="1:8">
       <c r="A415" s="5"/>
       <c r="B415" s="5"/>
       <c r="C415" s="5"/>
@@ -5445,8 +5882,9 @@
       <c r="E415" s="5"/>
       <c r="F415" s="5"/>
       <c r="G415" s="5"/>
-    </row>
-    <row r="416" spans="1:7">
+      <c r="H415" s="5"/>
+    </row>
+    <row r="416" spans="1:8">
       <c r="A416" s="5"/>
       <c r="B416" s="5"/>
       <c r="C416" s="5"/>
@@ -5454,8 +5892,9 @@
       <c r="E416" s="5"/>
       <c r="F416" s="5"/>
       <c r="G416" s="5"/>
-    </row>
-    <row r="417" spans="1:7">
+      <c r="H416" s="5"/>
+    </row>
+    <row r="417" spans="1:8">
       <c r="A417" s="5"/>
       <c r="B417" s="5"/>
       <c r="C417" s="5"/>
@@ -5463,8 +5902,9 @@
       <c r="E417" s="5"/>
       <c r="F417" s="5"/>
       <c r="G417" s="5"/>
-    </row>
-    <row r="418" spans="1:7">
+      <c r="H417" s="5"/>
+    </row>
+    <row r="418" spans="1:8">
       <c r="A418" s="5"/>
       <c r="B418" s="5"/>
       <c r="C418" s="5"/>
@@ -5472,8 +5912,9 @@
       <c r="E418" s="5"/>
       <c r="F418" s="5"/>
       <c r="G418" s="5"/>
-    </row>
-    <row r="419" spans="1:7">
+      <c r="H418" s="5"/>
+    </row>
+    <row r="419" spans="1:8">
       <c r="A419" s="5"/>
       <c r="B419" s="5"/>
       <c r="C419" s="5"/>
@@ -5481,8 +5922,9 @@
       <c r="E419" s="5"/>
       <c r="F419" s="5"/>
       <c r="G419" s="5"/>
-    </row>
-    <row r="420" spans="1:7">
+      <c r="H419" s="5"/>
+    </row>
+    <row r="420" spans="1:8">
       <c r="A420" s="5"/>
       <c r="B420" s="5"/>
       <c r="C420" s="5"/>
@@ -5490,8 +5932,9 @@
       <c r="E420" s="5"/>
       <c r="F420" s="5"/>
       <c r="G420" s="5"/>
-    </row>
-    <row r="421" spans="1:7">
+      <c r="H420" s="5"/>
+    </row>
+    <row r="421" spans="1:8">
       <c r="A421" s="5"/>
       <c r="B421" s="5"/>
       <c r="C421" s="5"/>
@@ -5499,8 +5942,9 @@
       <c r="E421" s="5"/>
       <c r="F421" s="5"/>
       <c r="G421" s="5"/>
-    </row>
-    <row r="422" spans="1:7">
+      <c r="H421" s="5"/>
+    </row>
+    <row r="422" spans="1:8">
       <c r="A422" s="5"/>
       <c r="B422" s="5"/>
       <c r="C422" s="5"/>
@@ -5508,8 +5952,9 @@
       <c r="E422" s="5"/>
       <c r="F422" s="5"/>
       <c r="G422" s="5"/>
-    </row>
-    <row r="423" spans="1:7">
+      <c r="H422" s="5"/>
+    </row>
+    <row r="423" spans="1:8">
       <c r="A423" s="5"/>
       <c r="B423" s="5"/>
       <c r="C423" s="5"/>
@@ -5517,8 +5962,9 @@
       <c r="E423" s="5"/>
       <c r="F423" s="5"/>
       <c r="G423" s="5"/>
-    </row>
-    <row r="424" spans="1:7">
+      <c r="H423" s="5"/>
+    </row>
+    <row r="424" spans="1:8">
       <c r="A424" s="5"/>
       <c r="B424" s="5"/>
       <c r="C424" s="5"/>
@@ -5526,8 +5972,9 @@
       <c r="E424" s="5"/>
       <c r="F424" s="5"/>
       <c r="G424" s="5"/>
-    </row>
-    <row r="425" spans="1:7">
+      <c r="H424" s="5"/>
+    </row>
+    <row r="425" spans="1:8">
       <c r="A425" s="5"/>
       <c r="B425" s="5"/>
       <c r="C425" s="5"/>
@@ -5535,8 +5982,9 @@
       <c r="E425" s="5"/>
       <c r="F425" s="5"/>
       <c r="G425" s="5"/>
-    </row>
-    <row r="426" spans="1:7">
+      <c r="H425" s="5"/>
+    </row>
+    <row r="426" spans="1:8">
       <c r="A426" s="5"/>
       <c r="B426" s="5"/>
       <c r="C426" s="5"/>
@@ -5544,8 +5992,9 @@
       <c r="E426" s="5"/>
       <c r="F426" s="5"/>
       <c r="G426" s="5"/>
-    </row>
-    <row r="427" spans="1:7">
+      <c r="H426" s="5"/>
+    </row>
+    <row r="427" spans="1:8">
       <c r="A427" s="5"/>
       <c r="B427" s="5"/>
       <c r="C427" s="5"/>
@@ -5553,8 +6002,9 @@
       <c r="E427" s="5"/>
       <c r="F427" s="5"/>
       <c r="G427" s="5"/>
-    </row>
-    <row r="428" spans="1:7">
+      <c r="H427" s="5"/>
+    </row>
+    <row r="428" spans="1:8">
       <c r="A428" s="5"/>
       <c r="B428" s="5"/>
       <c r="C428" s="5"/>
@@ -5562,8 +6012,9 @@
       <c r="E428" s="5"/>
       <c r="F428" s="5"/>
       <c r="G428" s="5"/>
-    </row>
-    <row r="429" spans="1:7">
+      <c r="H428" s="5"/>
+    </row>
+    <row r="429" spans="1:8">
       <c r="A429" s="5"/>
       <c r="B429" s="5"/>
       <c r="C429" s="5"/>
@@ -5571,8 +6022,9 @@
       <c r="E429" s="5"/>
       <c r="F429" s="5"/>
       <c r="G429" s="5"/>
-    </row>
-    <row r="430" spans="1:7">
+      <c r="H429" s="5"/>
+    </row>
+    <row r="430" spans="1:8">
       <c r="A430" s="5"/>
       <c r="B430" s="5"/>
       <c r="C430" s="5"/>
@@ -5580,8 +6032,9 @@
       <c r="E430" s="5"/>
       <c r="F430" s="5"/>
       <c r="G430" s="5"/>
-    </row>
-    <row r="431" spans="1:7">
+      <c r="H430" s="5"/>
+    </row>
+    <row r="431" spans="1:8">
       <c r="A431" s="5"/>
       <c r="B431" s="5"/>
       <c r="C431" s="5"/>
@@ -5589,8 +6042,9 @@
       <c r="E431" s="5"/>
       <c r="F431" s="5"/>
       <c r="G431" s="5"/>
-    </row>
-    <row r="432" spans="1:7">
+      <c r="H431" s="5"/>
+    </row>
+    <row r="432" spans="1:8">
       <c r="A432" s="5"/>
       <c r="B432" s="5"/>
       <c r="C432" s="5"/>
@@ -5598,8 +6052,9 @@
       <c r="E432" s="5"/>
       <c r="F432" s="5"/>
       <c r="G432" s="5"/>
-    </row>
-    <row r="433" spans="1:7">
+      <c r="H432" s="5"/>
+    </row>
+    <row r="433" spans="1:8">
       <c r="A433" s="5"/>
       <c r="B433" s="5"/>
       <c r="C433" s="5"/>
@@ -5607,8 +6062,9 @@
       <c r="E433" s="5"/>
       <c r="F433" s="5"/>
       <c r="G433" s="5"/>
-    </row>
-    <row r="434" spans="1:7">
+      <c r="H433" s="5"/>
+    </row>
+    <row r="434" spans="1:8">
       <c r="A434" s="5"/>
       <c r="B434" s="5"/>
       <c r="C434" s="5"/>
@@ -5616,8 +6072,9 @@
       <c r="E434" s="5"/>
       <c r="F434" s="5"/>
       <c r="G434" s="5"/>
-    </row>
-    <row r="435" spans="1:7">
+      <c r="H434" s="5"/>
+    </row>
+    <row r="435" spans="1:8">
       <c r="A435" s="5"/>
       <c r="B435" s="5"/>
       <c r="C435" s="5"/>
@@ -5625,8 +6082,9 @@
       <c r="E435" s="5"/>
       <c r="F435" s="5"/>
       <c r="G435" s="5"/>
-    </row>
-    <row r="436" spans="1:7">
+      <c r="H435" s="5"/>
+    </row>
+    <row r="436" spans="1:8">
       <c r="A436" s="5"/>
       <c r="B436" s="5"/>
       <c r="C436" s="5"/>
@@ -5634,8 +6092,9 @@
       <c r="E436" s="5"/>
       <c r="F436" s="5"/>
       <c r="G436" s="5"/>
-    </row>
-    <row r="437" spans="1:7">
+      <c r="H436" s="5"/>
+    </row>
+    <row r="437" spans="1:8">
       <c r="A437" s="5"/>
       <c r="B437" s="5"/>
       <c r="C437" s="5"/>
@@ -5643,8 +6102,9 @@
       <c r="E437" s="5"/>
       <c r="F437" s="5"/>
       <c r="G437" s="5"/>
-    </row>
-    <row r="438" spans="1:7">
+      <c r="H437" s="5"/>
+    </row>
+    <row r="438" spans="1:8">
       <c r="A438" s="5"/>
       <c r="B438" s="5"/>
       <c r="C438" s="5"/>
@@ -5652,8 +6112,9 @@
       <c r="E438" s="5"/>
       <c r="F438" s="5"/>
       <c r="G438" s="5"/>
-    </row>
-    <row r="439" spans="1:7">
+      <c r="H438" s="5"/>
+    </row>
+    <row r="439" spans="1:8">
       <c r="A439" s="5"/>
       <c r="B439" s="5"/>
       <c r="C439" s="5"/>
@@ -5661,8 +6122,9 @@
       <c r="E439" s="5"/>
       <c r="F439" s="5"/>
       <c r="G439" s="5"/>
-    </row>
-    <row r="440" spans="1:7">
+      <c r="H439" s="5"/>
+    </row>
+    <row r="440" spans="1:8">
       <c r="A440" s="5"/>
       <c r="B440" s="5"/>
       <c r="C440" s="5"/>
@@ -5670,8 +6132,9 @@
       <c r="E440" s="5"/>
       <c r="F440" s="5"/>
       <c r="G440" s="5"/>
-    </row>
-    <row r="441" spans="1:7">
+      <c r="H440" s="5"/>
+    </row>
+    <row r="441" spans="1:8">
       <c r="A441" s="5"/>
       <c r="B441" s="5"/>
       <c r="C441" s="5"/>
@@ -5679,8 +6142,9 @@
       <c r="E441" s="5"/>
       <c r="F441" s="5"/>
       <c r="G441" s="5"/>
-    </row>
-    <row r="442" spans="1:7">
+      <c r="H441" s="5"/>
+    </row>
+    <row r="442" spans="1:8">
       <c r="A442" s="5"/>
       <c r="B442" s="5"/>
       <c r="C442" s="5"/>
@@ -5688,8 +6152,9 @@
       <c r="E442" s="5"/>
       <c r="F442" s="5"/>
       <c r="G442" s="5"/>
-    </row>
-    <row r="443" spans="1:7">
+      <c r="H442" s="5"/>
+    </row>
+    <row r="443" spans="1:8">
       <c r="A443" s="5"/>
       <c r="B443" s="5"/>
       <c r="C443" s="5"/>
@@ -5697,8 +6162,9 @@
       <c r="E443" s="5"/>
       <c r="F443" s="5"/>
       <c r="G443" s="5"/>
-    </row>
-    <row r="444" spans="1:7">
+      <c r="H443" s="5"/>
+    </row>
+    <row r="444" spans="1:8">
       <c r="A444" s="5"/>
       <c r="B444" s="5"/>
       <c r="C444" s="5"/>
@@ -5706,8 +6172,9 @@
       <c r="E444" s="5"/>
       <c r="F444" s="5"/>
       <c r="G444" s="5"/>
-    </row>
-    <row r="445" spans="1:7">
+      <c r="H444" s="5"/>
+    </row>
+    <row r="445" spans="1:8">
       <c r="A445" s="5"/>
       <c r="B445" s="5"/>
       <c r="C445" s="5"/>
@@ -5715,8 +6182,9 @@
       <c r="E445" s="5"/>
       <c r="F445" s="5"/>
       <c r="G445" s="5"/>
-    </row>
-    <row r="446" spans="1:7">
+      <c r="H445" s="5"/>
+    </row>
+    <row r="446" spans="1:8">
       <c r="A446" s="5"/>
       <c r="B446" s="5"/>
       <c r="C446" s="5"/>
@@ -5724,8 +6192,9 @@
       <c r="E446" s="5"/>
       <c r="F446" s="5"/>
       <c r="G446" s="5"/>
-    </row>
-    <row r="447" spans="1:7">
+      <c r="H446" s="5"/>
+    </row>
+    <row r="447" spans="1:8">
       <c r="A447" s="5"/>
       <c r="B447" s="5"/>
       <c r="C447" s="5"/>
@@ -5733,8 +6202,9 @@
       <c r="E447" s="5"/>
       <c r="F447" s="5"/>
       <c r="G447" s="5"/>
-    </row>
-    <row r="448" spans="1:7">
+      <c r="H447" s="5"/>
+    </row>
+    <row r="448" spans="1:8">
       <c r="A448" s="5"/>
       <c r="B448" s="5"/>
       <c r="C448" s="5"/>
@@ -5742,8 +6212,9 @@
       <c r="E448" s="5"/>
       <c r="F448" s="5"/>
       <c r="G448" s="5"/>
-    </row>
-    <row r="449" spans="1:7">
+      <c r="H448" s="5"/>
+    </row>
+    <row r="449" spans="1:8">
       <c r="A449" s="5"/>
       <c r="B449" s="5"/>
       <c r="C449" s="5"/>
@@ -5751,8 +6222,9 @@
       <c r="E449" s="5"/>
       <c r="F449" s="5"/>
       <c r="G449" s="5"/>
-    </row>
-    <row r="450" spans="1:7">
+      <c r="H449" s="5"/>
+    </row>
+    <row r="450" spans="1:8">
       <c r="A450" s="5"/>
       <c r="B450" s="5"/>
       <c r="C450" s="5"/>
@@ -5760,8 +6232,9 @@
       <c r="E450" s="5"/>
       <c r="F450" s="5"/>
       <c r="G450" s="5"/>
-    </row>
-    <row r="451" spans="1:7">
+      <c r="H450" s="5"/>
+    </row>
+    <row r="451" spans="1:8">
       <c r="A451" s="5"/>
       <c r="B451" s="5"/>
       <c r="C451" s="5"/>
@@ -5769,8 +6242,9 @@
       <c r="E451" s="5"/>
       <c r="F451" s="5"/>
       <c r="G451" s="5"/>
-    </row>
-    <row r="452" spans="1:7">
+      <c r="H451" s="5"/>
+    </row>
+    <row r="452" spans="1:8">
       <c r="A452" s="5"/>
       <c r="B452" s="5"/>
       <c r="C452" s="5"/>
@@ -5778,8 +6252,9 @@
       <c r="E452" s="5"/>
       <c r="F452" s="5"/>
       <c r="G452" s="5"/>
-    </row>
-    <row r="453" spans="1:7">
+      <c r="H452" s="5"/>
+    </row>
+    <row r="453" spans="1:8">
       <c r="A453" s="5"/>
       <c r="B453" s="5"/>
       <c r="C453" s="5"/>
@@ -5787,8 +6262,9 @@
       <c r="E453" s="5"/>
       <c r="F453" s="5"/>
       <c r="G453" s="5"/>
-    </row>
-    <row r="454" spans="1:7">
+      <c r="H453" s="5"/>
+    </row>
+    <row r="454" spans="1:8">
       <c r="A454" s="5"/>
       <c r="B454" s="5"/>
       <c r="C454" s="5"/>
@@ -5796,35 +6272,36 @@
       <c r="E454" s="5"/>
       <c r="F454" s="5"/>
       <c r="G454" s="5"/>
-    </row>
-    <row r="455" spans="1:7">
+      <c r="H454" s="5"/>
+    </row>
+    <row r="455" spans="1:8">
       <c r="A455" s="5"/>
     </row>
-    <row r="456" spans="1:7">
+    <row r="456" spans="1:8">
       <c r="A456" s="5"/>
     </row>
-    <row r="457" spans="1:7">
+    <row r="457" spans="1:8">
       <c r="A457" s="5"/>
     </row>
-    <row r="458" spans="1:7">
+    <row r="458" spans="1:8">
       <c r="A458" s="5"/>
     </row>
-    <row r="459" spans="1:7">
+    <row r="459" spans="1:8">
       <c r="A459" s="5"/>
     </row>
-    <row r="460" spans="1:7">
+    <row r="460" spans="1:8">
       <c r="A460" s="5"/>
     </row>
-    <row r="461" spans="1:7">
+    <row r="461" spans="1:8">
       <c r="A461" s="5"/>
     </row>
-    <row r="462" spans="1:7">
+    <row r="462" spans="1:8">
       <c r="A462" s="5"/>
     </row>
-    <row r="463" spans="1:7">
+    <row r="463" spans="1:8">
       <c r="A463" s="5"/>
     </row>
-    <row r="464" spans="1:7">
+    <row r="464" spans="1:8">
       <c r="A464" s="5"/>
     </row>
     <row r="465" spans="1:1">

--- a/excel/item.xlsx
+++ b/excel/item.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gameSVN\game003\cocosProject\escape\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\svn\game003\cocosProject\escape\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -133,7 +133,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="41">
   <si>
     <t>编号</t>
   </si>
@@ -231,13 +231,31 @@
     <t>金色变卖物3</t>
   </si>
   <si>
-    <t>红色变卖物1</t>
+    <t>非洲之心</t>
   </si>
   <si>
-    <t>红色变卖物2</t>
+    <t>海洋之心</t>
   </si>
   <si>
-    <t>红色变卖物3</t>
+    <t>海洋之泪</t>
+  </si>
+  <si>
+    <t>机甲X号</t>
+  </si>
+  <si>
+    <t>钛金5090显卡</t>
+  </si>
+  <si>
+    <t>空天母舰模型</t>
+  </si>
+  <si>
+    <t>鼠鼠1号模型</t>
+  </si>
+  <si>
+    <t>劳力士</t>
+  </si>
+  <si>
+    <t>黎明手镯</t>
   </si>
 </sst>
 </file>
@@ -1915,14 +1933,30 @@
       <c r="R20" s="3"/>
     </row>
     <row r="21" s="1" customFormat="1" spans="1:18">
-      <c r="A21" s="3"/>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
+      <c r="A21" s="3">
+        <v>17</v>
+      </c>
+      <c r="B21" s="3">
+        <v>200018</v>
+      </c>
+      <c r="C21" s="3">
+        <v>0</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E21" s="3">
+        <v>4</v>
+      </c>
+      <c r="F21" s="3">
+        <v>506</v>
+      </c>
+      <c r="G21" s="3">
+        <v>11</v>
+      </c>
+      <c r="H21" s="3">
+        <v>2</v>
+      </c>
       <c r="I21" s="3"/>
       <c r="J21" s="3"/>
       <c r="K21" s="3"/>
@@ -1935,14 +1969,30 @@
       <c r="R21" s="3"/>
     </row>
     <row r="22" s="1" customFormat="1" spans="1:18">
-      <c r="A22" s="3"/>
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
+      <c r="A22" s="3">
+        <v>18</v>
+      </c>
+      <c r="B22" s="3">
+        <v>200019</v>
+      </c>
+      <c r="C22" s="3">
+        <v>0</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E22" s="3">
+        <v>4</v>
+      </c>
+      <c r="F22" s="3">
+        <v>507</v>
+      </c>
+      <c r="G22" s="3">
+        <v>12</v>
+      </c>
+      <c r="H22" s="3">
+        <v>3</v>
+      </c>
       <c r="I22" s="3"/>
       <c r="J22" s="3"/>
       <c r="K22" s="3"/>
@@ -1954,45 +2004,139 @@
       <c r="Q22" s="3"/>
       <c r="R22" s="3"/>
     </row>
-    <row r="23" spans="1:18">
-      <c r="A23" s="5"/>
-      <c r="B23" s="5"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
-      <c r="G23" s="5"/>
-      <c r="H23" s="5"/>
-    </row>
-    <row r="24" spans="1:18">
-      <c r="A24" s="5"/>
-      <c r="B24" s="5"/>
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
-      <c r="G24" s="5"/>
-      <c r="H24" s="5"/>
-    </row>
-    <row r="25" spans="1:18">
-      <c r="A25" s="5"/>
-      <c r="B25" s="5"/>
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
-      <c r="E25" s="5"/>
-      <c r="F25" s="5"/>
-      <c r="G25" s="5"/>
-      <c r="H25" s="5"/>
+    <row r="23" s="1" customFormat="1" spans="1:18">
+      <c r="A23" s="3">
+        <v>19</v>
+      </c>
+      <c r="B23" s="3">
+        <v>200020</v>
+      </c>
+      <c r="C23" s="3">
+        <v>0</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E23" s="3">
+        <v>4</v>
+      </c>
+      <c r="F23" s="3">
+        <v>508</v>
+      </c>
+      <c r="G23" s="3">
+        <v>13</v>
+      </c>
+      <c r="H23" s="3">
+        <v>4</v>
+      </c>
+      <c r="I23" s="3"/>
+      <c r="J23" s="3"/>
+      <c r="K23" s="3"/>
+      <c r="L23" s="3"/>
+      <c r="M23" s="3"/>
+      <c r="N23" s="3"/>
+      <c r="O23" s="3"/>
+      <c r="P23" s="3"/>
+      <c r="Q23" s="3"/>
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" s="1" customFormat="1" spans="1:18">
+      <c r="A24" s="3">
+        <v>20</v>
+      </c>
+      <c r="B24" s="3">
+        <v>200021</v>
+      </c>
+      <c r="C24" s="3">
+        <v>0</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E24" s="3">
+        <v>4</v>
+      </c>
+      <c r="F24" s="3">
+        <v>509</v>
+      </c>
+      <c r="G24" s="3">
+        <v>14</v>
+      </c>
+      <c r="H24" s="3">
+        <v>5</v>
+      </c>
+      <c r="I24" s="3"/>
+      <c r="J24" s="3"/>
+      <c r="K24" s="3"/>
+      <c r="L24" s="3"/>
+      <c r="M24" s="3"/>
+      <c r="N24" s="3"/>
+      <c r="O24" s="3"/>
+      <c r="P24" s="3"/>
+      <c r="Q24" s="3"/>
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" s="1" customFormat="1" spans="1:18">
+      <c r="A25" s="3">
+        <v>21</v>
+      </c>
+      <c r="B25" s="3">
+        <v>200022</v>
+      </c>
+      <c r="C25" s="3">
+        <v>0</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E25" s="3">
+        <v>4</v>
+      </c>
+      <c r="F25" s="3">
+        <v>510</v>
+      </c>
+      <c r="G25" s="3">
+        <v>15</v>
+      </c>
+      <c r="H25" s="3">
+        <v>6</v>
+      </c>
+      <c r="I25" s="3"/>
+      <c r="J25" s="3"/>
+      <c r="K25" s="3"/>
+      <c r="L25" s="3"/>
+      <c r="M25" s="3"/>
+      <c r="N25" s="3"/>
+      <c r="O25" s="3"/>
+      <c r="P25" s="3"/>
+      <c r="Q25" s="3"/>
+      <c r="R25" s="3"/>
     </row>
     <row r="26" spans="1:18">
-      <c r="A26" s="5"/>
-      <c r="B26" s="5"/>
-      <c r="C26" s="5"/>
-      <c r="D26" s="5"/>
-      <c r="E26" s="5"/>
-      <c r="F26" s="5"/>
-      <c r="G26" s="5"/>
-      <c r="H26" s="5"/>
+      <c r="A26" s="3">
+        <v>22</v>
+      </c>
+      <c r="B26" s="3">
+        <v>200023</v>
+      </c>
+      <c r="C26" s="3">
+        <v>0</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E26" s="3">
+        <v>5</v>
+      </c>
+      <c r="F26" s="3">
+        <v>511</v>
+      </c>
+      <c r="G26" s="3">
+        <v>16</v>
+      </c>
+      <c r="H26" s="3">
+        <v>7</v>
+      </c>
     </row>
     <row r="27" spans="1:18">
       <c r="A27" s="5"/>

--- a/excel/item.xlsx
+++ b/excel/item.xlsx
@@ -243,13 +243,13 @@
     <t>机甲X号</t>
   </si>
   <si>
-    <t>钛金5090显卡</t>
+    <t>钛金显卡</t>
   </si>
   <si>
-    <t>空天母舰模型</t>
+    <t>空天母舰</t>
   </si>
   <si>
-    <t>鼠鼠1号模型</t>
+    <t>鼠鼠1号</t>
   </si>
   <si>
     <t>劳力士</t>
@@ -432,12 +432,12 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>

--- a/excel/item.xlsx
+++ b/excel/item.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\svn\game003\cocosProject\escape\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gameSVN\game003\cocosProject\escape\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -432,12 +432,12 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2126,7 +2126,7 @@
         <v>40</v>
       </c>
       <c r="E26" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F26" s="3">
         <v>511</v>

--- a/excel/item.xlsx
+++ b/excel/item.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12360"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -183,10 +183,10 @@
     <t>weight</t>
   </si>
   <si>
-    <t>string</t>
+    <t>int</t>
   </si>
   <si>
-    <t>int</t>
+    <t>string</t>
   </si>
   <si>
     <t>银币</t>
@@ -432,12 +432,12 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1315,25 +1315,25 @@
         <v>16</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" s="4" t="s">
+      <c r="E3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="4" t="s">
-        <v>17</v>
-      </c>
       <c r="F3" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" spans="1:18">

--- a/excel/item.xlsx
+++ b/excel/item.xlsx
@@ -427,12 +427,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>

--- a/excel/item.xlsx
+++ b/excel/item.xlsx
@@ -427,17 +427,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>

--- a/excel/item.xlsx
+++ b/excel/item.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\svn\game003\cocosProject\escape\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gameSVN\game003\cocosProject\escape\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12360"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -591,13 +591,13 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="9"/>
+      <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
+      <b/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -2006,7 +2006,7 @@
         <v>14</v>
       </c>
       <c r="B18" s="5">
-        <v>200015</v>
+        <v>200065</v>
       </c>
       <c r="C18" s="5">
         <v>0</v>
@@ -2042,7 +2042,7 @@
         <v>15</v>
       </c>
       <c r="B19" s="5">
-        <v>200016</v>
+        <v>200066</v>
       </c>
       <c r="C19" s="5">
         <v>0</v>
@@ -2078,7 +2078,7 @@
         <v>16</v>
       </c>
       <c r="B20" s="5">
-        <v>200017</v>
+        <v>200067</v>
       </c>
       <c r="C20" s="5">
         <v>0</v>
@@ -2114,7 +2114,7 @@
         <v>17</v>
       </c>
       <c r="B21" s="5">
-        <v>200018</v>
+        <v>200068</v>
       </c>
       <c r="C21" s="5">
         <v>0</v>
@@ -2150,7 +2150,7 @@
         <v>18</v>
       </c>
       <c r="B22" s="5">
-        <v>200019</v>
+        <v>200069</v>
       </c>
       <c r="C22" s="5">
         <v>0</v>
@@ -2186,7 +2186,7 @@
         <v>19</v>
       </c>
       <c r="B23" s="5">
-        <v>200020</v>
+        <v>200070</v>
       </c>
       <c r="C23" s="5">
         <v>0</v>
@@ -2222,7 +2222,7 @@
         <v>20</v>
       </c>
       <c r="B24" s="5">
-        <v>200021</v>
+        <v>200071</v>
       </c>
       <c r="C24" s="5">
         <v>0</v>
@@ -2258,7 +2258,7 @@
         <v>21</v>
       </c>
       <c r="B25" s="5">
-        <v>200022</v>
+        <v>200072</v>
       </c>
       <c r="C25" s="5">
         <v>0</v>
@@ -2294,7 +2294,7 @@
         <v>22</v>
       </c>
       <c r="B26" s="5">
-        <v>200023</v>
+        <v>200073</v>
       </c>
       <c r="C26" s="5">
         <v>0</v>
@@ -3806,7 +3806,7 @@
         <v>64</v>
       </c>
       <c r="B68" s="5">
-        <v>200065</v>
+        <v>200015</v>
       </c>
       <c r="C68" s="5">
         <v>0</v>
@@ -3842,7 +3842,7 @@
         <v>65</v>
       </c>
       <c r="B69" s="5">
-        <v>200066</v>
+        <v>200016</v>
       </c>
       <c r="C69" s="5">
         <v>0</v>
@@ -3878,7 +3878,7 @@
         <v>66</v>
       </c>
       <c r="B70" s="5">
-        <v>200067</v>
+        <v>200017</v>
       </c>
       <c r="C70" s="5">
         <v>0</v>
@@ -3914,7 +3914,7 @@
         <v>67</v>
       </c>
       <c r="B71" s="5">
-        <v>200068</v>
+        <v>200018</v>
       </c>
       <c r="C71" s="5">
         <v>0</v>
@@ -3950,7 +3950,7 @@
         <v>68</v>
       </c>
       <c r="B72" s="5">
-        <v>200069</v>
+        <v>200019</v>
       </c>
       <c r="C72" s="5">
         <v>0</v>
@@ -3986,7 +3986,7 @@
         <v>69</v>
       </c>
       <c r="B73" s="5">
-        <v>200070</v>
+        <v>200020</v>
       </c>
       <c r="C73" s="5">
         <v>0</v>
@@ -4022,7 +4022,7 @@
         <v>70</v>
       </c>
       <c r="B74" s="5">
-        <v>200071</v>
+        <v>200021</v>
       </c>
       <c r="C74" s="5">
         <v>0</v>
@@ -4058,7 +4058,7 @@
         <v>71</v>
       </c>
       <c r="B75" s="5">
-        <v>200072</v>
+        <v>200022</v>
       </c>
       <c r="C75" s="5">
         <v>0</v>
@@ -4094,7 +4094,7 @@
         <v>72</v>
       </c>
       <c r="B76" s="5">
-        <v>200073</v>
+        <v>200023</v>
       </c>
       <c r="C76" s="5">
         <v>0</v>

--- a/excel/item.xlsx
+++ b/excel/item.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gameSVN\game003\cocosProject\escape\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\svn\game003\cocosProject\escape\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12360"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -591,13 +591,13 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
+      <b/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="9"/>
+      <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>

--- a/excel/item.xlsx
+++ b/excel/item.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\svn\game003\cocosProject\escape\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\svnNew\game003\cocosProject\escape\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -133,7 +133,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="95">
   <si>
     <t>编号</t>
   </si>
@@ -415,6 +415,9 @@
   </si>
   <si>
     <t>导弹模型</t>
+  </si>
+  <si>
+    <t>鼠鼠金币</t>
   </si>
 </sst>
 </file>
@@ -591,13 +594,13 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="9"/>
+      <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
+      <b/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1077,7 +1080,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1095,6 +1098,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4194,4737 +4200,4753 @@
       </c>
     </row>
     <row r="80" spans="1:18">
-      <c r="A80" s="8"/>
-      <c r="B80" s="8"/>
-      <c r="C80" s="8"/>
-      <c r="D80" s="8"/>
-      <c r="E80" s="8"/>
-      <c r="F80" s="8"/>
-      <c r="G80" s="8"/>
-      <c r="H80" s="8"/>
+      <c r="A80" s="5">
+        <v>76</v>
+      </c>
+      <c r="B80" s="5">
+        <v>200077</v>
+      </c>
+      <c r="C80" s="8">
+        <v>0</v>
+      </c>
+      <c r="D80" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="E80" s="8">
+        <v>4</v>
+      </c>
+      <c r="F80" s="8">
+        <v>1888888</v>
+      </c>
+      <c r="G80" s="8">
+        <v>5</v>
+      </c>
+      <c r="H80" s="8">
+        <v>30</v>
+      </c>
     </row>
     <row r="81" spans="1:8">
-      <c r="A81" s="8"/>
-      <c r="B81" s="8"/>
-      <c r="C81" s="8"/>
-      <c r="D81" s="8"/>
-      <c r="E81" s="8"/>
-      <c r="F81" s="8"/>
-      <c r="G81" s="8"/>
-      <c r="H81" s="8"/>
+      <c r="A81" s="9"/>
+      <c r="B81" s="9"/>
+      <c r="C81" s="9"/>
+      <c r="D81" s="9"/>
+      <c r="E81" s="9"/>
+      <c r="F81" s="9"/>
+      <c r="G81" s="9"/>
+      <c r="H81" s="9"/>
     </row>
     <row r="82" spans="1:8">
-      <c r="A82" s="8"/>
-      <c r="B82" s="8"/>
-      <c r="C82" s="8"/>
-      <c r="D82" s="8"/>
-      <c r="E82" s="8"/>
-      <c r="F82" s="8"/>
-      <c r="G82" s="8"/>
-      <c r="H82" s="8"/>
+      <c r="A82" s="9"/>
+      <c r="B82" s="9"/>
+      <c r="C82" s="9"/>
+      <c r="D82" s="9"/>
+      <c r="E82" s="9"/>
+      <c r="F82" s="9"/>
+      <c r="G82" s="9"/>
+      <c r="H82" s="9"/>
     </row>
     <row r="83" spans="1:8">
-      <c r="A83" s="8"/>
-      <c r="B83" s="8"/>
-      <c r="C83" s="8"/>
-      <c r="D83" s="8"/>
-      <c r="E83" s="8"/>
-      <c r="F83" s="8"/>
-      <c r="G83" s="8"/>
-      <c r="H83" s="8"/>
+      <c r="A83" s="9"/>
+      <c r="B83" s="9"/>
+      <c r="C83" s="9"/>
+      <c r="D83" s="9"/>
+      <c r="E83" s="9"/>
+      <c r="F83" s="9"/>
+      <c r="G83" s="9"/>
+      <c r="H83" s="9"/>
     </row>
     <row r="84" spans="1:8">
-      <c r="A84" s="8"/>
-      <c r="B84" s="8"/>
-      <c r="C84" s="8"/>
-      <c r="D84" s="8"/>
-      <c r="E84" s="8"/>
-      <c r="F84" s="8"/>
-      <c r="G84" s="8"/>
-      <c r="H84" s="8"/>
+      <c r="A84" s="9"/>
+      <c r="B84" s="9"/>
+      <c r="C84" s="9"/>
+      <c r="D84" s="9"/>
+      <c r="E84" s="9"/>
+      <c r="F84" s="9"/>
+      <c r="G84" s="9"/>
+      <c r="H84" s="9"/>
     </row>
     <row r="85" spans="1:8">
-      <c r="A85" s="8"/>
-      <c r="B85" s="8"/>
-      <c r="C85" s="8"/>
-      <c r="D85" s="8"/>
-      <c r="E85" s="8"/>
-      <c r="F85" s="8"/>
-      <c r="G85" s="8"/>
-      <c r="H85" s="8"/>
+      <c r="A85" s="9"/>
+      <c r="B85" s="9"/>
+      <c r="C85" s="9"/>
+      <c r="D85" s="9"/>
+      <c r="E85" s="9"/>
+      <c r="F85" s="9"/>
+      <c r="G85" s="9"/>
+      <c r="H85" s="9"/>
     </row>
     <row r="86" spans="1:8">
-      <c r="A86" s="8"/>
-      <c r="B86" s="8"/>
-      <c r="C86" s="8"/>
-      <c r="D86" s="8"/>
-      <c r="E86" s="8"/>
-      <c r="F86" s="8"/>
-      <c r="G86" s="8"/>
-      <c r="H86" s="8"/>
+      <c r="A86" s="9"/>
+      <c r="B86" s="9"/>
+      <c r="C86" s="9"/>
+      <c r="D86" s="9"/>
+      <c r="E86" s="9"/>
+      <c r="F86" s="9"/>
+      <c r="G86" s="9"/>
+      <c r="H86" s="9"/>
     </row>
     <row r="87" spans="1:8">
-      <c r="A87" s="8"/>
-      <c r="B87" s="8"/>
-      <c r="C87" s="8"/>
-      <c r="D87" s="8"/>
-      <c r="E87" s="8"/>
-      <c r="F87" s="8"/>
-      <c r="G87" s="8"/>
-      <c r="H87" s="8"/>
+      <c r="A87" s="9"/>
+      <c r="B87" s="9"/>
+      <c r="C87" s="9"/>
+      <c r="D87" s="9"/>
+      <c r="E87" s="9"/>
+      <c r="F87" s="9"/>
+      <c r="G87" s="9"/>
+      <c r="H87" s="9"/>
     </row>
     <row r="88" spans="1:8">
-      <c r="A88" s="8"/>
-      <c r="B88" s="8"/>
-      <c r="C88" s="8"/>
-      <c r="D88" s="8"/>
-      <c r="E88" s="8"/>
-      <c r="F88" s="8"/>
-      <c r="G88" s="8"/>
-      <c r="H88" s="8"/>
+      <c r="A88" s="9"/>
+      <c r="B88" s="9"/>
+      <c r="C88" s="9"/>
+      <c r="D88" s="9"/>
+      <c r="E88" s="9"/>
+      <c r="F88" s="9"/>
+      <c r="G88" s="9"/>
+      <c r="H88" s="9"/>
     </row>
     <row r="89" spans="1:8">
-      <c r="A89" s="8"/>
-      <c r="B89" s="8"/>
-      <c r="C89" s="8"/>
-      <c r="D89" s="8"/>
-      <c r="E89" s="8"/>
-      <c r="F89" s="8"/>
-      <c r="G89" s="8"/>
-      <c r="H89" s="8"/>
+      <c r="A89" s="9"/>
+      <c r="B89" s="9"/>
+      <c r="C89" s="9"/>
+      <c r="D89" s="9"/>
+      <c r="E89" s="9"/>
+      <c r="F89" s="9"/>
+      <c r="G89" s="9"/>
+      <c r="H89" s="9"/>
     </row>
     <row r="90" spans="1:8">
-      <c r="A90" s="8"/>
-      <c r="B90" s="8"/>
-      <c r="C90" s="8"/>
-      <c r="D90" s="8"/>
-      <c r="E90" s="8"/>
-      <c r="F90" s="8"/>
-      <c r="G90" s="8"/>
-      <c r="H90" s="8"/>
+      <c r="A90" s="9"/>
+      <c r="B90" s="9"/>
+      <c r="C90" s="9"/>
+      <c r="D90" s="9"/>
+      <c r="E90" s="9"/>
+      <c r="F90" s="9"/>
+      <c r="G90" s="9"/>
+      <c r="H90" s="9"/>
     </row>
     <row r="91" spans="1:8">
-      <c r="A91" s="8"/>
-      <c r="B91" s="8"/>
-      <c r="C91" s="8"/>
-      <c r="D91" s="8"/>
-      <c r="E91" s="8"/>
-      <c r="F91" s="8"/>
-      <c r="G91" s="8"/>
-      <c r="H91" s="8"/>
+      <c r="A91" s="9"/>
+      <c r="B91" s="9"/>
+      <c r="C91" s="9"/>
+      <c r="D91" s="9"/>
+      <c r="E91" s="9"/>
+      <c r="F91" s="9"/>
+      <c r="G91" s="9"/>
+      <c r="H91" s="9"/>
     </row>
     <row r="92" spans="1:8">
-      <c r="A92" s="8"/>
-      <c r="B92" s="8"/>
-      <c r="C92" s="8"/>
-      <c r="D92" s="8"/>
-      <c r="E92" s="8"/>
-      <c r="F92" s="8"/>
-      <c r="G92" s="8"/>
-      <c r="H92" s="8"/>
+      <c r="A92" s="9"/>
+      <c r="B92" s="9"/>
+      <c r="C92" s="9"/>
+      <c r="D92" s="9"/>
+      <c r="E92" s="9"/>
+      <c r="F92" s="9"/>
+      <c r="G92" s="9"/>
+      <c r="H92" s="9"/>
     </row>
     <row r="93" spans="1:8">
-      <c r="A93" s="8"/>
-      <c r="B93" s="8"/>
-      <c r="C93" s="8"/>
-      <c r="D93" s="8"/>
-      <c r="E93" s="8"/>
-      <c r="F93" s="8"/>
-      <c r="G93" s="8"/>
-      <c r="H93" s="8"/>
+      <c r="A93" s="9"/>
+      <c r="B93" s="9"/>
+      <c r="C93" s="9"/>
+      <c r="D93" s="9"/>
+      <c r="E93" s="9"/>
+      <c r="F93" s="9"/>
+      <c r="G93" s="9"/>
+      <c r="H93" s="9"/>
     </row>
     <row r="94" spans="1:8">
-      <c r="A94" s="8"/>
-      <c r="B94" s="8"/>
-      <c r="C94" s="8"/>
-      <c r="D94" s="8"/>
-      <c r="E94" s="8"/>
-      <c r="F94" s="8"/>
-      <c r="G94" s="8"/>
-      <c r="H94" s="8"/>
+      <c r="A94" s="9"/>
+      <c r="B94" s="9"/>
+      <c r="C94" s="9"/>
+      <c r="D94" s="9"/>
+      <c r="E94" s="9"/>
+      <c r="F94" s="9"/>
+      <c r="G94" s="9"/>
+      <c r="H94" s="9"/>
     </row>
     <row r="95" spans="1:8">
-      <c r="A95" s="8"/>
-      <c r="B95" s="8"/>
-      <c r="C95" s="8"/>
-      <c r="D95" s="8"/>
-      <c r="E95" s="8"/>
-      <c r="F95" s="8"/>
-      <c r="G95" s="8"/>
-      <c r="H95" s="8"/>
+      <c r="A95" s="9"/>
+      <c r="B95" s="9"/>
+      <c r="C95" s="9"/>
+      <c r="D95" s="9"/>
+      <c r="E95" s="9"/>
+      <c r="F95" s="9"/>
+      <c r="G95" s="9"/>
+      <c r="H95" s="9"/>
     </row>
     <row r="96" spans="1:8">
-      <c r="A96" s="8"/>
-      <c r="B96" s="8"/>
-      <c r="C96" s="8"/>
-      <c r="D96" s="8"/>
-      <c r="E96" s="8"/>
-      <c r="F96" s="8"/>
-      <c r="G96" s="8"/>
-      <c r="H96" s="8"/>
+      <c r="A96" s="9"/>
+      <c r="B96" s="9"/>
+      <c r="C96" s="9"/>
+      <c r="D96" s="9"/>
+      <c r="E96" s="9"/>
+      <c r="F96" s="9"/>
+      <c r="G96" s="9"/>
+      <c r="H96" s="9"/>
     </row>
     <row r="97" spans="1:8">
-      <c r="A97" s="8"/>
-      <c r="B97" s="8"/>
-      <c r="C97" s="8"/>
-      <c r="D97" s="8"/>
-      <c r="E97" s="8"/>
-      <c r="F97" s="8"/>
-      <c r="G97" s="8"/>
-      <c r="H97" s="8"/>
+      <c r="A97" s="9"/>
+      <c r="B97" s="9"/>
+      <c r="C97" s="9"/>
+      <c r="D97" s="9"/>
+      <c r="E97" s="9"/>
+      <c r="F97" s="9"/>
+      <c r="G97" s="9"/>
+      <c r="H97" s="9"/>
     </row>
     <row r="98" spans="1:8">
-      <c r="A98" s="8"/>
-      <c r="B98" s="8"/>
-      <c r="C98" s="8"/>
-      <c r="D98" s="8"/>
-      <c r="E98" s="8"/>
-      <c r="F98" s="8"/>
-      <c r="G98" s="8"/>
-      <c r="H98" s="8"/>
+      <c r="A98" s="9"/>
+      <c r="B98" s="9"/>
+      <c r="C98" s="9"/>
+      <c r="D98" s="9"/>
+      <c r="E98" s="9"/>
+      <c r="F98" s="9"/>
+      <c r="G98" s="9"/>
+      <c r="H98" s="9"/>
     </row>
     <row r="99" spans="1:8">
-      <c r="A99" s="8"/>
-      <c r="B99" s="8"/>
-      <c r="C99" s="8"/>
-      <c r="D99" s="8"/>
-      <c r="E99" s="8"/>
-      <c r="F99" s="8"/>
-      <c r="G99" s="8"/>
-      <c r="H99" s="8"/>
+      <c r="A99" s="9"/>
+      <c r="B99" s="9"/>
+      <c r="C99" s="9"/>
+      <c r="D99" s="9"/>
+      <c r="E99" s="9"/>
+      <c r="F99" s="9"/>
+      <c r="G99" s="9"/>
+      <c r="H99" s="9"/>
     </row>
     <row r="100" spans="1:8">
-      <c r="A100" s="8"/>
-      <c r="B100" s="8"/>
-      <c r="C100" s="8"/>
-      <c r="D100" s="8"/>
-      <c r="E100" s="8"/>
-      <c r="F100" s="8"/>
-      <c r="G100" s="8"/>
-      <c r="H100" s="8"/>
+      <c r="A100" s="9"/>
+      <c r="B100" s="9"/>
+      <c r="C100" s="9"/>
+      <c r="D100" s="9"/>
+      <c r="E100" s="9"/>
+      <c r="F100" s="9"/>
+      <c r="G100" s="9"/>
+      <c r="H100" s="9"/>
     </row>
     <row r="101" spans="1:8">
-      <c r="A101" s="8"/>
-      <c r="B101" s="8"/>
-      <c r="C101" s="8"/>
-      <c r="D101" s="8"/>
-      <c r="E101" s="8"/>
-      <c r="F101" s="8"/>
-      <c r="G101" s="8"/>
-      <c r="H101" s="8"/>
+      <c r="A101" s="9"/>
+      <c r="B101" s="9"/>
+      <c r="C101" s="9"/>
+      <c r="D101" s="9"/>
+      <c r="E101" s="9"/>
+      <c r="F101" s="9"/>
+      <c r="G101" s="9"/>
+      <c r="H101" s="9"/>
     </row>
     <row r="102" spans="1:8">
-      <c r="A102" s="8"/>
-      <c r="B102" s="8"/>
-      <c r="C102" s="8"/>
-      <c r="D102" s="8"/>
-      <c r="E102" s="8"/>
-      <c r="F102" s="8"/>
-      <c r="G102" s="8"/>
-      <c r="H102" s="8"/>
+      <c r="A102" s="9"/>
+      <c r="B102" s="9"/>
+      <c r="C102" s="9"/>
+      <c r="D102" s="9"/>
+      <c r="E102" s="9"/>
+      <c r="F102" s="9"/>
+      <c r="G102" s="9"/>
+      <c r="H102" s="9"/>
     </row>
     <row r="103" spans="1:8">
-      <c r="A103" s="8"/>
-      <c r="B103" s="8"/>
-      <c r="C103" s="8"/>
-      <c r="D103" s="8"/>
-      <c r="E103" s="8"/>
-      <c r="F103" s="8"/>
-      <c r="G103" s="8"/>
-      <c r="H103" s="8"/>
+      <c r="A103" s="9"/>
+      <c r="B103" s="9"/>
+      <c r="C103" s="9"/>
+      <c r="D103" s="9"/>
+      <c r="E103" s="9"/>
+      <c r="F103" s="9"/>
+      <c r="G103" s="9"/>
+      <c r="H103" s="9"/>
     </row>
     <row r="104" spans="1:8">
-      <c r="A104" s="8"/>
-      <c r="B104" s="8"/>
-      <c r="C104" s="8"/>
-      <c r="D104" s="8"/>
-      <c r="E104" s="8"/>
-      <c r="F104" s="8"/>
-      <c r="G104" s="8"/>
-      <c r="H104" s="8"/>
+      <c r="A104" s="9"/>
+      <c r="B104" s="9"/>
+      <c r="C104" s="9"/>
+      <c r="D104" s="9"/>
+      <c r="E104" s="9"/>
+      <c r="F104" s="9"/>
+      <c r="G104" s="9"/>
+      <c r="H104" s="9"/>
     </row>
     <row r="105" spans="1:8">
-      <c r="A105" s="8"/>
-      <c r="B105" s="8"/>
-      <c r="C105" s="8"/>
-      <c r="D105" s="8"/>
-      <c r="E105" s="8"/>
-      <c r="F105" s="8"/>
-      <c r="G105" s="8"/>
-      <c r="H105" s="8"/>
+      <c r="A105" s="9"/>
+      <c r="B105" s="9"/>
+      <c r="C105" s="9"/>
+      <c r="D105" s="9"/>
+      <c r="E105" s="9"/>
+      <c r="F105" s="9"/>
+      <c r="G105" s="9"/>
+      <c r="H105" s="9"/>
     </row>
     <row r="106" spans="1:8">
-      <c r="A106" s="8"/>
-      <c r="B106" s="8"/>
-      <c r="C106" s="8"/>
-      <c r="D106" s="8"/>
-      <c r="E106" s="8"/>
-      <c r="F106" s="8"/>
-      <c r="G106" s="8"/>
-      <c r="H106" s="8"/>
+      <c r="A106" s="9"/>
+      <c r="B106" s="9"/>
+      <c r="C106" s="9"/>
+      <c r="D106" s="9"/>
+      <c r="E106" s="9"/>
+      <c r="F106" s="9"/>
+      <c r="G106" s="9"/>
+      <c r="H106" s="9"/>
     </row>
     <row r="107" spans="1:8">
-      <c r="A107" s="8"/>
-      <c r="B107" s="8"/>
-      <c r="C107" s="8"/>
-      <c r="D107" s="8"/>
-      <c r="E107" s="8"/>
-      <c r="F107" s="8"/>
-      <c r="G107" s="8"/>
-      <c r="H107" s="8"/>
+      <c r="A107" s="9"/>
+      <c r="B107" s="9"/>
+      <c r="C107" s="9"/>
+      <c r="D107" s="9"/>
+      <c r="E107" s="9"/>
+      <c r="F107" s="9"/>
+      <c r="G107" s="9"/>
+      <c r="H107" s="9"/>
     </row>
     <row r="108" spans="1:8">
-      <c r="A108" s="8"/>
-      <c r="B108" s="8"/>
-      <c r="C108" s="8"/>
-      <c r="D108" s="8"/>
-      <c r="E108" s="8"/>
-      <c r="F108" s="8"/>
-      <c r="G108" s="8"/>
-      <c r="H108" s="8"/>
+      <c r="A108" s="9"/>
+      <c r="B108" s="9"/>
+      <c r="C108" s="9"/>
+      <c r="D108" s="9"/>
+      <c r="E108" s="9"/>
+      <c r="F108" s="9"/>
+      <c r="G108" s="9"/>
+      <c r="H108" s="9"/>
     </row>
     <row r="109" spans="1:8">
-      <c r="A109" s="8"/>
-      <c r="B109" s="8"/>
-      <c r="C109" s="8"/>
-      <c r="D109" s="8"/>
-      <c r="E109" s="8"/>
-      <c r="F109" s="8"/>
-      <c r="G109" s="8"/>
-      <c r="H109" s="8"/>
+      <c r="A109" s="9"/>
+      <c r="B109" s="9"/>
+      <c r="C109" s="9"/>
+      <c r="D109" s="9"/>
+      <c r="E109" s="9"/>
+      <c r="F109" s="9"/>
+      <c r="G109" s="9"/>
+      <c r="H109" s="9"/>
     </row>
     <row r="110" spans="1:8">
-      <c r="A110" s="8"/>
-      <c r="B110" s="8"/>
-      <c r="C110" s="8"/>
-      <c r="D110" s="8"/>
-      <c r="E110" s="8"/>
-      <c r="F110" s="8"/>
-      <c r="G110" s="8"/>
-      <c r="H110" s="8"/>
+      <c r="A110" s="9"/>
+      <c r="B110" s="9"/>
+      <c r="C110" s="9"/>
+      <c r="D110" s="9"/>
+      <c r="E110" s="9"/>
+      <c r="F110" s="9"/>
+      <c r="G110" s="9"/>
+      <c r="H110" s="9"/>
     </row>
     <row r="111" spans="1:8">
-      <c r="A111" s="8"/>
-      <c r="B111" s="8"/>
-      <c r="C111" s="8"/>
-      <c r="D111" s="8"/>
-      <c r="E111" s="8"/>
-      <c r="F111" s="8"/>
-      <c r="G111" s="8"/>
-      <c r="H111" s="8"/>
+      <c r="A111" s="9"/>
+      <c r="B111" s="9"/>
+      <c r="C111" s="9"/>
+      <c r="D111" s="9"/>
+      <c r="E111" s="9"/>
+      <c r="F111" s="9"/>
+      <c r="G111" s="9"/>
+      <c r="H111" s="9"/>
     </row>
     <row r="112" spans="1:8">
-      <c r="A112" s="8"/>
-      <c r="B112" s="8"/>
-      <c r="C112" s="8"/>
-      <c r="D112" s="8"/>
-      <c r="E112" s="8"/>
-      <c r="F112" s="8"/>
-      <c r="G112" s="8"/>
-      <c r="H112" s="8"/>
+      <c r="A112" s="9"/>
+      <c r="B112" s="9"/>
+      <c r="C112" s="9"/>
+      <c r="D112" s="9"/>
+      <c r="E112" s="9"/>
+      <c r="F112" s="9"/>
+      <c r="G112" s="9"/>
+      <c r="H112" s="9"/>
     </row>
     <row r="113" spans="1:8">
-      <c r="A113" s="8"/>
-      <c r="B113" s="8"/>
-      <c r="C113" s="8"/>
-      <c r="D113" s="8"/>
-      <c r="E113" s="8"/>
-      <c r="F113" s="8"/>
-      <c r="G113" s="8"/>
-      <c r="H113" s="8"/>
+      <c r="A113" s="9"/>
+      <c r="B113" s="9"/>
+      <c r="C113" s="9"/>
+      <c r="D113" s="9"/>
+      <c r="E113" s="9"/>
+      <c r="F113" s="9"/>
+      <c r="G113" s="9"/>
+      <c r="H113" s="9"/>
     </row>
     <row r="114" spans="1:8">
-      <c r="A114" s="8"/>
-      <c r="B114" s="8"/>
-      <c r="C114" s="8"/>
-      <c r="D114" s="8"/>
-      <c r="E114" s="8"/>
-      <c r="F114" s="8"/>
-      <c r="G114" s="8"/>
-      <c r="H114" s="8"/>
+      <c r="A114" s="9"/>
+      <c r="B114" s="9"/>
+      <c r="C114" s="9"/>
+      <c r="D114" s="9"/>
+      <c r="E114" s="9"/>
+      <c r="F114" s="9"/>
+      <c r="G114" s="9"/>
+      <c r="H114" s="9"/>
     </row>
     <row r="115" spans="1:8">
-      <c r="A115" s="8"/>
-      <c r="B115" s="8"/>
-      <c r="C115" s="8"/>
-      <c r="D115" s="8"/>
-      <c r="E115" s="8"/>
-      <c r="F115" s="8"/>
-      <c r="G115" s="8"/>
-      <c r="H115" s="8"/>
+      <c r="A115" s="9"/>
+      <c r="B115" s="9"/>
+      <c r="C115" s="9"/>
+      <c r="D115" s="9"/>
+      <c r="E115" s="9"/>
+      <c r="F115" s="9"/>
+      <c r="G115" s="9"/>
+      <c r="H115" s="9"/>
     </row>
     <row r="116" spans="1:8">
-      <c r="A116" s="8"/>
-      <c r="B116" s="8"/>
-      <c r="C116" s="8"/>
-      <c r="D116" s="8"/>
-      <c r="E116" s="8"/>
-      <c r="F116" s="8"/>
-      <c r="G116" s="8"/>
-      <c r="H116" s="8"/>
+      <c r="A116" s="9"/>
+      <c r="B116" s="9"/>
+      <c r="C116" s="9"/>
+      <c r="D116" s="9"/>
+      <c r="E116" s="9"/>
+      <c r="F116" s="9"/>
+      <c r="G116" s="9"/>
+      <c r="H116" s="9"/>
     </row>
     <row r="117" spans="1:8">
-      <c r="A117" s="8"/>
-      <c r="B117" s="8"/>
-      <c r="C117" s="8"/>
-      <c r="D117" s="8"/>
-      <c r="E117" s="8"/>
-      <c r="F117" s="8"/>
-      <c r="G117" s="8"/>
-      <c r="H117" s="8"/>
+      <c r="A117" s="9"/>
+      <c r="B117" s="9"/>
+      <c r="C117" s="9"/>
+      <c r="D117" s="9"/>
+      <c r="E117" s="9"/>
+      <c r="F117" s="9"/>
+      <c r="G117" s="9"/>
+      <c r="H117" s="9"/>
     </row>
     <row r="118" spans="1:8">
-      <c r="A118" s="8"/>
-      <c r="B118" s="8"/>
-      <c r="C118" s="8"/>
-      <c r="D118" s="8"/>
-      <c r="E118" s="8"/>
-      <c r="F118" s="8"/>
-      <c r="G118" s="8"/>
-      <c r="H118" s="8"/>
+      <c r="A118" s="9"/>
+      <c r="B118" s="9"/>
+      <c r="C118" s="9"/>
+      <c r="D118" s="9"/>
+      <c r="E118" s="9"/>
+      <c r="F118" s="9"/>
+      <c r="G118" s="9"/>
+      <c r="H118" s="9"/>
     </row>
     <row r="119" spans="1:8">
-      <c r="A119" s="8"/>
-      <c r="B119" s="8"/>
-      <c r="C119" s="8"/>
-      <c r="D119" s="8"/>
-      <c r="E119" s="8"/>
-      <c r="F119" s="8"/>
-      <c r="G119" s="8"/>
-      <c r="H119" s="8"/>
+      <c r="A119" s="9"/>
+      <c r="B119" s="9"/>
+      <c r="C119" s="9"/>
+      <c r="D119" s="9"/>
+      <c r="E119" s="9"/>
+      <c r="F119" s="9"/>
+      <c r="G119" s="9"/>
+      <c r="H119" s="9"/>
     </row>
     <row r="120" spans="1:8">
-      <c r="A120" s="8"/>
-      <c r="B120" s="8"/>
-      <c r="C120" s="8"/>
-      <c r="D120" s="8"/>
-      <c r="E120" s="8"/>
-      <c r="F120" s="8"/>
-      <c r="G120" s="8"/>
-      <c r="H120" s="8"/>
+      <c r="A120" s="9"/>
+      <c r="B120" s="9"/>
+      <c r="C120" s="9"/>
+      <c r="D120" s="9"/>
+      <c r="E120" s="9"/>
+      <c r="F120" s="9"/>
+      <c r="G120" s="9"/>
+      <c r="H120" s="9"/>
     </row>
     <row r="121" spans="1:8">
-      <c r="A121" s="8"/>
-      <c r="B121" s="8"/>
-      <c r="C121" s="8"/>
-      <c r="D121" s="8"/>
-      <c r="E121" s="8"/>
-      <c r="F121" s="8"/>
-      <c r="G121" s="8"/>
-      <c r="H121" s="8"/>
+      <c r="A121" s="9"/>
+      <c r="B121" s="9"/>
+      <c r="C121" s="9"/>
+      <c r="D121" s="9"/>
+      <c r="E121" s="9"/>
+      <c r="F121" s="9"/>
+      <c r="G121" s="9"/>
+      <c r="H121" s="9"/>
     </row>
     <row r="122" spans="1:8">
-      <c r="A122" s="8"/>
-      <c r="B122" s="8"/>
-      <c r="C122" s="8"/>
-      <c r="D122" s="8"/>
-      <c r="E122" s="8"/>
-      <c r="F122" s="8"/>
-      <c r="G122" s="8"/>
-      <c r="H122" s="8"/>
+      <c r="A122" s="9"/>
+      <c r="B122" s="9"/>
+      <c r="C122" s="9"/>
+      <c r="D122" s="9"/>
+      <c r="E122" s="9"/>
+      <c r="F122" s="9"/>
+      <c r="G122" s="9"/>
+      <c r="H122" s="9"/>
     </row>
     <row r="123" spans="1:8">
-      <c r="A123" s="8"/>
-      <c r="B123" s="8"/>
-      <c r="C123" s="8"/>
-      <c r="D123" s="8"/>
-      <c r="E123" s="8"/>
-      <c r="F123" s="8"/>
-      <c r="G123" s="8"/>
-      <c r="H123" s="8"/>
+      <c r="A123" s="9"/>
+      <c r="B123" s="9"/>
+      <c r="C123" s="9"/>
+      <c r="D123" s="9"/>
+      <c r="E123" s="9"/>
+      <c r="F123" s="9"/>
+      <c r="G123" s="9"/>
+      <c r="H123" s="9"/>
     </row>
     <row r="124" spans="1:8">
-      <c r="A124" s="8"/>
-      <c r="B124" s="8"/>
-      <c r="C124" s="8"/>
-      <c r="D124" s="8"/>
-      <c r="E124" s="8"/>
-      <c r="F124" s="8"/>
-      <c r="G124" s="8"/>
-      <c r="H124" s="8"/>
+      <c r="A124" s="9"/>
+      <c r="B124" s="9"/>
+      <c r="C124" s="9"/>
+      <c r="D124" s="9"/>
+      <c r="E124" s="9"/>
+      <c r="F124" s="9"/>
+      <c r="G124" s="9"/>
+      <c r="H124" s="9"/>
     </row>
     <row r="125" spans="1:8">
-      <c r="A125" s="8"/>
-      <c r="B125" s="8"/>
-      <c r="C125" s="8"/>
-      <c r="D125" s="8"/>
-      <c r="E125" s="8"/>
-      <c r="F125" s="8"/>
-      <c r="G125" s="8"/>
-      <c r="H125" s="8"/>
+      <c r="A125" s="9"/>
+      <c r="B125" s="9"/>
+      <c r="C125" s="9"/>
+      <c r="D125" s="9"/>
+      <c r="E125" s="9"/>
+      <c r="F125" s="9"/>
+      <c r="G125" s="9"/>
+      <c r="H125" s="9"/>
     </row>
     <row r="126" spans="1:8">
-      <c r="A126" s="8"/>
-      <c r="B126" s="8"/>
-      <c r="C126" s="8"/>
-      <c r="D126" s="8"/>
-      <c r="E126" s="8"/>
-      <c r="F126" s="8"/>
-      <c r="G126" s="8"/>
-      <c r="H126" s="8"/>
+      <c r="A126" s="9"/>
+      <c r="B126" s="9"/>
+      <c r="C126" s="9"/>
+      <c r="D126" s="9"/>
+      <c r="E126" s="9"/>
+      <c r="F126" s="9"/>
+      <c r="G126" s="9"/>
+      <c r="H126" s="9"/>
     </row>
     <row r="127" spans="1:8">
-      <c r="A127" s="8"/>
-      <c r="B127" s="8"/>
-      <c r="C127" s="8"/>
-      <c r="D127" s="8"/>
-      <c r="E127" s="8"/>
-      <c r="F127" s="8"/>
-      <c r="G127" s="8"/>
-      <c r="H127" s="8"/>
+      <c r="A127" s="9"/>
+      <c r="B127" s="9"/>
+      <c r="C127" s="9"/>
+      <c r="D127" s="9"/>
+      <c r="E127" s="9"/>
+      <c r="F127" s="9"/>
+      <c r="G127" s="9"/>
+      <c r="H127" s="9"/>
     </row>
     <row r="128" spans="1:8">
-      <c r="A128" s="8"/>
-      <c r="B128" s="8"/>
-      <c r="C128" s="8"/>
-      <c r="D128" s="8"/>
-      <c r="E128" s="8"/>
-      <c r="F128" s="8"/>
-      <c r="G128" s="8"/>
-      <c r="H128" s="8"/>
+      <c r="A128" s="9"/>
+      <c r="B128" s="9"/>
+      <c r="C128" s="9"/>
+      <c r="D128" s="9"/>
+      <c r="E128" s="9"/>
+      <c r="F128" s="9"/>
+      <c r="G128" s="9"/>
+      <c r="H128" s="9"/>
     </row>
     <row r="129" spans="1:8">
-      <c r="A129" s="8"/>
-      <c r="B129" s="8"/>
-      <c r="C129" s="8"/>
-      <c r="D129" s="8"/>
-      <c r="E129" s="8"/>
-      <c r="F129" s="8"/>
-      <c r="G129" s="8"/>
-      <c r="H129" s="8"/>
+      <c r="A129" s="9"/>
+      <c r="B129" s="9"/>
+      <c r="C129" s="9"/>
+      <c r="D129" s="9"/>
+      <c r="E129" s="9"/>
+      <c r="F129" s="9"/>
+      <c r="G129" s="9"/>
+      <c r="H129" s="9"/>
     </row>
     <row r="130" spans="1:8">
-      <c r="A130" s="8"/>
-      <c r="B130" s="8"/>
-      <c r="C130" s="8"/>
-      <c r="D130" s="8"/>
-      <c r="E130" s="8"/>
-      <c r="F130" s="8"/>
-      <c r="G130" s="8"/>
-      <c r="H130" s="8"/>
+      <c r="A130" s="9"/>
+      <c r="B130" s="9"/>
+      <c r="C130" s="9"/>
+      <c r="D130" s="9"/>
+      <c r="E130" s="9"/>
+      <c r="F130" s="9"/>
+      <c r="G130" s="9"/>
+      <c r="H130" s="9"/>
     </row>
     <row r="131" spans="1:8">
-      <c r="A131" s="8"/>
-      <c r="B131" s="8"/>
-      <c r="C131" s="8"/>
-      <c r="D131" s="8"/>
-      <c r="E131" s="8"/>
-      <c r="F131" s="8"/>
-      <c r="G131" s="8"/>
-      <c r="H131" s="8"/>
+      <c r="A131" s="9"/>
+      <c r="B131" s="9"/>
+      <c r="C131" s="9"/>
+      <c r="D131" s="9"/>
+      <c r="E131" s="9"/>
+      <c r="F131" s="9"/>
+      <c r="G131" s="9"/>
+      <c r="H131" s="9"/>
     </row>
     <row r="132" spans="1:8">
-      <c r="A132" s="8"/>
-      <c r="B132" s="8"/>
-      <c r="C132" s="8"/>
-      <c r="D132" s="8"/>
-      <c r="E132" s="8"/>
-      <c r="F132" s="8"/>
-      <c r="G132" s="8"/>
-      <c r="H132" s="8"/>
+      <c r="A132" s="9"/>
+      <c r="B132" s="9"/>
+      <c r="C132" s="9"/>
+      <c r="D132" s="9"/>
+      <c r="E132" s="9"/>
+      <c r="F132" s="9"/>
+      <c r="G132" s="9"/>
+      <c r="H132" s="9"/>
     </row>
     <row r="133" spans="1:8">
-      <c r="A133" s="8"/>
-      <c r="B133" s="8"/>
-      <c r="C133" s="8"/>
-      <c r="D133" s="8"/>
-      <c r="E133" s="8"/>
-      <c r="F133" s="8"/>
-      <c r="G133" s="8"/>
-      <c r="H133" s="8"/>
+      <c r="A133" s="9"/>
+      <c r="B133" s="9"/>
+      <c r="C133" s="9"/>
+      <c r="D133" s="9"/>
+      <c r="E133" s="9"/>
+      <c r="F133" s="9"/>
+      <c r="G133" s="9"/>
+      <c r="H133" s="9"/>
     </row>
     <row r="134" spans="1:8">
-      <c r="A134" s="8"/>
-      <c r="B134" s="8"/>
-      <c r="C134" s="8"/>
-      <c r="D134" s="8"/>
-      <c r="E134" s="8"/>
-      <c r="F134" s="8"/>
-      <c r="G134" s="8"/>
-      <c r="H134" s="8"/>
+      <c r="A134" s="9"/>
+      <c r="B134" s="9"/>
+      <c r="C134" s="9"/>
+      <c r="D134" s="9"/>
+      <c r="E134" s="9"/>
+      <c r="F134" s="9"/>
+      <c r="G134" s="9"/>
+      <c r="H134" s="9"/>
     </row>
     <row r="135" spans="1:8">
-      <c r="A135" s="8"/>
-      <c r="B135" s="8"/>
-      <c r="C135" s="8"/>
-      <c r="D135" s="8"/>
-      <c r="E135" s="8"/>
-      <c r="F135" s="8"/>
-      <c r="G135" s="8"/>
-      <c r="H135" s="8"/>
+      <c r="A135" s="9"/>
+      <c r="B135" s="9"/>
+      <c r="C135" s="9"/>
+      <c r="D135" s="9"/>
+      <c r="E135" s="9"/>
+      <c r="F135" s="9"/>
+      <c r="G135" s="9"/>
+      <c r="H135" s="9"/>
     </row>
     <row r="136" spans="1:8">
-      <c r="A136" s="8"/>
-      <c r="B136" s="8"/>
-      <c r="C136" s="8"/>
-      <c r="D136" s="8"/>
-      <c r="E136" s="8"/>
-      <c r="F136" s="8"/>
-      <c r="G136" s="8"/>
-      <c r="H136" s="8"/>
+      <c r="A136" s="9"/>
+      <c r="B136" s="9"/>
+      <c r="C136" s="9"/>
+      <c r="D136" s="9"/>
+      <c r="E136" s="9"/>
+      <c r="F136" s="9"/>
+      <c r="G136" s="9"/>
+      <c r="H136" s="9"/>
     </row>
     <row r="137" spans="1:8">
-      <c r="A137" s="8"/>
-      <c r="B137" s="8"/>
-      <c r="C137" s="8"/>
-      <c r="D137" s="8"/>
-      <c r="E137" s="8"/>
-      <c r="F137" s="8"/>
-      <c r="G137" s="8"/>
-      <c r="H137" s="8"/>
+      <c r="A137" s="9"/>
+      <c r="B137" s="9"/>
+      <c r="C137" s="9"/>
+      <c r="D137" s="9"/>
+      <c r="E137" s="9"/>
+      <c r="F137" s="9"/>
+      <c r="G137" s="9"/>
+      <c r="H137" s="9"/>
     </row>
     <row r="138" spans="1:8">
-      <c r="A138" s="8"/>
-      <c r="B138" s="8"/>
-      <c r="C138" s="8"/>
-      <c r="D138" s="8"/>
-      <c r="E138" s="8"/>
-      <c r="F138" s="8"/>
-      <c r="G138" s="8"/>
-      <c r="H138" s="8"/>
+      <c r="A138" s="9"/>
+      <c r="B138" s="9"/>
+      <c r="C138" s="9"/>
+      <c r="D138" s="9"/>
+      <c r="E138" s="9"/>
+      <c r="F138" s="9"/>
+      <c r="G138" s="9"/>
+      <c r="H138" s="9"/>
     </row>
     <row r="139" spans="1:8">
-      <c r="A139" s="8"/>
-      <c r="B139" s="8"/>
-      <c r="C139" s="8"/>
-      <c r="D139" s="8"/>
-      <c r="E139" s="8"/>
-      <c r="F139" s="8"/>
-      <c r="G139" s="8"/>
-      <c r="H139" s="8"/>
+      <c r="A139" s="9"/>
+      <c r="B139" s="9"/>
+      <c r="C139" s="9"/>
+      <c r="D139" s="9"/>
+      <c r="E139" s="9"/>
+      <c r="F139" s="9"/>
+      <c r="G139" s="9"/>
+      <c r="H139" s="9"/>
     </row>
     <row r="140" spans="1:8">
-      <c r="A140" s="8"/>
-      <c r="B140" s="8"/>
-      <c r="C140" s="8"/>
-      <c r="D140" s="8"/>
-      <c r="E140" s="8"/>
-      <c r="F140" s="8"/>
-      <c r="G140" s="8"/>
-      <c r="H140" s="8"/>
+      <c r="A140" s="9"/>
+      <c r="B140" s="9"/>
+      <c r="C140" s="9"/>
+      <c r="D140" s="9"/>
+      <c r="E140" s="9"/>
+      <c r="F140" s="9"/>
+      <c r="G140" s="9"/>
+      <c r="H140" s="9"/>
     </row>
     <row r="141" spans="1:8">
-      <c r="A141" s="8"/>
-      <c r="B141" s="8"/>
-      <c r="C141" s="8"/>
-      <c r="D141" s="8"/>
-      <c r="E141" s="8"/>
-      <c r="F141" s="8"/>
-      <c r="G141" s="8"/>
-      <c r="H141" s="8"/>
+      <c r="A141" s="9"/>
+      <c r="B141" s="9"/>
+      <c r="C141" s="9"/>
+      <c r="D141" s="9"/>
+      <c r="E141" s="9"/>
+      <c r="F141" s="9"/>
+      <c r="G141" s="9"/>
+      <c r="H141" s="9"/>
     </row>
     <row r="142" spans="1:8">
-      <c r="A142" s="8"/>
-      <c r="B142" s="8"/>
-      <c r="C142" s="8"/>
-      <c r="D142" s="8"/>
-      <c r="E142" s="8"/>
-      <c r="F142" s="8"/>
-      <c r="G142" s="8"/>
-      <c r="H142" s="8"/>
+      <c r="A142" s="9"/>
+      <c r="B142" s="9"/>
+      <c r="C142" s="9"/>
+      <c r="D142" s="9"/>
+      <c r="E142" s="9"/>
+      <c r="F142" s="9"/>
+      <c r="G142" s="9"/>
+      <c r="H142" s="9"/>
     </row>
     <row r="143" spans="1:8">
-      <c r="A143" s="8"/>
-      <c r="B143" s="8"/>
-      <c r="C143" s="8"/>
-      <c r="D143" s="8"/>
-      <c r="E143" s="8"/>
-      <c r="F143" s="8"/>
-      <c r="G143" s="8"/>
-      <c r="H143" s="8"/>
+      <c r="A143" s="9"/>
+      <c r="B143" s="9"/>
+      <c r="C143" s="9"/>
+      <c r="D143" s="9"/>
+      <c r="E143" s="9"/>
+      <c r="F143" s="9"/>
+      <c r="G143" s="9"/>
+      <c r="H143" s="9"/>
     </row>
     <row r="144" spans="1:8">
-      <c r="A144" s="8"/>
-      <c r="B144" s="8"/>
-      <c r="C144" s="8"/>
-      <c r="D144" s="8"/>
-      <c r="E144" s="8"/>
-      <c r="F144" s="8"/>
-      <c r="G144" s="8"/>
-      <c r="H144" s="8"/>
+      <c r="A144" s="9"/>
+      <c r="B144" s="9"/>
+      <c r="C144" s="9"/>
+      <c r="D144" s="9"/>
+      <c r="E144" s="9"/>
+      <c r="F144" s="9"/>
+      <c r="G144" s="9"/>
+      <c r="H144" s="9"/>
     </row>
     <row r="145" spans="1:8">
-      <c r="A145" s="8"/>
-      <c r="B145" s="8"/>
-      <c r="C145" s="8"/>
-      <c r="D145" s="8"/>
-      <c r="E145" s="8"/>
-      <c r="F145" s="8"/>
-      <c r="G145" s="8"/>
-      <c r="H145" s="8"/>
+      <c r="A145" s="9"/>
+      <c r="B145" s="9"/>
+      <c r="C145" s="9"/>
+      <c r="D145" s="9"/>
+      <c r="E145" s="9"/>
+      <c r="F145" s="9"/>
+      <c r="G145" s="9"/>
+      <c r="H145" s="9"/>
     </row>
     <row r="146" spans="1:8">
-      <c r="A146" s="8"/>
-      <c r="B146" s="8"/>
-      <c r="C146" s="8"/>
-      <c r="D146" s="8"/>
-      <c r="E146" s="8"/>
-      <c r="F146" s="8"/>
-      <c r="G146" s="8"/>
-      <c r="H146" s="8"/>
+      <c r="A146" s="9"/>
+      <c r="B146" s="9"/>
+      <c r="C146" s="9"/>
+      <c r="D146" s="9"/>
+      <c r="E146" s="9"/>
+      <c r="F146" s="9"/>
+      <c r="G146" s="9"/>
+      <c r="H146" s="9"/>
     </row>
     <row r="147" spans="1:8">
-      <c r="A147" s="8"/>
-      <c r="B147" s="8"/>
-      <c r="C147" s="8"/>
-      <c r="D147" s="8"/>
-      <c r="E147" s="8"/>
-      <c r="F147" s="8"/>
-      <c r="G147" s="8"/>
-      <c r="H147" s="8"/>
+      <c r="A147" s="9"/>
+      <c r="B147" s="9"/>
+      <c r="C147" s="9"/>
+      <c r="D147" s="9"/>
+      <c r="E147" s="9"/>
+      <c r="F147" s="9"/>
+      <c r="G147" s="9"/>
+      <c r="H147" s="9"/>
     </row>
     <row r="148" spans="1:8">
-      <c r="A148" s="8"/>
-      <c r="B148" s="8"/>
-      <c r="C148" s="8"/>
-      <c r="D148" s="8"/>
-      <c r="E148" s="8"/>
-      <c r="F148" s="8"/>
-      <c r="G148" s="8"/>
-      <c r="H148" s="8"/>
+      <c r="A148" s="9"/>
+      <c r="B148" s="9"/>
+      <c r="C148" s="9"/>
+      <c r="D148" s="9"/>
+      <c r="E148" s="9"/>
+      <c r="F148" s="9"/>
+      <c r="G148" s="9"/>
+      <c r="H148" s="9"/>
     </row>
     <row r="149" spans="1:8">
-      <c r="A149" s="8"/>
-      <c r="B149" s="8"/>
-      <c r="C149" s="8"/>
-      <c r="D149" s="8"/>
-      <c r="E149" s="8"/>
-      <c r="F149" s="8"/>
-      <c r="G149" s="8"/>
-      <c r="H149" s="8"/>
+      <c r="A149" s="9"/>
+      <c r="B149" s="9"/>
+      <c r="C149" s="9"/>
+      <c r="D149" s="9"/>
+      <c r="E149" s="9"/>
+      <c r="F149" s="9"/>
+      <c r="G149" s="9"/>
+      <c r="H149" s="9"/>
     </row>
     <row r="150" spans="1:8">
-      <c r="A150" s="8"/>
-      <c r="B150" s="8"/>
-      <c r="C150" s="8"/>
-      <c r="D150" s="8"/>
-      <c r="E150" s="8"/>
-      <c r="F150" s="8"/>
-      <c r="G150" s="8"/>
-      <c r="H150" s="8"/>
+      <c r="A150" s="9"/>
+      <c r="B150" s="9"/>
+      <c r="C150" s="9"/>
+      <c r="D150" s="9"/>
+      <c r="E150" s="9"/>
+      <c r="F150" s="9"/>
+      <c r="G150" s="9"/>
+      <c r="H150" s="9"/>
     </row>
     <row r="151" spans="1:8">
-      <c r="A151" s="8"/>
-      <c r="B151" s="8"/>
-      <c r="C151" s="8"/>
-      <c r="D151" s="8"/>
-      <c r="E151" s="8"/>
-      <c r="F151" s="8"/>
-      <c r="G151" s="8"/>
-      <c r="H151" s="8"/>
+      <c r="A151" s="9"/>
+      <c r="B151" s="9"/>
+      <c r="C151" s="9"/>
+      <c r="D151" s="9"/>
+      <c r="E151" s="9"/>
+      <c r="F151" s="9"/>
+      <c r="G151" s="9"/>
+      <c r="H151" s="9"/>
     </row>
     <row r="152" spans="1:8">
-      <c r="A152" s="8"/>
-      <c r="B152" s="8"/>
-      <c r="C152" s="8"/>
-      <c r="D152" s="8"/>
-      <c r="E152" s="8"/>
-      <c r="F152" s="8"/>
-      <c r="G152" s="8"/>
-      <c r="H152" s="8"/>
+      <c r="A152" s="9"/>
+      <c r="B152" s="9"/>
+      <c r="C152" s="9"/>
+      <c r="D152" s="9"/>
+      <c r="E152" s="9"/>
+      <c r="F152" s="9"/>
+      <c r="G152" s="9"/>
+      <c r="H152" s="9"/>
     </row>
     <row r="153" spans="1:8">
-      <c r="A153" s="8"/>
-      <c r="B153" s="8"/>
-      <c r="C153" s="8"/>
-      <c r="D153" s="8"/>
-      <c r="E153" s="8"/>
-      <c r="F153" s="8"/>
-      <c r="G153" s="8"/>
-      <c r="H153" s="8"/>
+      <c r="A153" s="9"/>
+      <c r="B153" s="9"/>
+      <c r="C153" s="9"/>
+      <c r="D153" s="9"/>
+      <c r="E153" s="9"/>
+      <c r="F153" s="9"/>
+      <c r="G153" s="9"/>
+      <c r="H153" s="9"/>
     </row>
     <row r="154" spans="1:8">
-      <c r="A154" s="8"/>
-      <c r="B154" s="8"/>
-      <c r="C154" s="8"/>
-      <c r="D154" s="8"/>
-      <c r="E154" s="8"/>
-      <c r="F154" s="8"/>
-      <c r="G154" s="8"/>
-      <c r="H154" s="8"/>
+      <c r="A154" s="9"/>
+      <c r="B154" s="9"/>
+      <c r="C154" s="9"/>
+      <c r="D154" s="9"/>
+      <c r="E154" s="9"/>
+      <c r="F154" s="9"/>
+      <c r="G154" s="9"/>
+      <c r="H154" s="9"/>
     </row>
     <row r="155" spans="1:8">
-      <c r="A155" s="8"/>
-      <c r="B155" s="8"/>
-      <c r="C155" s="8"/>
-      <c r="D155" s="8"/>
-      <c r="E155" s="8"/>
-      <c r="F155" s="8"/>
-      <c r="G155" s="8"/>
-      <c r="H155" s="8"/>
+      <c r="A155" s="9"/>
+      <c r="B155" s="9"/>
+      <c r="C155" s="9"/>
+      <c r="D155" s="9"/>
+      <c r="E155" s="9"/>
+      <c r="F155" s="9"/>
+      <c r="G155" s="9"/>
+      <c r="H155" s="9"/>
     </row>
     <row r="156" spans="1:8">
-      <c r="A156" s="8"/>
-      <c r="B156" s="8"/>
-      <c r="C156" s="8"/>
-      <c r="D156" s="8"/>
-      <c r="E156" s="8"/>
-      <c r="F156" s="8"/>
-      <c r="G156" s="8"/>
-      <c r="H156" s="8"/>
+      <c r="A156" s="9"/>
+      <c r="B156" s="9"/>
+      <c r="C156" s="9"/>
+      <c r="D156" s="9"/>
+      <c r="E156" s="9"/>
+      <c r="F156" s="9"/>
+      <c r="G156" s="9"/>
+      <c r="H156" s="9"/>
     </row>
     <row r="157" spans="1:8">
-      <c r="A157" s="8"/>
-      <c r="B157" s="8"/>
-      <c r="C157" s="8"/>
-      <c r="D157" s="8"/>
-      <c r="E157" s="8"/>
-      <c r="F157" s="8"/>
-      <c r="G157" s="8"/>
-      <c r="H157" s="8"/>
+      <c r="A157" s="9"/>
+      <c r="B157" s="9"/>
+      <c r="C157" s="9"/>
+      <c r="D157" s="9"/>
+      <c r="E157" s="9"/>
+      <c r="F157" s="9"/>
+      <c r="G157" s="9"/>
+      <c r="H157" s="9"/>
     </row>
     <row r="158" spans="1:8">
-      <c r="A158" s="8"/>
-      <c r="B158" s="8"/>
-      <c r="C158" s="8"/>
-      <c r="D158" s="8"/>
-      <c r="E158" s="8"/>
-      <c r="F158" s="8"/>
-      <c r="G158" s="8"/>
-      <c r="H158" s="8"/>
+      <c r="A158" s="9"/>
+      <c r="B158" s="9"/>
+      <c r="C158" s="9"/>
+      <c r="D158" s="9"/>
+      <c r="E158" s="9"/>
+      <c r="F158" s="9"/>
+      <c r="G158" s="9"/>
+      <c r="H158" s="9"/>
     </row>
     <row r="159" spans="1:8">
-      <c r="A159" s="8"/>
-      <c r="B159" s="8"/>
-      <c r="C159" s="8"/>
-      <c r="D159" s="8"/>
-      <c r="E159" s="8"/>
-      <c r="F159" s="8"/>
-      <c r="G159" s="8"/>
-      <c r="H159" s="8"/>
+      <c r="A159" s="9"/>
+      <c r="B159" s="9"/>
+      <c r="C159" s="9"/>
+      <c r="D159" s="9"/>
+      <c r="E159" s="9"/>
+      <c r="F159" s="9"/>
+      <c r="G159" s="9"/>
+      <c r="H159" s="9"/>
     </row>
     <row r="160" spans="1:8">
-      <c r="A160" s="8"/>
-      <c r="B160" s="8"/>
-      <c r="C160" s="8"/>
-      <c r="D160" s="8"/>
-      <c r="E160" s="8"/>
-      <c r="F160" s="8"/>
-      <c r="G160" s="8"/>
-      <c r="H160" s="8"/>
+      <c r="A160" s="9"/>
+      <c r="B160" s="9"/>
+      <c r="C160" s="9"/>
+      <c r="D160" s="9"/>
+      <c r="E160" s="9"/>
+      <c r="F160" s="9"/>
+      <c r="G160" s="9"/>
+      <c r="H160" s="9"/>
     </row>
     <row r="161" spans="1:8">
-      <c r="A161" s="8"/>
-      <c r="B161" s="8"/>
-      <c r="C161" s="8"/>
-      <c r="D161" s="8"/>
-      <c r="E161" s="8"/>
-      <c r="F161" s="8"/>
-      <c r="G161" s="8"/>
-      <c r="H161" s="8"/>
+      <c r="A161" s="9"/>
+      <c r="B161" s="9"/>
+      <c r="C161" s="9"/>
+      <c r="D161" s="9"/>
+      <c r="E161" s="9"/>
+      <c r="F161" s="9"/>
+      <c r="G161" s="9"/>
+      <c r="H161" s="9"/>
     </row>
     <row r="162" spans="1:8">
-      <c r="A162" s="8"/>
-      <c r="B162" s="8"/>
-      <c r="C162" s="8"/>
-      <c r="D162" s="8"/>
-      <c r="E162" s="8"/>
-      <c r="F162" s="8"/>
-      <c r="G162" s="8"/>
-      <c r="H162" s="8"/>
+      <c r="A162" s="9"/>
+      <c r="B162" s="9"/>
+      <c r="C162" s="9"/>
+      <c r="D162" s="9"/>
+      <c r="E162" s="9"/>
+      <c r="F162" s="9"/>
+      <c r="G162" s="9"/>
+      <c r="H162" s="9"/>
     </row>
     <row r="163" spans="1:8">
-      <c r="A163" s="8"/>
-      <c r="B163" s="8"/>
-      <c r="C163" s="8"/>
-      <c r="D163" s="8"/>
-      <c r="E163" s="8"/>
-      <c r="F163" s="8"/>
-      <c r="G163" s="8"/>
-      <c r="H163" s="8"/>
+      <c r="A163" s="9"/>
+      <c r="B163" s="9"/>
+      <c r="C163" s="9"/>
+      <c r="D163" s="9"/>
+      <c r="E163" s="9"/>
+      <c r="F163" s="9"/>
+      <c r="G163" s="9"/>
+      <c r="H163" s="9"/>
     </row>
     <row r="164" spans="1:8">
-      <c r="A164" s="8"/>
-      <c r="B164" s="8"/>
-      <c r="C164" s="8"/>
-      <c r="D164" s="8"/>
-      <c r="E164" s="8"/>
-      <c r="F164" s="8"/>
-      <c r="G164" s="8"/>
-      <c r="H164" s="8"/>
+      <c r="A164" s="9"/>
+      <c r="B164" s="9"/>
+      <c r="C164" s="9"/>
+      <c r="D164" s="9"/>
+      <c r="E164" s="9"/>
+      <c r="F164" s="9"/>
+      <c r="G164" s="9"/>
+      <c r="H164" s="9"/>
     </row>
     <row r="165" spans="1:8">
-      <c r="A165" s="8"/>
-      <c r="B165" s="8"/>
-      <c r="C165" s="8"/>
-      <c r="D165" s="8"/>
-      <c r="E165" s="8"/>
-      <c r="F165" s="8"/>
-      <c r="G165" s="8"/>
-      <c r="H165" s="8"/>
+      <c r="A165" s="9"/>
+      <c r="B165" s="9"/>
+      <c r="C165" s="9"/>
+      <c r="D165" s="9"/>
+      <c r="E165" s="9"/>
+      <c r="F165" s="9"/>
+      <c r="G165" s="9"/>
+      <c r="H165" s="9"/>
     </row>
     <row r="166" spans="1:8">
-      <c r="A166" s="8"/>
-      <c r="B166" s="8"/>
-      <c r="C166" s="8"/>
-      <c r="D166" s="8"/>
-      <c r="E166" s="8"/>
-      <c r="F166" s="8"/>
-      <c r="G166" s="8"/>
-      <c r="H166" s="8"/>
+      <c r="A166" s="9"/>
+      <c r="B166" s="9"/>
+      <c r="C166" s="9"/>
+      <c r="D166" s="9"/>
+      <c r="E166" s="9"/>
+      <c r="F166" s="9"/>
+      <c r="G166" s="9"/>
+      <c r="H166" s="9"/>
     </row>
     <row r="167" spans="1:8">
-      <c r="A167" s="8"/>
-      <c r="B167" s="8"/>
-      <c r="C167" s="8"/>
-      <c r="D167" s="8"/>
-      <c r="E167" s="8"/>
-      <c r="F167" s="8"/>
-      <c r="G167" s="8"/>
-      <c r="H167" s="8"/>
+      <c r="A167" s="9"/>
+      <c r="B167" s="9"/>
+      <c r="C167" s="9"/>
+      <c r="D167" s="9"/>
+      <c r="E167" s="9"/>
+      <c r="F167" s="9"/>
+      <c r="G167" s="9"/>
+      <c r="H167" s="9"/>
     </row>
     <row r="168" spans="1:8">
-      <c r="A168" s="8"/>
-      <c r="B168" s="8"/>
-      <c r="C168" s="8"/>
-      <c r="D168" s="8"/>
-      <c r="E168" s="8"/>
-      <c r="F168" s="8"/>
-      <c r="G168" s="8"/>
-      <c r="H168" s="8"/>
+      <c r="A168" s="9"/>
+      <c r="B168" s="9"/>
+      <c r="C168" s="9"/>
+      <c r="D168" s="9"/>
+      <c r="E168" s="9"/>
+      <c r="F168" s="9"/>
+      <c r="G168" s="9"/>
+      <c r="H168" s="9"/>
     </row>
     <row r="169" spans="1:8">
-      <c r="A169" s="8"/>
-      <c r="B169" s="8"/>
-      <c r="C169" s="8"/>
-      <c r="D169" s="8"/>
-      <c r="E169" s="8"/>
-      <c r="F169" s="8"/>
-      <c r="G169" s="8"/>
-      <c r="H169" s="8"/>
+      <c r="A169" s="9"/>
+      <c r="B169" s="9"/>
+      <c r="C169" s="9"/>
+      <c r="D169" s="9"/>
+      <c r="E169" s="9"/>
+      <c r="F169" s="9"/>
+      <c r="G169" s="9"/>
+      <c r="H169" s="9"/>
     </row>
     <row r="170" spans="1:8">
-      <c r="A170" s="8"/>
-      <c r="B170" s="8"/>
-      <c r="C170" s="8"/>
-      <c r="D170" s="8"/>
-      <c r="E170" s="8"/>
-      <c r="F170" s="8"/>
-      <c r="G170" s="8"/>
-      <c r="H170" s="8"/>
+      <c r="A170" s="9"/>
+      <c r="B170" s="9"/>
+      <c r="C170" s="9"/>
+      <c r="D170" s="9"/>
+      <c r="E170" s="9"/>
+      <c r="F170" s="9"/>
+      <c r="G170" s="9"/>
+      <c r="H170" s="9"/>
     </row>
     <row r="171" spans="1:8">
-      <c r="A171" s="8"/>
-      <c r="B171" s="8"/>
-      <c r="C171" s="8"/>
-      <c r="D171" s="8"/>
-      <c r="E171" s="8"/>
-      <c r="F171" s="8"/>
-      <c r="G171" s="8"/>
-      <c r="H171" s="8"/>
+      <c r="A171" s="9"/>
+      <c r="B171" s="9"/>
+      <c r="C171" s="9"/>
+      <c r="D171" s="9"/>
+      <c r="E171" s="9"/>
+      <c r="F171" s="9"/>
+      <c r="G171" s="9"/>
+      <c r="H171" s="9"/>
     </row>
     <row r="172" spans="1:8">
-      <c r="A172" s="8"/>
-      <c r="B172" s="8"/>
-      <c r="C172" s="8"/>
-      <c r="D172" s="8"/>
-      <c r="E172" s="8"/>
-      <c r="F172" s="8"/>
-      <c r="G172" s="8"/>
-      <c r="H172" s="8"/>
+      <c r="A172" s="9"/>
+      <c r="B172" s="9"/>
+      <c r="C172" s="9"/>
+      <c r="D172" s="9"/>
+      <c r="E172" s="9"/>
+      <c r="F172" s="9"/>
+      <c r="G172" s="9"/>
+      <c r="H172" s="9"/>
     </row>
     <row r="173" spans="1:8">
-      <c r="A173" s="8"/>
-      <c r="B173" s="8"/>
-      <c r="C173" s="8"/>
-      <c r="D173" s="8"/>
-      <c r="E173" s="8"/>
-      <c r="F173" s="8"/>
-      <c r="G173" s="8"/>
-      <c r="H173" s="8"/>
+      <c r="A173" s="9"/>
+      <c r="B173" s="9"/>
+      <c r="C173" s="9"/>
+      <c r="D173" s="9"/>
+      <c r="E173" s="9"/>
+      <c r="F173" s="9"/>
+      <c r="G173" s="9"/>
+      <c r="H173" s="9"/>
     </row>
     <row r="174" spans="1:8">
-      <c r="A174" s="8"/>
-      <c r="B174" s="8"/>
-      <c r="C174" s="8"/>
-      <c r="D174" s="8"/>
-      <c r="E174" s="8"/>
-      <c r="F174" s="8"/>
-      <c r="G174" s="8"/>
-      <c r="H174" s="8"/>
+      <c r="A174" s="9"/>
+      <c r="B174" s="9"/>
+      <c r="C174" s="9"/>
+      <c r="D174" s="9"/>
+      <c r="E174" s="9"/>
+      <c r="F174" s="9"/>
+      <c r="G174" s="9"/>
+      <c r="H174" s="9"/>
     </row>
     <row r="175" spans="1:8">
-      <c r="A175" s="8"/>
-      <c r="B175" s="8"/>
-      <c r="C175" s="8"/>
-      <c r="D175" s="8"/>
-      <c r="E175" s="8"/>
-      <c r="F175" s="8"/>
-      <c r="G175" s="8"/>
-      <c r="H175" s="8"/>
+      <c r="A175" s="9"/>
+      <c r="B175" s="9"/>
+      <c r="C175" s="9"/>
+      <c r="D175" s="9"/>
+      <c r="E175" s="9"/>
+      <c r="F175" s="9"/>
+      <c r="G175" s="9"/>
+      <c r="H175" s="9"/>
     </row>
     <row r="176" spans="1:8">
-      <c r="A176" s="8"/>
-      <c r="B176" s="8"/>
-      <c r="C176" s="8"/>
-      <c r="D176" s="8"/>
-      <c r="E176" s="8"/>
-      <c r="F176" s="8"/>
-      <c r="G176" s="8"/>
-      <c r="H176" s="8"/>
+      <c r="A176" s="9"/>
+      <c r="B176" s="9"/>
+      <c r="C176" s="9"/>
+      <c r="D176" s="9"/>
+      <c r="E176" s="9"/>
+      <c r="F176" s="9"/>
+      <c r="G176" s="9"/>
+      <c r="H176" s="9"/>
     </row>
     <row r="177" spans="1:8">
-      <c r="A177" s="8"/>
-      <c r="B177" s="8"/>
-      <c r="C177" s="8"/>
-      <c r="D177" s="8"/>
-      <c r="E177" s="8"/>
-      <c r="F177" s="8"/>
-      <c r="G177" s="8"/>
-      <c r="H177" s="8"/>
+      <c r="A177" s="9"/>
+      <c r="B177" s="9"/>
+      <c r="C177" s="9"/>
+      <c r="D177" s="9"/>
+      <c r="E177" s="9"/>
+      <c r="F177" s="9"/>
+      <c r="G177" s="9"/>
+      <c r="H177" s="9"/>
     </row>
     <row r="178" spans="1:8">
-      <c r="A178" s="8"/>
-      <c r="B178" s="8"/>
-      <c r="C178" s="8"/>
-      <c r="D178" s="8"/>
-      <c r="E178" s="8"/>
-      <c r="F178" s="8"/>
-      <c r="G178" s="8"/>
-      <c r="H178" s="8"/>
+      <c r="A178" s="9"/>
+      <c r="B178" s="9"/>
+      <c r="C178" s="9"/>
+      <c r="D178" s="9"/>
+      <c r="E178" s="9"/>
+      <c r="F178" s="9"/>
+      <c r="G178" s="9"/>
+      <c r="H178" s="9"/>
     </row>
     <row r="179" spans="1:8">
-      <c r="A179" s="8"/>
-      <c r="B179" s="8"/>
-      <c r="C179" s="8"/>
-      <c r="D179" s="8"/>
-      <c r="E179" s="8"/>
-      <c r="F179" s="8"/>
-      <c r="G179" s="8"/>
-      <c r="H179" s="8"/>
+      <c r="A179" s="9"/>
+      <c r="B179" s="9"/>
+      <c r="C179" s="9"/>
+      <c r="D179" s="9"/>
+      <c r="E179" s="9"/>
+      <c r="F179" s="9"/>
+      <c r="G179" s="9"/>
+      <c r="H179" s="9"/>
     </row>
     <row r="180" spans="1:8">
-      <c r="A180" s="8"/>
-      <c r="B180" s="8"/>
-      <c r="C180" s="8"/>
-      <c r="D180" s="8"/>
-      <c r="E180" s="8"/>
-      <c r="F180" s="8"/>
-      <c r="G180" s="8"/>
-      <c r="H180" s="8"/>
+      <c r="A180" s="9"/>
+      <c r="B180" s="9"/>
+      <c r="C180" s="9"/>
+      <c r="D180" s="9"/>
+      <c r="E180" s="9"/>
+      <c r="F180" s="9"/>
+      <c r="G180" s="9"/>
+      <c r="H180" s="9"/>
     </row>
     <row r="181" spans="1:8">
-      <c r="A181" s="8"/>
-      <c r="B181" s="8"/>
-      <c r="C181" s="8"/>
-      <c r="D181" s="8"/>
-      <c r="E181" s="8"/>
-      <c r="F181" s="8"/>
-      <c r="G181" s="8"/>
-      <c r="H181" s="8"/>
+      <c r="A181" s="9"/>
+      <c r="B181" s="9"/>
+      <c r="C181" s="9"/>
+      <c r="D181" s="9"/>
+      <c r="E181" s="9"/>
+      <c r="F181" s="9"/>
+      <c r="G181" s="9"/>
+      <c r="H181" s="9"/>
     </row>
     <row r="182" spans="1:8">
-      <c r="A182" s="8"/>
-      <c r="B182" s="8"/>
-      <c r="C182" s="8"/>
-      <c r="D182" s="8"/>
-      <c r="E182" s="8"/>
-      <c r="F182" s="8"/>
-      <c r="G182" s="8"/>
-      <c r="H182" s="8"/>
+      <c r="A182" s="9"/>
+      <c r="B182" s="9"/>
+      <c r="C182" s="9"/>
+      <c r="D182" s="9"/>
+      <c r="E182" s="9"/>
+      <c r="F182" s="9"/>
+      <c r="G182" s="9"/>
+      <c r="H182" s="9"/>
     </row>
     <row r="183" spans="1:8">
-      <c r="A183" s="8"/>
-      <c r="B183" s="8"/>
-      <c r="C183" s="8"/>
-      <c r="D183" s="8"/>
-      <c r="E183" s="8"/>
-      <c r="F183" s="8"/>
-      <c r="G183" s="8"/>
-      <c r="H183" s="8"/>
+      <c r="A183" s="9"/>
+      <c r="B183" s="9"/>
+      <c r="C183" s="9"/>
+      <c r="D183" s="9"/>
+      <c r="E183" s="9"/>
+      <c r="F183" s="9"/>
+      <c r="G183" s="9"/>
+      <c r="H183" s="9"/>
     </row>
     <row r="184" spans="1:8">
-      <c r="A184" s="8"/>
-      <c r="B184" s="8"/>
-      <c r="C184" s="8"/>
-      <c r="D184" s="8"/>
-      <c r="E184" s="8"/>
-      <c r="F184" s="8"/>
-      <c r="G184" s="8"/>
-      <c r="H184" s="8"/>
+      <c r="A184" s="9"/>
+      <c r="B184" s="9"/>
+      <c r="C184" s="9"/>
+      <c r="D184" s="9"/>
+      <c r="E184" s="9"/>
+      <c r="F184" s="9"/>
+      <c r="G184" s="9"/>
+      <c r="H184" s="9"/>
     </row>
     <row r="185" spans="1:8">
-      <c r="A185" s="8"/>
-      <c r="B185" s="8"/>
-      <c r="C185" s="8"/>
-      <c r="D185" s="8"/>
-      <c r="E185" s="8"/>
-      <c r="F185" s="8"/>
-      <c r="G185" s="8"/>
-      <c r="H185" s="8"/>
+      <c r="A185" s="9"/>
+      <c r="B185" s="9"/>
+      <c r="C185" s="9"/>
+      <c r="D185" s="9"/>
+      <c r="E185" s="9"/>
+      <c r="F185" s="9"/>
+      <c r="G185" s="9"/>
+      <c r="H185" s="9"/>
     </row>
     <row r="186" spans="1:8">
-      <c r="A186" s="8"/>
-      <c r="B186" s="8"/>
-      <c r="C186" s="8"/>
-      <c r="D186" s="8"/>
-      <c r="E186" s="8"/>
-      <c r="F186" s="8"/>
-      <c r="G186" s="8"/>
-      <c r="H186" s="8"/>
+      <c r="A186" s="9"/>
+      <c r="B186" s="9"/>
+      <c r="C186" s="9"/>
+      <c r="D186" s="9"/>
+      <c r="E186" s="9"/>
+      <c r="F186" s="9"/>
+      <c r="G186" s="9"/>
+      <c r="H186" s="9"/>
     </row>
     <row r="187" spans="1:8">
-      <c r="A187" s="8"/>
-      <c r="B187" s="8"/>
-      <c r="C187" s="8"/>
-      <c r="D187" s="8"/>
-      <c r="E187" s="8"/>
-      <c r="F187" s="8"/>
-      <c r="G187" s="8"/>
-      <c r="H187" s="8"/>
+      <c r="A187" s="9"/>
+      <c r="B187" s="9"/>
+      <c r="C187" s="9"/>
+      <c r="D187" s="9"/>
+      <c r="E187" s="9"/>
+      <c r="F187" s="9"/>
+      <c r="G187" s="9"/>
+      <c r="H187" s="9"/>
     </row>
     <row r="188" spans="1:8">
-      <c r="A188" s="8"/>
-      <c r="B188" s="8"/>
-      <c r="C188" s="8"/>
-      <c r="D188" s="8"/>
-      <c r="E188" s="8"/>
-      <c r="F188" s="8"/>
-      <c r="G188" s="8"/>
-      <c r="H188" s="8"/>
+      <c r="A188" s="9"/>
+      <c r="B188" s="9"/>
+      <c r="C188" s="9"/>
+      <c r="D188" s="9"/>
+      <c r="E188" s="9"/>
+      <c r="F188" s="9"/>
+      <c r="G188" s="9"/>
+      <c r="H188" s="9"/>
     </row>
     <row r="189" spans="1:8">
-      <c r="A189" s="8"/>
-      <c r="B189" s="8"/>
-      <c r="C189" s="8"/>
-      <c r="D189" s="8"/>
-      <c r="E189" s="8"/>
-      <c r="F189" s="8"/>
-      <c r="G189" s="8"/>
-      <c r="H189" s="8"/>
+      <c r="A189" s="9"/>
+      <c r="B189" s="9"/>
+      <c r="C189" s="9"/>
+      <c r="D189" s="9"/>
+      <c r="E189" s="9"/>
+      <c r="F189" s="9"/>
+      <c r="G189" s="9"/>
+      <c r="H189" s="9"/>
     </row>
     <row r="190" spans="1:8">
-      <c r="A190" s="8"/>
-      <c r="B190" s="8"/>
-      <c r="C190" s="8"/>
-      <c r="D190" s="8"/>
-      <c r="E190" s="8"/>
-      <c r="F190" s="8"/>
-      <c r="G190" s="8"/>
-      <c r="H190" s="8"/>
+      <c r="A190" s="9"/>
+      <c r="B190" s="9"/>
+      <c r="C190" s="9"/>
+      <c r="D190" s="9"/>
+      <c r="E190" s="9"/>
+      <c r="F190" s="9"/>
+      <c r="G190" s="9"/>
+      <c r="H190" s="9"/>
     </row>
     <row r="191" spans="1:8">
-      <c r="A191" s="8"/>
-      <c r="B191" s="8"/>
-      <c r="C191" s="8"/>
-      <c r="D191" s="8"/>
-      <c r="E191" s="8"/>
-      <c r="F191" s="8"/>
-      <c r="G191" s="8"/>
-      <c r="H191" s="8"/>
+      <c r="A191" s="9"/>
+      <c r="B191" s="9"/>
+      <c r="C191" s="9"/>
+      <c r="D191" s="9"/>
+      <c r="E191" s="9"/>
+      <c r="F191" s="9"/>
+      <c r="G191" s="9"/>
+      <c r="H191" s="9"/>
     </row>
     <row r="192" spans="1:8">
-      <c r="A192" s="8"/>
-      <c r="B192" s="8"/>
-      <c r="C192" s="8"/>
-      <c r="D192" s="8"/>
-      <c r="E192" s="8"/>
-      <c r="F192" s="8"/>
-      <c r="G192" s="8"/>
-      <c r="H192" s="8"/>
+      <c r="A192" s="9"/>
+      <c r="B192" s="9"/>
+      <c r="C192" s="9"/>
+      <c r="D192" s="9"/>
+      <c r="E192" s="9"/>
+      <c r="F192" s="9"/>
+      <c r="G192" s="9"/>
+      <c r="H192" s="9"/>
     </row>
     <row r="193" spans="1:8">
-      <c r="A193" s="8"/>
-      <c r="B193" s="8"/>
-      <c r="C193" s="8"/>
-      <c r="D193" s="8"/>
-      <c r="E193" s="8"/>
-      <c r="F193" s="8"/>
-      <c r="G193" s="8"/>
-      <c r="H193" s="8"/>
+      <c r="A193" s="9"/>
+      <c r="B193" s="9"/>
+      <c r="C193" s="9"/>
+      <c r="D193" s="9"/>
+      <c r="E193" s="9"/>
+      <c r="F193" s="9"/>
+      <c r="G193" s="9"/>
+      <c r="H193" s="9"/>
     </row>
     <row r="194" spans="1:8">
-      <c r="A194" s="8"/>
-      <c r="B194" s="8"/>
-      <c r="C194" s="8"/>
-      <c r="D194" s="8"/>
-      <c r="E194" s="8"/>
-      <c r="F194" s="8"/>
-      <c r="G194" s="8"/>
-      <c r="H194" s="8"/>
+      <c r="A194" s="9"/>
+      <c r="B194" s="9"/>
+      <c r="C194" s="9"/>
+      <c r="D194" s="9"/>
+      <c r="E194" s="9"/>
+      <c r="F194" s="9"/>
+      <c r="G194" s="9"/>
+      <c r="H194" s="9"/>
     </row>
     <row r="195" spans="1:8">
-      <c r="A195" s="8"/>
-      <c r="B195" s="8"/>
-      <c r="C195" s="8"/>
-      <c r="D195" s="8"/>
-      <c r="E195" s="8"/>
-      <c r="F195" s="8"/>
-      <c r="G195" s="8"/>
-      <c r="H195" s="8"/>
+      <c r="A195" s="9"/>
+      <c r="B195" s="9"/>
+      <c r="C195" s="9"/>
+      <c r="D195" s="9"/>
+      <c r="E195" s="9"/>
+      <c r="F195" s="9"/>
+      <c r="G195" s="9"/>
+      <c r="H195" s="9"/>
     </row>
     <row r="196" spans="1:8">
-      <c r="A196" s="8"/>
-      <c r="B196" s="8"/>
-      <c r="C196" s="8"/>
-      <c r="D196" s="8"/>
-      <c r="E196" s="8"/>
-      <c r="F196" s="8"/>
-      <c r="G196" s="8"/>
-      <c r="H196" s="8"/>
+      <c r="A196" s="9"/>
+      <c r="B196" s="9"/>
+      <c r="C196" s="9"/>
+      <c r="D196" s="9"/>
+      <c r="E196" s="9"/>
+      <c r="F196" s="9"/>
+      <c r="G196" s="9"/>
+      <c r="H196" s="9"/>
     </row>
     <row r="197" spans="1:8">
-      <c r="A197" s="8"/>
-      <c r="B197" s="8"/>
-      <c r="C197" s="8"/>
-      <c r="D197" s="8"/>
-      <c r="E197" s="8"/>
-      <c r="F197" s="8"/>
-      <c r="G197" s="8"/>
-      <c r="H197" s="8"/>
+      <c r="A197" s="9"/>
+      <c r="B197" s="9"/>
+      <c r="C197" s="9"/>
+      <c r="D197" s="9"/>
+      <c r="E197" s="9"/>
+      <c r="F197" s="9"/>
+      <c r="G197" s="9"/>
+      <c r="H197" s="9"/>
     </row>
     <row r="198" spans="1:8">
-      <c r="A198" s="8"/>
-      <c r="B198" s="8"/>
-      <c r="C198" s="8"/>
-      <c r="D198" s="8"/>
-      <c r="E198" s="8"/>
-      <c r="F198" s="8"/>
-      <c r="G198" s="8"/>
-      <c r="H198" s="8"/>
+      <c r="A198" s="9"/>
+      <c r="B198" s="9"/>
+      <c r="C198" s="9"/>
+      <c r="D198" s="9"/>
+      <c r="E198" s="9"/>
+      <c r="F198" s="9"/>
+      <c r="G198" s="9"/>
+      <c r="H198" s="9"/>
     </row>
     <row r="199" spans="1:8">
-      <c r="A199" s="8"/>
-      <c r="B199" s="8"/>
-      <c r="C199" s="8"/>
-      <c r="D199" s="8"/>
-      <c r="E199" s="8"/>
-      <c r="F199" s="8"/>
-      <c r="G199" s="8"/>
-      <c r="H199" s="8"/>
+      <c r="A199" s="9"/>
+      <c r="B199" s="9"/>
+      <c r="C199" s="9"/>
+      <c r="D199" s="9"/>
+      <c r="E199" s="9"/>
+      <c r="F199" s="9"/>
+      <c r="G199" s="9"/>
+      <c r="H199" s="9"/>
     </row>
     <row r="200" spans="1:8">
-      <c r="A200" s="8"/>
-      <c r="B200" s="8"/>
-      <c r="C200" s="8"/>
-      <c r="D200" s="8"/>
-      <c r="E200" s="8"/>
-      <c r="F200" s="8"/>
-      <c r="G200" s="8"/>
-      <c r="H200" s="8"/>
+      <c r="A200" s="9"/>
+      <c r="B200" s="9"/>
+      <c r="C200" s="9"/>
+      <c r="D200" s="9"/>
+      <c r="E200" s="9"/>
+      <c r="F200" s="9"/>
+      <c r="G200" s="9"/>
+      <c r="H200" s="9"/>
     </row>
     <row r="201" spans="1:8">
-      <c r="A201" s="8"/>
-      <c r="B201" s="8"/>
-      <c r="C201" s="8"/>
-      <c r="D201" s="8"/>
-      <c r="E201" s="8"/>
-      <c r="F201" s="8"/>
-      <c r="G201" s="8"/>
-      <c r="H201" s="8"/>
+      <c r="A201" s="9"/>
+      <c r="B201" s="9"/>
+      <c r="C201" s="9"/>
+      <c r="D201" s="9"/>
+      <c r="E201" s="9"/>
+      <c r="F201" s="9"/>
+      <c r="G201" s="9"/>
+      <c r="H201" s="9"/>
     </row>
     <row r="202" spans="1:8">
-      <c r="A202" s="8"/>
-      <c r="B202" s="8"/>
-      <c r="C202" s="8"/>
-      <c r="D202" s="8"/>
-      <c r="E202" s="8"/>
-      <c r="F202" s="8"/>
-      <c r="G202" s="8"/>
-      <c r="H202" s="8"/>
+      <c r="A202" s="9"/>
+      <c r="B202" s="9"/>
+      <c r="C202" s="9"/>
+      <c r="D202" s="9"/>
+      <c r="E202" s="9"/>
+      <c r="F202" s="9"/>
+      <c r="G202" s="9"/>
+      <c r="H202" s="9"/>
     </row>
     <row r="203" spans="1:8">
-      <c r="A203" s="8"/>
-      <c r="B203" s="8"/>
-      <c r="C203" s="8"/>
-      <c r="D203" s="8"/>
-      <c r="E203" s="8"/>
-      <c r="F203" s="8"/>
-      <c r="G203" s="8"/>
-      <c r="H203" s="8"/>
+      <c r="A203" s="9"/>
+      <c r="B203" s="9"/>
+      <c r="C203" s="9"/>
+      <c r="D203" s="9"/>
+      <c r="E203" s="9"/>
+      <c r="F203" s="9"/>
+      <c r="G203" s="9"/>
+      <c r="H203" s="9"/>
     </row>
     <row r="204" spans="1:8">
-      <c r="A204" s="8"/>
-      <c r="B204" s="8"/>
-      <c r="C204" s="8"/>
-      <c r="D204" s="8"/>
-      <c r="E204" s="8"/>
-      <c r="F204" s="8"/>
-      <c r="G204" s="8"/>
-      <c r="H204" s="8"/>
+      <c r="A204" s="9"/>
+      <c r="B204" s="9"/>
+      <c r="C204" s="9"/>
+      <c r="D204" s="9"/>
+      <c r="E204" s="9"/>
+      <c r="F204" s="9"/>
+      <c r="G204" s="9"/>
+      <c r="H204" s="9"/>
     </row>
     <row r="205" spans="1:8">
-      <c r="A205" s="8"/>
-      <c r="B205" s="8"/>
-      <c r="C205" s="8"/>
-      <c r="D205" s="8"/>
-      <c r="E205" s="8"/>
-      <c r="F205" s="8"/>
-      <c r="G205" s="8"/>
-      <c r="H205" s="8"/>
+      <c r="A205" s="9"/>
+      <c r="B205" s="9"/>
+      <c r="C205" s="9"/>
+      <c r="D205" s="9"/>
+      <c r="E205" s="9"/>
+      <c r="F205" s="9"/>
+      <c r="G205" s="9"/>
+      <c r="H205" s="9"/>
     </row>
     <row r="206" spans="1:8">
-      <c r="A206" s="8"/>
-      <c r="B206" s="8"/>
-      <c r="C206" s="8"/>
-      <c r="D206" s="8"/>
-      <c r="E206" s="8"/>
-      <c r="F206" s="8"/>
-      <c r="G206" s="8"/>
-      <c r="H206" s="8"/>
+      <c r="A206" s="9"/>
+      <c r="B206" s="9"/>
+      <c r="C206" s="9"/>
+      <c r="D206" s="9"/>
+      <c r="E206" s="9"/>
+      <c r="F206" s="9"/>
+      <c r="G206" s="9"/>
+      <c r="H206" s="9"/>
     </row>
     <row r="207" spans="1:8">
-      <c r="A207" s="8"/>
-      <c r="B207" s="8"/>
-      <c r="C207" s="8"/>
-      <c r="D207" s="8"/>
-      <c r="E207" s="8"/>
-      <c r="F207" s="8"/>
-      <c r="G207" s="8"/>
-      <c r="H207" s="8"/>
+      <c r="A207" s="9"/>
+      <c r="B207" s="9"/>
+      <c r="C207" s="9"/>
+      <c r="D207" s="9"/>
+      <c r="E207" s="9"/>
+      <c r="F207" s="9"/>
+      <c r="G207" s="9"/>
+      <c r="H207" s="9"/>
     </row>
     <row r="208" spans="1:8">
-      <c r="A208" s="8"/>
-      <c r="B208" s="8"/>
-      <c r="C208" s="8"/>
-      <c r="D208" s="8"/>
-      <c r="E208" s="8"/>
-      <c r="F208" s="8"/>
-      <c r="G208" s="8"/>
-      <c r="H208" s="8"/>
+      <c r="A208" s="9"/>
+      <c r="B208" s="9"/>
+      <c r="C208" s="9"/>
+      <c r="D208" s="9"/>
+      <c r="E208" s="9"/>
+      <c r="F208" s="9"/>
+      <c r="G208" s="9"/>
+      <c r="H208" s="9"/>
     </row>
     <row r="209" spans="1:8">
-      <c r="A209" s="8"/>
-      <c r="B209" s="8"/>
-      <c r="C209" s="8"/>
-      <c r="D209" s="8"/>
-      <c r="E209" s="8"/>
-      <c r="F209" s="8"/>
-      <c r="G209" s="8"/>
-      <c r="H209" s="8"/>
+      <c r="A209" s="9"/>
+      <c r="B209" s="9"/>
+      <c r="C209" s="9"/>
+      <c r="D209" s="9"/>
+      <c r="E209" s="9"/>
+      <c r="F209" s="9"/>
+      <c r="G209" s="9"/>
+      <c r="H209" s="9"/>
     </row>
     <row r="210" spans="1:8">
-      <c r="A210" s="8"/>
-      <c r="B210" s="8"/>
-      <c r="C210" s="8"/>
-      <c r="D210" s="8"/>
-      <c r="E210" s="8"/>
-      <c r="F210" s="8"/>
-      <c r="G210" s="8"/>
-      <c r="H210" s="8"/>
+      <c r="A210" s="9"/>
+      <c r="B210" s="9"/>
+      <c r="C210" s="9"/>
+      <c r="D210" s="9"/>
+      <c r="E210" s="9"/>
+      <c r="F210" s="9"/>
+      <c r="G210" s="9"/>
+      <c r="H210" s="9"/>
     </row>
     <row r="211" spans="1:8">
-      <c r="A211" s="8"/>
-      <c r="B211" s="8"/>
-      <c r="C211" s="8"/>
-      <c r="D211" s="8"/>
-      <c r="E211" s="8"/>
-      <c r="F211" s="8"/>
-      <c r="G211" s="8"/>
-      <c r="H211" s="8"/>
+      <c r="A211" s="9"/>
+      <c r="B211" s="9"/>
+      <c r="C211" s="9"/>
+      <c r="D211" s="9"/>
+      <c r="E211" s="9"/>
+      <c r="F211" s="9"/>
+      <c r="G211" s="9"/>
+      <c r="H211" s="9"/>
     </row>
     <row r="212" spans="1:8">
-      <c r="A212" s="8"/>
-      <c r="B212" s="8"/>
-      <c r="C212" s="8"/>
-      <c r="D212" s="8"/>
-      <c r="E212" s="8"/>
-      <c r="F212" s="8"/>
-      <c r="G212" s="8"/>
-      <c r="H212" s="8"/>
+      <c r="A212" s="9"/>
+      <c r="B212" s="9"/>
+      <c r="C212" s="9"/>
+      <c r="D212" s="9"/>
+      <c r="E212" s="9"/>
+      <c r="F212" s="9"/>
+      <c r="G212" s="9"/>
+      <c r="H212" s="9"/>
     </row>
     <row r="213" spans="1:8">
-      <c r="A213" s="8"/>
-      <c r="B213" s="8"/>
-      <c r="C213" s="8"/>
-      <c r="D213" s="8"/>
-      <c r="E213" s="8"/>
-      <c r="F213" s="8"/>
-      <c r="G213" s="8"/>
-      <c r="H213" s="8"/>
+      <c r="A213" s="9"/>
+      <c r="B213" s="9"/>
+      <c r="C213" s="9"/>
+      <c r="D213" s="9"/>
+      <c r="E213" s="9"/>
+      <c r="F213" s="9"/>
+      <c r="G213" s="9"/>
+      <c r="H213" s="9"/>
     </row>
     <row r="214" spans="1:8">
-      <c r="A214" s="8"/>
-      <c r="B214" s="8"/>
-      <c r="C214" s="8"/>
-      <c r="D214" s="8"/>
-      <c r="E214" s="8"/>
-      <c r="F214" s="8"/>
-      <c r="G214" s="8"/>
-      <c r="H214" s="8"/>
+      <c r="A214" s="9"/>
+      <c r="B214" s="9"/>
+      <c r="C214" s="9"/>
+      <c r="D214" s="9"/>
+      <c r="E214" s="9"/>
+      <c r="F214" s="9"/>
+      <c r="G214" s="9"/>
+      <c r="H214" s="9"/>
     </row>
     <row r="215" spans="1:8">
-      <c r="A215" s="8"/>
-      <c r="B215" s="8"/>
-      <c r="C215" s="8"/>
-      <c r="D215" s="8"/>
-      <c r="E215" s="8"/>
-      <c r="F215" s="8"/>
-      <c r="G215" s="8"/>
-      <c r="H215" s="8"/>
+      <c r="A215" s="9"/>
+      <c r="B215" s="9"/>
+      <c r="C215" s="9"/>
+      <c r="D215" s="9"/>
+      <c r="E215" s="9"/>
+      <c r="F215" s="9"/>
+      <c r="G215" s="9"/>
+      <c r="H215" s="9"/>
     </row>
     <row r="216" spans="1:8">
-      <c r="A216" s="8"/>
-      <c r="B216" s="8"/>
-      <c r="C216" s="8"/>
-      <c r="D216" s="8"/>
-      <c r="E216" s="8"/>
-      <c r="F216" s="8"/>
-      <c r="G216" s="8"/>
-      <c r="H216" s="8"/>
+      <c r="A216" s="9"/>
+      <c r="B216" s="9"/>
+      <c r="C216" s="9"/>
+      <c r="D216" s="9"/>
+      <c r="E216" s="9"/>
+      <c r="F216" s="9"/>
+      <c r="G216" s="9"/>
+      <c r="H216" s="9"/>
     </row>
     <row r="217" spans="1:8">
-      <c r="A217" s="8"/>
-      <c r="B217" s="8"/>
-      <c r="C217" s="8"/>
-      <c r="D217" s="8"/>
-      <c r="E217" s="8"/>
-      <c r="F217" s="8"/>
-      <c r="G217" s="8"/>
-      <c r="H217" s="8"/>
+      <c r="A217" s="9"/>
+      <c r="B217" s="9"/>
+      <c r="C217" s="9"/>
+      <c r="D217" s="9"/>
+      <c r="E217" s="9"/>
+      <c r="F217" s="9"/>
+      <c r="G217" s="9"/>
+      <c r="H217" s="9"/>
     </row>
     <row r="218" spans="1:8">
-      <c r="A218" s="8"/>
-      <c r="B218" s="8"/>
-      <c r="C218" s="8"/>
-      <c r="D218" s="8"/>
-      <c r="E218" s="8"/>
-      <c r="F218" s="8"/>
-      <c r="G218" s="8"/>
-      <c r="H218" s="8"/>
+      <c r="A218" s="9"/>
+      <c r="B218" s="9"/>
+      <c r="C218" s="9"/>
+      <c r="D218" s="9"/>
+      <c r="E218" s="9"/>
+      <c r="F218" s="9"/>
+      <c r="G218" s="9"/>
+      <c r="H218" s="9"/>
     </row>
     <row r="219" spans="1:8">
-      <c r="A219" s="8"/>
-      <c r="B219" s="8"/>
-      <c r="C219" s="8"/>
-      <c r="D219" s="8"/>
-      <c r="E219" s="8"/>
-      <c r="F219" s="8"/>
-      <c r="G219" s="8"/>
-      <c r="H219" s="8"/>
+      <c r="A219" s="9"/>
+      <c r="B219" s="9"/>
+      <c r="C219" s="9"/>
+      <c r="D219" s="9"/>
+      <c r="E219" s="9"/>
+      <c r="F219" s="9"/>
+      <c r="G219" s="9"/>
+      <c r="H219" s="9"/>
     </row>
     <row r="220" spans="1:8">
-      <c r="A220" s="8"/>
-      <c r="B220" s="8"/>
-      <c r="C220" s="8"/>
-      <c r="D220" s="8"/>
-      <c r="E220" s="8"/>
-      <c r="F220" s="8"/>
-      <c r="G220" s="8"/>
-      <c r="H220" s="8"/>
+      <c r="A220" s="9"/>
+      <c r="B220" s="9"/>
+      <c r="C220" s="9"/>
+      <c r="D220" s="9"/>
+      <c r="E220" s="9"/>
+      <c r="F220" s="9"/>
+      <c r="G220" s="9"/>
+      <c r="H220" s="9"/>
     </row>
     <row r="221" spans="1:8">
-      <c r="A221" s="8"/>
-      <c r="B221" s="8"/>
-      <c r="C221" s="8"/>
-      <c r="D221" s="8"/>
-      <c r="E221" s="8"/>
-      <c r="F221" s="8"/>
-      <c r="G221" s="8"/>
-      <c r="H221" s="8"/>
+      <c r="A221" s="9"/>
+      <c r="B221" s="9"/>
+      <c r="C221" s="9"/>
+      <c r="D221" s="9"/>
+      <c r="E221" s="9"/>
+      <c r="F221" s="9"/>
+      <c r="G221" s="9"/>
+      <c r="H221" s="9"/>
     </row>
     <row r="222" spans="1:8">
-      <c r="A222" s="8"/>
-      <c r="B222" s="8"/>
-      <c r="C222" s="8"/>
-      <c r="D222" s="8"/>
-      <c r="E222" s="8"/>
-      <c r="F222" s="8"/>
-      <c r="G222" s="8"/>
-      <c r="H222" s="8"/>
+      <c r="A222" s="9"/>
+      <c r="B222" s="9"/>
+      <c r="C222" s="9"/>
+      <c r="D222" s="9"/>
+      <c r="E222" s="9"/>
+      <c r="F222" s="9"/>
+      <c r="G222" s="9"/>
+      <c r="H222" s="9"/>
     </row>
     <row r="223" spans="1:8">
-      <c r="A223" s="8"/>
-      <c r="B223" s="8"/>
-      <c r="C223" s="8"/>
-      <c r="D223" s="8"/>
-      <c r="E223" s="8"/>
-      <c r="F223" s="8"/>
-      <c r="G223" s="8"/>
-      <c r="H223" s="8"/>
+      <c r="A223" s="9"/>
+      <c r="B223" s="9"/>
+      <c r="C223" s="9"/>
+      <c r="D223" s="9"/>
+      <c r="E223" s="9"/>
+      <c r="F223" s="9"/>
+      <c r="G223" s="9"/>
+      <c r="H223" s="9"/>
     </row>
     <row r="224" spans="1:8">
-      <c r="A224" s="8"/>
-      <c r="B224" s="8"/>
-      <c r="C224" s="8"/>
-      <c r="D224" s="8"/>
-      <c r="E224" s="8"/>
-      <c r="F224" s="8"/>
-      <c r="G224" s="8"/>
-      <c r="H224" s="8"/>
+      <c r="A224" s="9"/>
+      <c r="B224" s="9"/>
+      <c r="C224" s="9"/>
+      <c r="D224" s="9"/>
+      <c r="E224" s="9"/>
+      <c r="F224" s="9"/>
+      <c r="G224" s="9"/>
+      <c r="H224" s="9"/>
     </row>
     <row r="225" spans="1:8">
-      <c r="A225" s="8"/>
-      <c r="B225" s="8"/>
-      <c r="C225" s="8"/>
-      <c r="D225" s="8"/>
-      <c r="E225" s="8"/>
-      <c r="F225" s="8"/>
-      <c r="G225" s="8"/>
-      <c r="H225" s="8"/>
+      <c r="A225" s="9"/>
+      <c r="B225" s="9"/>
+      <c r="C225" s="9"/>
+      <c r="D225" s="9"/>
+      <c r="E225" s="9"/>
+      <c r="F225" s="9"/>
+      <c r="G225" s="9"/>
+      <c r="H225" s="9"/>
     </row>
     <row r="226" spans="1:8">
-      <c r="A226" s="8"/>
-      <c r="B226" s="8"/>
-      <c r="C226" s="8"/>
-      <c r="D226" s="8"/>
-      <c r="E226" s="8"/>
-      <c r="F226" s="8"/>
-      <c r="G226" s="8"/>
-      <c r="H226" s="8"/>
+      <c r="A226" s="9"/>
+      <c r="B226" s="9"/>
+      <c r="C226" s="9"/>
+      <c r="D226" s="9"/>
+      <c r="E226" s="9"/>
+      <c r="F226" s="9"/>
+      <c r="G226" s="9"/>
+      <c r="H226" s="9"/>
     </row>
     <row r="227" spans="1:8">
-      <c r="A227" s="8"/>
-      <c r="B227" s="8"/>
-      <c r="C227" s="8"/>
-      <c r="D227" s="8"/>
-      <c r="E227" s="8"/>
-      <c r="F227" s="8"/>
-      <c r="G227" s="8"/>
-      <c r="H227" s="8"/>
+      <c r="A227" s="9"/>
+      <c r="B227" s="9"/>
+      <c r="C227" s="9"/>
+      <c r="D227" s="9"/>
+      <c r="E227" s="9"/>
+      <c r="F227" s="9"/>
+      <c r="G227" s="9"/>
+      <c r="H227" s="9"/>
     </row>
     <row r="228" spans="1:8">
-      <c r="A228" s="8"/>
-      <c r="B228" s="8"/>
-      <c r="C228" s="8"/>
-      <c r="D228" s="8"/>
-      <c r="E228" s="8"/>
-      <c r="F228" s="8"/>
-      <c r="G228" s="8"/>
-      <c r="H228" s="8"/>
+      <c r="A228" s="9"/>
+      <c r="B228" s="9"/>
+      <c r="C228" s="9"/>
+      <c r="D228" s="9"/>
+      <c r="E228" s="9"/>
+      <c r="F228" s="9"/>
+      <c r="G228" s="9"/>
+      <c r="H228" s="9"/>
     </row>
     <row r="229" spans="1:8">
-      <c r="A229" s="8"/>
-      <c r="B229" s="8"/>
-      <c r="C229" s="8"/>
-      <c r="D229" s="8"/>
-      <c r="E229" s="8"/>
-      <c r="F229" s="8"/>
-      <c r="G229" s="8"/>
-      <c r="H229" s="8"/>
+      <c r="A229" s="9"/>
+      <c r="B229" s="9"/>
+      <c r="C229" s="9"/>
+      <c r="D229" s="9"/>
+      <c r="E229" s="9"/>
+      <c r="F229" s="9"/>
+      <c r="G229" s="9"/>
+      <c r="H229" s="9"/>
     </row>
     <row r="230" spans="1:8">
-      <c r="A230" s="8"/>
-      <c r="B230" s="8"/>
-      <c r="C230" s="8"/>
-      <c r="D230" s="8"/>
-      <c r="E230" s="8"/>
-      <c r="F230" s="8"/>
-      <c r="G230" s="8"/>
-      <c r="H230" s="8"/>
+      <c r="A230" s="9"/>
+      <c r="B230" s="9"/>
+      <c r="C230" s="9"/>
+      <c r="D230" s="9"/>
+      <c r="E230" s="9"/>
+      <c r="F230" s="9"/>
+      <c r="G230" s="9"/>
+      <c r="H230" s="9"/>
     </row>
     <row r="231" spans="1:8">
-      <c r="A231" s="8"/>
-      <c r="B231" s="8"/>
-      <c r="C231" s="8"/>
-      <c r="D231" s="8"/>
-      <c r="E231" s="8"/>
-      <c r="F231" s="8"/>
-      <c r="G231" s="8"/>
-      <c r="H231" s="8"/>
+      <c r="A231" s="9"/>
+      <c r="B231" s="9"/>
+      <c r="C231" s="9"/>
+      <c r="D231" s="9"/>
+      <c r="E231" s="9"/>
+      <c r="F231" s="9"/>
+      <c r="G231" s="9"/>
+      <c r="H231" s="9"/>
     </row>
     <row r="232" spans="1:8">
-      <c r="A232" s="8"/>
-      <c r="B232" s="8"/>
-      <c r="C232" s="8"/>
-      <c r="D232" s="8"/>
-      <c r="E232" s="8"/>
-      <c r="F232" s="8"/>
-      <c r="G232" s="8"/>
-      <c r="H232" s="8"/>
+      <c r="A232" s="9"/>
+      <c r="B232" s="9"/>
+      <c r="C232" s="9"/>
+      <c r="D232" s="9"/>
+      <c r="E232" s="9"/>
+      <c r="F232" s="9"/>
+      <c r="G232" s="9"/>
+      <c r="H232" s="9"/>
     </row>
     <row r="233" spans="1:8">
-      <c r="A233" s="8"/>
-      <c r="B233" s="8"/>
-      <c r="C233" s="8"/>
-      <c r="D233" s="8"/>
-      <c r="E233" s="8"/>
-      <c r="F233" s="8"/>
-      <c r="G233" s="8"/>
-      <c r="H233" s="8"/>
+      <c r="A233" s="9"/>
+      <c r="B233" s="9"/>
+      <c r="C233" s="9"/>
+      <c r="D233" s="9"/>
+      <c r="E233" s="9"/>
+      <c r="F233" s="9"/>
+      <c r="G233" s="9"/>
+      <c r="H233" s="9"/>
     </row>
     <row r="234" spans="1:8">
-      <c r="A234" s="8"/>
-      <c r="B234" s="8"/>
-      <c r="C234" s="8"/>
-      <c r="D234" s="8"/>
-      <c r="E234" s="8"/>
-      <c r="F234" s="8"/>
-      <c r="G234" s="8"/>
-      <c r="H234" s="8"/>
+      <c r="A234" s="9"/>
+      <c r="B234" s="9"/>
+      <c r="C234" s="9"/>
+      <c r="D234" s="9"/>
+      <c r="E234" s="9"/>
+      <c r="F234" s="9"/>
+      <c r="G234" s="9"/>
+      <c r="H234" s="9"/>
     </row>
     <row r="235" spans="1:8">
-      <c r="A235" s="8"/>
-      <c r="B235" s="8"/>
-      <c r="C235" s="8"/>
-      <c r="D235" s="8"/>
-      <c r="E235" s="8"/>
-      <c r="F235" s="8"/>
-      <c r="G235" s="8"/>
-      <c r="H235" s="8"/>
+      <c r="A235" s="9"/>
+      <c r="B235" s="9"/>
+      <c r="C235" s="9"/>
+      <c r="D235" s="9"/>
+      <c r="E235" s="9"/>
+      <c r="F235" s="9"/>
+      <c r="G235" s="9"/>
+      <c r="H235" s="9"/>
     </row>
     <row r="236" spans="1:8">
-      <c r="A236" s="8"/>
-      <c r="B236" s="8"/>
-      <c r="C236" s="8"/>
-      <c r="D236" s="8"/>
-      <c r="E236" s="8"/>
-      <c r="F236" s="8"/>
-      <c r="G236" s="8"/>
-      <c r="H236" s="8"/>
+      <c r="A236" s="9"/>
+      <c r="B236" s="9"/>
+      <c r="C236" s="9"/>
+      <c r="D236" s="9"/>
+      <c r="E236" s="9"/>
+      <c r="F236" s="9"/>
+      <c r="G236" s="9"/>
+      <c r="H236" s="9"/>
     </row>
     <row r="237" spans="1:8">
-      <c r="A237" s="8"/>
-      <c r="B237" s="8"/>
-      <c r="C237" s="8"/>
-      <c r="D237" s="8"/>
-      <c r="E237" s="8"/>
-      <c r="F237" s="8"/>
-      <c r="G237" s="8"/>
-      <c r="H237" s="8"/>
+      <c r="A237" s="9"/>
+      <c r="B237" s="9"/>
+      <c r="C237" s="9"/>
+      <c r="D237" s="9"/>
+      <c r="E237" s="9"/>
+      <c r="F237" s="9"/>
+      <c r="G237" s="9"/>
+      <c r="H237" s="9"/>
     </row>
     <row r="238" spans="1:8">
-      <c r="A238" s="8"/>
-      <c r="B238" s="8"/>
-      <c r="C238" s="8"/>
-      <c r="D238" s="8"/>
-      <c r="E238" s="8"/>
-      <c r="F238" s="8"/>
-      <c r="G238" s="8"/>
-      <c r="H238" s="8"/>
+      <c r="A238" s="9"/>
+      <c r="B238" s="9"/>
+      <c r="C238" s="9"/>
+      <c r="D238" s="9"/>
+      <c r="E238" s="9"/>
+      <c r="F238" s="9"/>
+      <c r="G238" s="9"/>
+      <c r="H238" s="9"/>
     </row>
     <row r="239" spans="1:8">
-      <c r="A239" s="8"/>
-      <c r="B239" s="8"/>
-      <c r="C239" s="8"/>
-      <c r="D239" s="8"/>
-      <c r="E239" s="8"/>
-      <c r="F239" s="8"/>
-      <c r="G239" s="8"/>
-      <c r="H239" s="8"/>
+      <c r="A239" s="9"/>
+      <c r="B239" s="9"/>
+      <c r="C239" s="9"/>
+      <c r="D239" s="9"/>
+      <c r="E239" s="9"/>
+      <c r="F239" s="9"/>
+      <c r="G239" s="9"/>
+      <c r="H239" s="9"/>
     </row>
     <row r="240" spans="1:8">
-      <c r="A240" s="8"/>
-      <c r="B240" s="8"/>
-      <c r="C240" s="8"/>
-      <c r="D240" s="8"/>
-      <c r="E240" s="8"/>
-      <c r="F240" s="8"/>
-      <c r="G240" s="8"/>
-      <c r="H240" s="8"/>
+      <c r="A240" s="9"/>
+      <c r="B240" s="9"/>
+      <c r="C240" s="9"/>
+      <c r="D240" s="9"/>
+      <c r="E240" s="9"/>
+      <c r="F240" s="9"/>
+      <c r="G240" s="9"/>
+      <c r="H240" s="9"/>
     </row>
     <row r="241" spans="1:8">
-      <c r="A241" s="8"/>
-      <c r="B241" s="8"/>
-      <c r="C241" s="8"/>
-      <c r="D241" s="8"/>
-      <c r="E241" s="8"/>
-      <c r="F241" s="8"/>
-      <c r="G241" s="8"/>
-      <c r="H241" s="8"/>
+      <c r="A241" s="9"/>
+      <c r="B241" s="9"/>
+      <c r="C241" s="9"/>
+      <c r="D241" s="9"/>
+      <c r="E241" s="9"/>
+      <c r="F241" s="9"/>
+      <c r="G241" s="9"/>
+      <c r="H241" s="9"/>
     </row>
     <row r="242" spans="1:8">
-      <c r="A242" s="8"/>
-      <c r="B242" s="8"/>
-      <c r="C242" s="8"/>
-      <c r="D242" s="8"/>
-      <c r="E242" s="8"/>
-      <c r="F242" s="8"/>
-      <c r="G242" s="8"/>
-      <c r="H242" s="8"/>
+      <c r="A242" s="9"/>
+      <c r="B242" s="9"/>
+      <c r="C242" s="9"/>
+      <c r="D242" s="9"/>
+      <c r="E242" s="9"/>
+      <c r="F242" s="9"/>
+      <c r="G242" s="9"/>
+      <c r="H242" s="9"/>
     </row>
     <row r="243" spans="1:8">
-      <c r="A243" s="8"/>
-      <c r="B243" s="8"/>
-      <c r="C243" s="8"/>
-      <c r="D243" s="8"/>
-      <c r="E243" s="8"/>
-      <c r="F243" s="8"/>
-      <c r="G243" s="8"/>
-      <c r="H243" s="8"/>
+      <c r="A243" s="9"/>
+      <c r="B243" s="9"/>
+      <c r="C243" s="9"/>
+      <c r="D243" s="9"/>
+      <c r="E243" s="9"/>
+      <c r="F243" s="9"/>
+      <c r="G243" s="9"/>
+      <c r="H243" s="9"/>
     </row>
     <row r="244" spans="1:8">
-      <c r="A244" s="8"/>
-      <c r="B244" s="8"/>
-      <c r="C244" s="8"/>
-      <c r="D244" s="8"/>
-      <c r="E244" s="8"/>
-      <c r="F244" s="8"/>
-      <c r="G244" s="8"/>
-      <c r="H244" s="8"/>
+      <c r="A244" s="9"/>
+      <c r="B244" s="9"/>
+      <c r="C244" s="9"/>
+      <c r="D244" s="9"/>
+      <c r="E244" s="9"/>
+      <c r="F244" s="9"/>
+      <c r="G244" s="9"/>
+      <c r="H244" s="9"/>
     </row>
     <row r="245" spans="1:8">
-      <c r="A245" s="8"/>
-      <c r="B245" s="8"/>
-      <c r="C245" s="8"/>
-      <c r="D245" s="8"/>
-      <c r="E245" s="8"/>
-      <c r="F245" s="8"/>
-      <c r="G245" s="8"/>
-      <c r="H245" s="8"/>
+      <c r="A245" s="9"/>
+      <c r="B245" s="9"/>
+      <c r="C245" s="9"/>
+      <c r="D245" s="9"/>
+      <c r="E245" s="9"/>
+      <c r="F245" s="9"/>
+      <c r="G245" s="9"/>
+      <c r="H245" s="9"/>
     </row>
     <row r="246" spans="1:8">
-      <c r="A246" s="8"/>
-      <c r="B246" s="8"/>
-      <c r="C246" s="8"/>
-      <c r="D246" s="8"/>
-      <c r="E246" s="8"/>
-      <c r="F246" s="8"/>
-      <c r="G246" s="8"/>
-      <c r="H246" s="8"/>
+      <c r="A246" s="9"/>
+      <c r="B246" s="9"/>
+      <c r="C246" s="9"/>
+      <c r="D246" s="9"/>
+      <c r="E246" s="9"/>
+      <c r="F246" s="9"/>
+      <c r="G246" s="9"/>
+      <c r="H246" s="9"/>
     </row>
     <row r="247" spans="1:8">
-      <c r="A247" s="8"/>
-      <c r="B247" s="8"/>
-      <c r="C247" s="8"/>
-      <c r="D247" s="8"/>
-      <c r="E247" s="8"/>
-      <c r="F247" s="8"/>
-      <c r="G247" s="8"/>
-      <c r="H247" s="8"/>
+      <c r="A247" s="9"/>
+      <c r="B247" s="9"/>
+      <c r="C247" s="9"/>
+      <c r="D247" s="9"/>
+      <c r="E247" s="9"/>
+      <c r="F247" s="9"/>
+      <c r="G247" s="9"/>
+      <c r="H247" s="9"/>
     </row>
     <row r="248" spans="1:8">
-      <c r="A248" s="8"/>
-      <c r="B248" s="8"/>
-      <c r="C248" s="8"/>
-      <c r="D248" s="8"/>
-      <c r="E248" s="8"/>
-      <c r="F248" s="8"/>
-      <c r="G248" s="8"/>
-      <c r="H248" s="8"/>
+      <c r="A248" s="9"/>
+      <c r="B248" s="9"/>
+      <c r="C248" s="9"/>
+      <c r="D248" s="9"/>
+      <c r="E248" s="9"/>
+      <c r="F248" s="9"/>
+      <c r="G248" s="9"/>
+      <c r="H248" s="9"/>
     </row>
     <row r="249" spans="1:8">
-      <c r="A249" s="8"/>
-      <c r="B249" s="8"/>
-      <c r="C249" s="8"/>
-      <c r="D249" s="8"/>
-      <c r="E249" s="8"/>
-      <c r="F249" s="8"/>
-      <c r="G249" s="8"/>
-      <c r="H249" s="8"/>
+      <c r="A249" s="9"/>
+      <c r="B249" s="9"/>
+      <c r="C249" s="9"/>
+      <c r="D249" s="9"/>
+      <c r="E249" s="9"/>
+      <c r="F249" s="9"/>
+      <c r="G249" s="9"/>
+      <c r="H249" s="9"/>
     </row>
     <row r="250" spans="1:8">
-      <c r="A250" s="8"/>
-      <c r="B250" s="8"/>
-      <c r="C250" s="8"/>
-      <c r="D250" s="8"/>
-      <c r="E250" s="8"/>
-      <c r="F250" s="8"/>
-      <c r="G250" s="8"/>
-      <c r="H250" s="8"/>
+      <c r="A250" s="9"/>
+      <c r="B250" s="9"/>
+      <c r="C250" s="9"/>
+      <c r="D250" s="9"/>
+      <c r="E250" s="9"/>
+      <c r="F250" s="9"/>
+      <c r="G250" s="9"/>
+      <c r="H250" s="9"/>
     </row>
     <row r="251" spans="1:8">
-      <c r="A251" s="8"/>
-      <c r="B251" s="8"/>
-      <c r="C251" s="8"/>
-      <c r="D251" s="8"/>
-      <c r="E251" s="8"/>
-      <c r="F251" s="8"/>
-      <c r="G251" s="8"/>
-      <c r="H251" s="8"/>
+      <c r="A251" s="9"/>
+      <c r="B251" s="9"/>
+      <c r="C251" s="9"/>
+      <c r="D251" s="9"/>
+      <c r="E251" s="9"/>
+      <c r="F251" s="9"/>
+      <c r="G251" s="9"/>
+      <c r="H251" s="9"/>
     </row>
     <row r="252" spans="1:8">
-      <c r="A252" s="8"/>
-      <c r="B252" s="8"/>
-      <c r="C252" s="8"/>
-      <c r="D252" s="8"/>
-      <c r="E252" s="8"/>
-      <c r="F252" s="8"/>
-      <c r="G252" s="8"/>
-      <c r="H252" s="8"/>
+      <c r="A252" s="9"/>
+      <c r="B252" s="9"/>
+      <c r="C252" s="9"/>
+      <c r="D252" s="9"/>
+      <c r="E252" s="9"/>
+      <c r="F252" s="9"/>
+      <c r="G252" s="9"/>
+      <c r="H252" s="9"/>
     </row>
     <row r="253" spans="1:8">
-      <c r="A253" s="8"/>
-      <c r="B253" s="8"/>
-      <c r="C253" s="8"/>
-      <c r="D253" s="8"/>
-      <c r="E253" s="8"/>
-      <c r="F253" s="8"/>
-      <c r="G253" s="8"/>
-      <c r="H253" s="8"/>
+      <c r="A253" s="9"/>
+      <c r="B253" s="9"/>
+      <c r="C253" s="9"/>
+      <c r="D253" s="9"/>
+      <c r="E253" s="9"/>
+      <c r="F253" s="9"/>
+      <c r="G253" s="9"/>
+      <c r="H253" s="9"/>
     </row>
     <row r="254" spans="1:8">
-      <c r="A254" s="8"/>
-      <c r="B254" s="8"/>
-      <c r="C254" s="8"/>
-      <c r="D254" s="8"/>
-      <c r="E254" s="8"/>
-      <c r="F254" s="8"/>
-      <c r="G254" s="8"/>
-      <c r="H254" s="8"/>
+      <c r="A254" s="9"/>
+      <c r="B254" s="9"/>
+      <c r="C254" s="9"/>
+      <c r="D254" s="9"/>
+      <c r="E254" s="9"/>
+      <c r="F254" s="9"/>
+      <c r="G254" s="9"/>
+      <c r="H254" s="9"/>
     </row>
     <row r="255" spans="1:8">
-      <c r="A255" s="8"/>
-      <c r="B255" s="8"/>
-      <c r="C255" s="8"/>
-      <c r="D255" s="8"/>
-      <c r="E255" s="8"/>
-      <c r="F255" s="8"/>
-      <c r="G255" s="8"/>
-      <c r="H255" s="8"/>
+      <c r="A255" s="9"/>
+      <c r="B255" s="9"/>
+      <c r="C255" s="9"/>
+      <c r="D255" s="9"/>
+      <c r="E255" s="9"/>
+      <c r="F255" s="9"/>
+      <c r="G255" s="9"/>
+      <c r="H255" s="9"/>
     </row>
     <row r="256" spans="1:8">
-      <c r="A256" s="8"/>
-      <c r="B256" s="8"/>
-      <c r="C256" s="8"/>
-      <c r="D256" s="8"/>
-      <c r="E256" s="8"/>
-      <c r="F256" s="8"/>
-      <c r="G256" s="8"/>
-      <c r="H256" s="8"/>
+      <c r="A256" s="9"/>
+      <c r="B256" s="9"/>
+      <c r="C256" s="9"/>
+      <c r="D256" s="9"/>
+      <c r="E256" s="9"/>
+      <c r="F256" s="9"/>
+      <c r="G256" s="9"/>
+      <c r="H256" s="9"/>
     </row>
     <row r="257" spans="1:8">
-      <c r="A257" s="8"/>
-      <c r="B257" s="8"/>
-      <c r="C257" s="8"/>
-      <c r="D257" s="8"/>
-      <c r="E257" s="8"/>
-      <c r="F257" s="8"/>
-      <c r="G257" s="8"/>
-      <c r="H257" s="8"/>
+      <c r="A257" s="9"/>
+      <c r="B257" s="9"/>
+      <c r="C257" s="9"/>
+      <c r="D257" s="9"/>
+      <c r="E257" s="9"/>
+      <c r="F257" s="9"/>
+      <c r="G257" s="9"/>
+      <c r="H257" s="9"/>
     </row>
     <row r="258" spans="1:8">
-      <c r="A258" s="8"/>
-      <c r="B258" s="8"/>
-      <c r="C258" s="8"/>
-      <c r="D258" s="8"/>
-      <c r="E258" s="8"/>
-      <c r="F258" s="8"/>
-      <c r="G258" s="8"/>
-      <c r="H258" s="8"/>
+      <c r="A258" s="9"/>
+      <c r="B258" s="9"/>
+      <c r="C258" s="9"/>
+      <c r="D258" s="9"/>
+      <c r="E258" s="9"/>
+      <c r="F258" s="9"/>
+      <c r="G258" s="9"/>
+      <c r="H258" s="9"/>
     </row>
     <row r="259" spans="1:8">
-      <c r="A259" s="8"/>
-      <c r="B259" s="8"/>
-      <c r="C259" s="8"/>
-      <c r="D259" s="8"/>
-      <c r="E259" s="8"/>
-      <c r="F259" s="8"/>
-      <c r="G259" s="8"/>
-      <c r="H259" s="8"/>
+      <c r="A259" s="9"/>
+      <c r="B259" s="9"/>
+      <c r="C259" s="9"/>
+      <c r="D259" s="9"/>
+      <c r="E259" s="9"/>
+      <c r="F259" s="9"/>
+      <c r="G259" s="9"/>
+      <c r="H259" s="9"/>
     </row>
     <row r="260" spans="1:8">
-      <c r="A260" s="8"/>
-      <c r="B260" s="8"/>
-      <c r="C260" s="8"/>
-      <c r="D260" s="8"/>
-      <c r="E260" s="8"/>
-      <c r="F260" s="8"/>
-      <c r="G260" s="8"/>
-      <c r="H260" s="8"/>
+      <c r="A260" s="9"/>
+      <c r="B260" s="9"/>
+      <c r="C260" s="9"/>
+      <c r="D260" s="9"/>
+      <c r="E260" s="9"/>
+      <c r="F260" s="9"/>
+      <c r="G260" s="9"/>
+      <c r="H260" s="9"/>
     </row>
     <row r="261" spans="1:8">
-      <c r="A261" s="8"/>
-      <c r="B261" s="8"/>
-      <c r="C261" s="8"/>
-      <c r="D261" s="8"/>
-      <c r="E261" s="8"/>
-      <c r="F261" s="8"/>
-      <c r="G261" s="8"/>
-      <c r="H261" s="8"/>
+      <c r="A261" s="9"/>
+      <c r="B261" s="9"/>
+      <c r="C261" s="9"/>
+      <c r="D261" s="9"/>
+      <c r="E261" s="9"/>
+      <c r="F261" s="9"/>
+      <c r="G261" s="9"/>
+      <c r="H261" s="9"/>
     </row>
     <row r="262" spans="1:8">
-      <c r="A262" s="8"/>
-      <c r="B262" s="8"/>
-      <c r="C262" s="8"/>
-      <c r="D262" s="8"/>
-      <c r="E262" s="8"/>
-      <c r="F262" s="8"/>
-      <c r="G262" s="8"/>
-      <c r="H262" s="8"/>
+      <c r="A262" s="9"/>
+      <c r="B262" s="9"/>
+      <c r="C262" s="9"/>
+      <c r="D262" s="9"/>
+      <c r="E262" s="9"/>
+      <c r="F262" s="9"/>
+      <c r="G262" s="9"/>
+      <c r="H262" s="9"/>
     </row>
     <row r="263" spans="1:8">
-      <c r="A263" s="8"/>
-      <c r="B263" s="8"/>
-      <c r="C263" s="8"/>
-      <c r="D263" s="8"/>
-      <c r="E263" s="8"/>
-      <c r="F263" s="8"/>
-      <c r="G263" s="8"/>
-      <c r="H263" s="8"/>
+      <c r="A263" s="9"/>
+      <c r="B263" s="9"/>
+      <c r="C263" s="9"/>
+      <c r="D263" s="9"/>
+      <c r="E263" s="9"/>
+      <c r="F263" s="9"/>
+      <c r="G263" s="9"/>
+      <c r="H263" s="9"/>
     </row>
     <row r="264" spans="1:8">
-      <c r="A264" s="8"/>
-      <c r="B264" s="8"/>
-      <c r="C264" s="8"/>
-      <c r="D264" s="8"/>
-      <c r="E264" s="8"/>
-      <c r="F264" s="8"/>
-      <c r="G264" s="8"/>
-      <c r="H264" s="8"/>
+      <c r="A264" s="9"/>
+      <c r="B264" s="9"/>
+      <c r="C264" s="9"/>
+      <c r="D264" s="9"/>
+      <c r="E264" s="9"/>
+      <c r="F264" s="9"/>
+      <c r="G264" s="9"/>
+      <c r="H264" s="9"/>
     </row>
     <row r="265" spans="1:8">
-      <c r="A265" s="8"/>
-      <c r="B265" s="8"/>
-      <c r="C265" s="8"/>
-      <c r="D265" s="8"/>
-      <c r="E265" s="8"/>
-      <c r="F265" s="8"/>
-      <c r="G265" s="8"/>
-      <c r="H265" s="8"/>
+      <c r="A265" s="9"/>
+      <c r="B265" s="9"/>
+      <c r="C265" s="9"/>
+      <c r="D265" s="9"/>
+      <c r="E265" s="9"/>
+      <c r="F265" s="9"/>
+      <c r="G265" s="9"/>
+      <c r="H265" s="9"/>
     </row>
     <row r="266" spans="1:8">
-      <c r="A266" s="8"/>
-      <c r="B266" s="8"/>
-      <c r="C266" s="8"/>
-      <c r="D266" s="8"/>
-      <c r="E266" s="8"/>
-      <c r="F266" s="8"/>
-      <c r="G266" s="8"/>
-      <c r="H266" s="8"/>
+      <c r="A266" s="9"/>
+      <c r="B266" s="9"/>
+      <c r="C266" s="9"/>
+      <c r="D266" s="9"/>
+      <c r="E266" s="9"/>
+      <c r="F266" s="9"/>
+      <c r="G266" s="9"/>
+      <c r="H266" s="9"/>
     </row>
     <row r="267" spans="1:8">
-      <c r="A267" s="8"/>
-      <c r="B267" s="8"/>
-      <c r="C267" s="8"/>
-      <c r="D267" s="8"/>
-      <c r="E267" s="8"/>
-      <c r="F267" s="8"/>
-      <c r="G267" s="8"/>
-      <c r="H267" s="8"/>
+      <c r="A267" s="9"/>
+      <c r="B267" s="9"/>
+      <c r="C267" s="9"/>
+      <c r="D267" s="9"/>
+      <c r="E267" s="9"/>
+      <c r="F267" s="9"/>
+      <c r="G267" s="9"/>
+      <c r="H267" s="9"/>
     </row>
     <row r="268" spans="1:8">
-      <c r="A268" s="8"/>
-      <c r="B268" s="8"/>
-      <c r="C268" s="8"/>
-      <c r="D268" s="8"/>
-      <c r="E268" s="8"/>
-      <c r="F268" s="8"/>
-      <c r="G268" s="8"/>
-      <c r="H268" s="8"/>
+      <c r="A268" s="9"/>
+      <c r="B268" s="9"/>
+      <c r="C268" s="9"/>
+      <c r="D268" s="9"/>
+      <c r="E268" s="9"/>
+      <c r="F268" s="9"/>
+      <c r="G268" s="9"/>
+      <c r="H268" s="9"/>
     </row>
     <row r="269" spans="1:8">
-      <c r="A269" s="8"/>
-      <c r="B269" s="8"/>
-      <c r="C269" s="8"/>
-      <c r="D269" s="8"/>
-      <c r="E269" s="8"/>
-      <c r="F269" s="8"/>
-      <c r="G269" s="8"/>
-      <c r="H269" s="8"/>
+      <c r="A269" s="9"/>
+      <c r="B269" s="9"/>
+      <c r="C269" s="9"/>
+      <c r="D269" s="9"/>
+      <c r="E269" s="9"/>
+      <c r="F269" s="9"/>
+      <c r="G269" s="9"/>
+      <c r="H269" s="9"/>
     </row>
     <row r="270" spans="1:8">
-      <c r="A270" s="8"/>
-      <c r="B270" s="8"/>
-      <c r="C270" s="8"/>
-      <c r="D270" s="8"/>
-      <c r="E270" s="8"/>
-      <c r="F270" s="8"/>
-      <c r="G270" s="8"/>
-      <c r="H270" s="8"/>
+      <c r="A270" s="9"/>
+      <c r="B270" s="9"/>
+      <c r="C270" s="9"/>
+      <c r="D270" s="9"/>
+      <c r="E270" s="9"/>
+      <c r="F270" s="9"/>
+      <c r="G270" s="9"/>
+      <c r="H270" s="9"/>
     </row>
     <row r="271" spans="1:8">
-      <c r="A271" s="8"/>
-      <c r="B271" s="8"/>
-      <c r="C271" s="8"/>
-      <c r="D271" s="8"/>
-      <c r="E271" s="8"/>
-      <c r="F271" s="8"/>
-      <c r="G271" s="8"/>
-      <c r="H271" s="8"/>
+      <c r="A271" s="9"/>
+      <c r="B271" s="9"/>
+      <c r="C271" s="9"/>
+      <c r="D271" s="9"/>
+      <c r="E271" s="9"/>
+      <c r="F271" s="9"/>
+      <c r="G271" s="9"/>
+      <c r="H271" s="9"/>
     </row>
     <row r="272" spans="1:8">
-      <c r="A272" s="8"/>
-      <c r="B272" s="8"/>
-      <c r="C272" s="8"/>
-      <c r="D272" s="8"/>
-      <c r="E272" s="8"/>
-      <c r="F272" s="8"/>
-      <c r="G272" s="8"/>
-      <c r="H272" s="8"/>
+      <c r="A272" s="9"/>
+      <c r="B272" s="9"/>
+      <c r="C272" s="9"/>
+      <c r="D272" s="9"/>
+      <c r="E272" s="9"/>
+      <c r="F272" s="9"/>
+      <c r="G272" s="9"/>
+      <c r="H272" s="9"/>
     </row>
     <row r="273" spans="1:8">
-      <c r="A273" s="8"/>
-      <c r="B273" s="8"/>
-      <c r="C273" s="8"/>
-      <c r="D273" s="8"/>
-      <c r="E273" s="8"/>
-      <c r="F273" s="8"/>
-      <c r="G273" s="8"/>
-      <c r="H273" s="8"/>
+      <c r="A273" s="9"/>
+      <c r="B273" s="9"/>
+      <c r="C273" s="9"/>
+      <c r="D273" s="9"/>
+      <c r="E273" s="9"/>
+      <c r="F273" s="9"/>
+      <c r="G273" s="9"/>
+      <c r="H273" s="9"/>
     </row>
     <row r="274" spans="1:8">
-      <c r="A274" s="8"/>
-      <c r="B274" s="8"/>
-      <c r="C274" s="8"/>
-      <c r="D274" s="8"/>
-      <c r="E274" s="8"/>
-      <c r="F274" s="8"/>
-      <c r="G274" s="8"/>
-      <c r="H274" s="8"/>
+      <c r="A274" s="9"/>
+      <c r="B274" s="9"/>
+      <c r="C274" s="9"/>
+      <c r="D274" s="9"/>
+      <c r="E274" s="9"/>
+      <c r="F274" s="9"/>
+      <c r="G274" s="9"/>
+      <c r="H274" s="9"/>
     </row>
     <row r="275" spans="1:8">
-      <c r="A275" s="8"/>
-      <c r="B275" s="8"/>
-      <c r="C275" s="8"/>
-      <c r="D275" s="8"/>
-      <c r="E275" s="8"/>
-      <c r="F275" s="8"/>
-      <c r="G275" s="8"/>
-      <c r="H275" s="8"/>
+      <c r="A275" s="9"/>
+      <c r="B275" s="9"/>
+      <c r="C275" s="9"/>
+      <c r="D275" s="9"/>
+      <c r="E275" s="9"/>
+      <c r="F275" s="9"/>
+      <c r="G275" s="9"/>
+      <c r="H275" s="9"/>
     </row>
     <row r="276" spans="1:8">
-      <c r="A276" s="8"/>
-      <c r="B276" s="8"/>
-      <c r="C276" s="8"/>
-      <c r="D276" s="8"/>
-      <c r="E276" s="8"/>
-      <c r="F276" s="8"/>
-      <c r="G276" s="8"/>
-      <c r="H276" s="8"/>
+      <c r="A276" s="9"/>
+      <c r="B276" s="9"/>
+      <c r="C276" s="9"/>
+      <c r="D276" s="9"/>
+      <c r="E276" s="9"/>
+      <c r="F276" s="9"/>
+      <c r="G276" s="9"/>
+      <c r="H276" s="9"/>
     </row>
     <row r="277" spans="1:8">
-      <c r="A277" s="8"/>
-      <c r="B277" s="8"/>
-      <c r="C277" s="8"/>
-      <c r="D277" s="8"/>
-      <c r="E277" s="8"/>
-      <c r="F277" s="8"/>
-      <c r="G277" s="8"/>
-      <c r="H277" s="8"/>
+      <c r="A277" s="9"/>
+      <c r="B277" s="9"/>
+      <c r="C277" s="9"/>
+      <c r="D277" s="9"/>
+      <c r="E277" s="9"/>
+      <c r="F277" s="9"/>
+      <c r="G277" s="9"/>
+      <c r="H277" s="9"/>
     </row>
     <row r="278" spans="1:8">
-      <c r="A278" s="8"/>
-      <c r="B278" s="8"/>
-      <c r="C278" s="8"/>
-      <c r="D278" s="8"/>
-      <c r="E278" s="8"/>
-      <c r="F278" s="8"/>
-      <c r="G278" s="8"/>
-      <c r="H278" s="8"/>
+      <c r="A278" s="9"/>
+      <c r="B278" s="9"/>
+      <c r="C278" s="9"/>
+      <c r="D278" s="9"/>
+      <c r="E278" s="9"/>
+      <c r="F278" s="9"/>
+      <c r="G278" s="9"/>
+      <c r="H278" s="9"/>
     </row>
     <row r="279" spans="1:8">
-      <c r="A279" s="8"/>
-      <c r="B279" s="8"/>
-      <c r="C279" s="8"/>
-      <c r="D279" s="8"/>
-      <c r="E279" s="8"/>
-      <c r="F279" s="8"/>
-      <c r="G279" s="8"/>
-      <c r="H279" s="8"/>
+      <c r="A279" s="9"/>
+      <c r="B279" s="9"/>
+      <c r="C279" s="9"/>
+      <c r="D279" s="9"/>
+      <c r="E279" s="9"/>
+      <c r="F279" s="9"/>
+      <c r="G279" s="9"/>
+      <c r="H279" s="9"/>
     </row>
     <row r="280" spans="1:8">
-      <c r="A280" s="8"/>
-      <c r="B280" s="8"/>
-      <c r="C280" s="8"/>
-      <c r="D280" s="8"/>
-      <c r="E280" s="8"/>
-      <c r="F280" s="8"/>
-      <c r="G280" s="8"/>
-      <c r="H280" s="8"/>
+      <c r="A280" s="9"/>
+      <c r="B280" s="9"/>
+      <c r="C280" s="9"/>
+      <c r="D280" s="9"/>
+      <c r="E280" s="9"/>
+      <c r="F280" s="9"/>
+      <c r="G280" s="9"/>
+      <c r="H280" s="9"/>
     </row>
     <row r="281" spans="1:8">
-      <c r="A281" s="8"/>
-      <c r="B281" s="8"/>
-      <c r="C281" s="8"/>
-      <c r="D281" s="8"/>
-      <c r="E281" s="8"/>
-      <c r="F281" s="8"/>
-      <c r="G281" s="8"/>
-      <c r="H281" s="8"/>
+      <c r="A281" s="9"/>
+      <c r="B281" s="9"/>
+      <c r="C281" s="9"/>
+      <c r="D281" s="9"/>
+      <c r="E281" s="9"/>
+      <c r="F281" s="9"/>
+      <c r="G281" s="9"/>
+      <c r="H281" s="9"/>
     </row>
     <row r="282" spans="1:8">
-      <c r="A282" s="8"/>
-      <c r="B282" s="8"/>
-      <c r="C282" s="8"/>
-      <c r="D282" s="8"/>
-      <c r="E282" s="8"/>
-      <c r="F282" s="8"/>
-      <c r="G282" s="8"/>
-      <c r="H282" s="8"/>
+      <c r="A282" s="9"/>
+      <c r="B282" s="9"/>
+      <c r="C282" s="9"/>
+      <c r="D282" s="9"/>
+      <c r="E282" s="9"/>
+      <c r="F282" s="9"/>
+      <c r="G282" s="9"/>
+      <c r="H282" s="9"/>
     </row>
     <row r="283" spans="1:8">
-      <c r="A283" s="8"/>
-      <c r="B283" s="8"/>
-      <c r="C283" s="8"/>
-      <c r="D283" s="8"/>
-      <c r="E283" s="8"/>
-      <c r="F283" s="8"/>
-      <c r="G283" s="8"/>
-      <c r="H283" s="8"/>
+      <c r="A283" s="9"/>
+      <c r="B283" s="9"/>
+      <c r="C283" s="9"/>
+      <c r="D283" s="9"/>
+      <c r="E283" s="9"/>
+      <c r="F283" s="9"/>
+      <c r="G283" s="9"/>
+      <c r="H283" s="9"/>
     </row>
     <row r="284" spans="1:8">
-      <c r="A284" s="8"/>
-      <c r="B284" s="8"/>
-      <c r="C284" s="8"/>
-      <c r="D284" s="8"/>
-      <c r="E284" s="8"/>
-      <c r="F284" s="8"/>
-      <c r="G284" s="8"/>
-      <c r="H284" s="8"/>
+      <c r="A284" s="9"/>
+      <c r="B284" s="9"/>
+      <c r="C284" s="9"/>
+      <c r="D284" s="9"/>
+      <c r="E284" s="9"/>
+      <c r="F284" s="9"/>
+      <c r="G284" s="9"/>
+      <c r="H284" s="9"/>
     </row>
     <row r="285" spans="1:8">
-      <c r="A285" s="8"/>
-      <c r="B285" s="8"/>
-      <c r="C285" s="8"/>
-      <c r="D285" s="8"/>
-      <c r="E285" s="8"/>
-      <c r="F285" s="8"/>
-      <c r="G285" s="8"/>
-      <c r="H285" s="8"/>
+      <c r="A285" s="9"/>
+      <c r="B285" s="9"/>
+      <c r="C285" s="9"/>
+      <c r="D285" s="9"/>
+      <c r="E285" s="9"/>
+      <c r="F285" s="9"/>
+      <c r="G285" s="9"/>
+      <c r="H285" s="9"/>
     </row>
     <row r="286" spans="1:8">
-      <c r="A286" s="8"/>
-      <c r="B286" s="8"/>
-      <c r="C286" s="8"/>
-      <c r="D286" s="8"/>
-      <c r="E286" s="8"/>
-      <c r="F286" s="8"/>
-      <c r="G286" s="8"/>
-      <c r="H286" s="8"/>
+      <c r="A286" s="9"/>
+      <c r="B286" s="9"/>
+      <c r="C286" s="9"/>
+      <c r="D286" s="9"/>
+      <c r="E286" s="9"/>
+      <c r="F286" s="9"/>
+      <c r="G286" s="9"/>
+      <c r="H286" s="9"/>
     </row>
     <row r="287" spans="1:8">
-      <c r="A287" s="8"/>
-      <c r="B287" s="8"/>
-      <c r="C287" s="8"/>
-      <c r="D287" s="8"/>
-      <c r="E287" s="8"/>
-      <c r="F287" s="8"/>
-      <c r="G287" s="8"/>
-      <c r="H287" s="8"/>
+      <c r="A287" s="9"/>
+      <c r="B287" s="9"/>
+      <c r="C287" s="9"/>
+      <c r="D287" s="9"/>
+      <c r="E287" s="9"/>
+      <c r="F287" s="9"/>
+      <c r="G287" s="9"/>
+      <c r="H287" s="9"/>
     </row>
     <row r="288" spans="1:8">
-      <c r="A288" s="8"/>
-      <c r="B288" s="8"/>
-      <c r="C288" s="8"/>
-      <c r="D288" s="8"/>
-      <c r="E288" s="8"/>
-      <c r="F288" s="8"/>
-      <c r="G288" s="8"/>
-      <c r="H288" s="8"/>
+      <c r="A288" s="9"/>
+      <c r="B288" s="9"/>
+      <c r="C288" s="9"/>
+      <c r="D288" s="9"/>
+      <c r="E288" s="9"/>
+      <c r="F288" s="9"/>
+      <c r="G288" s="9"/>
+      <c r="H288" s="9"/>
     </row>
     <row r="289" spans="1:8">
-      <c r="A289" s="8"/>
-      <c r="B289" s="8"/>
-      <c r="C289" s="8"/>
-      <c r="D289" s="8"/>
-      <c r="E289" s="8"/>
-      <c r="F289" s="8"/>
-      <c r="G289" s="8"/>
-      <c r="H289" s="8"/>
+      <c r="A289" s="9"/>
+      <c r="B289" s="9"/>
+      <c r="C289" s="9"/>
+      <c r="D289" s="9"/>
+      <c r="E289" s="9"/>
+      <c r="F289" s="9"/>
+      <c r="G289" s="9"/>
+      <c r="H289" s="9"/>
     </row>
     <row r="290" spans="1:8">
-      <c r="A290" s="8"/>
-      <c r="B290" s="8"/>
-      <c r="C290" s="8"/>
-      <c r="D290" s="8"/>
-      <c r="E290" s="8"/>
-      <c r="F290" s="8"/>
-      <c r="G290" s="8"/>
-      <c r="H290" s="8"/>
+      <c r="A290" s="9"/>
+      <c r="B290" s="9"/>
+      <c r="C290" s="9"/>
+      <c r="D290" s="9"/>
+      <c r="E290" s="9"/>
+      <c r="F290" s="9"/>
+      <c r="G290" s="9"/>
+      <c r="H290" s="9"/>
     </row>
     <row r="291" spans="1:8">
-      <c r="A291" s="8"/>
-      <c r="B291" s="8"/>
-      <c r="C291" s="8"/>
-      <c r="D291" s="8"/>
-      <c r="E291" s="8"/>
-      <c r="F291" s="8"/>
-      <c r="G291" s="8"/>
-      <c r="H291" s="8"/>
+      <c r="A291" s="9"/>
+      <c r="B291" s="9"/>
+      <c r="C291" s="9"/>
+      <c r="D291" s="9"/>
+      <c r="E291" s="9"/>
+      <c r="F291" s="9"/>
+      <c r="G291" s="9"/>
+      <c r="H291" s="9"/>
     </row>
     <row r="292" spans="1:8">
-      <c r="A292" s="8"/>
-      <c r="B292" s="8"/>
-      <c r="C292" s="8"/>
-      <c r="D292" s="8"/>
-      <c r="E292" s="8"/>
-      <c r="F292" s="8"/>
-      <c r="G292" s="8"/>
-      <c r="H292" s="8"/>
+      <c r="A292" s="9"/>
+      <c r="B292" s="9"/>
+      <c r="C292" s="9"/>
+      <c r="D292" s="9"/>
+      <c r="E292" s="9"/>
+      <c r="F292" s="9"/>
+      <c r="G292" s="9"/>
+      <c r="H292" s="9"/>
     </row>
     <row r="293" spans="1:8">
-      <c r="A293" s="8"/>
-      <c r="B293" s="8"/>
-      <c r="C293" s="8"/>
-      <c r="D293" s="8"/>
-      <c r="E293" s="8"/>
-      <c r="F293" s="8"/>
-      <c r="G293" s="8"/>
-      <c r="H293" s="8"/>
+      <c r="A293" s="9"/>
+      <c r="B293" s="9"/>
+      <c r="C293" s="9"/>
+      <c r="D293" s="9"/>
+      <c r="E293" s="9"/>
+      <c r="F293" s="9"/>
+      <c r="G293" s="9"/>
+      <c r="H293" s="9"/>
     </row>
     <row r="294" spans="1:8">
-      <c r="A294" s="8"/>
-      <c r="B294" s="8"/>
-      <c r="C294" s="8"/>
-      <c r="D294" s="8"/>
-      <c r="E294" s="8"/>
-      <c r="F294" s="8"/>
-      <c r="G294" s="8"/>
-      <c r="H294" s="8"/>
+      <c r="A294" s="9"/>
+      <c r="B294" s="9"/>
+      <c r="C294" s="9"/>
+      <c r="D294" s="9"/>
+      <c r="E294" s="9"/>
+      <c r="F294" s="9"/>
+      <c r="G294" s="9"/>
+      <c r="H294" s="9"/>
     </row>
     <row r="295" spans="1:8">
-      <c r="A295" s="8"/>
-      <c r="B295" s="8"/>
-      <c r="C295" s="8"/>
-      <c r="D295" s="8"/>
-      <c r="E295" s="8"/>
-      <c r="F295" s="8"/>
-      <c r="G295" s="8"/>
-      <c r="H295" s="8"/>
+      <c r="A295" s="9"/>
+      <c r="B295" s="9"/>
+      <c r="C295" s="9"/>
+      <c r="D295" s="9"/>
+      <c r="E295" s="9"/>
+      <c r="F295" s="9"/>
+      <c r="G295" s="9"/>
+      <c r="H295" s="9"/>
     </row>
     <row r="296" spans="1:8">
-      <c r="A296" s="8"/>
-      <c r="B296" s="8"/>
-      <c r="C296" s="8"/>
-      <c r="D296" s="8"/>
-      <c r="E296" s="8"/>
-      <c r="F296" s="8"/>
-      <c r="G296" s="8"/>
-      <c r="H296" s="8"/>
+      <c r="A296" s="9"/>
+      <c r="B296" s="9"/>
+      <c r="C296" s="9"/>
+      <c r="D296" s="9"/>
+      <c r="E296" s="9"/>
+      <c r="F296" s="9"/>
+      <c r="G296" s="9"/>
+      <c r="H296" s="9"/>
     </row>
     <row r="297" spans="1:8">
-      <c r="A297" s="8"/>
-      <c r="B297" s="8"/>
-      <c r="C297" s="8"/>
-      <c r="D297" s="8"/>
-      <c r="E297" s="8"/>
-      <c r="F297" s="8"/>
-      <c r="G297" s="8"/>
-      <c r="H297" s="8"/>
+      <c r="A297" s="9"/>
+      <c r="B297" s="9"/>
+      <c r="C297" s="9"/>
+      <c r="D297" s="9"/>
+      <c r="E297" s="9"/>
+      <c r="F297" s="9"/>
+      <c r="G297" s="9"/>
+      <c r="H297" s="9"/>
     </row>
     <row r="298" spans="1:8">
-      <c r="A298" s="8"/>
-      <c r="B298" s="8"/>
-      <c r="C298" s="8"/>
-      <c r="D298" s="8"/>
-      <c r="E298" s="8"/>
-      <c r="F298" s="8"/>
-      <c r="G298" s="8"/>
-      <c r="H298" s="8"/>
+      <c r="A298" s="9"/>
+      <c r="B298" s="9"/>
+      <c r="C298" s="9"/>
+      <c r="D298" s="9"/>
+      <c r="E298" s="9"/>
+      <c r="F298" s="9"/>
+      <c r="G298" s="9"/>
+      <c r="H298" s="9"/>
     </row>
     <row r="299" spans="1:8">
-      <c r="A299" s="8"/>
-      <c r="B299" s="8"/>
-      <c r="C299" s="8"/>
-      <c r="D299" s="8"/>
-      <c r="E299" s="8"/>
-      <c r="F299" s="8"/>
-      <c r="G299" s="8"/>
-      <c r="H299" s="8"/>
+      <c r="A299" s="9"/>
+      <c r="B299" s="9"/>
+      <c r="C299" s="9"/>
+      <c r="D299" s="9"/>
+      <c r="E299" s="9"/>
+      <c r="F299" s="9"/>
+      <c r="G299" s="9"/>
+      <c r="H299" s="9"/>
     </row>
     <row r="300" spans="1:8">
-      <c r="A300" s="8"/>
-      <c r="B300" s="8"/>
-      <c r="C300" s="8"/>
-      <c r="D300" s="8"/>
-      <c r="E300" s="8"/>
-      <c r="F300" s="8"/>
-      <c r="G300" s="8"/>
-      <c r="H300" s="8"/>
+      <c r="A300" s="9"/>
+      <c r="B300" s="9"/>
+      <c r="C300" s="9"/>
+      <c r="D300" s="9"/>
+      <c r="E300" s="9"/>
+      <c r="F300" s="9"/>
+      <c r="G300" s="9"/>
+      <c r="H300" s="9"/>
     </row>
     <row r="301" spans="1:8">
-      <c r="A301" s="8"/>
-      <c r="B301" s="8"/>
-      <c r="C301" s="8"/>
-      <c r="D301" s="8"/>
-      <c r="E301" s="8"/>
-      <c r="F301" s="8"/>
-      <c r="G301" s="8"/>
-      <c r="H301" s="8"/>
+      <c r="A301" s="9"/>
+      <c r="B301" s="9"/>
+      <c r="C301" s="9"/>
+      <c r="D301" s="9"/>
+      <c r="E301" s="9"/>
+      <c r="F301" s="9"/>
+      <c r="G301" s="9"/>
+      <c r="H301" s="9"/>
     </row>
     <row r="302" spans="1:8">
-      <c r="A302" s="8"/>
-      <c r="B302" s="8"/>
-      <c r="C302" s="8"/>
-      <c r="D302" s="8"/>
-      <c r="E302" s="8"/>
-      <c r="F302" s="8"/>
-      <c r="G302" s="8"/>
-      <c r="H302" s="8"/>
+      <c r="A302" s="9"/>
+      <c r="B302" s="9"/>
+      <c r="C302" s="9"/>
+      <c r="D302" s="9"/>
+      <c r="E302" s="9"/>
+      <c r="F302" s="9"/>
+      <c r="G302" s="9"/>
+      <c r="H302" s="9"/>
     </row>
     <row r="303" spans="1:8">
-      <c r="A303" s="8"/>
-      <c r="B303" s="8"/>
-      <c r="C303" s="8"/>
-      <c r="D303" s="8"/>
-      <c r="E303" s="8"/>
-      <c r="F303" s="8"/>
-      <c r="G303" s="8"/>
-      <c r="H303" s="8"/>
+      <c r="A303" s="9"/>
+      <c r="B303" s="9"/>
+      <c r="C303" s="9"/>
+      <c r="D303" s="9"/>
+      <c r="E303" s="9"/>
+      <c r="F303" s="9"/>
+      <c r="G303" s="9"/>
+      <c r="H303" s="9"/>
     </row>
     <row r="304" spans="1:8">
-      <c r="A304" s="8"/>
-      <c r="B304" s="8"/>
-      <c r="C304" s="8"/>
-      <c r="D304" s="8"/>
-      <c r="E304" s="8"/>
-      <c r="F304" s="8"/>
-      <c r="G304" s="8"/>
-      <c r="H304" s="8"/>
+      <c r="A304" s="9"/>
+      <c r="B304" s="9"/>
+      <c r="C304" s="9"/>
+      <c r="D304" s="9"/>
+      <c r="E304" s="9"/>
+      <c r="F304" s="9"/>
+      <c r="G304" s="9"/>
+      <c r="H304" s="9"/>
     </row>
     <row r="305" spans="1:8">
-      <c r="A305" s="8"/>
-      <c r="B305" s="8"/>
-      <c r="C305" s="8"/>
-      <c r="D305" s="8"/>
-      <c r="E305" s="8"/>
-      <c r="F305" s="8"/>
-      <c r="G305" s="8"/>
-      <c r="H305" s="8"/>
+      <c r="A305" s="9"/>
+      <c r="B305" s="9"/>
+      <c r="C305" s="9"/>
+      <c r="D305" s="9"/>
+      <c r="E305" s="9"/>
+      <c r="F305" s="9"/>
+      <c r="G305" s="9"/>
+      <c r="H305" s="9"/>
     </row>
     <row r="306" spans="1:8">
-      <c r="A306" s="8"/>
-      <c r="B306" s="8"/>
-      <c r="C306" s="8"/>
-      <c r="D306" s="8"/>
-      <c r="E306" s="8"/>
-      <c r="F306" s="8"/>
-      <c r="G306" s="8"/>
-      <c r="H306" s="8"/>
+      <c r="A306" s="9"/>
+      <c r="B306" s="9"/>
+      <c r="C306" s="9"/>
+      <c r="D306" s="9"/>
+      <c r="E306" s="9"/>
+      <c r="F306" s="9"/>
+      <c r="G306" s="9"/>
+      <c r="H306" s="9"/>
     </row>
     <row r="307" spans="1:8">
-      <c r="A307" s="8"/>
-      <c r="B307" s="8"/>
-      <c r="C307" s="8"/>
-      <c r="D307" s="8"/>
-      <c r="E307" s="8"/>
-      <c r="F307" s="8"/>
-      <c r="G307" s="8"/>
-      <c r="H307" s="8"/>
+      <c r="A307" s="9"/>
+      <c r="B307" s="9"/>
+      <c r="C307" s="9"/>
+      <c r="D307" s="9"/>
+      <c r="E307" s="9"/>
+      <c r="F307" s="9"/>
+      <c r="G307" s="9"/>
+      <c r="H307" s="9"/>
     </row>
     <row r="308" spans="1:8">
-      <c r="A308" s="8"/>
-      <c r="B308" s="8"/>
-      <c r="C308" s="8"/>
-      <c r="D308" s="8"/>
-      <c r="E308" s="8"/>
-      <c r="F308" s="8"/>
-      <c r="G308" s="8"/>
-      <c r="H308" s="8"/>
+      <c r="A308" s="9"/>
+      <c r="B308" s="9"/>
+      <c r="C308" s="9"/>
+      <c r="D308" s="9"/>
+      <c r="E308" s="9"/>
+      <c r="F308" s="9"/>
+      <c r="G308" s="9"/>
+      <c r="H308" s="9"/>
     </row>
     <row r="309" spans="1:8">
-      <c r="A309" s="8"/>
-      <c r="B309" s="8"/>
-      <c r="C309" s="8"/>
-      <c r="D309" s="8"/>
-      <c r="E309" s="8"/>
-      <c r="F309" s="8"/>
-      <c r="G309" s="8"/>
-      <c r="H309" s="8"/>
+      <c r="A309" s="9"/>
+      <c r="B309" s="9"/>
+      <c r="C309" s="9"/>
+      <c r="D309" s="9"/>
+      <c r="E309" s="9"/>
+      <c r="F309" s="9"/>
+      <c r="G309" s="9"/>
+      <c r="H309" s="9"/>
     </row>
     <row r="310" spans="1:8">
-      <c r="A310" s="8"/>
-      <c r="B310" s="8"/>
-      <c r="C310" s="8"/>
-      <c r="D310" s="8"/>
-      <c r="E310" s="8"/>
-      <c r="F310" s="8"/>
-      <c r="G310" s="8"/>
-      <c r="H310" s="8"/>
+      <c r="A310" s="9"/>
+      <c r="B310" s="9"/>
+      <c r="C310" s="9"/>
+      <c r="D310" s="9"/>
+      <c r="E310" s="9"/>
+      <c r="F310" s="9"/>
+      <c r="G310" s="9"/>
+      <c r="H310" s="9"/>
     </row>
     <row r="311" spans="1:8">
-      <c r="A311" s="8"/>
-      <c r="B311" s="8"/>
-      <c r="C311" s="8"/>
-      <c r="D311" s="8"/>
-      <c r="E311" s="8"/>
-      <c r="F311" s="8"/>
-      <c r="G311" s="8"/>
-      <c r="H311" s="8"/>
+      <c r="A311" s="9"/>
+      <c r="B311" s="9"/>
+      <c r="C311" s="9"/>
+      <c r="D311" s="9"/>
+      <c r="E311" s="9"/>
+      <c r="F311" s="9"/>
+      <c r="G311" s="9"/>
+      <c r="H311" s="9"/>
     </row>
     <row r="312" spans="1:8">
-      <c r="A312" s="8"/>
-      <c r="B312" s="8"/>
-      <c r="C312" s="8"/>
-      <c r="D312" s="8"/>
-      <c r="E312" s="8"/>
-      <c r="F312" s="8"/>
-      <c r="G312" s="8"/>
-      <c r="H312" s="8"/>
+      <c r="A312" s="9"/>
+      <c r="B312" s="9"/>
+      <c r="C312" s="9"/>
+      <c r="D312" s="9"/>
+      <c r="E312" s="9"/>
+      <c r="F312" s="9"/>
+      <c r="G312" s="9"/>
+      <c r="H312" s="9"/>
     </row>
     <row r="313" spans="1:8">
-      <c r="A313" s="8"/>
-      <c r="B313" s="8"/>
-      <c r="C313" s="8"/>
-      <c r="D313" s="8"/>
-      <c r="E313" s="8"/>
-      <c r="F313" s="8"/>
-      <c r="G313" s="8"/>
-      <c r="H313" s="8"/>
+      <c r="A313" s="9"/>
+      <c r="B313" s="9"/>
+      <c r="C313" s="9"/>
+      <c r="D313" s="9"/>
+      <c r="E313" s="9"/>
+      <c r="F313" s="9"/>
+      <c r="G313" s="9"/>
+      <c r="H313" s="9"/>
     </row>
     <row r="314" spans="1:8">
-      <c r="A314" s="8"/>
-      <c r="B314" s="8"/>
-      <c r="C314" s="8"/>
-      <c r="D314" s="8"/>
-      <c r="E314" s="8"/>
-      <c r="F314" s="8"/>
-      <c r="G314" s="8"/>
-      <c r="H314" s="8"/>
+      <c r="A314" s="9"/>
+      <c r="B314" s="9"/>
+      <c r="C314" s="9"/>
+      <c r="D314" s="9"/>
+      <c r="E314" s="9"/>
+      <c r="F314" s="9"/>
+      <c r="G314" s="9"/>
+      <c r="H314" s="9"/>
     </row>
     <row r="315" spans="1:8">
-      <c r="A315" s="8"/>
-      <c r="B315" s="8"/>
-      <c r="C315" s="8"/>
-      <c r="D315" s="8"/>
-      <c r="E315" s="8"/>
-      <c r="F315" s="8"/>
-      <c r="G315" s="8"/>
-      <c r="H315" s="8"/>
+      <c r="A315" s="9"/>
+      <c r="B315" s="9"/>
+      <c r="C315" s="9"/>
+      <c r="D315" s="9"/>
+      <c r="E315" s="9"/>
+      <c r="F315" s="9"/>
+      <c r="G315" s="9"/>
+      <c r="H315" s="9"/>
     </row>
     <row r="316" spans="1:8">
-      <c r="A316" s="8"/>
-      <c r="B316" s="8"/>
-      <c r="C316" s="8"/>
-      <c r="D316" s="8"/>
-      <c r="E316" s="8"/>
-      <c r="F316" s="8"/>
-      <c r="G316" s="8"/>
-      <c r="H316" s="8"/>
+      <c r="A316" s="9"/>
+      <c r="B316" s="9"/>
+      <c r="C316" s="9"/>
+      <c r="D316" s="9"/>
+      <c r="E316" s="9"/>
+      <c r="F316" s="9"/>
+      <c r="G316" s="9"/>
+      <c r="H316" s="9"/>
     </row>
     <row r="317" spans="1:8">
-      <c r="A317" s="8"/>
-      <c r="B317" s="8"/>
-      <c r="C317" s="8"/>
-      <c r="D317" s="8"/>
-      <c r="E317" s="8"/>
-      <c r="F317" s="8"/>
-      <c r="G317" s="8"/>
-      <c r="H317" s="8"/>
+      <c r="A317" s="9"/>
+      <c r="B317" s="9"/>
+      <c r="C317" s="9"/>
+      <c r="D317" s="9"/>
+      <c r="E317" s="9"/>
+      <c r="F317" s="9"/>
+      <c r="G317" s="9"/>
+      <c r="H317" s="9"/>
     </row>
     <row r="318" spans="1:8">
-      <c r="A318" s="8"/>
-      <c r="B318" s="8"/>
-      <c r="C318" s="8"/>
-      <c r="D318" s="8"/>
-      <c r="E318" s="8"/>
-      <c r="F318" s="8"/>
-      <c r="G318" s="8"/>
-      <c r="H318" s="8"/>
+      <c r="A318" s="9"/>
+      <c r="B318" s="9"/>
+      <c r="C318" s="9"/>
+      <c r="D318" s="9"/>
+      <c r="E318" s="9"/>
+      <c r="F318" s="9"/>
+      <c r="G318" s="9"/>
+      <c r="H318" s="9"/>
     </row>
     <row r="319" spans="1:8">
-      <c r="A319" s="8"/>
-      <c r="B319" s="8"/>
-      <c r="C319" s="8"/>
-      <c r="D319" s="8"/>
-      <c r="E319" s="8"/>
-      <c r="F319" s="8"/>
-      <c r="G319" s="8"/>
-      <c r="H319" s="8"/>
+      <c r="A319" s="9"/>
+      <c r="B319" s="9"/>
+      <c r="C319" s="9"/>
+      <c r="D319" s="9"/>
+      <c r="E319" s="9"/>
+      <c r="F319" s="9"/>
+      <c r="G319" s="9"/>
+      <c r="H319" s="9"/>
     </row>
     <row r="320" spans="1:8">
-      <c r="A320" s="8"/>
-      <c r="B320" s="8"/>
-      <c r="C320" s="8"/>
-      <c r="D320" s="8"/>
-      <c r="E320" s="8"/>
-      <c r="F320" s="8"/>
-      <c r="G320" s="8"/>
-      <c r="H320" s="8"/>
+      <c r="A320" s="9"/>
+      <c r="B320" s="9"/>
+      <c r="C320" s="9"/>
+      <c r="D320" s="9"/>
+      <c r="E320" s="9"/>
+      <c r="F320" s="9"/>
+      <c r="G320" s="9"/>
+      <c r="H320" s="9"/>
     </row>
     <row r="321" spans="1:8">
-      <c r="A321" s="8"/>
-      <c r="B321" s="8"/>
-      <c r="C321" s="8"/>
-      <c r="D321" s="8"/>
-      <c r="E321" s="8"/>
-      <c r="F321" s="8"/>
-      <c r="G321" s="8"/>
-      <c r="H321" s="8"/>
+      <c r="A321" s="9"/>
+      <c r="B321" s="9"/>
+      <c r="C321" s="9"/>
+      <c r="D321" s="9"/>
+      <c r="E321" s="9"/>
+      <c r="F321" s="9"/>
+      <c r="G321" s="9"/>
+      <c r="H321" s="9"/>
     </row>
     <row r="322" spans="1:8">
-      <c r="A322" s="8"/>
-      <c r="B322" s="8"/>
-      <c r="C322" s="8"/>
-      <c r="D322" s="8"/>
-      <c r="E322" s="8"/>
-      <c r="F322" s="8"/>
-      <c r="G322" s="8"/>
-      <c r="H322" s="8"/>
+      <c r="A322" s="9"/>
+      <c r="B322" s="9"/>
+      <c r="C322" s="9"/>
+      <c r="D322" s="9"/>
+      <c r="E322" s="9"/>
+      <c r="F322" s="9"/>
+      <c r="G322" s="9"/>
+      <c r="H322" s="9"/>
     </row>
     <row r="323" spans="1:8">
-      <c r="A323" s="8"/>
-      <c r="B323" s="8"/>
-      <c r="C323" s="8"/>
-      <c r="D323" s="8"/>
-      <c r="E323" s="8"/>
-      <c r="F323" s="8"/>
-      <c r="G323" s="8"/>
-      <c r="H323" s="8"/>
+      <c r="A323" s="9"/>
+      <c r="B323" s="9"/>
+      <c r="C323" s="9"/>
+      <c r="D323" s="9"/>
+      <c r="E323" s="9"/>
+      <c r="F323" s="9"/>
+      <c r="G323" s="9"/>
+      <c r="H323" s="9"/>
     </row>
     <row r="324" spans="1:8">
-      <c r="A324" s="8"/>
-      <c r="B324" s="8"/>
-      <c r="C324" s="8"/>
-      <c r="D324" s="8"/>
-      <c r="E324" s="8"/>
-      <c r="F324" s="8"/>
-      <c r="G324" s="8"/>
-      <c r="H324" s="8"/>
+      <c r="A324" s="9"/>
+      <c r="B324" s="9"/>
+      <c r="C324" s="9"/>
+      <c r="D324" s="9"/>
+      <c r="E324" s="9"/>
+      <c r="F324" s="9"/>
+      <c r="G324" s="9"/>
+      <c r="H324" s="9"/>
     </row>
     <row r="325" spans="1:8">
-      <c r="A325" s="8"/>
-      <c r="B325" s="8"/>
-      <c r="C325" s="8"/>
-      <c r="D325" s="8"/>
-      <c r="E325" s="8"/>
-      <c r="F325" s="8"/>
-      <c r="G325" s="8"/>
-      <c r="H325" s="8"/>
+      <c r="A325" s="9"/>
+      <c r="B325" s="9"/>
+      <c r="C325" s="9"/>
+      <c r="D325" s="9"/>
+      <c r="E325" s="9"/>
+      <c r="F325" s="9"/>
+      <c r="G325" s="9"/>
+      <c r="H325" s="9"/>
     </row>
     <row r="326" spans="1:8">
-      <c r="A326" s="8"/>
-      <c r="B326" s="8"/>
-      <c r="C326" s="8"/>
-      <c r="D326" s="8"/>
-      <c r="E326" s="8"/>
-      <c r="F326" s="8"/>
-      <c r="G326" s="8"/>
-      <c r="H326" s="8"/>
+      <c r="A326" s="9"/>
+      <c r="B326" s="9"/>
+      <c r="C326" s="9"/>
+      <c r="D326" s="9"/>
+      <c r="E326" s="9"/>
+      <c r="F326" s="9"/>
+      <c r="G326" s="9"/>
+      <c r="H326" s="9"/>
     </row>
     <row r="327" spans="1:8">
-      <c r="A327" s="8"/>
-      <c r="B327" s="8"/>
-      <c r="C327" s="8"/>
-      <c r="D327" s="8"/>
-      <c r="E327" s="8"/>
-      <c r="F327" s="8"/>
-      <c r="G327" s="8"/>
-      <c r="H327" s="8"/>
+      <c r="A327" s="9"/>
+      <c r="B327" s="9"/>
+      <c r="C327" s="9"/>
+      <c r="D327" s="9"/>
+      <c r="E327" s="9"/>
+      <c r="F327" s="9"/>
+      <c r="G327" s="9"/>
+      <c r="H327" s="9"/>
     </row>
     <row r="328" spans="1:8">
-      <c r="A328" s="8"/>
-      <c r="B328" s="8"/>
-      <c r="C328" s="8"/>
-      <c r="D328" s="8"/>
-      <c r="E328" s="8"/>
-      <c r="F328" s="8"/>
-      <c r="G328" s="8"/>
-      <c r="H328" s="8"/>
+      <c r="A328" s="9"/>
+      <c r="B328" s="9"/>
+      <c r="C328" s="9"/>
+      <c r="D328" s="9"/>
+      <c r="E328" s="9"/>
+      <c r="F328" s="9"/>
+      <c r="G328" s="9"/>
+      <c r="H328" s="9"/>
     </row>
     <row r="329" spans="1:8">
-      <c r="A329" s="8"/>
-      <c r="B329" s="8"/>
-      <c r="C329" s="8"/>
-      <c r="D329" s="8"/>
-      <c r="E329" s="8"/>
-      <c r="F329" s="8"/>
-      <c r="G329" s="8"/>
-      <c r="H329" s="8"/>
+      <c r="A329" s="9"/>
+      <c r="B329" s="9"/>
+      <c r="C329" s="9"/>
+      <c r="D329" s="9"/>
+      <c r="E329" s="9"/>
+      <c r="F329" s="9"/>
+      <c r="G329" s="9"/>
+      <c r="H329" s="9"/>
     </row>
     <row r="330" spans="1:8">
-      <c r="A330" s="8"/>
-      <c r="B330" s="8"/>
-      <c r="C330" s="8"/>
-      <c r="D330" s="8"/>
-      <c r="E330" s="8"/>
-      <c r="F330" s="8"/>
-      <c r="G330" s="8"/>
-      <c r="H330" s="8"/>
+      <c r="A330" s="9"/>
+      <c r="B330" s="9"/>
+      <c r="C330" s="9"/>
+      <c r="D330" s="9"/>
+      <c r="E330" s="9"/>
+      <c r="F330" s="9"/>
+      <c r="G330" s="9"/>
+      <c r="H330" s="9"/>
     </row>
     <row r="331" spans="1:8">
-      <c r="A331" s="8"/>
-      <c r="B331" s="8"/>
-      <c r="C331" s="8"/>
-      <c r="D331" s="8"/>
-      <c r="E331" s="8"/>
-      <c r="F331" s="8"/>
-      <c r="G331" s="8"/>
-      <c r="H331" s="8"/>
+      <c r="A331" s="9"/>
+      <c r="B331" s="9"/>
+      <c r="C331" s="9"/>
+      <c r="D331" s="9"/>
+      <c r="E331" s="9"/>
+      <c r="F331" s="9"/>
+      <c r="G331" s="9"/>
+      <c r="H331" s="9"/>
     </row>
     <row r="332" spans="1:8">
-      <c r="A332" s="8"/>
-      <c r="B332" s="8"/>
-      <c r="C332" s="8"/>
-      <c r="D332" s="8"/>
-      <c r="E332" s="8"/>
-      <c r="F332" s="8"/>
-      <c r="G332" s="8"/>
-      <c r="H332" s="8"/>
+      <c r="A332" s="9"/>
+      <c r="B332" s="9"/>
+      <c r="C332" s="9"/>
+      <c r="D332" s="9"/>
+      <c r="E332" s="9"/>
+      <c r="F332" s="9"/>
+      <c r="G332" s="9"/>
+      <c r="H332" s="9"/>
     </row>
     <row r="333" spans="1:8">
-      <c r="A333" s="8"/>
-      <c r="B333" s="8"/>
-      <c r="C333" s="8"/>
-      <c r="D333" s="8"/>
-      <c r="E333" s="8"/>
-      <c r="F333" s="8"/>
-      <c r="G333" s="8"/>
-      <c r="H333" s="8"/>
+      <c r="A333" s="9"/>
+      <c r="B333" s="9"/>
+      <c r="C333" s="9"/>
+      <c r="D333" s="9"/>
+      <c r="E333" s="9"/>
+      <c r="F333" s="9"/>
+      <c r="G333" s="9"/>
+      <c r="H333" s="9"/>
     </row>
     <row r="334" spans="1:8">
-      <c r="A334" s="8"/>
-      <c r="B334" s="8"/>
-      <c r="C334" s="8"/>
-      <c r="D334" s="8"/>
-      <c r="E334" s="8"/>
-      <c r="F334" s="8"/>
-      <c r="G334" s="8"/>
-      <c r="H334" s="8"/>
+      <c r="A334" s="9"/>
+      <c r="B334" s="9"/>
+      <c r="C334" s="9"/>
+      <c r="D334" s="9"/>
+      <c r="E334" s="9"/>
+      <c r="F334" s="9"/>
+      <c r="G334" s="9"/>
+      <c r="H334" s="9"/>
     </row>
     <row r="335" spans="1:8">
-      <c r="A335" s="8"/>
-      <c r="B335" s="8"/>
-      <c r="C335" s="8"/>
-      <c r="D335" s="8"/>
-      <c r="E335" s="8"/>
-      <c r="F335" s="8"/>
-      <c r="G335" s="8"/>
-      <c r="H335" s="8"/>
+      <c r="A335" s="9"/>
+      <c r="B335" s="9"/>
+      <c r="C335" s="9"/>
+      <c r="D335" s="9"/>
+      <c r="E335" s="9"/>
+      <c r="F335" s="9"/>
+      <c r="G335" s="9"/>
+      <c r="H335" s="9"/>
     </row>
     <row r="336" spans="1:8">
-      <c r="A336" s="8"/>
-      <c r="B336" s="8"/>
-      <c r="C336" s="8"/>
-      <c r="D336" s="8"/>
-      <c r="E336" s="8"/>
-      <c r="F336" s="8"/>
-      <c r="G336" s="8"/>
-      <c r="H336" s="8"/>
+      <c r="A336" s="9"/>
+      <c r="B336" s="9"/>
+      <c r="C336" s="9"/>
+      <c r="D336" s="9"/>
+      <c r="E336" s="9"/>
+      <c r="F336" s="9"/>
+      <c r="G336" s="9"/>
+      <c r="H336" s="9"/>
     </row>
     <row r="337" spans="1:8">
-      <c r="A337" s="8"/>
-      <c r="B337" s="8"/>
-      <c r="C337" s="8"/>
-      <c r="D337" s="8"/>
-      <c r="E337" s="8"/>
-      <c r="F337" s="8"/>
-      <c r="G337" s="8"/>
-      <c r="H337" s="8"/>
+      <c r="A337" s="9"/>
+      <c r="B337" s="9"/>
+      <c r="C337" s="9"/>
+      <c r="D337" s="9"/>
+      <c r="E337" s="9"/>
+      <c r="F337" s="9"/>
+      <c r="G337" s="9"/>
+      <c r="H337" s="9"/>
     </row>
     <row r="338" spans="1:8">
-      <c r="A338" s="8"/>
-      <c r="B338" s="8"/>
-      <c r="C338" s="8"/>
-      <c r="D338" s="8"/>
-      <c r="E338" s="8"/>
-      <c r="F338" s="8"/>
-      <c r="G338" s="8"/>
-      <c r="H338" s="8"/>
+      <c r="A338" s="9"/>
+      <c r="B338" s="9"/>
+      <c r="C338" s="9"/>
+      <c r="D338" s="9"/>
+      <c r="E338" s="9"/>
+      <c r="F338" s="9"/>
+      <c r="G338" s="9"/>
+      <c r="H338" s="9"/>
     </row>
     <row r="339" spans="1:8">
-      <c r="A339" s="8"/>
-      <c r="B339" s="8"/>
-      <c r="C339" s="8"/>
-      <c r="D339" s="8"/>
-      <c r="E339" s="8"/>
-      <c r="F339" s="8"/>
-      <c r="G339" s="8"/>
-      <c r="H339" s="8"/>
+      <c r="A339" s="9"/>
+      <c r="B339" s="9"/>
+      <c r="C339" s="9"/>
+      <c r="D339" s="9"/>
+      <c r="E339" s="9"/>
+      <c r="F339" s="9"/>
+      <c r="G339" s="9"/>
+      <c r="H339" s="9"/>
     </row>
     <row r="340" spans="1:8">
-      <c r="A340" s="8"/>
-      <c r="B340" s="8"/>
-      <c r="C340" s="8"/>
-      <c r="D340" s="8"/>
-      <c r="E340" s="8"/>
-      <c r="F340" s="8"/>
-      <c r="G340" s="8"/>
-      <c r="H340" s="8"/>
+      <c r="A340" s="9"/>
+      <c r="B340" s="9"/>
+      <c r="C340" s="9"/>
+      <c r="D340" s="9"/>
+      <c r="E340" s="9"/>
+      <c r="F340" s="9"/>
+      <c r="G340" s="9"/>
+      <c r="H340" s="9"/>
     </row>
     <row r="341" spans="1:8">
-      <c r="A341" s="8"/>
-      <c r="B341" s="8"/>
-      <c r="C341" s="8"/>
-      <c r="D341" s="8"/>
-      <c r="E341" s="8"/>
-      <c r="F341" s="8"/>
-      <c r="G341" s="8"/>
-      <c r="H341" s="8"/>
+      <c r="A341" s="9"/>
+      <c r="B341" s="9"/>
+      <c r="C341" s="9"/>
+      <c r="D341" s="9"/>
+      <c r="E341" s="9"/>
+      <c r="F341" s="9"/>
+      <c r="G341" s="9"/>
+      <c r="H341" s="9"/>
     </row>
     <row r="342" spans="1:8">
-      <c r="A342" s="8"/>
-      <c r="B342" s="8"/>
-      <c r="C342" s="8"/>
-      <c r="D342" s="8"/>
-      <c r="E342" s="8"/>
-      <c r="F342" s="8"/>
-      <c r="G342" s="8"/>
-      <c r="H342" s="8"/>
+      <c r="A342" s="9"/>
+      <c r="B342" s="9"/>
+      <c r="C342" s="9"/>
+      <c r="D342" s="9"/>
+      <c r="E342" s="9"/>
+      <c r="F342" s="9"/>
+      <c r="G342" s="9"/>
+      <c r="H342" s="9"/>
     </row>
     <row r="343" spans="1:8">
-      <c r="A343" s="8"/>
-      <c r="B343" s="8"/>
-      <c r="C343" s="8"/>
-      <c r="D343" s="8"/>
-      <c r="E343" s="8"/>
-      <c r="F343" s="8"/>
-      <c r="G343" s="8"/>
-      <c r="H343" s="8"/>
+      <c r="A343" s="9"/>
+      <c r="B343" s="9"/>
+      <c r="C343" s="9"/>
+      <c r="D343" s="9"/>
+      <c r="E343" s="9"/>
+      <c r="F343" s="9"/>
+      <c r="G343" s="9"/>
+      <c r="H343" s="9"/>
     </row>
     <row r="344" spans="1:8">
-      <c r="A344" s="8"/>
-      <c r="B344" s="8"/>
-      <c r="C344" s="8"/>
-      <c r="D344" s="8"/>
-      <c r="E344" s="8"/>
-      <c r="F344" s="8"/>
-      <c r="G344" s="8"/>
-      <c r="H344" s="8"/>
+      <c r="A344" s="9"/>
+      <c r="B344" s="9"/>
+      <c r="C344" s="9"/>
+      <c r="D344" s="9"/>
+      <c r="E344" s="9"/>
+      <c r="F344" s="9"/>
+      <c r="G344" s="9"/>
+      <c r="H344" s="9"/>
     </row>
     <row r="345" spans="1:8">
-      <c r="A345" s="8"/>
-      <c r="B345" s="8"/>
-      <c r="C345" s="8"/>
-      <c r="D345" s="8"/>
-      <c r="E345" s="8"/>
-      <c r="F345" s="8"/>
-      <c r="G345" s="8"/>
-      <c r="H345" s="8"/>
+      <c r="A345" s="9"/>
+      <c r="B345" s="9"/>
+      <c r="C345" s="9"/>
+      <c r="D345" s="9"/>
+      <c r="E345" s="9"/>
+      <c r="F345" s="9"/>
+      <c r="G345" s="9"/>
+      <c r="H345" s="9"/>
     </row>
     <row r="346" spans="1:8">
-      <c r="A346" s="8"/>
-      <c r="B346" s="8"/>
-      <c r="C346" s="8"/>
-      <c r="D346" s="8"/>
-      <c r="E346" s="8"/>
-      <c r="F346" s="8"/>
-      <c r="G346" s="8"/>
-      <c r="H346" s="8"/>
+      <c r="A346" s="9"/>
+      <c r="B346" s="9"/>
+      <c r="C346" s="9"/>
+      <c r="D346" s="9"/>
+      <c r="E346" s="9"/>
+      <c r="F346" s="9"/>
+      <c r="G346" s="9"/>
+      <c r="H346" s="9"/>
     </row>
     <row r="347" spans="1:8">
-      <c r="A347" s="8"/>
-      <c r="B347" s="8"/>
-      <c r="C347" s="8"/>
-      <c r="D347" s="8"/>
-      <c r="E347" s="8"/>
-      <c r="F347" s="8"/>
-      <c r="G347" s="8"/>
-      <c r="H347" s="8"/>
+      <c r="A347" s="9"/>
+      <c r="B347" s="9"/>
+      <c r="C347" s="9"/>
+      <c r="D347" s="9"/>
+      <c r="E347" s="9"/>
+      <c r="F347" s="9"/>
+      <c r="G347" s="9"/>
+      <c r="H347" s="9"/>
     </row>
     <row r="348" spans="1:8">
-      <c r="A348" s="8"/>
-      <c r="B348" s="8"/>
-      <c r="C348" s="8"/>
-      <c r="D348" s="8"/>
-      <c r="E348" s="8"/>
-      <c r="F348" s="8"/>
-      <c r="G348" s="8"/>
-      <c r="H348" s="8"/>
+      <c r="A348" s="9"/>
+      <c r="B348" s="9"/>
+      <c r="C348" s="9"/>
+      <c r="D348" s="9"/>
+      <c r="E348" s="9"/>
+      <c r="F348" s="9"/>
+      <c r="G348" s="9"/>
+      <c r="H348" s="9"/>
     </row>
     <row r="349" spans="1:8">
-      <c r="A349" s="8"/>
-      <c r="B349" s="8"/>
-      <c r="C349" s="8"/>
-      <c r="D349" s="8"/>
-      <c r="E349" s="8"/>
-      <c r="F349" s="8"/>
-      <c r="G349" s="8"/>
-      <c r="H349" s="8"/>
+      <c r="A349" s="9"/>
+      <c r="B349" s="9"/>
+      <c r="C349" s="9"/>
+      <c r="D349" s="9"/>
+      <c r="E349" s="9"/>
+      <c r="F349" s="9"/>
+      <c r="G349" s="9"/>
+      <c r="H349" s="9"/>
     </row>
     <row r="350" spans="1:8">
-      <c r="A350" s="8"/>
-      <c r="B350" s="8"/>
-      <c r="C350" s="8"/>
-      <c r="D350" s="8"/>
-      <c r="E350" s="8"/>
-      <c r="F350" s="8"/>
-      <c r="G350" s="8"/>
-      <c r="H350" s="8"/>
+      <c r="A350" s="9"/>
+      <c r="B350" s="9"/>
+      <c r="C350" s="9"/>
+      <c r="D350" s="9"/>
+      <c r="E350" s="9"/>
+      <c r="F350" s="9"/>
+      <c r="G350" s="9"/>
+      <c r="H350" s="9"/>
     </row>
     <row r="351" spans="1:8">
-      <c r="A351" s="8"/>
-      <c r="B351" s="8"/>
-      <c r="C351" s="8"/>
-      <c r="D351" s="8"/>
-      <c r="E351" s="8"/>
-      <c r="F351" s="8"/>
-      <c r="G351" s="8"/>
-      <c r="H351" s="8"/>
+      <c r="A351" s="9"/>
+      <c r="B351" s="9"/>
+      <c r="C351" s="9"/>
+      <c r="D351" s="9"/>
+      <c r="E351" s="9"/>
+      <c r="F351" s="9"/>
+      <c r="G351" s="9"/>
+      <c r="H351" s="9"/>
     </row>
     <row r="352" spans="1:8">
-      <c r="A352" s="8"/>
-      <c r="B352" s="8"/>
-      <c r="C352" s="8"/>
-      <c r="D352" s="8"/>
-      <c r="E352" s="8"/>
-      <c r="F352" s="8"/>
-      <c r="G352" s="8"/>
-      <c r="H352" s="8"/>
+      <c r="A352" s="9"/>
+      <c r="B352" s="9"/>
+      <c r="C352" s="9"/>
+      <c r="D352" s="9"/>
+      <c r="E352" s="9"/>
+      <c r="F352" s="9"/>
+      <c r="G352" s="9"/>
+      <c r="H352" s="9"/>
     </row>
     <row r="353" spans="1:8">
-      <c r="A353" s="8"/>
-      <c r="B353" s="8"/>
-      <c r="C353" s="8"/>
-      <c r="D353" s="8"/>
-      <c r="E353" s="8"/>
-      <c r="F353" s="8"/>
-      <c r="G353" s="8"/>
-      <c r="H353" s="8"/>
+      <c r="A353" s="9"/>
+      <c r="B353" s="9"/>
+      <c r="C353" s="9"/>
+      <c r="D353" s="9"/>
+      <c r="E353" s="9"/>
+      <c r="F353" s="9"/>
+      <c r="G353" s="9"/>
+      <c r="H353" s="9"/>
     </row>
     <row r="354" spans="1:8">
-      <c r="A354" s="8"/>
-      <c r="B354" s="8"/>
-      <c r="C354" s="8"/>
-      <c r="D354" s="8"/>
-      <c r="E354" s="8"/>
-      <c r="F354" s="8"/>
-      <c r="G354" s="8"/>
-      <c r="H354" s="8"/>
+      <c r="A354" s="9"/>
+      <c r="B354" s="9"/>
+      <c r="C354" s="9"/>
+      <c r="D354" s="9"/>
+      <c r="E354" s="9"/>
+      <c r="F354" s="9"/>
+      <c r="G354" s="9"/>
+      <c r="H354" s="9"/>
     </row>
     <row r="355" spans="1:8">
-      <c r="A355" s="8"/>
-      <c r="B355" s="8"/>
-      <c r="C355" s="8"/>
-      <c r="D355" s="8"/>
-      <c r="E355" s="8"/>
-      <c r="F355" s="8"/>
-      <c r="G355" s="8"/>
-      <c r="H355" s="8"/>
+      <c r="A355" s="9"/>
+      <c r="B355" s="9"/>
+      <c r="C355" s="9"/>
+      <c r="D355" s="9"/>
+      <c r="E355" s="9"/>
+      <c r="F355" s="9"/>
+      <c r="G355" s="9"/>
+      <c r="H355" s="9"/>
     </row>
     <row r="356" spans="1:8">
-      <c r="A356" s="8"/>
-      <c r="B356" s="8"/>
-      <c r="C356" s="8"/>
-      <c r="D356" s="8"/>
-      <c r="E356" s="8"/>
-      <c r="F356" s="8"/>
-      <c r="G356" s="8"/>
-      <c r="H356" s="8"/>
+      <c r="A356" s="9"/>
+      <c r="B356" s="9"/>
+      <c r="C356" s="9"/>
+      <c r="D356" s="9"/>
+      <c r="E356" s="9"/>
+      <c r="F356" s="9"/>
+      <c r="G356" s="9"/>
+      <c r="H356" s="9"/>
     </row>
     <row r="357" spans="1:8">
-      <c r="A357" s="8"/>
-      <c r="B357" s="8"/>
-      <c r="C357" s="8"/>
-      <c r="D357" s="8"/>
-      <c r="E357" s="8"/>
-      <c r="F357" s="8"/>
-      <c r="G357" s="8"/>
-      <c r="H357" s="8"/>
+      <c r="A357" s="9"/>
+      <c r="B357" s="9"/>
+      <c r="C357" s="9"/>
+      <c r="D357" s="9"/>
+      <c r="E357" s="9"/>
+      <c r="F357" s="9"/>
+      <c r="G357" s="9"/>
+      <c r="H357" s="9"/>
     </row>
     <row r="358" spans="1:8">
-      <c r="A358" s="8"/>
-      <c r="B358" s="8"/>
-      <c r="C358" s="8"/>
-      <c r="D358" s="8"/>
-      <c r="E358" s="8"/>
-      <c r="F358" s="8"/>
-      <c r="G358" s="8"/>
-      <c r="H358" s="8"/>
+      <c r="A358" s="9"/>
+      <c r="B358" s="9"/>
+      <c r="C358" s="9"/>
+      <c r="D358" s="9"/>
+      <c r="E358" s="9"/>
+      <c r="F358" s="9"/>
+      <c r="G358" s="9"/>
+      <c r="H358" s="9"/>
     </row>
     <row r="359" spans="1:8">
-      <c r="A359" s="8"/>
-      <c r="B359" s="8"/>
-      <c r="C359" s="8"/>
-      <c r="D359" s="8"/>
-      <c r="E359" s="8"/>
-      <c r="F359" s="8"/>
-      <c r="G359" s="8"/>
-      <c r="H359" s="8"/>
+      <c r="A359" s="9"/>
+      <c r="B359" s="9"/>
+      <c r="C359" s="9"/>
+      <c r="D359" s="9"/>
+      <c r="E359" s="9"/>
+      <c r="F359" s="9"/>
+      <c r="G359" s="9"/>
+      <c r="H359" s="9"/>
     </row>
     <row r="360" spans="1:8">
-      <c r="A360" s="8"/>
-      <c r="B360" s="8"/>
-      <c r="C360" s="8"/>
-      <c r="D360" s="8"/>
-      <c r="E360" s="8"/>
-      <c r="F360" s="8"/>
-      <c r="G360" s="8"/>
-      <c r="H360" s="8"/>
+      <c r="A360" s="9"/>
+      <c r="B360" s="9"/>
+      <c r="C360" s="9"/>
+      <c r="D360" s="9"/>
+      <c r="E360" s="9"/>
+      <c r="F360" s="9"/>
+      <c r="G360" s="9"/>
+      <c r="H360" s="9"/>
     </row>
     <row r="361" spans="1:8">
-      <c r="A361" s="8"/>
-      <c r="B361" s="8"/>
-      <c r="C361" s="8"/>
-      <c r="D361" s="8"/>
-      <c r="E361" s="8"/>
-      <c r="F361" s="8"/>
-      <c r="G361" s="8"/>
-      <c r="H361" s="8"/>
+      <c r="A361" s="9"/>
+      <c r="B361" s="9"/>
+      <c r="C361" s="9"/>
+      <c r="D361" s="9"/>
+      <c r="E361" s="9"/>
+      <c r="F361" s="9"/>
+      <c r="G361" s="9"/>
+      <c r="H361" s="9"/>
     </row>
     <row r="362" spans="1:8">
-      <c r="A362" s="8"/>
-      <c r="B362" s="8"/>
-      <c r="C362" s="8"/>
-      <c r="D362" s="8"/>
-      <c r="E362" s="8"/>
-      <c r="F362" s="8"/>
-      <c r="G362" s="8"/>
-      <c r="H362" s="8"/>
+      <c r="A362" s="9"/>
+      <c r="B362" s="9"/>
+      <c r="C362" s="9"/>
+      <c r="D362" s="9"/>
+      <c r="E362" s="9"/>
+      <c r="F362" s="9"/>
+      <c r="G362" s="9"/>
+      <c r="H362" s="9"/>
     </row>
     <row r="363" spans="1:8">
-      <c r="A363" s="8"/>
-      <c r="B363" s="8"/>
-      <c r="C363" s="8"/>
-      <c r="D363" s="8"/>
-      <c r="E363" s="8"/>
-      <c r="F363" s="8"/>
-      <c r="G363" s="8"/>
-      <c r="H363" s="8"/>
+      <c r="A363" s="9"/>
+      <c r="B363" s="9"/>
+      <c r="C363" s="9"/>
+      <c r="D363" s="9"/>
+      <c r="E363" s="9"/>
+      <c r="F363" s="9"/>
+      <c r="G363" s="9"/>
+      <c r="H363" s="9"/>
     </row>
     <row r="364" spans="1:8">
-      <c r="A364" s="8"/>
-      <c r="B364" s="8"/>
-      <c r="C364" s="8"/>
-      <c r="D364" s="8"/>
-      <c r="E364" s="8"/>
-      <c r="F364" s="8"/>
-      <c r="G364" s="8"/>
-      <c r="H364" s="8"/>
+      <c r="A364" s="9"/>
+      <c r="B364" s="9"/>
+      <c r="C364" s="9"/>
+      <c r="D364" s="9"/>
+      <c r="E364" s="9"/>
+      <c r="F364" s="9"/>
+      <c r="G364" s="9"/>
+      <c r="H364" s="9"/>
     </row>
     <row r="365" spans="1:8">
-      <c r="A365" s="8"/>
-      <c r="B365" s="8"/>
-      <c r="C365" s="8"/>
-      <c r="D365" s="8"/>
-      <c r="E365" s="8"/>
-      <c r="F365" s="8"/>
-      <c r="G365" s="8"/>
-      <c r="H365" s="8"/>
+      <c r="A365" s="9"/>
+      <c r="B365" s="9"/>
+      <c r="C365" s="9"/>
+      <c r="D365" s="9"/>
+      <c r="E365" s="9"/>
+      <c r="F365" s="9"/>
+      <c r="G365" s="9"/>
+      <c r="H365" s="9"/>
     </row>
     <row r="366" spans="1:8">
-      <c r="A366" s="8"/>
-      <c r="B366" s="8"/>
-      <c r="C366" s="8"/>
-      <c r="D366" s="8"/>
-      <c r="E366" s="8"/>
-      <c r="F366" s="8"/>
-      <c r="G366" s="8"/>
-      <c r="H366" s="8"/>
+      <c r="A366" s="9"/>
+      <c r="B366" s="9"/>
+      <c r="C366" s="9"/>
+      <c r="D366" s="9"/>
+      <c r="E366" s="9"/>
+      <c r="F366" s="9"/>
+      <c r="G366" s="9"/>
+      <c r="H366" s="9"/>
     </row>
     <row r="367" spans="1:8">
-      <c r="A367" s="8"/>
-      <c r="B367" s="8"/>
-      <c r="C367" s="8"/>
-      <c r="D367" s="8"/>
-      <c r="E367" s="8"/>
-      <c r="F367" s="8"/>
-      <c r="G367" s="8"/>
-      <c r="H367" s="8"/>
+      <c r="A367" s="9"/>
+      <c r="B367" s="9"/>
+      <c r="C367" s="9"/>
+      <c r="D367" s="9"/>
+      <c r="E367" s="9"/>
+      <c r="F367" s="9"/>
+      <c r="G367" s="9"/>
+      <c r="H367" s="9"/>
     </row>
     <row r="368" spans="1:8">
-      <c r="A368" s="8"/>
-      <c r="B368" s="8"/>
-      <c r="C368" s="8"/>
-      <c r="D368" s="8"/>
-      <c r="E368" s="8"/>
-      <c r="F368" s="8"/>
-      <c r="G368" s="8"/>
-      <c r="H368" s="8"/>
+      <c r="A368" s="9"/>
+      <c r="B368" s="9"/>
+      <c r="C368" s="9"/>
+      <c r="D368" s="9"/>
+      <c r="E368" s="9"/>
+      <c r="F368" s="9"/>
+      <c r="G368" s="9"/>
+      <c r="H368" s="9"/>
     </row>
     <row r="369" spans="1:8">
-      <c r="A369" s="8"/>
-      <c r="B369" s="8"/>
-      <c r="C369" s="8"/>
-      <c r="D369" s="8"/>
-      <c r="E369" s="8"/>
-      <c r="F369" s="8"/>
-      <c r="G369" s="8"/>
-      <c r="H369" s="8"/>
+      <c r="A369" s="9"/>
+      <c r="B369" s="9"/>
+      <c r="C369" s="9"/>
+      <c r="D369" s="9"/>
+      <c r="E369" s="9"/>
+      <c r="F369" s="9"/>
+      <c r="G369" s="9"/>
+      <c r="H369" s="9"/>
     </row>
     <row r="370" spans="1:8">
-      <c r="A370" s="8"/>
-      <c r="B370" s="8"/>
-      <c r="C370" s="8"/>
-      <c r="D370" s="8"/>
-      <c r="E370" s="8"/>
-      <c r="F370" s="8"/>
-      <c r="G370" s="8"/>
-      <c r="H370" s="8"/>
+      <c r="A370" s="9"/>
+      <c r="B370" s="9"/>
+      <c r="C370" s="9"/>
+      <c r="D370" s="9"/>
+      <c r="E370" s="9"/>
+      <c r="F370" s="9"/>
+      <c r="G370" s="9"/>
+      <c r="H370" s="9"/>
     </row>
     <row r="371" spans="1:8">
-      <c r="A371" s="8"/>
-      <c r="B371" s="8"/>
-      <c r="C371" s="8"/>
-      <c r="D371" s="8"/>
-      <c r="E371" s="8"/>
-      <c r="F371" s="8"/>
-      <c r="G371" s="8"/>
-      <c r="H371" s="8"/>
+      <c r="A371" s="9"/>
+      <c r="B371" s="9"/>
+      <c r="C371" s="9"/>
+      <c r="D371" s="9"/>
+      <c r="E371" s="9"/>
+      <c r="F371" s="9"/>
+      <c r="G371" s="9"/>
+      <c r="H371" s="9"/>
     </row>
     <row r="372" spans="1:8">
-      <c r="A372" s="8"/>
-      <c r="B372" s="8"/>
-      <c r="C372" s="8"/>
-      <c r="D372" s="8"/>
-      <c r="E372" s="8"/>
-      <c r="F372" s="8"/>
-      <c r="G372" s="8"/>
-      <c r="H372" s="8"/>
+      <c r="A372" s="9"/>
+      <c r="B372" s="9"/>
+      <c r="C372" s="9"/>
+      <c r="D372" s="9"/>
+      <c r="E372" s="9"/>
+      <c r="F372" s="9"/>
+      <c r="G372" s="9"/>
+      <c r="H372" s="9"/>
     </row>
     <row r="373" spans="1:8">
-      <c r="A373" s="8"/>
-      <c r="B373" s="8"/>
-      <c r="C373" s="8"/>
-      <c r="D373" s="8"/>
-      <c r="E373" s="8"/>
-      <c r="F373" s="8"/>
-      <c r="G373" s="8"/>
-      <c r="H373" s="8"/>
+      <c r="A373" s="9"/>
+      <c r="B373" s="9"/>
+      <c r="C373" s="9"/>
+      <c r="D373" s="9"/>
+      <c r="E373" s="9"/>
+      <c r="F373" s="9"/>
+      <c r="G373" s="9"/>
+      <c r="H373" s="9"/>
     </row>
     <row r="374" spans="1:8">
-      <c r="A374" s="8"/>
-      <c r="B374" s="8"/>
-      <c r="C374" s="8"/>
-      <c r="D374" s="8"/>
-      <c r="E374" s="8"/>
-      <c r="F374" s="8"/>
-      <c r="G374" s="8"/>
-      <c r="H374" s="8"/>
+      <c r="A374" s="9"/>
+      <c r="B374" s="9"/>
+      <c r="C374" s="9"/>
+      <c r="D374" s="9"/>
+      <c r="E374" s="9"/>
+      <c r="F374" s="9"/>
+      <c r="G374" s="9"/>
+      <c r="H374" s="9"/>
     </row>
     <row r="375" spans="1:8">
-      <c r="A375" s="8"/>
-      <c r="B375" s="8"/>
-      <c r="C375" s="8"/>
-      <c r="D375" s="8"/>
-      <c r="E375" s="8"/>
-      <c r="F375" s="8"/>
-      <c r="G375" s="8"/>
-      <c r="H375" s="8"/>
+      <c r="A375" s="9"/>
+      <c r="B375" s="9"/>
+      <c r="C375" s="9"/>
+      <c r="D375" s="9"/>
+      <c r="E375" s="9"/>
+      <c r="F375" s="9"/>
+      <c r="G375" s="9"/>
+      <c r="H375" s="9"/>
     </row>
     <row r="376" spans="1:8">
-      <c r="A376" s="8"/>
-      <c r="B376" s="8"/>
-      <c r="C376" s="8"/>
-      <c r="D376" s="8"/>
-      <c r="E376" s="8"/>
-      <c r="F376" s="8"/>
-      <c r="G376" s="8"/>
-      <c r="H376" s="8"/>
+      <c r="A376" s="9"/>
+      <c r="B376" s="9"/>
+      <c r="C376" s="9"/>
+      <c r="D376" s="9"/>
+      <c r="E376" s="9"/>
+      <c r="F376" s="9"/>
+      <c r="G376" s="9"/>
+      <c r="H376" s="9"/>
     </row>
     <row r="377" spans="1:8">
-      <c r="A377" s="8"/>
-      <c r="B377" s="8"/>
-      <c r="C377" s="8"/>
-      <c r="D377" s="8"/>
-      <c r="E377" s="8"/>
-      <c r="F377" s="8"/>
-      <c r="G377" s="8"/>
-      <c r="H377" s="8"/>
+      <c r="A377" s="9"/>
+      <c r="B377" s="9"/>
+      <c r="C377" s="9"/>
+      <c r="D377" s="9"/>
+      <c r="E377" s="9"/>
+      <c r="F377" s="9"/>
+      <c r="G377" s="9"/>
+      <c r="H377" s="9"/>
     </row>
     <row r="378" spans="1:8">
-      <c r="A378" s="8"/>
-      <c r="B378" s="8"/>
-      <c r="C378" s="8"/>
-      <c r="D378" s="8"/>
-      <c r="E378" s="8"/>
-      <c r="F378" s="8"/>
-      <c r="G378" s="8"/>
-      <c r="H378" s="8"/>
+      <c r="A378" s="9"/>
+      <c r="B378" s="9"/>
+      <c r="C378" s="9"/>
+      <c r="D378" s="9"/>
+      <c r="E378" s="9"/>
+      <c r="F378" s="9"/>
+      <c r="G378" s="9"/>
+      <c r="H378" s="9"/>
     </row>
     <row r="379" spans="1:8">
-      <c r="A379" s="8"/>
-      <c r="B379" s="8"/>
-      <c r="C379" s="8"/>
-      <c r="D379" s="8"/>
-      <c r="E379" s="8"/>
-      <c r="F379" s="8"/>
-      <c r="G379" s="8"/>
-      <c r="H379" s="8"/>
+      <c r="A379" s="9"/>
+      <c r="B379" s="9"/>
+      <c r="C379" s="9"/>
+      <c r="D379" s="9"/>
+      <c r="E379" s="9"/>
+      <c r="F379" s="9"/>
+      <c r="G379" s="9"/>
+      <c r="H379" s="9"/>
     </row>
     <row r="380" spans="1:8">
-      <c r="A380" s="8"/>
-      <c r="B380" s="8"/>
-      <c r="C380" s="8"/>
-      <c r="D380" s="8"/>
-      <c r="E380" s="8"/>
-      <c r="F380" s="8"/>
-      <c r="G380" s="8"/>
-      <c r="H380" s="8"/>
+      <c r="A380" s="9"/>
+      <c r="B380" s="9"/>
+      <c r="C380" s="9"/>
+      <c r="D380" s="9"/>
+      <c r="E380" s="9"/>
+      <c r="F380" s="9"/>
+      <c r="G380" s="9"/>
+      <c r="H380" s="9"/>
     </row>
     <row r="381" spans="1:8">
-      <c r="A381" s="8"/>
-      <c r="B381" s="8"/>
-      <c r="C381" s="8"/>
-      <c r="D381" s="8"/>
-      <c r="E381" s="8"/>
-      <c r="F381" s="8"/>
-      <c r="G381" s="8"/>
-      <c r="H381" s="8"/>
+      <c r="A381" s="9"/>
+      <c r="B381" s="9"/>
+      <c r="C381" s="9"/>
+      <c r="D381" s="9"/>
+      <c r="E381" s="9"/>
+      <c r="F381" s="9"/>
+      <c r="G381" s="9"/>
+      <c r="H381" s="9"/>
     </row>
     <row r="382" spans="1:8">
-      <c r="A382" s="8"/>
-      <c r="B382" s="8"/>
-      <c r="C382" s="8"/>
-      <c r="D382" s="8"/>
-      <c r="E382" s="8"/>
-      <c r="F382" s="8"/>
-      <c r="G382" s="8"/>
-      <c r="H382" s="8"/>
+      <c r="A382" s="9"/>
+      <c r="B382" s="9"/>
+      <c r="C382" s="9"/>
+      <c r="D382" s="9"/>
+      <c r="E382" s="9"/>
+      <c r="F382" s="9"/>
+      <c r="G382" s="9"/>
+      <c r="H382" s="9"/>
     </row>
     <row r="383" spans="1:8">
-      <c r="A383" s="8"/>
-      <c r="B383" s="8"/>
-      <c r="C383" s="8"/>
-      <c r="D383" s="8"/>
-      <c r="E383" s="8"/>
-      <c r="F383" s="8"/>
-      <c r="G383" s="8"/>
-      <c r="H383" s="8"/>
+      <c r="A383" s="9"/>
+      <c r="B383" s="9"/>
+      <c r="C383" s="9"/>
+      <c r="D383" s="9"/>
+      <c r="E383" s="9"/>
+      <c r="F383" s="9"/>
+      <c r="G383" s="9"/>
+      <c r="H383" s="9"/>
     </row>
     <row r="384" spans="1:8">
-      <c r="A384" s="8"/>
-      <c r="B384" s="8"/>
-      <c r="C384" s="8"/>
-      <c r="D384" s="8"/>
-      <c r="E384" s="8"/>
-      <c r="F384" s="8"/>
-      <c r="G384" s="8"/>
-      <c r="H384" s="8"/>
+      <c r="A384" s="9"/>
+      <c r="B384" s="9"/>
+      <c r="C384" s="9"/>
+      <c r="D384" s="9"/>
+      <c r="E384" s="9"/>
+      <c r="F384" s="9"/>
+      <c r="G384" s="9"/>
+      <c r="H384" s="9"/>
     </row>
     <row r="385" spans="1:8">
-      <c r="A385" s="8"/>
-      <c r="B385" s="8"/>
-      <c r="C385" s="8"/>
-      <c r="D385" s="8"/>
-      <c r="E385" s="8"/>
-      <c r="F385" s="8"/>
-      <c r="G385" s="8"/>
-      <c r="H385" s="8"/>
+      <c r="A385" s="9"/>
+      <c r="B385" s="9"/>
+      <c r="C385" s="9"/>
+      <c r="D385" s="9"/>
+      <c r="E385" s="9"/>
+      <c r="F385" s="9"/>
+      <c r="G385" s="9"/>
+      <c r="H385" s="9"/>
     </row>
     <row r="386" spans="1:8">
-      <c r="A386" s="8"/>
-      <c r="B386" s="8"/>
-      <c r="C386" s="8"/>
-      <c r="D386" s="8"/>
-      <c r="E386" s="8"/>
-      <c r="F386" s="8"/>
-      <c r="G386" s="8"/>
-      <c r="H386" s="8"/>
+      <c r="A386" s="9"/>
+      <c r="B386" s="9"/>
+      <c r="C386" s="9"/>
+      <c r="D386" s="9"/>
+      <c r="E386" s="9"/>
+      <c r="F386" s="9"/>
+      <c r="G386" s="9"/>
+      <c r="H386" s="9"/>
     </row>
     <row r="387" spans="1:8">
-      <c r="A387" s="8"/>
-      <c r="B387" s="8"/>
-      <c r="C387" s="8"/>
-      <c r="D387" s="8"/>
-      <c r="E387" s="8"/>
-      <c r="F387" s="8"/>
-      <c r="G387" s="8"/>
-      <c r="H387" s="8"/>
+      <c r="A387" s="9"/>
+      <c r="B387" s="9"/>
+      <c r="C387" s="9"/>
+      <c r="D387" s="9"/>
+      <c r="E387" s="9"/>
+      <c r="F387" s="9"/>
+      <c r="G387" s="9"/>
+      <c r="H387" s="9"/>
     </row>
     <row r="388" spans="1:8">
-      <c r="A388" s="8"/>
-      <c r="B388" s="8"/>
-      <c r="C388" s="8"/>
-      <c r="D388" s="8"/>
-      <c r="E388" s="8"/>
-      <c r="F388" s="8"/>
-      <c r="G388" s="8"/>
-      <c r="H388" s="8"/>
+      <c r="A388" s="9"/>
+      <c r="B388" s="9"/>
+      <c r="C388" s="9"/>
+      <c r="D388" s="9"/>
+      <c r="E388" s="9"/>
+      <c r="F388" s="9"/>
+      <c r="G388" s="9"/>
+      <c r="H388" s="9"/>
     </row>
     <row r="389" spans="1:8">
-      <c r="A389" s="8"/>
-      <c r="B389" s="8"/>
-      <c r="C389" s="8"/>
-      <c r="D389" s="8"/>
-      <c r="E389" s="8"/>
-      <c r="F389" s="8"/>
-      <c r="G389" s="8"/>
-      <c r="H389" s="8"/>
+      <c r="A389" s="9"/>
+      <c r="B389" s="9"/>
+      <c r="C389" s="9"/>
+      <c r="D389" s="9"/>
+      <c r="E389" s="9"/>
+      <c r="F389" s="9"/>
+      <c r="G389" s="9"/>
+      <c r="H389" s="9"/>
     </row>
     <row r="390" spans="1:8">
-      <c r="A390" s="8"/>
-      <c r="B390" s="8"/>
-      <c r="C390" s="8"/>
-      <c r="D390" s="8"/>
-      <c r="E390" s="8"/>
-      <c r="F390" s="8"/>
-      <c r="G390" s="8"/>
-      <c r="H390" s="8"/>
+      <c r="A390" s="9"/>
+      <c r="B390" s="9"/>
+      <c r="C390" s="9"/>
+      <c r="D390" s="9"/>
+      <c r="E390" s="9"/>
+      <c r="F390" s="9"/>
+      <c r="G390" s="9"/>
+      <c r="H390" s="9"/>
     </row>
     <row r="391" spans="1:8">
-      <c r="A391" s="8"/>
-      <c r="B391" s="8"/>
-      <c r="C391" s="8"/>
-      <c r="D391" s="8"/>
-      <c r="E391" s="8"/>
-      <c r="F391" s="8"/>
-      <c r="G391" s="8"/>
-      <c r="H391" s="8"/>
+      <c r="A391" s="9"/>
+      <c r="B391" s="9"/>
+      <c r="C391" s="9"/>
+      <c r="D391" s="9"/>
+      <c r="E391" s="9"/>
+      <c r="F391" s="9"/>
+      <c r="G391" s="9"/>
+      <c r="H391" s="9"/>
     </row>
     <row r="392" spans="1:8">
-      <c r="A392" s="8"/>
-      <c r="B392" s="8"/>
-      <c r="C392" s="8"/>
-      <c r="D392" s="8"/>
-      <c r="E392" s="8"/>
-      <c r="F392" s="8"/>
-      <c r="G392" s="8"/>
-      <c r="H392" s="8"/>
+      <c r="A392" s="9"/>
+      <c r="B392" s="9"/>
+      <c r="C392" s="9"/>
+      <c r="D392" s="9"/>
+      <c r="E392" s="9"/>
+      <c r="F392" s="9"/>
+      <c r="G392" s="9"/>
+      <c r="H392" s="9"/>
     </row>
     <row r="393" spans="1:8">
-      <c r="A393" s="8"/>
-      <c r="B393" s="8"/>
-      <c r="C393" s="8"/>
-      <c r="D393" s="8"/>
-      <c r="E393" s="8"/>
-      <c r="F393" s="8"/>
-      <c r="G393" s="8"/>
-      <c r="H393" s="8"/>
+      <c r="A393" s="9"/>
+      <c r="B393" s="9"/>
+      <c r="C393" s="9"/>
+      <c r="D393" s="9"/>
+      <c r="E393" s="9"/>
+      <c r="F393" s="9"/>
+      <c r="G393" s="9"/>
+      <c r="H393" s="9"/>
     </row>
     <row r="394" spans="1:8">
-      <c r="A394" s="8"/>
-      <c r="B394" s="8"/>
-      <c r="C394" s="8"/>
-      <c r="D394" s="8"/>
-      <c r="E394" s="8"/>
-      <c r="F394" s="8"/>
-      <c r="G394" s="8"/>
-      <c r="H394" s="8"/>
+      <c r="A394" s="9"/>
+      <c r="B394" s="9"/>
+      <c r="C394" s="9"/>
+      <c r="D394" s="9"/>
+      <c r="E394" s="9"/>
+      <c r="F394" s="9"/>
+      <c r="G394" s="9"/>
+      <c r="H394" s="9"/>
     </row>
     <row r="395" spans="1:8">
-      <c r="A395" s="8"/>
-      <c r="B395" s="8"/>
-      <c r="C395" s="8"/>
-      <c r="D395" s="8"/>
-      <c r="E395" s="8"/>
-      <c r="F395" s="8"/>
-      <c r="G395" s="8"/>
-      <c r="H395" s="8"/>
+      <c r="A395" s="9"/>
+      <c r="B395" s="9"/>
+      <c r="C395" s="9"/>
+      <c r="D395" s="9"/>
+      <c r="E395" s="9"/>
+      <c r="F395" s="9"/>
+      <c r="G395" s="9"/>
+      <c r="H395" s="9"/>
     </row>
     <row r="396" spans="1:8">
-      <c r="A396" s="8"/>
-      <c r="B396" s="8"/>
-      <c r="C396" s="8"/>
-      <c r="D396" s="8"/>
-      <c r="E396" s="8"/>
-      <c r="F396" s="8"/>
-      <c r="G396" s="8"/>
-      <c r="H396" s="8"/>
+      <c r="A396" s="9"/>
+      <c r="B396" s="9"/>
+      <c r="C396" s="9"/>
+      <c r="D396" s="9"/>
+      <c r="E396" s="9"/>
+      <c r="F396" s="9"/>
+      <c r="G396" s="9"/>
+      <c r="H396" s="9"/>
     </row>
     <row r="397" spans="1:8">
-      <c r="A397" s="8"/>
-      <c r="B397" s="8"/>
-      <c r="C397" s="8"/>
-      <c r="D397" s="8"/>
-      <c r="E397" s="8"/>
-      <c r="F397" s="8"/>
-      <c r="G397" s="8"/>
-      <c r="H397" s="8"/>
+      <c r="A397" s="9"/>
+      <c r="B397" s="9"/>
+      <c r="C397" s="9"/>
+      <c r="D397" s="9"/>
+      <c r="E397" s="9"/>
+      <c r="F397" s="9"/>
+      <c r="G397" s="9"/>
+      <c r="H397" s="9"/>
     </row>
     <row r="398" spans="1:8">
-      <c r="A398" s="8"/>
-      <c r="B398" s="8"/>
-      <c r="C398" s="8"/>
-      <c r="D398" s="8"/>
-      <c r="E398" s="8"/>
-      <c r="F398" s="8"/>
-      <c r="G398" s="8"/>
-      <c r="H398" s="8"/>
+      <c r="A398" s="9"/>
+      <c r="B398" s="9"/>
+      <c r="C398" s="9"/>
+      <c r="D398" s="9"/>
+      <c r="E398" s="9"/>
+      <c r="F398" s="9"/>
+      <c r="G398" s="9"/>
+      <c r="H398" s="9"/>
     </row>
     <row r="399" spans="1:8">
-      <c r="A399" s="8"/>
-      <c r="B399" s="8"/>
-      <c r="C399" s="8"/>
-      <c r="D399" s="8"/>
-      <c r="E399" s="8"/>
-      <c r="F399" s="8"/>
-      <c r="G399" s="8"/>
-      <c r="H399" s="8"/>
+      <c r="A399" s="9"/>
+      <c r="B399" s="9"/>
+      <c r="C399" s="9"/>
+      <c r="D399" s="9"/>
+      <c r="E399" s="9"/>
+      <c r="F399" s="9"/>
+      <c r="G399" s="9"/>
+      <c r="H399" s="9"/>
     </row>
     <row r="400" spans="1:8">
-      <c r="A400" s="8"/>
-      <c r="B400" s="8"/>
-      <c r="C400" s="8"/>
-      <c r="D400" s="8"/>
-      <c r="E400" s="8"/>
-      <c r="F400" s="8"/>
-      <c r="G400" s="8"/>
-      <c r="H400" s="8"/>
+      <c r="A400" s="9"/>
+      <c r="B400" s="9"/>
+      <c r="C400" s="9"/>
+      <c r="D400" s="9"/>
+      <c r="E400" s="9"/>
+      <c r="F400" s="9"/>
+      <c r="G400" s="9"/>
+      <c r="H400" s="9"/>
     </row>
     <row r="401" spans="1:8">
-      <c r="A401" s="8"/>
-      <c r="B401" s="8"/>
-      <c r="C401" s="8"/>
-      <c r="D401" s="8"/>
-      <c r="E401" s="8"/>
-      <c r="F401" s="8"/>
-      <c r="G401" s="8"/>
-      <c r="H401" s="8"/>
+      <c r="A401" s="9"/>
+      <c r="B401" s="9"/>
+      <c r="C401" s="9"/>
+      <c r="D401" s="9"/>
+      <c r="E401" s="9"/>
+      <c r="F401" s="9"/>
+      <c r="G401" s="9"/>
+      <c r="H401" s="9"/>
     </row>
     <row r="402" spans="1:8">
-      <c r="A402" s="8"/>
-      <c r="B402" s="8"/>
-      <c r="C402" s="8"/>
-      <c r="D402" s="8"/>
-      <c r="E402" s="8"/>
-      <c r="F402" s="8"/>
-      <c r="G402" s="8"/>
-      <c r="H402" s="8"/>
+      <c r="A402" s="9"/>
+      <c r="B402" s="9"/>
+      <c r="C402" s="9"/>
+      <c r="D402" s="9"/>
+      <c r="E402" s="9"/>
+      <c r="F402" s="9"/>
+      <c r="G402" s="9"/>
+      <c r="H402" s="9"/>
     </row>
     <row r="403" spans="1:8">
-      <c r="A403" s="8"/>
-      <c r="B403" s="8"/>
-      <c r="C403" s="8"/>
-      <c r="D403" s="8"/>
-      <c r="E403" s="8"/>
-      <c r="F403" s="8"/>
-      <c r="G403" s="8"/>
-      <c r="H403" s="8"/>
+      <c r="A403" s="9"/>
+      <c r="B403" s="9"/>
+      <c r="C403" s="9"/>
+      <c r="D403" s="9"/>
+      <c r="E403" s="9"/>
+      <c r="F403" s="9"/>
+      <c r="G403" s="9"/>
+      <c r="H403" s="9"/>
     </row>
     <row r="404" spans="1:8">
-      <c r="A404" s="8"/>
-      <c r="B404" s="8"/>
-      <c r="C404" s="8"/>
-      <c r="D404" s="8"/>
-      <c r="E404" s="8"/>
-      <c r="F404" s="8"/>
-      <c r="G404" s="8"/>
-      <c r="H404" s="8"/>
+      <c r="A404" s="9"/>
+      <c r="B404" s="9"/>
+      <c r="C404" s="9"/>
+      <c r="D404" s="9"/>
+      <c r="E404" s="9"/>
+      <c r="F404" s="9"/>
+      <c r="G404" s="9"/>
+      <c r="H404" s="9"/>
     </row>
     <row r="405" spans="1:8">
-      <c r="A405" s="8"/>
-      <c r="B405" s="8"/>
-      <c r="C405" s="8"/>
-      <c r="D405" s="8"/>
-      <c r="E405" s="8"/>
-      <c r="F405" s="8"/>
-      <c r="G405" s="8"/>
-      <c r="H405" s="8"/>
+      <c r="A405" s="9"/>
+      <c r="B405" s="9"/>
+      <c r="C405" s="9"/>
+      <c r="D405" s="9"/>
+      <c r="E405" s="9"/>
+      <c r="F405" s="9"/>
+      <c r="G405" s="9"/>
+      <c r="H405" s="9"/>
     </row>
     <row r="406" spans="1:8">
-      <c r="A406" s="8"/>
-      <c r="B406" s="8"/>
-      <c r="C406" s="8"/>
-      <c r="D406" s="8"/>
-      <c r="E406" s="8"/>
-      <c r="F406" s="8"/>
-      <c r="G406" s="8"/>
-      <c r="H406" s="8"/>
+      <c r="A406" s="9"/>
+      <c r="B406" s="9"/>
+      <c r="C406" s="9"/>
+      <c r="D406" s="9"/>
+      <c r="E406" s="9"/>
+      <c r="F406" s="9"/>
+      <c r="G406" s="9"/>
+      <c r="H406" s="9"/>
     </row>
     <row r="407" spans="1:8">
-      <c r="A407" s="8"/>
-      <c r="B407" s="8"/>
-      <c r="C407" s="8"/>
-      <c r="D407" s="8"/>
-      <c r="E407" s="8"/>
-      <c r="F407" s="8"/>
-      <c r="G407" s="8"/>
-      <c r="H407" s="8"/>
+      <c r="A407" s="9"/>
+      <c r="B407" s="9"/>
+      <c r="C407" s="9"/>
+      <c r="D407" s="9"/>
+      <c r="E407" s="9"/>
+      <c r="F407" s="9"/>
+      <c r="G407" s="9"/>
+      <c r="H407" s="9"/>
     </row>
     <row r="408" spans="1:8">
-      <c r="A408" s="8"/>
-      <c r="B408" s="8"/>
-      <c r="C408" s="8"/>
-      <c r="D408" s="8"/>
-      <c r="E408" s="8"/>
-      <c r="F408" s="8"/>
-      <c r="G408" s="8"/>
-      <c r="H408" s="8"/>
+      <c r="A408" s="9"/>
+      <c r="B408" s="9"/>
+      <c r="C408" s="9"/>
+      <c r="D408" s="9"/>
+      <c r="E408" s="9"/>
+      <c r="F408" s="9"/>
+      <c r="G408" s="9"/>
+      <c r="H408" s="9"/>
     </row>
     <row r="409" spans="1:8">
-      <c r="A409" s="8"/>
-      <c r="B409" s="8"/>
-      <c r="C409" s="8"/>
-      <c r="D409" s="8"/>
-      <c r="E409" s="8"/>
-      <c r="F409" s="8"/>
-      <c r="G409" s="8"/>
-      <c r="H409" s="8"/>
+      <c r="A409" s="9"/>
+      <c r="B409" s="9"/>
+      <c r="C409" s="9"/>
+      <c r="D409" s="9"/>
+      <c r="E409" s="9"/>
+      <c r="F409" s="9"/>
+      <c r="G409" s="9"/>
+      <c r="H409" s="9"/>
     </row>
     <row r="410" spans="1:8">
-      <c r="A410" s="8"/>
-      <c r="B410" s="8"/>
-      <c r="C410" s="8"/>
-      <c r="D410" s="8"/>
-      <c r="E410" s="8"/>
-      <c r="F410" s="8"/>
-      <c r="G410" s="8"/>
-      <c r="H410" s="8"/>
+      <c r="A410" s="9"/>
+      <c r="B410" s="9"/>
+      <c r="C410" s="9"/>
+      <c r="D410" s="9"/>
+      <c r="E410" s="9"/>
+      <c r="F410" s="9"/>
+      <c r="G410" s="9"/>
+      <c r="H410" s="9"/>
     </row>
     <row r="411" spans="1:8">
-      <c r="A411" s="8"/>
-      <c r="B411" s="8"/>
-      <c r="C411" s="8"/>
-      <c r="D411" s="8"/>
-      <c r="E411" s="8"/>
-      <c r="F411" s="8"/>
-      <c r="G411" s="8"/>
-      <c r="H411" s="8"/>
+      <c r="A411" s="9"/>
+      <c r="B411" s="9"/>
+      <c r="C411" s="9"/>
+      <c r="D411" s="9"/>
+      <c r="E411" s="9"/>
+      <c r="F411" s="9"/>
+      <c r="G411" s="9"/>
+      <c r="H411" s="9"/>
     </row>
     <row r="412" spans="1:8">
-      <c r="A412" s="8"/>
-      <c r="B412" s="8"/>
-      <c r="C412" s="8"/>
-      <c r="D412" s="8"/>
-      <c r="E412" s="8"/>
-      <c r="F412" s="8"/>
-      <c r="G412" s="8"/>
-      <c r="H412" s="8"/>
+      <c r="A412" s="9"/>
+      <c r="B412" s="9"/>
+      <c r="C412" s="9"/>
+      <c r="D412" s="9"/>
+      <c r="E412" s="9"/>
+      <c r="F412" s="9"/>
+      <c r="G412" s="9"/>
+      <c r="H412" s="9"/>
     </row>
     <row r="413" spans="1:8">
-      <c r="A413" s="8"/>
-      <c r="B413" s="8"/>
-      <c r="C413" s="8"/>
-      <c r="D413" s="8"/>
-      <c r="E413" s="8"/>
-      <c r="F413" s="8"/>
-      <c r="G413" s="8"/>
-      <c r="H413" s="8"/>
+      <c r="A413" s="9"/>
+      <c r="B413" s="9"/>
+      <c r="C413" s="9"/>
+      <c r="D413" s="9"/>
+      <c r="E413" s="9"/>
+      <c r="F413" s="9"/>
+      <c r="G413" s="9"/>
+      <c r="H413" s="9"/>
     </row>
     <row r="414" spans="1:8">
-      <c r="A414" s="8"/>
-      <c r="B414" s="8"/>
-      <c r="C414" s="8"/>
-      <c r="D414" s="8"/>
-      <c r="E414" s="8"/>
-      <c r="F414" s="8"/>
-      <c r="G414" s="8"/>
-      <c r="H414" s="8"/>
+      <c r="A414" s="9"/>
+      <c r="B414" s="9"/>
+      <c r="C414" s="9"/>
+      <c r="D414" s="9"/>
+      <c r="E414" s="9"/>
+      <c r="F414" s="9"/>
+      <c r="G414" s="9"/>
+      <c r="H414" s="9"/>
     </row>
     <row r="415" spans="1:8">
-      <c r="A415" s="8"/>
-      <c r="B415" s="8"/>
-      <c r="C415" s="8"/>
-      <c r="D415" s="8"/>
-      <c r="E415" s="8"/>
-      <c r="F415" s="8"/>
-      <c r="G415" s="8"/>
-      <c r="H415" s="8"/>
+      <c r="A415" s="9"/>
+      <c r="B415" s="9"/>
+      <c r="C415" s="9"/>
+      <c r="D415" s="9"/>
+      <c r="E415" s="9"/>
+      <c r="F415" s="9"/>
+      <c r="G415" s="9"/>
+      <c r="H415" s="9"/>
     </row>
     <row r="416" spans="1:8">
-      <c r="A416" s="8"/>
-      <c r="B416" s="8"/>
-      <c r="C416" s="8"/>
-      <c r="D416" s="8"/>
-      <c r="E416" s="8"/>
-      <c r="F416" s="8"/>
-      <c r="G416" s="8"/>
-      <c r="H416" s="8"/>
+      <c r="A416" s="9"/>
+      <c r="B416" s="9"/>
+      <c r="C416" s="9"/>
+      <c r="D416" s="9"/>
+      <c r="E416" s="9"/>
+      <c r="F416" s="9"/>
+      <c r="G416" s="9"/>
+      <c r="H416" s="9"/>
     </row>
     <row r="417" spans="1:8">
-      <c r="A417" s="8"/>
-      <c r="B417" s="8"/>
-      <c r="C417" s="8"/>
-      <c r="D417" s="8"/>
-      <c r="E417" s="8"/>
-      <c r="F417" s="8"/>
-      <c r="G417" s="8"/>
-      <c r="H417" s="8"/>
+      <c r="A417" s="9"/>
+      <c r="B417" s="9"/>
+      <c r="C417" s="9"/>
+      <c r="D417" s="9"/>
+      <c r="E417" s="9"/>
+      <c r="F417" s="9"/>
+      <c r="G417" s="9"/>
+      <c r="H417" s="9"/>
     </row>
     <row r="418" spans="1:8">
-      <c r="A418" s="8"/>
-      <c r="B418" s="8"/>
-      <c r="C418" s="8"/>
-      <c r="D418" s="8"/>
-      <c r="E418" s="8"/>
-      <c r="F418" s="8"/>
-      <c r="G418" s="8"/>
-      <c r="H418" s="8"/>
+      <c r="A418" s="9"/>
+      <c r="B418" s="9"/>
+      <c r="C418" s="9"/>
+      <c r="D418" s="9"/>
+      <c r="E418" s="9"/>
+      <c r="F418" s="9"/>
+      <c r="G418" s="9"/>
+      <c r="H418" s="9"/>
     </row>
     <row r="419" spans="1:8">
-      <c r="A419" s="8"/>
-      <c r="B419" s="8"/>
-      <c r="C419" s="8"/>
-      <c r="D419" s="8"/>
-      <c r="E419" s="8"/>
-      <c r="F419" s="8"/>
-      <c r="G419" s="8"/>
-      <c r="H419" s="8"/>
+      <c r="A419" s="9"/>
+      <c r="B419" s="9"/>
+      <c r="C419" s="9"/>
+      <c r="D419" s="9"/>
+      <c r="E419" s="9"/>
+      <c r="F419" s="9"/>
+      <c r="G419" s="9"/>
+      <c r="H419" s="9"/>
     </row>
     <row r="420" spans="1:8">
-      <c r="A420" s="8"/>
-      <c r="B420" s="8"/>
-      <c r="C420" s="8"/>
-      <c r="D420" s="8"/>
-      <c r="E420" s="8"/>
-      <c r="F420" s="8"/>
-      <c r="G420" s="8"/>
-      <c r="H420" s="8"/>
+      <c r="A420" s="9"/>
+      <c r="B420" s="9"/>
+      <c r="C420" s="9"/>
+      <c r="D420" s="9"/>
+      <c r="E420" s="9"/>
+      <c r="F420" s="9"/>
+      <c r="G420" s="9"/>
+      <c r="H420" s="9"/>
     </row>
     <row r="421" spans="1:8">
-      <c r="A421" s="8"/>
-      <c r="B421" s="8"/>
-      <c r="C421" s="8"/>
-      <c r="D421" s="8"/>
-      <c r="E421" s="8"/>
-      <c r="F421" s="8"/>
-      <c r="G421" s="8"/>
-      <c r="H421" s="8"/>
+      <c r="A421" s="9"/>
+      <c r="B421" s="9"/>
+      <c r="C421" s="9"/>
+      <c r="D421" s="9"/>
+      <c r="E421" s="9"/>
+      <c r="F421" s="9"/>
+      <c r="G421" s="9"/>
+      <c r="H421" s="9"/>
     </row>
     <row r="422" spans="1:8">
-      <c r="A422" s="8"/>
-      <c r="B422" s="8"/>
-      <c r="C422" s="8"/>
-      <c r="D422" s="8"/>
-      <c r="E422" s="8"/>
-      <c r="F422" s="8"/>
-      <c r="G422" s="8"/>
-      <c r="H422" s="8"/>
+      <c r="A422" s="9"/>
+      <c r="B422" s="9"/>
+      <c r="C422" s="9"/>
+      <c r="D422" s="9"/>
+      <c r="E422" s="9"/>
+      <c r="F422" s="9"/>
+      <c r="G422" s="9"/>
+      <c r="H422" s="9"/>
     </row>
     <row r="423" spans="1:8">
-      <c r="A423" s="8"/>
-      <c r="B423" s="8"/>
-      <c r="C423" s="8"/>
-      <c r="D423" s="8"/>
-      <c r="E423" s="8"/>
-      <c r="F423" s="8"/>
-      <c r="G423" s="8"/>
-      <c r="H423" s="8"/>
+      <c r="A423" s="9"/>
+      <c r="B423" s="9"/>
+      <c r="C423" s="9"/>
+      <c r="D423" s="9"/>
+      <c r="E423" s="9"/>
+      <c r="F423" s="9"/>
+      <c r="G423" s="9"/>
+      <c r="H423" s="9"/>
     </row>
     <row r="424" spans="1:8">
-      <c r="A424" s="8"/>
-      <c r="B424" s="8"/>
-      <c r="C424" s="8"/>
-      <c r="D424" s="8"/>
-      <c r="E424" s="8"/>
-      <c r="F424" s="8"/>
-      <c r="G424" s="8"/>
-      <c r="H424" s="8"/>
+      <c r="A424" s="9"/>
+      <c r="B424" s="9"/>
+      <c r="C424" s="9"/>
+      <c r="D424" s="9"/>
+      <c r="E424" s="9"/>
+      <c r="F424" s="9"/>
+      <c r="G424" s="9"/>
+      <c r="H424" s="9"/>
     </row>
     <row r="425" spans="1:8">
-      <c r="A425" s="8"/>
-      <c r="B425" s="8"/>
-      <c r="C425" s="8"/>
-      <c r="D425" s="8"/>
-      <c r="E425" s="8"/>
-      <c r="F425" s="8"/>
-      <c r="G425" s="8"/>
-      <c r="H425" s="8"/>
+      <c r="A425" s="9"/>
+      <c r="B425" s="9"/>
+      <c r="C425" s="9"/>
+      <c r="D425" s="9"/>
+      <c r="E425" s="9"/>
+      <c r="F425" s="9"/>
+      <c r="G425" s="9"/>
+      <c r="H425" s="9"/>
     </row>
     <row r="426" spans="1:8">
-      <c r="A426" s="8"/>
-      <c r="B426" s="8"/>
-      <c r="C426" s="8"/>
-      <c r="D426" s="8"/>
-      <c r="E426" s="8"/>
-      <c r="F426" s="8"/>
-      <c r="G426" s="8"/>
-      <c r="H426" s="8"/>
+      <c r="A426" s="9"/>
+      <c r="B426" s="9"/>
+      <c r="C426" s="9"/>
+      <c r="D426" s="9"/>
+      <c r="E426" s="9"/>
+      <c r="F426" s="9"/>
+      <c r="G426" s="9"/>
+      <c r="H426" s="9"/>
     </row>
     <row r="427" spans="1:8">
-      <c r="A427" s="8"/>
-      <c r="B427" s="8"/>
-      <c r="C427" s="8"/>
-      <c r="D427" s="8"/>
-      <c r="E427" s="8"/>
-      <c r="F427" s="8"/>
-      <c r="G427" s="8"/>
-      <c r="H427" s="8"/>
+      <c r="A427" s="9"/>
+      <c r="B427" s="9"/>
+      <c r="C427" s="9"/>
+      <c r="D427" s="9"/>
+      <c r="E427" s="9"/>
+      <c r="F427" s="9"/>
+      <c r="G427" s="9"/>
+      <c r="H427" s="9"/>
     </row>
     <row r="428" spans="1:8">
-      <c r="A428" s="8"/>
-      <c r="B428" s="8"/>
-      <c r="C428" s="8"/>
-      <c r="D428" s="8"/>
-      <c r="E428" s="8"/>
-      <c r="F428" s="8"/>
-      <c r="G428" s="8"/>
-      <c r="H428" s="8"/>
+      <c r="A428" s="9"/>
+      <c r="B428" s="9"/>
+      <c r="C428" s="9"/>
+      <c r="D428" s="9"/>
+      <c r="E428" s="9"/>
+      <c r="F428" s="9"/>
+      <c r="G428" s="9"/>
+      <c r="H428" s="9"/>
     </row>
     <row r="429" spans="1:8">
-      <c r="A429" s="8"/>
-      <c r="B429" s="8"/>
-      <c r="C429" s="8"/>
-      <c r="D429" s="8"/>
-      <c r="E429" s="8"/>
-      <c r="F429" s="8"/>
-      <c r="G429" s="8"/>
-      <c r="H429" s="8"/>
+      <c r="A429" s="9"/>
+      <c r="B429" s="9"/>
+      <c r="C429" s="9"/>
+      <c r="D429" s="9"/>
+      <c r="E429" s="9"/>
+      <c r="F429" s="9"/>
+      <c r="G429" s="9"/>
+      <c r="H429" s="9"/>
     </row>
     <row r="430" spans="1:8">
-      <c r="A430" s="8"/>
-      <c r="B430" s="8"/>
-      <c r="C430" s="8"/>
-      <c r="D430" s="8"/>
-      <c r="E430" s="8"/>
-      <c r="F430" s="8"/>
-      <c r="G430" s="8"/>
-      <c r="H430" s="8"/>
+      <c r="A430" s="9"/>
+      <c r="B430" s="9"/>
+      <c r="C430" s="9"/>
+      <c r="D430" s="9"/>
+      <c r="E430" s="9"/>
+      <c r="F430" s="9"/>
+      <c r="G430" s="9"/>
+      <c r="H430" s="9"/>
     </row>
     <row r="431" spans="1:8">
-      <c r="A431" s="8"/>
-      <c r="B431" s="8"/>
-      <c r="C431" s="8"/>
-      <c r="D431" s="8"/>
-      <c r="E431" s="8"/>
-      <c r="F431" s="8"/>
-      <c r="G431" s="8"/>
-      <c r="H431" s="8"/>
+      <c r="A431" s="9"/>
+      <c r="B431" s="9"/>
+      <c r="C431" s="9"/>
+      <c r="D431" s="9"/>
+      <c r="E431" s="9"/>
+      <c r="F431" s="9"/>
+      <c r="G431" s="9"/>
+      <c r="H431" s="9"/>
     </row>
     <row r="432" spans="1:8">
-      <c r="A432" s="8"/>
-      <c r="B432" s="8"/>
-      <c r="C432" s="8"/>
-      <c r="D432" s="8"/>
-      <c r="E432" s="8"/>
-      <c r="F432" s="8"/>
-      <c r="G432" s="8"/>
-      <c r="H432" s="8"/>
+      <c r="A432" s="9"/>
+      <c r="B432" s="9"/>
+      <c r="C432" s="9"/>
+      <c r="D432" s="9"/>
+      <c r="E432" s="9"/>
+      <c r="F432" s="9"/>
+      <c r="G432" s="9"/>
+      <c r="H432" s="9"/>
     </row>
     <row r="433" spans="1:8">
-      <c r="A433" s="8"/>
-      <c r="B433" s="8"/>
-      <c r="C433" s="8"/>
-      <c r="D433" s="8"/>
-      <c r="E433" s="8"/>
-      <c r="F433" s="8"/>
-      <c r="G433" s="8"/>
-      <c r="H433" s="8"/>
+      <c r="A433" s="9"/>
+      <c r="B433" s="9"/>
+      <c r="C433" s="9"/>
+      <c r="D433" s="9"/>
+      <c r="E433" s="9"/>
+      <c r="F433" s="9"/>
+      <c r="G433" s="9"/>
+      <c r="H433" s="9"/>
     </row>
     <row r="434" spans="1:8">
-      <c r="A434" s="8"/>
-      <c r="B434" s="8"/>
-      <c r="C434" s="8"/>
-      <c r="D434" s="8"/>
-      <c r="E434" s="8"/>
-      <c r="F434" s="8"/>
-      <c r="G434" s="8"/>
-      <c r="H434" s="8"/>
+      <c r="A434" s="9"/>
+      <c r="B434" s="9"/>
+      <c r="C434" s="9"/>
+      <c r="D434" s="9"/>
+      <c r="E434" s="9"/>
+      <c r="F434" s="9"/>
+      <c r="G434" s="9"/>
+      <c r="H434" s="9"/>
     </row>
     <row r="435" spans="1:8">
-      <c r="A435" s="8"/>
-      <c r="B435" s="8"/>
-      <c r="C435" s="8"/>
-      <c r="D435" s="8"/>
-      <c r="E435" s="8"/>
-      <c r="F435" s="8"/>
-      <c r="G435" s="8"/>
-      <c r="H435" s="8"/>
+      <c r="A435" s="9"/>
+      <c r="B435" s="9"/>
+      <c r="C435" s="9"/>
+      <c r="D435" s="9"/>
+      <c r="E435" s="9"/>
+      <c r="F435" s="9"/>
+      <c r="G435" s="9"/>
+      <c r="H435" s="9"/>
     </row>
     <row r="436" spans="1:8">
-      <c r="A436" s="8"/>
-      <c r="B436" s="8"/>
-      <c r="C436" s="8"/>
-      <c r="D436" s="8"/>
-      <c r="E436" s="8"/>
-      <c r="F436" s="8"/>
-      <c r="G436" s="8"/>
-      <c r="H436" s="8"/>
+      <c r="A436" s="9"/>
+      <c r="B436" s="9"/>
+      <c r="C436" s="9"/>
+      <c r="D436" s="9"/>
+      <c r="E436" s="9"/>
+      <c r="F436" s="9"/>
+      <c r="G436" s="9"/>
+      <c r="H436" s="9"/>
     </row>
     <row r="437" spans="1:8">
-      <c r="A437" s="8"/>
-      <c r="B437" s="8"/>
-      <c r="C437" s="8"/>
-      <c r="D437" s="8"/>
-      <c r="E437" s="8"/>
-      <c r="F437" s="8"/>
-      <c r="G437" s="8"/>
-      <c r="H437" s="8"/>
+      <c r="A437" s="9"/>
+      <c r="B437" s="9"/>
+      <c r="C437" s="9"/>
+      <c r="D437" s="9"/>
+      <c r="E437" s="9"/>
+      <c r="F437" s="9"/>
+      <c r="G437" s="9"/>
+      <c r="H437" s="9"/>
     </row>
     <row r="438" spans="1:8">
-      <c r="A438" s="8"/>
-      <c r="B438" s="8"/>
-      <c r="C438" s="8"/>
-      <c r="D438" s="8"/>
-      <c r="E438" s="8"/>
-      <c r="F438" s="8"/>
-      <c r="G438" s="8"/>
-      <c r="H438" s="8"/>
+      <c r="A438" s="9"/>
+      <c r="B438" s="9"/>
+      <c r="C438" s="9"/>
+      <c r="D438" s="9"/>
+      <c r="E438" s="9"/>
+      <c r="F438" s="9"/>
+      <c r="G438" s="9"/>
+      <c r="H438" s="9"/>
     </row>
     <row r="439" spans="1:8">
-      <c r="A439" s="8"/>
-      <c r="B439" s="8"/>
-      <c r="C439" s="8"/>
-      <c r="D439" s="8"/>
-      <c r="E439" s="8"/>
-      <c r="F439" s="8"/>
-      <c r="G439" s="8"/>
-      <c r="H439" s="8"/>
+      <c r="A439" s="9"/>
+      <c r="B439" s="9"/>
+      <c r="C439" s="9"/>
+      <c r="D439" s="9"/>
+      <c r="E439" s="9"/>
+      <c r="F439" s="9"/>
+      <c r="G439" s="9"/>
+      <c r="H439" s="9"/>
     </row>
     <row r="440" spans="1:8">
-      <c r="A440" s="8"/>
-      <c r="B440" s="8"/>
-      <c r="C440" s="8"/>
-      <c r="D440" s="8"/>
-      <c r="E440" s="8"/>
-      <c r="F440" s="8"/>
-      <c r="G440" s="8"/>
-      <c r="H440" s="8"/>
+      <c r="A440" s="9"/>
+      <c r="B440" s="9"/>
+      <c r="C440" s="9"/>
+      <c r="D440" s="9"/>
+      <c r="E440" s="9"/>
+      <c r="F440" s="9"/>
+      <c r="G440" s="9"/>
+      <c r="H440" s="9"/>
     </row>
     <row r="441" spans="1:8">
-      <c r="A441" s="8"/>
-      <c r="B441" s="8"/>
-      <c r="C441" s="8"/>
-      <c r="D441" s="8"/>
-      <c r="E441" s="8"/>
-      <c r="F441" s="8"/>
-      <c r="G441" s="8"/>
-      <c r="H441" s="8"/>
+      <c r="A441" s="9"/>
+      <c r="B441" s="9"/>
+      <c r="C441" s="9"/>
+      <c r="D441" s="9"/>
+      <c r="E441" s="9"/>
+      <c r="F441" s="9"/>
+      <c r="G441" s="9"/>
+      <c r="H441" s="9"/>
     </row>
     <row r="442" spans="1:8">
-      <c r="A442" s="8"/>
-      <c r="B442" s="8"/>
-      <c r="C442" s="8"/>
-      <c r="D442" s="8"/>
-      <c r="E442" s="8"/>
-      <c r="F442" s="8"/>
-      <c r="G442" s="8"/>
-      <c r="H442" s="8"/>
+      <c r="A442" s="9"/>
+      <c r="B442" s="9"/>
+      <c r="C442" s="9"/>
+      <c r="D442" s="9"/>
+      <c r="E442" s="9"/>
+      <c r="F442" s="9"/>
+      <c r="G442" s="9"/>
+      <c r="H442" s="9"/>
     </row>
     <row r="443" spans="1:8">
-      <c r="A443" s="8"/>
-      <c r="B443" s="8"/>
-      <c r="C443" s="8"/>
-      <c r="D443" s="8"/>
-      <c r="E443" s="8"/>
-      <c r="F443" s="8"/>
-      <c r="G443" s="8"/>
-      <c r="H443" s="8"/>
+      <c r="A443" s="9"/>
+      <c r="B443" s="9"/>
+      <c r="C443" s="9"/>
+      <c r="D443" s="9"/>
+      <c r="E443" s="9"/>
+      <c r="F443" s="9"/>
+      <c r="G443" s="9"/>
+      <c r="H443" s="9"/>
     </row>
     <row r="444" spans="1:8">
-      <c r="A444" s="8"/>
-      <c r="B444" s="8"/>
-      <c r="C444" s="8"/>
-      <c r="D444" s="8"/>
-      <c r="E444" s="8"/>
-      <c r="F444" s="8"/>
-      <c r="G444" s="8"/>
-      <c r="H444" s="8"/>
+      <c r="A444" s="9"/>
+      <c r="B444" s="9"/>
+      <c r="C444" s="9"/>
+      <c r="D444" s="9"/>
+      <c r="E444" s="9"/>
+      <c r="F444" s="9"/>
+      <c r="G444" s="9"/>
+      <c r="H444" s="9"/>
     </row>
     <row r="445" spans="1:8">
-      <c r="A445" s="8"/>
-      <c r="B445" s="8"/>
-      <c r="C445" s="8"/>
-      <c r="D445" s="8"/>
-      <c r="E445" s="8"/>
-      <c r="F445" s="8"/>
-      <c r="G445" s="8"/>
-      <c r="H445" s="8"/>
+      <c r="A445" s="9"/>
+      <c r="B445" s="9"/>
+      <c r="C445" s="9"/>
+      <c r="D445" s="9"/>
+      <c r="E445" s="9"/>
+      <c r="F445" s="9"/>
+      <c r="G445" s="9"/>
+      <c r="H445" s="9"/>
     </row>
     <row r="446" spans="1:8">
-      <c r="A446" s="8"/>
-      <c r="B446" s="8"/>
-      <c r="C446" s="8"/>
-      <c r="D446" s="8"/>
-      <c r="E446" s="8"/>
-      <c r="F446" s="8"/>
-      <c r="G446" s="8"/>
-      <c r="H446" s="8"/>
+      <c r="A446" s="9"/>
+      <c r="B446" s="9"/>
+      <c r="C446" s="9"/>
+      <c r="D446" s="9"/>
+      <c r="E446" s="9"/>
+      <c r="F446" s="9"/>
+      <c r="G446" s="9"/>
+      <c r="H446" s="9"/>
     </row>
     <row r="447" spans="1:8">
-      <c r="A447" s="8"/>
-      <c r="B447" s="8"/>
-      <c r="C447" s="8"/>
-      <c r="D447" s="8"/>
-      <c r="E447" s="8"/>
-      <c r="F447" s="8"/>
-      <c r="G447" s="8"/>
-      <c r="H447" s="8"/>
+      <c r="A447" s="9"/>
+      <c r="B447" s="9"/>
+      <c r="C447" s="9"/>
+      <c r="D447" s="9"/>
+      <c r="E447" s="9"/>
+      <c r="F447" s="9"/>
+      <c r="G447" s="9"/>
+      <c r="H447" s="9"/>
     </row>
     <row r="448" spans="1:8">
-      <c r="A448" s="8"/>
-      <c r="B448" s="8"/>
-      <c r="C448" s="8"/>
-      <c r="D448" s="8"/>
-      <c r="E448" s="8"/>
-      <c r="F448" s="8"/>
-      <c r="G448" s="8"/>
-      <c r="H448" s="8"/>
+      <c r="A448" s="9"/>
+      <c r="B448" s="9"/>
+      <c r="C448" s="9"/>
+      <c r="D448" s="9"/>
+      <c r="E448" s="9"/>
+      <c r="F448" s="9"/>
+      <c r="G448" s="9"/>
+      <c r="H448" s="9"/>
     </row>
     <row r="449" spans="1:8">
-      <c r="A449" s="8"/>
-      <c r="B449" s="8"/>
-      <c r="C449" s="8"/>
-      <c r="D449" s="8"/>
-      <c r="E449" s="8"/>
-      <c r="F449" s="8"/>
-      <c r="G449" s="8"/>
-      <c r="H449" s="8"/>
+      <c r="A449" s="9"/>
+      <c r="B449" s="9"/>
+      <c r="C449" s="9"/>
+      <c r="D449" s="9"/>
+      <c r="E449" s="9"/>
+      <c r="F449" s="9"/>
+      <c r="G449" s="9"/>
+      <c r="H449" s="9"/>
     </row>
     <row r="450" spans="1:8">
-      <c r="A450" s="8"/>
-      <c r="B450" s="8"/>
-      <c r="C450" s="8"/>
-      <c r="D450" s="8"/>
-      <c r="E450" s="8"/>
-      <c r="F450" s="8"/>
-      <c r="G450" s="8"/>
-      <c r="H450" s="8"/>
+      <c r="A450" s="9"/>
+      <c r="B450" s="9"/>
+      <c r="C450" s="9"/>
+      <c r="D450" s="9"/>
+      <c r="E450" s="9"/>
+      <c r="F450" s="9"/>
+      <c r="G450" s="9"/>
+      <c r="H450" s="9"/>
     </row>
     <row r="451" spans="1:8">
-      <c r="A451" s="8"/>
-      <c r="B451" s="8"/>
-      <c r="C451" s="8"/>
-      <c r="D451" s="8"/>
-      <c r="E451" s="8"/>
-      <c r="F451" s="8"/>
-      <c r="G451" s="8"/>
-      <c r="H451" s="8"/>
+      <c r="A451" s="9"/>
+      <c r="B451" s="9"/>
+      <c r="C451" s="9"/>
+      <c r="D451" s="9"/>
+      <c r="E451" s="9"/>
+      <c r="F451" s="9"/>
+      <c r="G451" s="9"/>
+      <c r="H451" s="9"/>
     </row>
     <row r="452" spans="1:8">
-      <c r="A452" s="8"/>
-      <c r="B452" s="8"/>
-      <c r="C452" s="8"/>
-      <c r="D452" s="8"/>
-      <c r="E452" s="8"/>
-      <c r="F452" s="8"/>
-      <c r="G452" s="8"/>
-      <c r="H452" s="8"/>
+      <c r="A452" s="9"/>
+      <c r="B452" s="9"/>
+      <c r="C452" s="9"/>
+      <c r="D452" s="9"/>
+      <c r="E452" s="9"/>
+      <c r="F452" s="9"/>
+      <c r="G452" s="9"/>
+      <c r="H452" s="9"/>
     </row>
     <row r="453" spans="1:8">
-      <c r="A453" s="8"/>
-      <c r="B453" s="8"/>
-      <c r="C453" s="8"/>
-      <c r="D453" s="8"/>
-      <c r="E453" s="8"/>
-      <c r="F453" s="8"/>
-      <c r="G453" s="8"/>
-      <c r="H453" s="8"/>
+      <c r="A453" s="9"/>
+      <c r="B453" s="9"/>
+      <c r="C453" s="9"/>
+      <c r="D453" s="9"/>
+      <c r="E453" s="9"/>
+      <c r="F453" s="9"/>
+      <c r="G453" s="9"/>
+      <c r="H453" s="9"/>
     </row>
     <row r="454" spans="1:8">
-      <c r="A454" s="8"/>
-      <c r="B454" s="8"/>
-      <c r="C454" s="8"/>
-      <c r="D454" s="8"/>
-      <c r="E454" s="8"/>
-      <c r="F454" s="8"/>
-      <c r="G454" s="8"/>
-      <c r="H454" s="8"/>
+      <c r="A454" s="9"/>
+      <c r="B454" s="9"/>
+      <c r="C454" s="9"/>
+      <c r="D454" s="9"/>
+      <c r="E454" s="9"/>
+      <c r="F454" s="9"/>
+      <c r="G454" s="9"/>
+      <c r="H454" s="9"/>
     </row>
     <row r="455" spans="1:8">
-      <c r="A455" s="8"/>
-      <c r="B455" s="8"/>
-      <c r="C455" s="8"/>
-      <c r="D455" s="8"/>
-      <c r="E455" s="8"/>
-      <c r="F455" s="8"/>
-      <c r="G455" s="8"/>
-      <c r="H455" s="8"/>
+      <c r="A455" s="9"/>
+      <c r="B455" s="9"/>
+      <c r="C455" s="9"/>
+      <c r="D455" s="9"/>
+      <c r="E455" s="9"/>
+      <c r="F455" s="9"/>
+      <c r="G455" s="9"/>
+      <c r="H455" s="9"/>
     </row>
     <row r="456" spans="1:8">
-      <c r="A456" s="8"/>
-      <c r="B456" s="8"/>
-      <c r="C456" s="8"/>
-      <c r="D456" s="8"/>
-      <c r="E456" s="8"/>
-      <c r="F456" s="8"/>
-      <c r="G456" s="8"/>
-      <c r="H456" s="8"/>
+      <c r="A456" s="9"/>
+      <c r="B456" s="9"/>
+      <c r="C456" s="9"/>
+      <c r="D456" s="9"/>
+      <c r="E456" s="9"/>
+      <c r="F456" s="9"/>
+      <c r="G456" s="9"/>
+      <c r="H456" s="9"/>
     </row>
     <row r="457" spans="1:8">
-      <c r="A457" s="8"/>
-      <c r="B457" s="8"/>
-      <c r="C457" s="8"/>
-      <c r="D457" s="8"/>
-      <c r="E457" s="8"/>
-      <c r="F457" s="8"/>
-      <c r="G457" s="8"/>
-      <c r="H457" s="8"/>
+      <c r="A457" s="9"/>
+      <c r="B457" s="9"/>
+      <c r="C457" s="9"/>
+      <c r="D457" s="9"/>
+      <c r="E457" s="9"/>
+      <c r="F457" s="9"/>
+      <c r="G457" s="9"/>
+      <c r="H457" s="9"/>
     </row>
     <row r="458" spans="1:8">
-      <c r="A458" s="8"/>
-      <c r="B458" s="8"/>
-      <c r="C458" s="8"/>
-      <c r="D458" s="8"/>
-      <c r="E458" s="8"/>
-      <c r="F458" s="8"/>
-      <c r="G458" s="8"/>
-      <c r="H458" s="8"/>
+      <c r="A458" s="9"/>
+      <c r="B458" s="9"/>
+      <c r="C458" s="9"/>
+      <c r="D458" s="9"/>
+      <c r="E458" s="9"/>
+      <c r="F458" s="9"/>
+      <c r="G458" s="9"/>
+      <c r="H458" s="9"/>
     </row>
     <row r="459" spans="1:8">
-      <c r="A459" s="8"/>
-      <c r="B459" s="8"/>
-      <c r="C459" s="8"/>
-      <c r="D459" s="8"/>
-      <c r="E459" s="8"/>
-      <c r="F459" s="8"/>
-      <c r="G459" s="8"/>
-      <c r="H459" s="8"/>
+      <c r="A459" s="9"/>
+      <c r="B459" s="9"/>
+      <c r="C459" s="9"/>
+      <c r="D459" s="9"/>
+      <c r="E459" s="9"/>
+      <c r="F459" s="9"/>
+      <c r="G459" s="9"/>
+      <c r="H459" s="9"/>
     </row>
     <row r="460" spans="1:8">
-      <c r="A460" s="8"/>
-      <c r="B460" s="8"/>
-      <c r="C460" s="8"/>
-      <c r="D460" s="8"/>
-      <c r="E460" s="8"/>
-      <c r="F460" s="8"/>
-      <c r="G460" s="8"/>
-      <c r="H460" s="8"/>
+      <c r="A460" s="9"/>
+      <c r="B460" s="9"/>
+      <c r="C460" s="9"/>
+      <c r="D460" s="9"/>
+      <c r="E460" s="9"/>
+      <c r="F460" s="9"/>
+      <c r="G460" s="9"/>
+      <c r="H460" s="9"/>
     </row>
     <row r="461" spans="1:8">
-      <c r="A461" s="8"/>
-      <c r="B461" s="8"/>
-      <c r="C461" s="8"/>
-      <c r="D461" s="8"/>
-      <c r="E461" s="8"/>
-      <c r="F461" s="8"/>
-      <c r="G461" s="8"/>
-      <c r="H461" s="8"/>
+      <c r="A461" s="9"/>
+      <c r="B461" s="9"/>
+      <c r="C461" s="9"/>
+      <c r="D461" s="9"/>
+      <c r="E461" s="9"/>
+      <c r="F461" s="9"/>
+      <c r="G461" s="9"/>
+      <c r="H461" s="9"/>
     </row>
     <row r="462" spans="1:8">
-      <c r="A462" s="8"/>
-      <c r="B462" s="8"/>
-      <c r="C462" s="8"/>
-      <c r="D462" s="8"/>
-      <c r="E462" s="8"/>
-      <c r="F462" s="8"/>
-      <c r="G462" s="8"/>
-      <c r="H462" s="8"/>
+      <c r="A462" s="9"/>
+      <c r="B462" s="9"/>
+      <c r="C462" s="9"/>
+      <c r="D462" s="9"/>
+      <c r="E462" s="9"/>
+      <c r="F462" s="9"/>
+      <c r="G462" s="9"/>
+      <c r="H462" s="9"/>
     </row>
     <row r="463" spans="1:8">
-      <c r="A463" s="8"/>
-      <c r="B463" s="8"/>
-      <c r="C463" s="8"/>
-      <c r="D463" s="8"/>
-      <c r="E463" s="8"/>
-      <c r="F463" s="8"/>
-      <c r="G463" s="8"/>
-      <c r="H463" s="8"/>
+      <c r="A463" s="9"/>
+      <c r="B463" s="9"/>
+      <c r="C463" s="9"/>
+      <c r="D463" s="9"/>
+      <c r="E463" s="9"/>
+      <c r="F463" s="9"/>
+      <c r="G463" s="9"/>
+      <c r="H463" s="9"/>
     </row>
     <row r="464" spans="1:8">
-      <c r="A464" s="8"/>
-      <c r="B464" s="8"/>
-      <c r="C464" s="8"/>
-      <c r="D464" s="8"/>
-      <c r="E464" s="8"/>
-      <c r="F464" s="8"/>
-      <c r="G464" s="8"/>
-      <c r="H464" s="8"/>
+      <c r="A464" s="9"/>
+      <c r="B464" s="9"/>
+      <c r="C464" s="9"/>
+      <c r="D464" s="9"/>
+      <c r="E464" s="9"/>
+      <c r="F464" s="9"/>
+      <c r="G464" s="9"/>
+      <c r="H464" s="9"/>
     </row>
     <row r="465" spans="1:8">
-      <c r="A465" s="8"/>
-      <c r="B465" s="8"/>
-      <c r="C465" s="8"/>
-      <c r="D465" s="8"/>
-      <c r="E465" s="8"/>
-      <c r="F465" s="8"/>
-      <c r="G465" s="8"/>
-      <c r="H465" s="8"/>
+      <c r="A465" s="9"/>
+      <c r="B465" s="9"/>
+      <c r="C465" s="9"/>
+      <c r="D465" s="9"/>
+      <c r="E465" s="9"/>
+      <c r="F465" s="9"/>
+      <c r="G465" s="9"/>
+      <c r="H465" s="9"/>
     </row>
     <row r="466" spans="1:8">
-      <c r="A466" s="8"/>
-      <c r="B466" s="8"/>
-      <c r="C466" s="8"/>
-      <c r="D466" s="8"/>
-      <c r="E466" s="8"/>
-      <c r="F466" s="8"/>
-      <c r="G466" s="8"/>
-      <c r="H466" s="8"/>
+      <c r="A466" s="9"/>
+      <c r="B466" s="9"/>
+      <c r="C466" s="9"/>
+      <c r="D466" s="9"/>
+      <c r="E466" s="9"/>
+      <c r="F466" s="9"/>
+      <c r="G466" s="9"/>
+      <c r="H466" s="9"/>
     </row>
     <row r="467" spans="1:8">
-      <c r="A467" s="8"/>
-      <c r="B467" s="8"/>
-      <c r="C467" s="8"/>
-      <c r="D467" s="8"/>
-      <c r="E467" s="8"/>
-      <c r="F467" s="8"/>
-      <c r="G467" s="8"/>
-      <c r="H467" s="8"/>
+      <c r="A467" s="9"/>
+      <c r="B467" s="9"/>
+      <c r="C467" s="9"/>
+      <c r="D467" s="9"/>
+      <c r="E467" s="9"/>
+      <c r="F467" s="9"/>
+      <c r="G467" s="9"/>
+      <c r="H467" s="9"/>
     </row>
     <row r="468" spans="1:8">
-      <c r="A468" s="8"/>
-      <c r="B468" s="8"/>
-      <c r="C468" s="8"/>
-      <c r="D468" s="8"/>
-      <c r="E468" s="8"/>
-      <c r="F468" s="8"/>
-      <c r="G468" s="8"/>
-      <c r="H468" s="8"/>
+      <c r="A468" s="9"/>
+      <c r="B468" s="9"/>
+      <c r="C468" s="9"/>
+      <c r="D468" s="9"/>
+      <c r="E468" s="9"/>
+      <c r="F468" s="9"/>
+      <c r="G468" s="9"/>
+      <c r="H468" s="9"/>
     </row>
     <row r="469" spans="1:8">
-      <c r="A469" s="8"/>
-      <c r="B469" s="8"/>
-      <c r="C469" s="8"/>
-      <c r="D469" s="8"/>
-      <c r="E469" s="8"/>
-      <c r="F469" s="8"/>
-      <c r="G469" s="8"/>
-      <c r="H469" s="8"/>
+      <c r="A469" s="9"/>
+      <c r="B469" s="9"/>
+      <c r="C469" s="9"/>
+      <c r="D469" s="9"/>
+      <c r="E469" s="9"/>
+      <c r="F469" s="9"/>
+      <c r="G469" s="9"/>
+      <c r="H469" s="9"/>
     </row>
     <row r="470" spans="1:8">
-      <c r="A470" s="8"/>
-      <c r="B470" s="8"/>
-      <c r="C470" s="8"/>
-      <c r="D470" s="8"/>
-      <c r="E470" s="8"/>
-      <c r="F470" s="8"/>
-      <c r="G470" s="8"/>
-      <c r="H470" s="8"/>
+      <c r="A470" s="9"/>
+      <c r="B470" s="9"/>
+      <c r="C470" s="9"/>
+      <c r="D470" s="9"/>
+      <c r="E470" s="9"/>
+      <c r="F470" s="9"/>
+      <c r="G470" s="9"/>
+      <c r="H470" s="9"/>
     </row>
     <row r="471" spans="1:8">
-      <c r="A471" s="8"/>
-      <c r="B471" s="8"/>
-      <c r="C471" s="8"/>
-      <c r="D471" s="8"/>
-      <c r="E471" s="8"/>
-      <c r="F471" s="8"/>
-      <c r="G471" s="8"/>
-      <c r="H471" s="8"/>
+      <c r="A471" s="9"/>
+      <c r="B471" s="9"/>
+      <c r="C471" s="9"/>
+      <c r="D471" s="9"/>
+      <c r="E471" s="9"/>
+      <c r="F471" s="9"/>
+      <c r="G471" s="9"/>
+      <c r="H471" s="9"/>
     </row>
     <row r="472" spans="1:8">
-      <c r="A472" s="8"/>
-      <c r="B472" s="8"/>
-      <c r="C472" s="8"/>
-      <c r="D472" s="8"/>
-      <c r="E472" s="8"/>
-      <c r="F472" s="8"/>
-      <c r="G472" s="8"/>
-      <c r="H472" s="8"/>
+      <c r="A472" s="9"/>
+      <c r="B472" s="9"/>
+      <c r="C472" s="9"/>
+      <c r="D472" s="9"/>
+      <c r="E472" s="9"/>
+      <c r="F472" s="9"/>
+      <c r="G472" s="9"/>
+      <c r="H472" s="9"/>
     </row>
     <row r="473" spans="1:8">
-      <c r="A473" s="8"/>
-      <c r="B473" s="8"/>
-      <c r="C473" s="8"/>
-      <c r="D473" s="8"/>
-      <c r="E473" s="8"/>
-      <c r="F473" s="8"/>
-      <c r="G473" s="8"/>
-      <c r="H473" s="8"/>
+      <c r="A473" s="9"/>
+      <c r="B473" s="9"/>
+      <c r="C473" s="9"/>
+      <c r="D473" s="9"/>
+      <c r="E473" s="9"/>
+      <c r="F473" s="9"/>
+      <c r="G473" s="9"/>
+      <c r="H473" s="9"/>
     </row>
     <row r="474" spans="1:8">
-      <c r="A474" s="8"/>
-      <c r="B474" s="8"/>
-      <c r="C474" s="8"/>
-      <c r="D474" s="8"/>
-      <c r="E474" s="8"/>
-      <c r="F474" s="8"/>
-      <c r="G474" s="8"/>
-      <c r="H474" s="8"/>
+      <c r="A474" s="9"/>
+      <c r="B474" s="9"/>
+      <c r="C474" s="9"/>
+      <c r="D474" s="9"/>
+      <c r="E474" s="9"/>
+      <c r="F474" s="9"/>
+      <c r="G474" s="9"/>
+      <c r="H474" s="9"/>
     </row>
     <row r="475" spans="1:8">
-      <c r="A475" s="8"/>
-      <c r="B475" s="8"/>
-      <c r="C475" s="8"/>
-      <c r="D475" s="8"/>
-      <c r="E475" s="8"/>
-      <c r="F475" s="8"/>
-      <c r="G475" s="8"/>
-      <c r="H475" s="8"/>
+      <c r="A475" s="9"/>
+      <c r="B475" s="9"/>
+      <c r="C475" s="9"/>
+      <c r="D475" s="9"/>
+      <c r="E475" s="9"/>
+      <c r="F475" s="9"/>
+      <c r="G475" s="9"/>
+      <c r="H475" s="9"/>
     </row>
     <row r="476" spans="1:8">
-      <c r="A476" s="8"/>
-      <c r="B476" s="8"/>
-      <c r="C476" s="8"/>
-      <c r="D476" s="8"/>
-      <c r="E476" s="8"/>
-      <c r="F476" s="8"/>
-      <c r="G476" s="8"/>
-      <c r="H476" s="8"/>
+      <c r="A476" s="9"/>
+      <c r="B476" s="9"/>
+      <c r="C476" s="9"/>
+      <c r="D476" s="9"/>
+      <c r="E476" s="9"/>
+      <c r="F476" s="9"/>
+      <c r="G476" s="9"/>
+      <c r="H476" s="9"/>
     </row>
     <row r="477" spans="1:8">
-      <c r="A477" s="8"/>
-      <c r="B477" s="8"/>
-      <c r="C477" s="8"/>
-      <c r="D477" s="8"/>
-      <c r="E477" s="8"/>
-      <c r="F477" s="8"/>
-      <c r="G477" s="8"/>
-      <c r="H477" s="8"/>
+      <c r="A477" s="9"/>
+      <c r="B477" s="9"/>
+      <c r="C477" s="9"/>
+      <c r="D477" s="9"/>
+      <c r="E477" s="9"/>
+      <c r="F477" s="9"/>
+      <c r="G477" s="9"/>
+      <c r="H477" s="9"/>
     </row>
     <row r="478" spans="1:8">
-      <c r="A478" s="8"/>
-      <c r="B478" s="8"/>
-      <c r="C478" s="8"/>
-      <c r="D478" s="8"/>
-      <c r="E478" s="8"/>
-      <c r="F478" s="8"/>
-      <c r="G478" s="8"/>
-      <c r="H478" s="8"/>
+      <c r="A478" s="9"/>
+      <c r="B478" s="9"/>
+      <c r="C478" s="9"/>
+      <c r="D478" s="9"/>
+      <c r="E478" s="9"/>
+      <c r="F478" s="9"/>
+      <c r="G478" s="9"/>
+      <c r="H478" s="9"/>
     </row>
     <row r="479" spans="1:8">
-      <c r="A479" s="8"/>
-      <c r="B479" s="8"/>
-      <c r="C479" s="8"/>
-      <c r="D479" s="8"/>
-      <c r="E479" s="8"/>
-      <c r="F479" s="8"/>
-      <c r="G479" s="8"/>
-      <c r="H479" s="8"/>
+      <c r="A479" s="9"/>
+      <c r="B479" s="9"/>
+      <c r="C479" s="9"/>
+      <c r="D479" s="9"/>
+      <c r="E479" s="9"/>
+      <c r="F479" s="9"/>
+      <c r="G479" s="9"/>
+      <c r="H479" s="9"/>
     </row>
     <row r="480" spans="1:8">
-      <c r="A480" s="8"/>
-      <c r="B480" s="8"/>
-      <c r="C480" s="8"/>
-      <c r="D480" s="8"/>
-      <c r="E480" s="8"/>
-      <c r="F480" s="8"/>
-      <c r="G480" s="8"/>
-      <c r="H480" s="8"/>
+      <c r="A480" s="9"/>
+      <c r="B480" s="9"/>
+      <c r="C480" s="9"/>
+      <c r="D480" s="9"/>
+      <c r="E480" s="9"/>
+      <c r="F480" s="9"/>
+      <c r="G480" s="9"/>
+      <c r="H480" s="9"/>
     </row>
     <row r="481" spans="1:8">
-      <c r="A481" s="8"/>
-      <c r="B481" s="8"/>
-      <c r="C481" s="8"/>
-      <c r="D481" s="8"/>
-      <c r="E481" s="8"/>
-      <c r="F481" s="8"/>
-      <c r="G481" s="8"/>
-      <c r="H481" s="8"/>
+      <c r="A481" s="9"/>
+      <c r="B481" s="9"/>
+      <c r="C481" s="9"/>
+      <c r="D481" s="9"/>
+      <c r="E481" s="9"/>
+      <c r="F481" s="9"/>
+      <c r="G481" s="9"/>
+      <c r="H481" s="9"/>
     </row>
     <row r="482" spans="1:8">
-      <c r="A482" s="8"/>
-      <c r="B482" s="8"/>
-      <c r="C482" s="8"/>
-      <c r="D482" s="8"/>
-      <c r="E482" s="8"/>
-      <c r="F482" s="8"/>
-      <c r="G482" s="8"/>
-      <c r="H482" s="8"/>
+      <c r="A482" s="9"/>
+      <c r="B482" s="9"/>
+      <c r="C482" s="9"/>
+      <c r="D482" s="9"/>
+      <c r="E482" s="9"/>
+      <c r="F482" s="9"/>
+      <c r="G482" s="9"/>
+      <c r="H482" s="9"/>
     </row>
     <row r="483" spans="1:8">
-      <c r="A483" s="8"/>
-      <c r="B483" s="8"/>
-      <c r="C483" s="8"/>
-      <c r="D483" s="8"/>
-      <c r="E483" s="8"/>
-      <c r="F483" s="8"/>
-      <c r="G483" s="8"/>
-      <c r="H483" s="8"/>
+      <c r="A483" s="9"/>
+      <c r="B483" s="9"/>
+      <c r="C483" s="9"/>
+      <c r="D483" s="9"/>
+      <c r="E483" s="9"/>
+      <c r="F483" s="9"/>
+      <c r="G483" s="9"/>
+      <c r="H483" s="9"/>
     </row>
     <row r="484" spans="1:8">
-      <c r="A484" s="8"/>
-      <c r="B484" s="8"/>
-      <c r="C484" s="8"/>
-      <c r="D484" s="8"/>
-      <c r="E484" s="8"/>
-      <c r="F484" s="8"/>
-      <c r="G484" s="8"/>
-      <c r="H484" s="8"/>
+      <c r="A484" s="9"/>
+      <c r="B484" s="9"/>
+      <c r="C484" s="9"/>
+      <c r="D484" s="9"/>
+      <c r="E484" s="9"/>
+      <c r="F484" s="9"/>
+      <c r="G484" s="9"/>
+      <c r="H484" s="9"/>
     </row>
     <row r="485" spans="1:8">
-      <c r="A485" s="8"/>
-      <c r="B485" s="8"/>
-      <c r="C485" s="8"/>
-      <c r="D485" s="8"/>
-      <c r="E485" s="8"/>
-      <c r="F485" s="8"/>
-      <c r="G485" s="8"/>
-      <c r="H485" s="8"/>
+      <c r="A485" s="9"/>
+      <c r="B485" s="9"/>
+      <c r="C485" s="9"/>
+      <c r="D485" s="9"/>
+      <c r="E485" s="9"/>
+      <c r="F485" s="9"/>
+      <c r="G485" s="9"/>
+      <c r="H485" s="9"/>
     </row>
     <row r="486" spans="1:8">
-      <c r="A486" s="8"/>
-      <c r="B486" s="8"/>
-      <c r="C486" s="8"/>
-      <c r="D486" s="8"/>
-      <c r="E486" s="8"/>
-      <c r="F486" s="8"/>
-      <c r="G486" s="8"/>
-      <c r="H486" s="8"/>
+      <c r="A486" s="9"/>
+      <c r="B486" s="9"/>
+      <c r="C486" s="9"/>
+      <c r="D486" s="9"/>
+      <c r="E486" s="9"/>
+      <c r="F486" s="9"/>
+      <c r="G486" s="9"/>
+      <c r="H486" s="9"/>
     </row>
     <row r="487" spans="1:8">
-      <c r="A487" s="8"/>
-      <c r="B487" s="8"/>
-      <c r="C487" s="8"/>
-      <c r="D487" s="8"/>
-      <c r="E487" s="8"/>
-      <c r="F487" s="8"/>
-      <c r="G487" s="8"/>
-      <c r="H487" s="8"/>
+      <c r="A487" s="9"/>
+      <c r="B487" s="9"/>
+      <c r="C487" s="9"/>
+      <c r="D487" s="9"/>
+      <c r="E487" s="9"/>
+      <c r="F487" s="9"/>
+      <c r="G487" s="9"/>
+      <c r="H487" s="9"/>
     </row>
     <row r="488" spans="1:8">
-      <c r="A488" s="8"/>
-      <c r="B488" s="8"/>
-      <c r="C488" s="8"/>
-      <c r="D488" s="8"/>
-      <c r="E488" s="8"/>
-      <c r="F488" s="8"/>
-      <c r="G488" s="8"/>
-      <c r="H488" s="8"/>
+      <c r="A488" s="9"/>
+      <c r="B488" s="9"/>
+      <c r="C488" s="9"/>
+      <c r="D488" s="9"/>
+      <c r="E488" s="9"/>
+      <c r="F488" s="9"/>
+      <c r="G488" s="9"/>
+      <c r="H488" s="9"/>
     </row>
     <row r="489" spans="1:8">
-      <c r="A489" s="8"/>
-      <c r="B489" s="8"/>
-      <c r="C489" s="8"/>
-      <c r="D489" s="8"/>
-      <c r="E489" s="8"/>
-      <c r="F489" s="8"/>
-      <c r="G489" s="8"/>
-      <c r="H489" s="8"/>
+      <c r="A489" s="9"/>
+      <c r="B489" s="9"/>
+      <c r="C489" s="9"/>
+      <c r="D489" s="9"/>
+      <c r="E489" s="9"/>
+      <c r="F489" s="9"/>
+      <c r="G489" s="9"/>
+      <c r="H489" s="9"/>
     </row>
     <row r="490" spans="1:8">
-      <c r="A490" s="8"/>
-      <c r="B490" s="8"/>
-      <c r="C490" s="8"/>
-      <c r="D490" s="8"/>
-      <c r="E490" s="8"/>
-      <c r="F490" s="8"/>
-      <c r="G490" s="8"/>
-      <c r="H490" s="8"/>
+      <c r="A490" s="9"/>
+      <c r="B490" s="9"/>
+      <c r="C490" s="9"/>
+      <c r="D490" s="9"/>
+      <c r="E490" s="9"/>
+      <c r="F490" s="9"/>
+      <c r="G490" s="9"/>
+      <c r="H490" s="9"/>
     </row>
     <row r="491" spans="1:8">
-      <c r="A491" s="8"/>
-      <c r="B491" s="8"/>
-      <c r="C491" s="8"/>
-      <c r="D491" s="8"/>
-      <c r="E491" s="8"/>
-      <c r="F491" s="8"/>
-      <c r="G491" s="8"/>
-      <c r="H491" s="8"/>
+      <c r="A491" s="9"/>
+      <c r="B491" s="9"/>
+      <c r="C491" s="9"/>
+      <c r="D491" s="9"/>
+      <c r="E491" s="9"/>
+      <c r="F491" s="9"/>
+      <c r="G491" s="9"/>
+      <c r="H491" s="9"/>
     </row>
     <row r="492" spans="1:8">
-      <c r="A492" s="8"/>
-      <c r="B492" s="8"/>
-      <c r="C492" s="8"/>
-      <c r="D492" s="8"/>
-      <c r="E492" s="8"/>
-      <c r="F492" s="8"/>
-      <c r="G492" s="8"/>
-      <c r="H492" s="8"/>
+      <c r="A492" s="9"/>
+      <c r="B492" s="9"/>
+      <c r="C492" s="9"/>
+      <c r="D492" s="9"/>
+      <c r="E492" s="9"/>
+      <c r="F492" s="9"/>
+      <c r="G492" s="9"/>
+      <c r="H492" s="9"/>
     </row>
     <row r="493" spans="1:8">
-      <c r="A493" s="8"/>
-      <c r="B493" s="8"/>
-      <c r="C493" s="8"/>
-      <c r="D493" s="8"/>
-      <c r="E493" s="8"/>
-      <c r="F493" s="8"/>
-      <c r="G493" s="8"/>
-      <c r="H493" s="8"/>
+      <c r="A493" s="9"/>
+      <c r="B493" s="9"/>
+      <c r="C493" s="9"/>
+      <c r="D493" s="9"/>
+      <c r="E493" s="9"/>
+      <c r="F493" s="9"/>
+      <c r="G493" s="9"/>
+      <c r="H493" s="9"/>
     </row>
     <row r="494" spans="1:8">
-      <c r="A494" s="8"/>
-      <c r="B494" s="8"/>
-      <c r="C494" s="8"/>
-      <c r="D494" s="8"/>
-      <c r="E494" s="8"/>
-      <c r="F494" s="8"/>
-      <c r="G494" s="8"/>
-      <c r="H494" s="8"/>
+      <c r="A494" s="9"/>
+      <c r="B494" s="9"/>
+      <c r="C494" s="9"/>
+      <c r="D494" s="9"/>
+      <c r="E494" s="9"/>
+      <c r="F494" s="9"/>
+      <c r="G494" s="9"/>
+      <c r="H494" s="9"/>
     </row>
     <row r="495" spans="1:8">
-      <c r="A495" s="8"/>
-      <c r="B495" s="8"/>
-      <c r="C495" s="8"/>
-      <c r="D495" s="8"/>
-      <c r="E495" s="8"/>
-      <c r="F495" s="8"/>
-      <c r="G495" s="8"/>
-      <c r="H495" s="8"/>
+      <c r="A495" s="9"/>
+      <c r="B495" s="9"/>
+      <c r="C495" s="9"/>
+      <c r="D495" s="9"/>
+      <c r="E495" s="9"/>
+      <c r="F495" s="9"/>
+      <c r="G495" s="9"/>
+      <c r="H495" s="9"/>
     </row>
     <row r="496" spans="1:8">
-      <c r="A496" s="8"/>
-      <c r="B496" s="8"/>
-      <c r="C496" s="8"/>
-      <c r="D496" s="8"/>
-      <c r="E496" s="8"/>
-      <c r="F496" s="8"/>
-      <c r="G496" s="8"/>
-      <c r="H496" s="8"/>
+      <c r="A496" s="9"/>
+      <c r="B496" s="9"/>
+      <c r="C496" s="9"/>
+      <c r="D496" s="9"/>
+      <c r="E496" s="9"/>
+      <c r="F496" s="9"/>
+      <c r="G496" s="9"/>
+      <c r="H496" s="9"/>
     </row>
     <row r="497" spans="1:8">
-      <c r="A497" s="8"/>
-      <c r="B497" s="8"/>
-      <c r="C497" s="8"/>
-      <c r="D497" s="8"/>
-      <c r="E497" s="8"/>
-      <c r="F497" s="8"/>
-      <c r="G497" s="8"/>
-      <c r="H497" s="8"/>
+      <c r="A497" s="9"/>
+      <c r="B497" s="9"/>
+      <c r="C497" s="9"/>
+      <c r="D497" s="9"/>
+      <c r="E497" s="9"/>
+      <c r="F497" s="9"/>
+      <c r="G497" s="9"/>
+      <c r="H497" s="9"/>
     </row>
     <row r="498" spans="1:8">
-      <c r="A498" s="8"/>
-      <c r="B498" s="8"/>
-      <c r="C498" s="8"/>
-      <c r="D498" s="8"/>
-      <c r="E498" s="8"/>
-      <c r="F498" s="8"/>
-      <c r="G498" s="8"/>
-      <c r="H498" s="8"/>
+      <c r="A498" s="9"/>
+      <c r="B498" s="9"/>
+      <c r="C498" s="9"/>
+      <c r="D498" s="9"/>
+      <c r="E498" s="9"/>
+      <c r="F498" s="9"/>
+      <c r="G498" s="9"/>
+      <c r="H498" s="9"/>
     </row>
     <row r="499" spans="1:8">
-      <c r="A499" s="8"/>
-      <c r="B499" s="8"/>
-      <c r="C499" s="8"/>
-      <c r="D499" s="8"/>
-      <c r="E499" s="8"/>
-      <c r="F499" s="8"/>
-      <c r="G499" s="8"/>
-      <c r="H499" s="8"/>
+      <c r="A499" s="9"/>
+      <c r="B499" s="9"/>
+      <c r="C499" s="9"/>
+      <c r="D499" s="9"/>
+      <c r="E499" s="9"/>
+      <c r="F499" s="9"/>
+      <c r="G499" s="9"/>
+      <c r="H499" s="9"/>
     </row>
     <row r="500" spans="1:8">
-      <c r="A500" s="8"/>
-      <c r="B500" s="8"/>
-      <c r="C500" s="8"/>
-      <c r="D500" s="8"/>
-      <c r="E500" s="8"/>
-      <c r="F500" s="8"/>
-      <c r="G500" s="8"/>
-      <c r="H500" s="8"/>
+      <c r="A500" s="9"/>
+      <c r="B500" s="9"/>
+      <c r="C500" s="9"/>
+      <c r="D500" s="9"/>
+      <c r="E500" s="9"/>
+      <c r="F500" s="9"/>
+      <c r="G500" s="9"/>
+      <c r="H500" s="9"/>
     </row>
     <row r="501" spans="1:8">
-      <c r="A501" s="8"/>
-      <c r="B501" s="8"/>
-      <c r="C501" s="8"/>
-      <c r="D501" s="8"/>
-      <c r="E501" s="8"/>
-      <c r="F501" s="8"/>
-      <c r="G501" s="8"/>
-      <c r="H501" s="8"/>
+      <c r="A501" s="9"/>
+      <c r="B501" s="9"/>
+      <c r="C501" s="9"/>
+      <c r="D501" s="9"/>
+      <c r="E501" s="9"/>
+      <c r="F501" s="9"/>
+      <c r="G501" s="9"/>
+      <c r="H501" s="9"/>
     </row>
     <row r="502" spans="1:8">
-      <c r="A502" s="8"/>
-      <c r="B502" s="8"/>
-      <c r="C502" s="8"/>
-      <c r="D502" s="8"/>
-      <c r="E502" s="8"/>
-      <c r="F502" s="8"/>
-      <c r="G502" s="8"/>
-      <c r="H502" s="8"/>
+      <c r="A502" s="9"/>
+      <c r="B502" s="9"/>
+      <c r="C502" s="9"/>
+      <c r="D502" s="9"/>
+      <c r="E502" s="9"/>
+      <c r="F502" s="9"/>
+      <c r="G502" s="9"/>
+      <c r="H502" s="9"/>
     </row>
     <row r="503" spans="1:8">
-      <c r="A503" s="8"/>
-      <c r="B503" s="8"/>
-      <c r="C503" s="8"/>
-      <c r="D503" s="8"/>
-      <c r="E503" s="8"/>
-      <c r="F503" s="8"/>
-      <c r="G503" s="8"/>
-      <c r="H503" s="8"/>
+      <c r="A503" s="9"/>
+      <c r="B503" s="9"/>
+      <c r="C503" s="9"/>
+      <c r="D503" s="9"/>
+      <c r="E503" s="9"/>
+      <c r="F503" s="9"/>
+      <c r="G503" s="9"/>
+      <c r="H503" s="9"/>
     </row>
     <row r="504" spans="1:8">
-      <c r="A504" s="8"/>
-      <c r="B504" s="8"/>
-      <c r="C504" s="8"/>
-      <c r="D504" s="8"/>
-      <c r="E504" s="8"/>
-      <c r="F504" s="8"/>
-      <c r="G504" s="8"/>
-      <c r="H504" s="8"/>
+      <c r="A504" s="9"/>
+      <c r="B504" s="9"/>
+      <c r="C504" s="9"/>
+      <c r="D504" s="9"/>
+      <c r="E504" s="9"/>
+      <c r="F504" s="9"/>
+      <c r="G504" s="9"/>
+      <c r="H504" s="9"/>
     </row>
     <row r="505" spans="1:8">
-      <c r="A505" s="8"/>
+      <c r="A505" s="9"/>
     </row>
     <row r="506" spans="1:8">
-      <c r="A506" s="8"/>
+      <c r="A506" s="9"/>
     </row>
     <row r="507" spans="1:8">
-      <c r="A507" s="8"/>
+      <c r="A507" s="9"/>
     </row>
     <row r="508" spans="1:8">
-      <c r="A508" s="8"/>
+      <c r="A508" s="9"/>
     </row>
     <row r="509" spans="1:8">
-      <c r="A509" s="8"/>
+      <c r="A509" s="9"/>
     </row>
     <row r="510" spans="1:8">
-      <c r="A510" s="8"/>
+      <c r="A510" s="9"/>
     </row>
     <row r="511" spans="1:8">
-      <c r="A511" s="8"/>
+      <c r="A511" s="9"/>
     </row>
     <row r="512" spans="1:8">
-      <c r="A512" s="8"/>
+      <c r="A512" s="9"/>
     </row>
     <row r="513" spans="1:1">
-      <c r="A513" s="8"/>
+      <c r="A513" s="9"/>
     </row>
     <row r="514" spans="1:1">
-      <c r="A514" s="8"/>
+      <c r="A514" s="9"/>
     </row>
     <row r="515" spans="1:1">
-      <c r="A515" s="8"/>
+      <c r="A515" s="9"/>
     </row>
     <row r="516" spans="1:1">
-      <c r="A516" s="8"/>
+      <c r="A516" s="9"/>
     </row>
     <row r="517" spans="1:1">
-      <c r="A517" s="8"/>
+      <c r="A517" s="9"/>
     </row>
     <row r="518" spans="1:1">
-      <c r="A518" s="8"/>
+      <c r="A518" s="9"/>
     </row>
     <row r="519" spans="1:1">
-      <c r="A519" s="8"/>
+      <c r="A519" s="9"/>
     </row>
     <row r="520" spans="1:1">
-      <c r="A520" s="8"/>
+      <c r="A520" s="9"/>
     </row>
     <row r="521" spans="1:1">
-      <c r="A521" s="8"/>
+      <c r="A521" s="9"/>
     </row>
     <row r="522" spans="1:1">
-      <c r="A522" s="8"/>
+      <c r="A522" s="9"/>
     </row>
     <row r="523" spans="1:1">
-      <c r="A523" s="8"/>
+      <c r="A523" s="9"/>
     </row>
     <row r="524" spans="1:1">
-      <c r="A524" s="8"/>
+      <c r="A524" s="9"/>
     </row>
     <row r="525" spans="1:1">
-      <c r="A525" s="8"/>
+      <c r="A525" s="9"/>
     </row>
     <row r="526" spans="1:1">
-      <c r="A526" s="8"/>
+      <c r="A526" s="9"/>
     </row>
     <row r="527" spans="1:1">
-      <c r="A527" s="8"/>
+      <c r="A527" s="9"/>
     </row>
     <row r="528" spans="1:1">
-      <c r="A528" s="8"/>
+      <c r="A528" s="9"/>
     </row>
     <row r="529" spans="1:1">
-      <c r="A529" s="8"/>
+      <c r="A529" s="9"/>
     </row>
     <row r="530" spans="1:1">
-      <c r="A530" s="8"/>
+      <c r="A530" s="9"/>
     </row>
     <row r="531" spans="1:1">
-      <c r="A531" s="8"/>
+      <c r="A531" s="9"/>
     </row>
     <row r="532" spans="1:1">
-      <c r="A532" s="8"/>
+      <c r="A532" s="9"/>
     </row>
     <row r="533" spans="1:1">
-      <c r="A533" s="8"/>
+      <c r="A533" s="9"/>
     </row>
     <row r="534" spans="1:1">
-      <c r="A534" s="8"/>
+      <c r="A534" s="9"/>
     </row>
     <row r="535" spans="1:1">
-      <c r="A535" s="8"/>
+      <c r="A535" s="9"/>
     </row>
     <row r="536" spans="1:1">
-      <c r="A536" s="8"/>
+      <c r="A536" s="9"/>
     </row>
     <row r="537" spans="1:1">
-      <c r="A537" s="8"/>
+      <c r="A537" s="9"/>
     </row>
     <row r="538" spans="1:1">
-      <c r="A538" s="8"/>
+      <c r="A538" s="9"/>
     </row>
     <row r="539" spans="1:1">
-      <c r="A539" s="8"/>
+      <c r="A539" s="9"/>
     </row>
     <row r="540" spans="1:1">
-      <c r="A540" s="8"/>
+      <c r="A540" s="9"/>
     </row>
     <row r="541" spans="1:1">
-      <c r="A541" s="8"/>
+      <c r="A541" s="9"/>
     </row>
     <row r="542" spans="1:1">
-      <c r="A542" s="8"/>
+      <c r="A542" s="9"/>
     </row>
     <row r="543" spans="1:1">
-      <c r="A543" s="8"/>
+      <c r="A543" s="9"/>
     </row>
     <row r="544" spans="1:1">
-      <c r="A544" s="8"/>
+      <c r="A544" s="9"/>
     </row>
     <row r="545" spans="1:1">
-      <c r="A545" s="8"/>
+      <c r="A545" s="9"/>
     </row>
     <row r="546" spans="1:1">
-      <c r="A546" s="8"/>
+      <c r="A546" s="9"/>
     </row>
     <row r="547" spans="1:1">
-      <c r="A547" s="8"/>
+      <c r="A547" s="9"/>
     </row>
     <row r="548" spans="1:1">
-      <c r="A548" s="8"/>
+      <c r="A548" s="9"/>
     </row>
     <row r="549" spans="1:1">
-      <c r="A549" s="8"/>
+      <c r="A549" s="9"/>
     </row>
     <row r="550" spans="1:1">
-      <c r="A550" s="8"/>
+      <c r="A550" s="9"/>
     </row>
     <row r="551" spans="1:1">
-      <c r="A551" s="8"/>
+      <c r="A551" s="9"/>
     </row>
     <row r="552" spans="1:1">
-      <c r="A552" s="8"/>
+      <c r="A552" s="9"/>
     </row>
     <row r="553" spans="1:1">
-      <c r="A553" s="8"/>
+      <c r="A553" s="9"/>
     </row>
     <row r="554" spans="1:1">
-      <c r="A554" s="8"/>
+      <c r="A554" s="9"/>
     </row>
     <row r="555" spans="1:1">
-      <c r="A555" s="8"/>
+      <c r="A555" s="9"/>
     </row>
     <row r="556" spans="1:1">
-      <c r="A556" s="8"/>
+      <c r="A556" s="9"/>
     </row>
     <row r="557" spans="1:1">
-      <c r="A557" s="8"/>
+      <c r="A557" s="9"/>
     </row>
     <row r="558" spans="1:1">
-      <c r="A558" s="8"/>
+      <c r="A558" s="9"/>
     </row>
     <row r="559" spans="1:1">
-      <c r="A559" s="8"/>
+      <c r="A559" s="9"/>
     </row>
     <row r="560" spans="1:1">
-      <c r="A560" s="8"/>
+      <c r="A560" s="9"/>
     </row>
     <row r="561" spans="1:1">
-      <c r="A561" s="8"/>
+      <c r="A561" s="9"/>
     </row>
     <row r="562" spans="1:1">
-      <c r="A562" s="8"/>
+      <c r="A562" s="9"/>
     </row>
     <row r="563" spans="1:1">
-      <c r="A563" s="8"/>
+      <c r="A563" s="9"/>
     </row>
     <row r="564" spans="1:1">
-      <c r="A564" s="8"/>
+      <c r="A564" s="9"/>
     </row>
     <row r="565" spans="1:1">
-      <c r="A565" s="8"/>
+      <c r="A565" s="9"/>
     </row>
     <row r="566" spans="1:1">
-      <c r="A566" s="8"/>
+      <c r="A566" s="9"/>
     </row>
     <row r="567" spans="1:1">
-      <c r="A567" s="8"/>
+      <c r="A567" s="9"/>
     </row>
     <row r="568" spans="1:1">
-      <c r="A568" s="8"/>
+      <c r="A568" s="9"/>
     </row>
     <row r="569" spans="1:1">
-      <c r="A569" s="8"/>
+      <c r="A569" s="9"/>
     </row>
     <row r="570" spans="1:1">
-      <c r="A570" s="8"/>
+      <c r="A570" s="9"/>
     </row>
     <row r="571" spans="1:1">
-      <c r="A571" s="8"/>
+      <c r="A571" s="9"/>
     </row>
     <row r="572" spans="1:1">
-      <c r="A572" s="8"/>
+      <c r="A572" s="9"/>
     </row>
     <row r="573" spans="1:1">
-      <c r="A573" s="8"/>
+      <c r="A573" s="9"/>
     </row>
     <row r="574" spans="1:1">
-      <c r="A574" s="8"/>
+      <c r="A574" s="9"/>
     </row>
     <row r="575" spans="1:1">
-      <c r="A575" s="8"/>
+      <c r="A575" s="9"/>
     </row>
     <row r="576" spans="1:1">
-      <c r="A576" s="8"/>
+      <c r="A576" s="9"/>
     </row>
     <row r="577" spans="1:1">
-      <c r="A577" s="8"/>
+      <c r="A577" s="9"/>
     </row>
     <row r="578" spans="1:1">
-      <c r="A578" s="8"/>
+      <c r="A578" s="9"/>
     </row>
     <row r="579" spans="1:1">
-      <c r="A579" s="8"/>
+      <c r="A579" s="9"/>
     </row>
     <row r="580" spans="1:1">
-      <c r="A580" s="8"/>
+      <c r="A580" s="9"/>
     </row>
     <row r="581" spans="1:1">
-      <c r="A581" s="8"/>
+      <c r="A581" s="9"/>
     </row>
     <row r="582" spans="1:1">
-      <c r="A582" s="8"/>
+      <c r="A582" s="9"/>
     </row>
     <row r="583" spans="1:1">
-      <c r="A583" s="8"/>
+      <c r="A583" s="9"/>
     </row>
     <row r="584" spans="1:1">
-      <c r="A584" s="8"/>
+      <c r="A584" s="9"/>
     </row>
     <row r="585" spans="1:1">
-      <c r="A585" s="8"/>
+      <c r="A585" s="9"/>
     </row>
     <row r="586" spans="1:1">
-      <c r="A586" s="8"/>
+      <c r="A586" s="9"/>
     </row>
     <row r="587" spans="1:1">
-      <c r="A587" s="8"/>
+      <c r="A587" s="9"/>
     </row>
     <row r="588" spans="1:1">
-      <c r="A588" s="8"/>
+      <c r="A588" s="9"/>
     </row>
     <row r="589" spans="1:1">
-      <c r="A589" s="8"/>
+      <c r="A589" s="9"/>
     </row>
     <row r="590" spans="1:1">
-      <c r="A590" s="8"/>
+      <c r="A590" s="9"/>
     </row>
     <row r="591" spans="1:1">
-      <c r="A591" s="8"/>
+      <c r="A591" s="9"/>
     </row>
     <row r="592" spans="1:1">
-      <c r="A592" s="8"/>
+      <c r="A592" s="9"/>
     </row>
     <row r="593" spans="1:1">
-      <c r="A593" s="8"/>
+      <c r="A593" s="9"/>
     </row>
     <row r="594" spans="1:1">
-      <c r="A594" s="8"/>
+      <c r="A594" s="9"/>
     </row>
     <row r="595" spans="1:1">
-      <c r="A595" s="8"/>
+      <c r="A595" s="9"/>
     </row>
     <row r="596" spans="1:1">
-      <c r="A596" s="8"/>
+      <c r="A596" s="9"/>
     </row>
     <row r="597" spans="1:1">
-      <c r="A597" s="8"/>
+      <c r="A597" s="9"/>
     </row>
     <row r="598" spans="1:1">
-      <c r="A598" s="8"/>
+      <c r="A598" s="9"/>
     </row>
     <row r="599" spans="1:1">
-      <c r="A599" s="8"/>
+      <c r="A599" s="9"/>
     </row>
     <row r="600" spans="1:1">
-      <c r="A600" s="8"/>
+      <c r="A600" s="9"/>
     </row>
     <row r="601" spans="1:1">
-      <c r="A601" s="8"/>
+      <c r="A601" s="9"/>
     </row>
     <row r="602" spans="1:1">
-      <c r="A602" s="8"/>
+      <c r="A602" s="9"/>
     </row>
     <row r="603" spans="1:1">
-      <c r="A603" s="8"/>
+      <c r="A603" s="9"/>
     </row>
     <row r="604" spans="1:1">
-      <c r="A604" s="8"/>
+      <c r="A604" s="9"/>
     </row>
     <row r="605" spans="1:1">
-      <c r="A605" s="8"/>
+      <c r="A605" s="9"/>
     </row>
     <row r="606" spans="1:1">
-      <c r="A606" s="8"/>
+      <c r="A606" s="9"/>
     </row>
     <row r="607" spans="1:1">
-      <c r="A607" s="8"/>
+      <c r="A607" s="9"/>
     </row>
     <row r="608" spans="1:1">
-      <c r="A608" s="8"/>
+      <c r="A608" s="9"/>
     </row>
     <row r="609" spans="1:1">
-      <c r="A609" s="8"/>
+      <c r="A609" s="9"/>
     </row>
     <row r="610" spans="1:1">
-      <c r="A610" s="8"/>
+      <c r="A610" s="9"/>
     </row>
     <row r="611" spans="1:1">
-      <c r="A611" s="8"/>
+      <c r="A611" s="9"/>
     </row>
     <row r="612" spans="1:1">
-      <c r="A612" s="8"/>
+      <c r="A612" s="9"/>
     </row>
     <row r="613" spans="1:1">
-      <c r="A613" s="8"/>
+      <c r="A613" s="9"/>
     </row>
     <row r="614" spans="1:1">
-      <c r="A614" s="8"/>
+      <c r="A614" s="9"/>
     </row>
     <row r="615" spans="1:1">
-      <c r="A615" s="8"/>
+      <c r="A615" s="9"/>
     </row>
     <row r="616" spans="1:1">
-      <c r="A616" s="8"/>
+      <c r="A616" s="9"/>
     </row>
     <row r="617" spans="1:1">
-      <c r="A617" s="8"/>
+      <c r="A617" s="9"/>
     </row>
     <row r="618" spans="1:1">
-      <c r="A618" s="8"/>
+      <c r="A618" s="9"/>
     </row>
     <row r="619" spans="1:1">
-      <c r="A619" s="8"/>
+      <c r="A619" s="9"/>
     </row>
     <row r="620" spans="1:1">
-      <c r="A620" s="8"/>
+      <c r="A620" s="9"/>
     </row>
     <row r="621" spans="1:1">
-      <c r="A621" s="8"/>
+      <c r="A621" s="9"/>
     </row>
     <row r="622" spans="1:1">
-      <c r="A622" s="8"/>
+      <c r="A622" s="9"/>
     </row>
     <row r="623" spans="1:1">
-      <c r="A623" s="8"/>
+      <c r="A623" s="9"/>
     </row>
     <row r="624" spans="1:1">
-      <c r="A624" s="8"/>
+      <c r="A624" s="9"/>
     </row>
     <row r="625" spans="1:1">
-      <c r="A625" s="8"/>
+      <c r="A625" s="9"/>
     </row>
     <row r="626" spans="1:1">
-      <c r="A626" s="8"/>
+      <c r="A626" s="9"/>
     </row>
     <row r="627" spans="1:1">
-      <c r="A627" s="8"/>
+      <c r="A627" s="9"/>
     </row>
     <row r="628" spans="1:1">
-      <c r="A628" s="8"/>
+      <c r="A628" s="9"/>
     </row>
     <row r="629" spans="1:1">
-      <c r="A629" s="8"/>
+      <c r="A629" s="9"/>
     </row>
     <row r="630" spans="1:1">
-      <c r="A630" s="8"/>
+      <c r="A630" s="9"/>
     </row>
     <row r="631" spans="1:1">
-      <c r="A631" s="8"/>
+      <c r="A631" s="9"/>
     </row>
     <row r="632" spans="1:1">
-      <c r="A632" s="8"/>
+      <c r="A632" s="9"/>
     </row>
     <row r="633" spans="1:1">
-      <c r="A633" s="8"/>
+      <c r="A633" s="9"/>
     </row>
     <row r="634" spans="1:1">
-      <c r="A634" s="8"/>
+      <c r="A634" s="9"/>
     </row>
     <row r="635" spans="1:1">
-      <c r="A635" s="8"/>
+      <c r="A635" s="9"/>
     </row>
     <row r="636" spans="1:1">
-      <c r="A636" s="8"/>
+      <c r="A636" s="9"/>
     </row>
     <row r="637" spans="1:1">
-      <c r="A637" s="8"/>
+      <c r="A637" s="9"/>
     </row>
     <row r="638" spans="1:1">
-      <c r="A638" s="8"/>
+      <c r="A638" s="9"/>
     </row>
     <row r="639" spans="1:1">
-      <c r="A639" s="8"/>
+      <c r="A639" s="9"/>
     </row>
     <row r="640" spans="1:1">
-      <c r="A640" s="8"/>
+      <c r="A640" s="9"/>
     </row>
     <row r="641" spans="1:1">
-      <c r="A641" s="8"/>
+      <c r="A641" s="9"/>
     </row>
     <row r="642" spans="1:1">
-      <c r="A642" s="8"/>
+      <c r="A642" s="9"/>
     </row>
     <row r="643" spans="1:1">
-      <c r="A643" s="8"/>
+      <c r="A643" s="9"/>
     </row>
     <row r="644" spans="1:1">
-      <c r="A644" s="8"/>
+      <c r="A644" s="9"/>
     </row>
     <row r="645" spans="1:1">
-      <c r="A645" s="8"/>
+      <c r="A645" s="9"/>
     </row>
     <row r="646" spans="1:1">
-      <c r="A646" s="8"/>
+      <c r="A646" s="9"/>
     </row>
     <row r="647" spans="1:1">
-      <c r="A647" s="8"/>
+      <c r="A647" s="9"/>
     </row>
     <row r="648" spans="1:1">
-      <c r="A648" s="8"/>
+      <c r="A648" s="9"/>
     </row>
     <row r="649" spans="1:1">
-      <c r="A649" s="8"/>
+      <c r="A649" s="9"/>
     </row>
     <row r="650" spans="1:1">
-      <c r="A650" s="8"/>
+      <c r="A650" s="9"/>
     </row>
     <row r="651" spans="1:1">
-      <c r="A651" s="8"/>
+      <c r="A651" s="9"/>
     </row>
     <row r="652" spans="1:1">
-      <c r="A652" s="8"/>
+      <c r="A652" s="9"/>
     </row>
     <row r="653" spans="1:1">
-      <c r="A653" s="8"/>
+      <c r="A653" s="9"/>
     </row>
     <row r="654" spans="1:1">
-      <c r="A654" s="8"/>
+      <c r="A654" s="9"/>
     </row>
     <row r="655" spans="1:1">
-      <c r="A655" s="8"/>
+      <c r="A655" s="9"/>
     </row>
     <row r="656" spans="1:1">
-      <c r="A656" s="8"/>
+      <c r="A656" s="9"/>
     </row>
     <row r="657" spans="1:1">
-      <c r="A657" s="8"/>
+      <c r="A657" s="9"/>
     </row>
     <row r="658" spans="1:1">
-      <c r="A658" s="8"/>
+      <c r="A658" s="9"/>
     </row>
     <row r="659" spans="1:1">
-      <c r="A659" s="8"/>
+      <c r="A659" s="9"/>
     </row>
     <row r="660" spans="1:1">
-      <c r="A660" s="8"/>
+      <c r="A660" s="9"/>
     </row>
     <row r="661" spans="1:1">
-      <c r="A661" s="8"/>
+      <c r="A661" s="9"/>
     </row>
     <row r="662" spans="1:1">
-      <c r="A662" s="8"/>
+      <c r="A662" s="9"/>
     </row>
     <row r="663" spans="1:1">
-      <c r="A663" s="8"/>
+      <c r="A663" s="9"/>
     </row>
     <row r="664" spans="1:1">
-      <c r="A664" s="8"/>
+      <c r="A664" s="9"/>
     </row>
     <row r="665" spans="1:1">
-      <c r="A665" s="8"/>
+      <c r="A665" s="9"/>
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:H665" etc:filterBottomFollowUsedRange="0">
